--- a/tame_output/ON/bt/strategyON_20240916.xlsx
+++ b/tame_output/ON/bt/strategyON_20240916.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-71.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-606.1%</t>
+          <t>-599.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-102.6%</t>
+          <t>-100.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-58.2%</t>
+          <t>-58.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-328.0%</t>
+          <t>-330.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-80.6%</t>
+          <t>-57.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>117.9%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>107.5%</t>
+          <t>112.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>105.6%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626475</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
@@ -46154,10 +46154,10 @@
         <v>1.222132721163475</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.8671223126921025</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.105786698710449</v>
+        <v>3.209931805444421</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
@@ -46177,10 +46177,10 @@
         <v>1.201044499758648</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.8671223126921025</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.081528727471656</v>
+        <v>3.185673834205628</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
@@ -46200,10 +46200,10 @@
         <v>1.132094094188037</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6998253373719983</v>
+        <v>0.8734005152619515</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.013833962415015</v>
+        <v>3.117979069148987</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
@@ -46223,10 +46223,10 @@
         <v>1.166207528301659</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6998253373719983</v>
+        <v>0.8734005152619515</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.024006348847148</v>
+        <v>3.12815145558112</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
@@ -46246,10 +46246,10 @@
         <v>1.19565118408607</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6998253373719983</v>
+        <v>0.8734005152619515</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.018952619421008</v>
+        <v>3.12309772615498</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
@@ -46269,10 +46269,10 @@
         <v>1.169304231771004</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6590151743627675</v>
+        <v>0.8325903522527207</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.986242297059995</v>
+        <v>3.090387403793967</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
@@ -46292,10 +46292,10 @@
         <v>1.158242862923185</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6590151743627675</v>
+        <v>0.8325903522527207</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.986794170093097</v>
+        <v>3.090939276827068</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
@@ -46315,10 +46315,10 @@
         <v>1.124639747394894</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7518256558136268</v>
+        <v>0.9254008337035801</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.971753150854978</v>
+        <v>3.07589825758895</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
@@ -46338,10 +46338,10 @@
         <v>1.108757435587724</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7074361864841991</v>
+        <v>0.8810113643741524</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.946992945181922</v>
+        <v>3.051138051915894</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
@@ -46361,10 +46361,10 @@
         <v>1.112034621653646</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7279398803696965</v>
+        <v>0.9015150582596497</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.954370870024944</v>
+        <v>3.058515976758915</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
@@ -46384,10 +46384,10 @@
         <v>1.101556279651284</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7279398803696965</v>
+        <v>0.9015150582596497</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.959862165855611</v>
+        <v>3.064007272589583</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
@@ -46407,10 +46407,10 @@
         <v>1.101941322259282</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7001594824683435</v>
+        <v>0.8737346603582967</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.954691128883338</v>
+        <v>3.05883623561731</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
@@ -46430,10 +46430,10 @@
         <v>0.8929447731678799</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6329416303173673</v>
+        <v>0.8065168082073205</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.752716137593405</v>
+        <v>2.856861244327378</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
@@ -46453,10 +46453,10 @@
         <v>0.9696488025097532</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6329416303173673</v>
+        <v>0.8065168082073205</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.872865798312611</v>
+        <v>2.977010905046583</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
@@ -46476,10 +46476,10 @@
         <v>0.9983254439113332</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6329416303173673</v>
+        <v>0.8065168082073205</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.887378824414934</v>
+        <v>2.991523931148906</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
@@ -46499,10 +46499,10 @@
         <v>0.9923604177915175</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6244804616619062</v>
+        <v>0.7980556395518594</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.879721564564026</v>
+        <v>2.983866671297998</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
@@ -46522,10 +46522,10 @@
         <v>1.059935978650886</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6244804616619062</v>
+        <v>0.7980556395518594</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.876450593409329</v>
+        <v>2.980595700143301</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
@@ -46545,10 +46545,10 @@
         <v>1.042582472479381</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5625844184925164</v>
+        <v>0.7361595963824696</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.839996359269608</v>
+        <v>2.94414146600358</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
@@ -46568,10 +46568,10 @@
         <v>1.108119616281303</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7193611766632351</v>
+        <v>0.8929363545531883</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.927849389478454</v>
+        <v>3.031994496212425</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
@@ -46591,10 +46591,10 @@
         <v>1.07092138620465</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6890122813486305</v>
+        <v>0.8625874592385837</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.890447507621281</v>
+        <v>2.994592614355252</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
@@ -46614,10 +46614,10 @@
         <v>0.9698111444346214</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4946492433056819</v>
+        <v>0.6682244211956352</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.779521247134457</v>
+        <v>2.883666353868429</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
@@ -46637,10 +46637,10 @@
         <v>0.9285359537562536</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4262404297603627</v>
+        <v>0.5998156076503161</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.737679880903767</v>
+        <v>2.841824987637739</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
@@ -46660,10 +46660,10 @@
         <v>0.9287403019562954</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4262404297603627</v>
+        <v>0.5998156076503161</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.735279842458084</v>
+        <v>2.839424949192056</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
@@ -46683,10 +46683,10 @@
         <v>0.9328802722474592</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3680568184291682</v>
+        <v>0.5416319963191215</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.696894394867612</v>
+        <v>2.801039501601584</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
@@ -46706,10 +46706,10 @@
         <v>1.031168352971722</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3680568184291682</v>
+        <v>0.5416319963191215</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.816188796501802</v>
+        <v>2.920333903235774</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
@@ -46729,10 +46729,10 @@
         <v>1.030638357384023</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4005733874385456</v>
+        <v>0.5741485653284989</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.836532066893562</v>
+        <v>2.940677173627534</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
@@ -46752,10 +46752,10 @@
         <v>1.044389342138488</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4005733874385456</v>
+        <v>0.5741485653284989</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.842540597290488</v>
+        <v>2.94668570402446</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
@@ -46775,10 +46775,10 @@
         <v>1.001436751509688</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5683807446734288</v>
+        <v>0.7419559225633821</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.841175232908618</v>
+        <v>2.945320339642589</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
@@ -46798,10 +46798,10 @@
         <v>0.97070188453129</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5683807446734288</v>
+        <v>0.7419559225633821</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.843968854440099</v>
+        <v>2.94811396117407</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
@@ -46821,10 +46821,10 @@
         <v>0.9738253153440621</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5745334507262131</v>
+        <v>0.7481086286161663</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.848322826463427</v>
+        <v>2.952467933197399</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
@@ -46844,10 +46844,10 @@
         <v>0.9661820728239718</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5577241525757115</v>
+        <v>0.7312993304656648</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.837317724313237</v>
+        <v>2.941462831047209</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
@@ -46867,10 +46867,10 @@
         <v>1.057436826131241</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6030184168501536</v>
+        <v>0.7765935947401068</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.930829836674723</v>
+        <v>3.034974943408695</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
@@ -46890,10 +46890,10 @@
         <v>0.9404449069114318</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.801036609019308</v>
+        <v>0.9746117869092612</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.851932753690343</v>
+        <v>2.956077860424315</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
@@ -46913,10 +46913,10 @@
         <v>0.990380454159129</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7501498963331135</v>
+        <v>0.9237250742230667</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.891690958400801</v>
+        <v>2.995836065134773</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319539</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
@@ -46936,10 +46936,10 @@
         <v>1.039652487335096</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8287756275382717</v>
+        <v>1.002350805428225</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.95349413323994</v>
+        <v>3.057639239973912</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
@@ -46959,10 +46959,10 @@
         <v>1.014104748957654</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7685663295329872</v>
+        <v>0.9421415074229403</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.915904535261441</v>
+        <v>3.020049641995413</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397788</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
@@ -46982,10 +46982,10 @@
         <v>1.032271026471323</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7685663295329872</v>
+        <v>0.9421415074229403</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.914396153301369</v>
+        <v>3.018541260035341</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316243</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
@@ -47005,10 +47005,10 @@
         <v>1.049883146562186</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8129394611715558</v>
+        <v>0.9865146390615089</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.940882899719947</v>
+        <v>3.045028006453919</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
@@ -47028,10 +47028,10 @@
         <v>1.035284800357223</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8129394611715558</v>
+        <v>0.9865146390615089</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.935276693858537</v>
+        <v>3.039421800592509</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
@@ -47051,10 +47051,10 @@
         <v>1.06072884960945</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8605951917326115</v>
+        <v>1.034170369622565</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.970251889222975</v>
+        <v>3.074396995956947</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
@@ -47074,10 +47074,10 @@
         <v>1.105828486383676</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.961113350231366</v>
+        <v>1.134688528121319</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.035455157696953</v>
+        <v>3.139600264430925</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
@@ -47097,10 +47097,10 @@
         <v>1.09894529063249</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8820006895221271</v>
+        <v>1.05557586741208</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.974742233747282</v>
+        <v>3.078887340481254</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
@@ -47120,10 +47120,10 @@
         <v>1.120978353886477</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8865441224669965</v>
+        <v>1.06011930035695</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.981565996124832</v>
+        <v>3.085711102858804</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
@@ -47143,10 +47143,10 @@
         <v>1.117339911020752</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8384594811870922</v>
+        <v>1.012034659077045</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.956876150987967</v>
+        <v>3.061021257721939</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
@@ -47166,10 +47166,10 @@
         <v>1.14090064838295</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8826623182729927</v>
+        <v>1.056237496162946</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.989277455767345</v>
+        <v>3.093422562501317</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
@@ -47189,10 +47189,10 @@
         <v>1.136286782517378</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.937465722282812</v>
+        <v>1.111040900172765</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.020569498642484</v>
+        <v>3.124714605376456</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284876</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
@@ -47212,10 +47212,10 @@
         <v>1.250851114716127</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.937465722282812</v>
+        <v>1.111040900172765</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.071817263825523</v>
+        <v>3.175962370559495</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
@@ -47235,10 +47235,10 @@
         <v>1.332348620764171</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.145107725917288</v>
+        <v>1.318682903807241</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.194843170600462</v>
+        <v>3.298988277334434</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
@@ -47258,10 +47258,10 @@
         <v>1.347709686091452</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.196139818639816</v>
+        <v>1.369714996529769</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.220410654472249</v>
+        <v>3.324555761206221</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.884375679476946</v>
+        <v>-2.821427451080693</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.365807471276538</v>
+        <v>1.390986762635039</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.198415771370769</v>
+        <v>1.434939177656975</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.238963630203526</v>
+        <v>3.380877673975249</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.846948659405812</v>
+        <v>-2.784000431009559</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.376739251604272</v>
+        <v>1.401918542962773</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.20366730939995</v>
+        <v>1.440190715686157</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.238075525320315</v>
+        <v>3.379989569092039</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.86706031544052</v>
+        <v>-2.804112087044267</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.369951381521629</v>
+        <v>1.39513067288013</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.21469465439737</v>
+        <v>1.451218060683576</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.245948724650007</v>
+        <v>3.387862768421731</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636281</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.838647052340637</v>
+        <v>-2.775698823944384</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.541874457782793</v>
+        <v>1.567053749141294</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.155719091650941</v>
+        <v>1.392242497937147</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.37112115802336</v>
+        <v>3.513035201795084</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.81322282095762</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.763864791315624</v>
+        <v>-2.700916562919371</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.691900271410615</v>
+        <v>1.717079562769116</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.230501352675953</v>
+        <v>1.46702475896216</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.536103423856185</v>
+        <v>3.678017467627909</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.737780707051816</v>
+        <v>-2.674832478655563</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.694041881129997</v>
+        <v>1.719221172488498</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.230501352675953</v>
+        <v>1.46702475896216</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.527811399870044</v>
+        <v>3.669725443641768</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.649902793942696</v>
+        <v>-2.586954565546443</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.727386241957425</v>
+        <v>1.752565533315926</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.346426995099304</v>
+        <v>1.582950401385511</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.595559980907834</v>
+        <v>3.737474024679558</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.641010332549413</v>
+        <v>-2.578062104153159</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.74849763224153</v>
+        <v>1.773676923600031</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.346426995099304</v>
+        <v>1.582950401385511</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.613114386634626</v>
+        <v>3.755028430406349</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.80948644951929</v>
+        <v>-2.746538221123037</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.672962232858162</v>
+        <v>1.698141524216664</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.318479159382724</v>
+        <v>1.55500256566893</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.588200732609261</v>
+        <v>3.730114776380985</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.36323025688985</v>
+        <v>-2.300282028493597</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.8327344070978</v>
+        <v>1.857913698456302</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.223760489713091</v>
+        <v>1.460283895999297</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.512639227995343</v>
+        <v>3.654553271767067</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.340509153206698</v>
+        <v>-2.277560924810444</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.832486871067966</v>
+        <v>1.857666162426467</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.223760489713091</v>
+        <v>1.460283895999297</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.503303250492248</v>
+        <v>3.645217294263972</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.46971096650074</v>
+        <v>-2.406762738104487</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.939712271601518</v>
+        <v>1.964891562960019</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.094558676419049</v>
+        <v>1.331082082705255</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.584688288366991</v>
+        <v>3.726602332138715</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.495585364974766</v>
+        <v>-2.432637136578513</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.966440334705554</v>
+        <v>1.991619626064056</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.13947028513079</v>
+        <v>1.375993691416996</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.648713076087683</v>
+        <v>3.790627119859407</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.488530674759593</v>
+        <v>-2.425582446363339</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.965937566781169</v>
+        <v>1.99111685813967</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.146524975345964</v>
+        <v>1.38304838163217</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.649621246206332</v>
+        <v>3.791535289978056</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.461579450433105</v>
+        <v>-2.398631222036851</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.986724210156505</v>
+        <v>2.011903501515007</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.161405321373683</v>
+        <v>1.397928727659889</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.668555607467705</v>
+        <v>3.810469651239429</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.483123678263892</v>
+        <v>-2.420175449867638</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.16220965116915</v>
+        <v>2.187388942527652</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.161405321373683</v>
+        <v>1.397928727659889</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.852658739612665</v>
+        <v>3.994572783384389</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.505531796068764</v>
+        <v>-2.44258356767251</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.145363098950195</v>
+        <v>2.170542390308696</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.161405321373683</v>
+        <v>1.397928727659889</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.844775434515658</v>
+        <v>3.986689478287382</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.533756031646364</v>
+        <v>-2.470807803250111</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.136127404268792</v>
+        <v>2.161306695627293</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.179382073824991</v>
+        <v>1.415905480111198</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.857615485536081</v>
+        <v>3.999529529307805</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.543196957534894</v>
+        <v>-2.480248729138641</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.188604751635227</v>
+        <v>2.213784042993729</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.301809191368383</v>
+        <v>1.538332597654589</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.987325473783963</v>
+        <v>4.129239517555686</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.632073588703368</v>
+        <v>-2.569125360307114</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.155945193713138</v>
+        <v>2.18112448507164</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.212932560199909</v>
+        <v>1.449455966486116</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.936890589628179</v>
+        <v>4.078804633399903</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.708403566304274</v>
+        <v>-2.64545533790802</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.123525015566551</v>
+        <v>2.148704306925053</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.212932560199909</v>
+        <v>1.449455966486116</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.935002402521954</v>
+        <v>4.076916446293678</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.802067510981815</v>
+        <v>-2.739119282585562</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.080879667298397</v>
+        <v>2.106058958656899</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.119268615522368</v>
+        <v>1.355792021808574</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.873624265318292</v>
+        <v>4.015538309090016</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.96363593650907</v>
+        <v>-2.900687708112817</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.014686307297647</v>
+        <v>2.039865598656148</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9924856917244882</v>
+        <v>1.229009098010695</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.795988521249717</v>
+        <v>3.937902565021441</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.07193659837919</v>
+        <v>-3.008988369982936</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.984439449415518</v>
+        <v>2.00961874077402</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9924856917244882</v>
+        <v>1.229009098010695</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.809061928115635</v>
+        <v>3.950975971887359</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.089740570099934</v>
+        <v>-3.02679234170368</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.96932305751016</v>
+        <v>1.994502348868662</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9219510688192871</v>
+        <v>1.158474475105494</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.758746351155454</v>
+        <v>3.900660394927178</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.117641357209407</v>
+        <v>-3.054693128813153</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.956686783793373</v>
+        <v>1.981866075151875</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8873541446763523</v>
+        <v>1.123877550962559</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.736512237796696</v>
+        <v>3.878426281568419</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.240167459912301</v>
+        <v>-3.177219231516047</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.904440786689414</v>
+        <v>1.929620078047916</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7648280419734584</v>
+        <v>1.001351448259665</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.659761020152158</v>
+        <v>3.801675063923882</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.47068195609789</v>
+        <v>-3.407733727701636</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.878940947805683</v>
+        <v>1.904120239164184</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5343135457878697</v>
+        <v>0.7708369520740763</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.588158282031308</v>
+        <v>3.730072325803032</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.819427041322333</v>
+        <v>-3.75647881292608</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.879754632717752</v>
+        <v>1.904933924076254</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4255655918689719</v>
+        <v>0.6620889981551785</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.663221228681817</v>
+        <v>3.805135272453541</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.973413459098474</v>
+        <v>-3.91046523070222</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.887140334752936</v>
+        <v>1.912319626111437</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4255655918689719</v>
+        <v>0.6620889981551785</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.732201497827456</v>
+        <v>3.874115541599181</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.178012893961482</v>
+        <v>-4.115064665565229</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.791351762927853</v>
+        <v>1.816531054286355</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4255655918689719</v>
+        <v>0.6620889981551785</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.718252699947578</v>
+        <v>3.860166743719302</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.430488047969207</v>
+        <v>-4.367539819572953</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.702232190380177</v>
+        <v>1.727411481738679</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4255655918689719</v>
+        <v>0.6620889981551785</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.730123189002992</v>
+        <v>3.872037232774716</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.723383804448619</v>
+        <v>-4.660435576052365</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.586284422307356</v>
+        <v>1.611463713665858</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4255655918689719</v>
+        <v>0.6620889981551785</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.731333723521935</v>
+        <v>3.873247767293659</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.910047932583427</v>
+        <v>-4.847099704187174</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.515740513280754</v>
+        <v>1.540919804639256</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.398826621044412</v>
+        <v>0.6353500273306186</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.719412083254521</v>
+        <v>3.861326127026245</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.056068619497389</v>
+        <v>-4.993120391101136</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.452410091251359</v>
+        <v>1.477589382609861</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3897435292505551</v>
+        <v>0.6262669355367616</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.709040080914396</v>
+        <v>3.85095412468612</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830323</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.147782628606974</v>
+        <v>-5.08483440021072</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.577928544306569</v>
+        <v>1.603107835665071</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3897435292505551</v>
+        <v>0.6262669355367616</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.87124413761344</v>
+        <v>4.013158181385164</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.179434287666943</v>
+        <v>-5.11648605927069</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.560114518646396</v>
+        <v>1.585293810004897</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3845750720061148</v>
+        <v>0.6210984782923215</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.86298970123059</v>
+        <v>4.004903745002314</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.75004401586814</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.261369105935827</v>
+        <v>-5.198420877539573</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.537570008907334</v>
+        <v>1.562749300265835</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3746403264190347</v>
+        <v>0.6111637327052413</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.867258271446833</v>
+        <v>4.009172315218557</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.783632867332685</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.363345228184234</v>
+        <v>-5.300396999787981</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.505705198463873</v>
+        <v>1.530884489822375</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2726642041706271</v>
+        <v>0.5091876104568337</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.814998236553691</v>
+        <v>3.956912280325415</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231801</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.253338944707012</v>
+        <v>-5.190390716310759</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.541860599098937</v>
+        <v>1.567039890457438</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2958687760879023</v>
+        <v>0.5323921823741089</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.821073866948232</v>
+        <v>3.962987910719955</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818516</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.110279368966086</v>
+        <v>-5.047331140569833</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.603334440117282</v>
+        <v>1.628513731475783</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3038822026778816</v>
+        <v>0.5404056089640882</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.830131933624194</v>
+        <v>3.972045977395918</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051782</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.808832643494249</v>
+        <v>-4.745884415097995</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.731174013188553</v>
+        <v>1.756353304547054</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6053289281497188</v>
+        <v>0.8418523344359254</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.018260851789832</v>
+        <v>4.160174895561556</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.833422887729433</v>
+        <v>-4.770474659333179</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.72230909324719</v>
+        <v>1.747488384605691</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6053289281497188</v>
+        <v>0.8418523344359254</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.019232029542542</v>
+        <v>4.161146073314266</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.782384511722912</v>
+        <v>-4.719436283326659</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.743567348029553</v>
+        <v>1.768746639388055</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6053289281497188</v>
+        <v>0.8418523344359254</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.020074933922298</v>
+        <v>4.161988977694022</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.741245216856282</v>
+        <v>-4.678296988460028</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.779061164850351</v>
+        <v>1.804240456208853</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6464682230163497</v>
+        <v>0.8829916293025563</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.063796609716422</v>
+        <v>4.205710653488146</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700472</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.644610304837641</v>
+        <v>-4.581662076441388</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.633899125781742</v>
+        <v>1.659078417140243</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7431031350349896</v>
+        <v>0.9796265413211962</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.93796155305154</v>
+        <v>4.079875596823264</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077634</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.775191039368484</v>
+        <v>-4.712242810972231</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.585168876043369</v>
+        <v>1.61034816740187</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6125224005041471</v>
+        <v>0.8490458067903537</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.863115156406999</v>
+        <v>4.005029200178723</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833451</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.610694705177522</v>
+        <v>-4.547746476781269</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.635394228795836</v>
+        <v>1.660573520154338</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.777018734695109</v>
+        <v>1.013542140981316</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.946239775997658</v>
+        <v>4.088153819769383</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077623</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.53359610363565</v>
+        <v>-4.470647875239396</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.665421379849015</v>
+        <v>1.690600671207516</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.777018734695109</v>
+        <v>1.013542140981316</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.945427486434088</v>
+        <v>4.087341530205812</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.543981298525539</v>
+        <v>-4.481033070129286</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.671136081018132</v>
+        <v>1.696315372376633</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.7666335398052196</v>
+        <v>1.003156946091426</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.949065148625227</v>
+        <v>4.090979192396952</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.834415493735275</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.562569457247764</v>
+        <v>-4.499621228851511</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.734537823305667</v>
+        <v>1.759717114664168</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.7480453810829943</v>
+        <v>0.9845687873692008</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.008749259168317</v>
+        <v>4.150663302940041</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.5628680039438</v>
+        <v>-4.499919775547546</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.731287415445551</v>
+        <v>1.756466706804052</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.7477468343869584</v>
+        <v>0.9842702406731649</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.005439141968994</v>
+        <v>4.147353185740718</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.815643212108851</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.462044870253372</v>
+        <v>-4.399096641857119</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.776147563861113</v>
+        <v>1.801326855219615</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.7602110498713123</v>
+        <v>0.9967344561575189</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.017448566198998</v>
+        <v>4.159362609970722</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.80735616812146</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.271263509500965</v>
+        <v>-4.208315281104712</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.852589361640619</v>
+        <v>1.877768652999121</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.9509924106237196</v>
+        <v>1.187515816909926</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.132046636128986</v>
+        <v>4.27396067990071</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.164300151651544</v>
+        <v>-4.10135192325529</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.875211550517985</v>
+        <v>1.900390841876486</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.009457018583521</v>
+        <v>1.245980424869728</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.146962246642463</v>
+        <v>4.288876290414187</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912985</v>
+        <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.108969563749781</v>
+        <v>-4.046021335353528</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.932310722290748</v>
+        <v>1.95749001364925</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.064787606485283</v>
+        <v>1.30131101277149</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.215127535995578</v>
+        <v>4.357041579767302</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.096915436836818</v>
+        <v>-4.033967208440565</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.930818940957371</v>
+        <v>1.955998232315872</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.076841733398246</v>
+        <v>1.313365139684453</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.216046580044794</v>
+        <v>4.357960623816518</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.138070556405039</v>
+        <v>-4.075122328008786</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.916237523314218</v>
+        <v>1.94141681467272</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.035686613830025</v>
+        <v>1.272210020116232</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.193234138487997</v>
+        <v>4.335148182259721</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.070021993713509</v>
+        <v>-4.007073765317256</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.956307974268713</v>
+        <v>1.981487265627214</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.103735176521555</v>
+        <v>1.340258582807762</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.246914301980798</v>
+        <v>4.388828345752522</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013428</v>
+        <v>3.645256780013421</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.30162238688301</v>
+        <v>-4.238674158486757</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.883870487174507</v>
+        <v>1.909049778533008</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.103735176521555</v>
+        <v>1.340258582807762</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.267116972154392</v>
+        <v>4.409031015926116</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.351673932412229</v>
+        <v>-4.288725704015976</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.847456105029701</v>
+        <v>1.872635396388203</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.103735176521555</v>
+        <v>1.340258582807762</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.250723208221274</v>
+        <v>4.392637251992998</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.526780764988674</v>
+        <v>-4.46383253659242</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.73766528559259</v>
+        <v>1.762844576951091</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.103735176521555</v>
+        <v>1.340258582807762</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.210975121814741</v>
+        <v>4.352889165586465</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.330680611558151</v>
+        <v>-4.267732383161897</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.823127965961739</v>
+        <v>1.848307257320241</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.299835329952078</v>
+        <v>1.536358736238284</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.335657832869995</v>
+        <v>4.477571876641719</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.730570473395084</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.177655219444866</v>
+        <v>-4.114706991048613</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.983509122379957</v>
+        <v>2.008688413738459</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.452860722065362</v>
+        <v>1.689384128351568</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.526644067710869</v>
+        <v>4.668558111482593</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791148</v>
+        <v>3.741278332791146</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.205962533318137</v>
+        <v>-4.143014304921883</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.159652421738942</v>
+        <v>2.184831713097443</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.452860722065362</v>
+        <v>1.689384128351568</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.714110292619162</v>
+        <v>4.856024336390885</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.372555758431659</v>
+        <v>-4.309607530035406</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.062418083047616</v>
+        <v>2.087597374406117</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.28626749695184</v>
+        <v>1.522790903238046</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.583557308905132</v>
+        <v>4.725471352676855</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.349519965070093</v>
+        <v>-4.28657173667384</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.07530880305396</v>
+        <v>2.100488094412461</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.28626749695184</v>
+        <v>1.522790903238046</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.587233711566849</v>
+        <v>4.729147755338573</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399468</v>
+        <v>3.740581401399466</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.320273984614396</v>
+        <v>-4.257325756218143</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.084625250359734</v>
+        <v>2.109804541718235</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.28626749695184</v>
+        <v>1.522790903238046</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.584851766690344</v>
+        <v>4.726765810462068</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256371</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.427199532492248</v>
+        <v>-4.364251304095994</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.039148270366228</v>
+        <v>2.064327561724729</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.179341949073988</v>
+        <v>1.415865355360195</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.517989677121268</v>
+        <v>4.659903720892992</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701002</v>
+        <v>3.689942600700997</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.572218090999496</v>
+        <v>-4.509269862603243</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.982569649106563</v>
+        <v>2.007748940465064</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.03432339056674</v>
+        <v>1.270846796852946</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.432407344160153</v>
+        <v>4.574321387931877</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687008</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.690559856784214</v>
+        <v>-4.62761162838796</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.035164182050429</v>
+        <v>2.06034347340893</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.04500942912963</v>
+        <v>1.281532835415836</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.53875020655564</v>
+        <v>4.680664250327364</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790804</v>
+        <v>3.714879051790798</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.741970279104922</v>
+        <v>-4.679022050708668</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.012385710248085</v>
+        <v>2.037565001606586</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.04500942912963</v>
+        <v>1.281532835415836</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.53653590368158</v>
+        <v>4.678449947453304</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437332</v>
+        <v>3.704757949437326</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.821389730312673</v>
+        <v>-4.75844150191642</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.980521057839273</v>
+        <v>2.005700349197775</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.04500942912963</v>
+        <v>1.281532835415836</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.536439031755869</v>
+        <v>4.678353075527593</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298399</v>
+        <v>3.736804952298392</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.916852728229891</v>
+        <v>-4.853904499833638</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.942329752230429</v>
+        <v>1.96750904358893</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.04500942912963</v>
+        <v>1.281532835415836</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.536432925313912</v>
+        <v>4.678346969085636</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218002</v>
+        <v>3.715372960217994</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.852476817379176</v>
+        <v>-4.789528588982923</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.966176513133326</v>
+        <v>1.991355804491827</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.109385339980345</v>
+        <v>1.345908746266552</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.573154868386951</v>
+        <v>4.715068912158675</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353538</v>
+        <v>3.73608941335353</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.90784597951137</v>
+        <v>-4.844897751115116</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.949762666028175</v>
+        <v>1.974941957386676</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.109385339980345</v>
+        <v>1.345908746266552</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.578888686134678</v>
+        <v>4.720802729906402</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113281</v>
+        <v>3.736822870113273</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.953283759342197</v>
+        <v>-4.890335530945944</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.931125917438777</v>
+        <v>1.956305208797278</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.066540349302185</v>
+        <v>1.303063755588392</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.552720055070715</v>
+        <v>4.694634098842439</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.79027250011369</v>
+        <v>3.790272500113682</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.865076925194619</v>
+        <v>-4.802128696798365</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.986283043948126</v>
+        <v>2.011462335306628</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.066540349302185</v>
+        <v>1.303063755588392</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.572594447921033</v>
+        <v>4.714508491692757</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.794486844016435</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.759041929989309</v>
+        <v>-4.696093701593056</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.012397742554978</v>
+        <v>2.03757703391348</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.066540349302185</v>
+        <v>1.303063755588392</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.556295148445761</v>
+        <v>4.698209192217485</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307667</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.575830266856214</v>
+        <v>-4.512882038459961</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.088113357272261</v>
+        <v>2.113292648630763</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.066540349302185</v>
+        <v>1.303063755588392</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.558726097909807</v>
+        <v>4.70064014168153</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863548</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.504108819842363</v>
+        <v>-4.44116059144611</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.082593121925692</v>
+        <v>2.107772413284193</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.138261796316036</v>
+        <v>1.374785202602243</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.567550151966008</v>
+        <v>4.709464195737731</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394113</v>
+        <v>3.723789705394108</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.481735794234657</v>
+        <v>-4.418787565838404</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.038458078089946</v>
+        <v>2.063637369448447</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.149517547428938</v>
+        <v>1.386040953715144</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.521219348554919</v>
+        <v>4.663133392326643</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456724</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.514752090145402</v>
+        <v>-4.451803861749148</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.210449764611004</v>
+        <v>2.235629055969505</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.080080170762186</v>
+        <v>1.316603577048393</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.664755127440224</v>
+        <v>4.806669171211948</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883678</v>
+        <v>3.713762536883671</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.503224454495793</v>
+        <v>-4.44027622609954</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.206982044699096</v>
+        <v>2.232161336057597</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.139080828963549</v>
+        <v>1.375604235249755</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.69207674818929</v>
+        <v>4.833990791961014</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236299</v>
+        <v>3.71715069923629</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.600565955838162</v>
+        <v>-4.537617727441908</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.171713556683937</v>
+        <v>2.196892848042438</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.09466064679806</v>
+        <v>1.331184053084267</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.669092751411786</v>
+        <v>4.81100679518351</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427686</v>
+        <v>3.705201079427678</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.686421985178129</v>
+        <v>-4.623473756781875</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.138622227140789</v>
+        <v>2.16380151849929</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.052284577571925</v>
+        <v>1.288807983858132</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.644918192068944</v>
+        <v>4.786832235840667</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610377</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.695258782594248</v>
+        <v>-4.632310554197995</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.117506709994842</v>
+        <v>2.142686001353344</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.044842404930574</v>
+        <v>1.281365811216781</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.622872090304634</v>
+        <v>4.764786134076358</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667456</v>
+        <v>3.715544411667449</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.786641345159707</v>
+        <v>-4.723693116763453</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.091118196013708</v>
+        <v>2.11629748737221</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.00827752021123</v>
+        <v>1.244800926497436</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.611097670518078</v>
+        <v>4.753011714289801</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889192</v>
+        <v>3.673978374889185</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.7749346271727</v>
+        <v>-4.711986398776447</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.197929141032778</v>
+        <v>2.22310843239128</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.019984238198236</v>
+        <v>1.256507644484443</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.720249959134549</v>
+        <v>4.862164002906272</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409567</v>
+        <v>3.68247609940956</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.675271123089038</v>
+        <v>-4.612322894692785</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.240826881397648</v>
+        <v>2.266006172756149</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.083171321401923</v>
+        <v>1.319694727688129</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.761194547788165</v>
+        <v>4.903108591559889</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452567</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.68558722125539</v>
+        <v>-4.622638992859136</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.449605275409165</v>
+        <v>2.474784566767667</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.083171321401923</v>
+        <v>1.319694727688129</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.974099381066223</v>
+        <v>5.116013424837947</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762288</v>
+        <v>3.623960959762281</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.685493253238017</v>
+        <v>-4.622545024841764</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.448821529528204</v>
+        <v>2.474000820886705</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.083541182749241</v>
+        <v>1.320064589035447</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.973499964786703</v>
+        <v>5.115414008558427</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988019</v>
+        <v>3.633213467988012</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.692712077437862</v>
+        <v>-4.629763849041608</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.44016598579262</v>
+        <v>2.465345277151122</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.083541182749241</v>
+        <v>1.320064589035447</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.967731950731057</v>
+        <v>5.109645994502781</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740918</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.691763654319823</v>
+        <v>-4.62881542592357</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.440545355039835</v>
+        <v>2.465724646398337</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.083541182749241</v>
+        <v>1.320064589035447</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.967731950731057</v>
+        <v>5.109645994502781</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.848832112575447</v>
+        <v>-4.785883884179194</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.390445579718678</v>
+        <v>2.415624871077179</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.083541182749241</v>
+        <v>1.320064589035447</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.980459558712149</v>
+        <v>5.122373602483873</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.842839865786636</v>
+        <v>-4.779891637390382</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.39478847685859</v>
+        <v>2.419967768217091</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.083541182749241</v>
+        <v>1.320064589035447</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.982405557136537</v>
+        <v>5.124319600908261</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.754281904655868</v>
+        <v>-4.691333676259615</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.423865797328666</v>
+        <v>2.449045088687168</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.083541182749241</v>
+        <v>1.320064589035447</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.976059693154306</v>
+        <v>5.11797373692603</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383087</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.736522827152794</v>
+        <v>-4.673574598756541</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.430278105768891</v>
+        <v>2.455457397127393</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.083541182749241</v>
+        <v>1.320064589035447</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.975368370593301</v>
+        <v>5.117282414365025</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.636892676103726</v>
+        <v>-4.573944447707473</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.482912352097105</v>
+        <v>2.508091643455606</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.183171333798308</v>
+        <v>1.419694740084515</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.047928647131329</v>
+        <v>5.189842690903053</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455269</v>
+        <v>3.775357097455267</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.686292184792737</v>
+        <v>-4.623343956396484</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.652306814120228</v>
+        <v>2.677486105478729</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.193430167230053</v>
+        <v>1.42995357351626</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.243238212689103</v>
+        <v>5.385152256460827</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.806035203503999</v>
+        <v>3.80723192675306</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.445711488069167</v>
+        <v>-4.383724663270193</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.735727765912518</v>
+        <v>2.760522495832107</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.434010863953624</v>
+        <v>1.669572866642551</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.374775303826107</v>
+        <v>5.516112505439462</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240916.xlsx
+++ b/tame_output/ON/bt/strategyON_20240916.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>20.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.3%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.1%</t>
+          <t>420.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-599.9%</t>
+          <t>-623.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-100.2%</t>
+          <t>-109.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-58.9%</t>
+          <t>-60.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.4%</t>
+          <t>-331.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-77.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>118.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>112.3%</t>
+          <t>111.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>105.6%</t>
+          <t>93.2%</t>
         </is>
       </c>
     </row>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199279</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969587</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923079</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232414</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631707943623</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879959</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -46148,16 +46148,16 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.66792318087984</v>
+        <v>-3.867780146422016</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.222132721163475</v>
+        <v>1.142189934946605</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8671223126921025</v>
+        <v>0.6935471348021492</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.209931805444421</v>
+        <v>3.105786698710449</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.659998806294926</v>
+        <v>-3.859855771837102</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.201044499758648</v>
+        <v>1.121101713541778</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8671223126921025</v>
+        <v>0.6935471348021492</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.185673834205628</v>
+        <v>3.081528727471656</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.653720603725077</v>
+        <v>-3.853577569267253</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.132094094188037</v>
+        <v>1.052151307971167</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8734005152619515</v>
+        <v>0.6998253373719983</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.117979069148987</v>
+        <v>3.013833962415015</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.593867984521354</v>
+        <v>-3.79372495006353</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.166207528301659</v>
+        <v>1.086264742084789</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8734005152619515</v>
+        <v>0.6998253373719983</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.12815145558112</v>
+        <v>3.024006348847148</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.507624521494977</v>
+        <v>-3.707481487037152</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.19565118408607</v>
+        <v>1.1157083978692</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8734005152619515</v>
+        <v>0.6998253373719983</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.12309772615498</v>
+        <v>3.018952619421008</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.552931340893957</v>
+        <v>-3.752788306436132</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.169304231771004</v>
+        <v>1.089361445554134</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8325903522527207</v>
+        <v>0.6590151743627675</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.090387403793967</v>
+        <v>2.986242297059995</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.581964445596258</v>
+        <v>-3.781821411138434</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.158242862923185</v>
+        <v>1.078300076706314</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8325903522527207</v>
+        <v>0.6590151743627675</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.090939276827068</v>
+        <v>2.986794170093097</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.489153964145399</v>
+        <v>-3.689010929687575</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.124639747394894</v>
+        <v>1.044696961178024</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.9254008337035801</v>
+        <v>0.7518256558136268</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.07589825758895</v>
+        <v>2.971753150854978</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.533543433474827</v>
+        <v>-3.733400399017002</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.108757435587724</v>
+        <v>1.028814649370854</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8810113643741524</v>
+        <v>0.7074361864841991</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.051138051915894</v>
+        <v>2.946992945181922</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.513039739589329</v>
+        <v>-3.712896705131505</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.112034621653646</v>
+        <v>1.032091835436776</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.9015150582596497</v>
+        <v>0.7279398803696965</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.058515976758915</v>
+        <v>2.954370870024944</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.552963834171901</v>
+        <v>-3.752820799714077</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.101556279651284</v>
+        <v>1.021613493434414</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.9015150582596497</v>
+        <v>0.7279398803696965</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.064007272589583</v>
+        <v>2.959862165855611</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.580744232073255</v>
+        <v>-3.78060119761543</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.101941322259282</v>
+        <v>1.021998536042412</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.8737346603582967</v>
+        <v>0.7001594824683435</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.05883623561731</v>
+        <v>2.954691128883338</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.699124904803393</v>
+        <v>-3.898981870345569</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8929447731678799</v>
+        <v>0.8130019869510097</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.8065168082073205</v>
+        <v>0.6329416303173673</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.856861244327378</v>
+        <v>2.752716137593405</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.807738983246724</v>
+        <v>-4.0075959487889</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9696488025097532</v>
+        <v>0.8897060162928829</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.8065168082073205</v>
+        <v>0.6329416303173673</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.977010905046583</v>
+        <v>2.872865798312611</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.772329944998581</v>
+        <v>-3.972186910540757</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9983254439113332</v>
+        <v>0.9183826576944629</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.8065168082073205</v>
+        <v>0.6329416303173673</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.991523931148906</v>
+        <v>2.887378824414934</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.780791113654042</v>
+        <v>-3.980648079196218</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9923604177915175</v>
+        <v>0.9124176315746473</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7980556395518594</v>
+        <v>0.6244804616619062</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.983866671297998</v>
+        <v>2.879721564564026</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.603674783618876</v>
+        <v>-3.803531749161052</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.059935978650886</v>
+        <v>0.9799931924340159</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7980556395518594</v>
+        <v>0.6244804616619062</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.980595700143301</v>
+        <v>2.876450593409329</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.648767028452422</v>
+        <v>-3.848623993994598</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.042582472479381</v>
+        <v>0.9626396862625108</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.7361595963824696</v>
+        <v>0.5625844184925164</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.94414146600358</v>
+        <v>2.839996359269608</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011229</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.469391607213654</v>
+        <v>-3.66924857275583</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.108119616281303</v>
+        <v>1.028176830064432</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8929363545531883</v>
+        <v>0.7193611766632351</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.031994496212425</v>
+        <v>2.927849389478454</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.716991718982223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.514405820734261</v>
+        <v>-3.714262786276437</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.07092138620465</v>
+        <v>0.9909785999877796</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.8625874592385837</v>
+        <v>0.6890122813486305</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.994592614355252</v>
+        <v>2.890447507621281</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509532</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.781410331006696</v>
+        <v>-3.981267296548872</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9698111444346214</v>
+        <v>0.8898683582177511</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6682244211956352</v>
+        <v>0.4946492433056819</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.883666353868429</v>
+        <v>2.779521247134457</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.882608112443869</v>
+        <v>-4.082465077986045</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9285359537562536</v>
+        <v>0.8485931675393834</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5998156076503161</v>
+        <v>0.4262404297603627</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.841824987637739</v>
+        <v>2.737679880903767</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.876097145829556</v>
+        <v>-4.075954111371733</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9287403019562954</v>
+        <v>0.8487975157394252</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5998156076503161</v>
+        <v>0.4262404297603627</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.839424949192056</v>
+        <v>2.735279842458084</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.857059018122259</v>
+        <v>-4.056915983664435</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9328802722474592</v>
+        <v>0.8529374860305889</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.5416319963191215</v>
+        <v>0.3680568184291682</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.801039501601584</v>
+        <v>2.696894394867612</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.909574820397079</v>
+        <v>-4.109431785939256</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.031168352971722</v>
+        <v>0.9512255667548513</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.5416319963191215</v>
+        <v>0.3680568184291682</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.920333903235774</v>
+        <v>2.816188796501802</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.912983131831659</v>
+        <v>-4.112840097373835</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.030638357384023</v>
+        <v>0.9506955711671528</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5741485653284989</v>
+        <v>0.4005733874385456</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.940677173627534</v>
+        <v>2.836532066893562</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.893626995937812</v>
+        <v>-4.093483961479988</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.044389342138488</v>
+        <v>0.9644465559216178</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5741485653284989</v>
+        <v>0.4005733874385456</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.94668570402446</v>
+        <v>2.842540597290488</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.745884025702809</v>
+        <v>-3.945740991244986</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.001436751509688</v>
+        <v>0.921493965292818</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.7419559225633821</v>
+        <v>0.5683807446734288</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.945320339642589</v>
+        <v>2.841175232908618</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181166</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.829705246977507</v>
+        <v>-4.029562212519684</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.97070188453129</v>
+        <v>0.8907590983144198</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.7419559225633821</v>
+        <v>0.5683807446734288</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.94811396117407</v>
+        <v>2.843968854440099</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.823552540924723</v>
+        <v>-4.0234095064669</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9738253153440621</v>
+        <v>0.8938825291271919</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.7481086286161663</v>
+        <v>0.5745334507262131</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.952467933197399</v>
+        <v>2.848322826463427</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.840361839075225</v>
+        <v>-4.040218804617401</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9661820728239718</v>
+        <v>0.8862392866071014</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.7312993304656648</v>
+        <v>0.5577241525757115</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.941462831047209</v>
+        <v>2.837317724313237</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.778063840299103</v>
+        <v>-3.97792080584128</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.057436826131241</v>
+        <v>0.977494039914371</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7765935947401068</v>
+        <v>0.6030184168501536</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.034974943408695</v>
+        <v>2.930829836674723</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.576273642633945</v>
+        <v>-3.776130608176122</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9404449069114318</v>
+        <v>0.8605021206945613</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.9746117869092612</v>
+        <v>0.801036609019308</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.956077860424315</v>
+        <v>2.851932753690343</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.627160355320139</v>
+        <v>-3.827017320862316</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.990380454159129</v>
+        <v>0.9104376679422588</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9237250742230667</v>
+        <v>0.7501498963331135</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.995836065134773</v>
+        <v>2.891690958400801</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319539</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.540549612670332</v>
+        <v>-3.740406578212509</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.039652487335096</v>
+        <v>0.9597097011182252</v>
       </c>
       <c r="F1973" t="n">
-        <v>1.002350805428225</v>
+        <v>0.8287756275382717</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.057639239973912</v>
+        <v>2.95349413323994</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.600758910675617</v>
+        <v>-3.800615876217794</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.014104748957654</v>
+        <v>0.9341619627407831</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.9421415074229403</v>
+        <v>0.7685663295329872</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.020049641995413</v>
+        <v>2.915904535261441</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397788</v>
+        <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.551572261991265</v>
+        <v>-3.751429227533442</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.032271026471323</v>
+        <v>0.9523282402544522</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.9421415074229403</v>
+        <v>0.7685663295329872</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.018541260035341</v>
+        <v>2.914396153301369</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316243</v>
+        <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.507199130352697</v>
+        <v>-3.707056095894874</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.049883146562186</v>
+        <v>0.9699403603453158</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9865146390615089</v>
+        <v>0.8129394611715558</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.045028006453919</v>
+        <v>2.940882899719947</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.529679481211581</v>
+        <v>-3.729536446753758</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.035284800357223</v>
+        <v>0.9553420141403524</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9865146390615089</v>
+        <v>0.8129394611715558</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.039421800592509</v>
+        <v>2.935276693858537</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.482023750650526</v>
+        <v>-3.681880716192703</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.06072884960945</v>
+        <v>0.9807860633925793</v>
       </c>
       <c r="F1978" t="n">
-        <v>1.034170369622565</v>
+        <v>0.8605951917326115</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.074396995956947</v>
+        <v>2.970251889222975</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569612</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.381505592151771</v>
+        <v>-3.581362557693948</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.105828486383676</v>
+        <v>1.025885700166806</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.134688528121319</v>
+        <v>0.961113350231366</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.139600264430925</v>
+        <v>3.035455157696953</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.365600262719418</v>
+        <v>-3.565457228261596</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.09894529063249</v>
+        <v>1.019002504415619</v>
       </c>
       <c r="F1980" t="n">
-        <v>1.05557586741208</v>
+        <v>0.8820006895221271</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.078887340481254</v>
+        <v>2.974742233747282</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.32076186111102</v>
+        <v>-3.520618826653198</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.120978353886477</v>
+        <v>1.041035567669607</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.06011930035695</v>
+        <v>0.8865441224669965</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.085711102858804</v>
+        <v>2.981565996124832</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.340260317353029</v>
+        <v>-3.540117282895206</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.117339911020752</v>
+        <v>1.037397124803882</v>
       </c>
       <c r="F1982" t="n">
-        <v>1.012034659077045</v>
+        <v>0.8384594811870922</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.061021257721939</v>
+        <v>2.956876150987967</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.296057480267128</v>
+        <v>-3.495914445809305</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.14090064838295</v>
+        <v>1.060957862166079</v>
       </c>
       <c r="F1983" t="n">
-        <v>1.056237496162946</v>
+        <v>0.8826623182729927</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.093422562501317</v>
+        <v>2.989277455767345</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.303617146104175</v>
+        <v>-3.503474111646352</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.136286782517378</v>
+        <v>1.056343996300508</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.111040900172765</v>
+        <v>0.937465722282812</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.124714605376456</v>
+        <v>3.020569498642484</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284876</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.145325728564903</v>
+        <v>-3.34518269410708</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.250851114716127</v>
+        <v>1.170908328499256</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.111040900172765</v>
+        <v>0.937465722282812</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.175962370559495</v>
+        <v>3.071817263825523</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.937683724930427</v>
+        <v>-3.137540690472604</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.332348620764171</v>
+        <v>1.2524058345473</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.318682903807241</v>
+        <v>1.145107725917288</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.298988277334434</v>
+        <v>3.194843170600462</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.886651632207899</v>
+        <v>-3.086508597750076</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.347709686091452</v>
+        <v>1.267766899874581</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.369714996529769</v>
+        <v>1.196139818639816</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.324555761206221</v>
+        <v>3.220410654472249</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.821427451080693</v>
+        <v>-3.02128441662287</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.390986762635039</v>
+        <v>1.311043976418168</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.434939177656975</v>
+        <v>1.261363999767022</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.380877673975249</v>
+        <v>3.276732567241277</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.784000431009559</v>
+        <v>-2.983857396551736</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.401918542962773</v>
+        <v>1.321975756745902</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.440190715686157</v>
+        <v>1.266615537796203</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.379989569092039</v>
+        <v>3.275844462358067</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992655</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.804112087044267</v>
+        <v>-3.003969052586445</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.39513067288013</v>
+        <v>1.315187886663259</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.451218060683576</v>
+        <v>1.277642882793623</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.387862768421731</v>
+        <v>3.283717661687759</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636281</v>
+        <v>3.828661445636282</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.775698823944384</v>
+        <v>-2.975555789486561</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.567053749141294</v>
+        <v>1.487110962924423</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.392242497937147</v>
+        <v>1.218667320047194</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.513035201795084</v>
+        <v>3.408890095061112</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095762</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.700916562919371</v>
+        <v>-2.900773528461548</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.717079562769116</v>
+        <v>1.637136776552246</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.46702475896216</v>
+        <v>1.293449581072206</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.678017467627909</v>
+        <v>3.573872360893937</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.674832478655563</v>
+        <v>-2.87468944419774</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.719221172488498</v>
+        <v>1.639278386271628</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.46702475896216</v>
+        <v>1.293449581072206</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.669725443641768</v>
+        <v>3.565580336907796</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.586954565546443</v>
+        <v>-2.78681153108862</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.752565533315926</v>
+        <v>1.672622747099056</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.582950401385511</v>
+        <v>1.409375223495557</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.737474024679558</v>
+        <v>3.633328917945586</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.578062104153159</v>
+        <v>-2.777919069695336</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.773676923600031</v>
+        <v>1.69373413738316</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.582950401385511</v>
+        <v>1.409375223495557</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.755028430406349</v>
+        <v>3.650883323672377</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.746538221123037</v>
+        <v>-2.946395186665214</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.698141524216664</v>
+        <v>1.618198737999793</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.55500256566893</v>
+        <v>1.381427387778977</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.730114776380985</v>
+        <v>3.625969669647013</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.300282028493597</v>
+        <v>-2.500138994035774</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.857913698456302</v>
+        <v>1.777970912239431</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.460283895999297</v>
+        <v>1.286708718109344</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.654553271767067</v>
+        <v>3.550408165033095</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.277560924810444</v>
+        <v>-2.477417890352622</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.857666162426467</v>
+        <v>1.777723376209597</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.460283895999297</v>
+        <v>1.286708718109344</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.645217294263972</v>
+        <v>3.541072187529999</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.406762738104487</v>
+        <v>-2.606619703646664</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.964891562960019</v>
+        <v>1.884948776743149</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.331082082705255</v>
+        <v>1.157506904815302</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.726602332138715</v>
+        <v>3.622457225404743</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.432637136578513</v>
+        <v>-2.63249410212069</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.991619626064056</v>
+        <v>1.911676839847185</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.375993691416996</v>
+        <v>1.202418513527043</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.790627119859407</v>
+        <v>3.686482013125434</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.425582446363339</v>
+        <v>-2.625439411905516</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.99111685813967</v>
+        <v>1.911174071922799</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.38304838163217</v>
+        <v>1.209473203742217</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.791535289978056</v>
+        <v>3.687390183244084</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.398631222036851</v>
+        <v>-2.598488187579028</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.011903501515007</v>
+        <v>1.931960715298136</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.397928727659889</v>
+        <v>1.224353549769936</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.810469651239429</v>
+        <v>3.706324544505457</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.420175449867638</v>
+        <v>-2.620032415409816</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.187388942527652</v>
+        <v>2.107446156310781</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.397928727659889</v>
+        <v>1.224353549769936</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.994572783384389</v>
+        <v>3.890427676650417</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.44258356767251</v>
+        <v>-2.642440533214688</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.170542390308696</v>
+        <v>2.090599604091826</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.397928727659889</v>
+        <v>1.224353549769936</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.986689478287382</v>
+        <v>3.88254437155341</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.470807803250111</v>
+        <v>-2.670664768792288</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.161306695627293</v>
+        <v>2.081363909410423</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.415905480111198</v>
+        <v>1.242330302221244</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.999529529307805</v>
+        <v>3.895384422573832</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.480248729138641</v>
+        <v>-2.680105694680818</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.213784042993729</v>
+        <v>2.133841256776858</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.538332597654589</v>
+        <v>1.364757419764636</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.129239517555686</v>
+        <v>4.025094410821715</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.569125360307114</v>
+        <v>-2.768982325849292</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.18112448507164</v>
+        <v>2.101181698854769</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.449455966486116</v>
+        <v>1.275880788596162</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.078804633399903</v>
+        <v>3.974659526665931</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.64545533790802</v>
+        <v>-2.845312303450198</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.148704306925053</v>
+        <v>2.068761520708182</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.449455966486116</v>
+        <v>1.275880788596162</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.076916446293678</v>
+        <v>3.972771339559706</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.739119282585562</v>
+        <v>-2.938976248127739</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.106058958656899</v>
+        <v>2.026116172440028</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.355792021808574</v>
+        <v>1.182216843918621</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.015538309090016</v>
+        <v>3.911393202356043</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.900687708112817</v>
+        <v>-3.100544673654994</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.039865598656148</v>
+        <v>1.959922812439278</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.229009098010695</v>
+        <v>1.055433920120741</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.937902565021441</v>
+        <v>3.833757458287468</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.008988369982936</v>
+        <v>-3.208845335525114</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.00961874077402</v>
+        <v>1.929675954557149</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.229009098010695</v>
+        <v>1.055433920120741</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.950975971887359</v>
+        <v>3.846830865153387</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.02679234170368</v>
+        <v>-3.226649307245858</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.994502348868662</v>
+        <v>1.914559562651792</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.158474475105494</v>
+        <v>0.9848992972155401</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.900660394927178</v>
+        <v>3.796515288193206</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.054693128813153</v>
+        <v>-3.254550094355331</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.981866075151875</v>
+        <v>1.901923288935004</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.123877550962559</v>
+        <v>0.9503023730726053</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.878426281568419</v>
+        <v>3.774281174834448</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.177219231516047</v>
+        <v>-3.377076197058225</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.929620078047916</v>
+        <v>1.849677291831045</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.001351448259665</v>
+        <v>0.8277762703697115</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.801675063923882</v>
+        <v>3.69752995718991</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.407733727701636</v>
+        <v>-3.607590693243814</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.904120239164184</v>
+        <v>1.824177452947313</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7708369520740763</v>
+        <v>0.5972617741841227</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.730072325803032</v>
+        <v>3.625927219069061</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.75647881292608</v>
+        <v>-3.956335778468257</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.904933924076254</v>
+        <v>1.824991137859383</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6620889981551785</v>
+        <v>0.4885138202652249</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.805135272453541</v>
+        <v>3.700990165719569</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.91046523070222</v>
+        <v>-4.110322196244398</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.912319626111437</v>
+        <v>1.832376839894567</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6620889981551785</v>
+        <v>0.4885138202652249</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.874115541599181</v>
+        <v>3.769970434865209</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.115064665565229</v>
+        <v>-4.314921631107406</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.816531054286355</v>
+        <v>1.736588268069484</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6620889981551785</v>
+        <v>0.4885138202652249</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.860166743719302</v>
+        <v>3.756021636985329</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.367539819572953</v>
+        <v>-4.567396785115131</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.727411481738679</v>
+        <v>1.647468695521808</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6620889981551785</v>
+        <v>0.4885138202652249</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.872037232774716</v>
+        <v>3.767892126040743</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.660435576052365</v>
+        <v>-4.860292541594543</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.611463713665858</v>
+        <v>1.531520927448987</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6620889981551785</v>
+        <v>0.4885138202652249</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.873247767293659</v>
+        <v>3.769102660559687</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.847099704187174</v>
+        <v>-5.046956669729351</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.540919804639256</v>
+        <v>1.460977018422385</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6353500273306186</v>
+        <v>0.461774849440665</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.861326127026245</v>
+        <v>3.757181020292272</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.993120391101136</v>
+        <v>-5.192977356643313</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.477589382609861</v>
+        <v>1.39764659639299</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.6262669355367616</v>
+        <v>0.4526917576468081</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.85095412468612</v>
+        <v>3.746809017952148</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830323</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.08483440021072</v>
+        <v>-5.284691365752898</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.603107835665071</v>
+        <v>1.5231650494482</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.6262669355367616</v>
+        <v>0.4526917576468081</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.013158181385164</v>
+        <v>3.909013074651192</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.11648605927069</v>
+        <v>-5.316343024812867</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.585293810004897</v>
+        <v>1.505351023788026</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6210984782923215</v>
+        <v>0.4475233004023679</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.004903745002314</v>
+        <v>3.900758638268342</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.75004401586814</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.198420877539573</v>
+        <v>-5.39827784308175</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.562749300265835</v>
+        <v>1.482806514048964</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6111637327052413</v>
+        <v>0.4375885548152877</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.009172315218557</v>
+        <v>3.905027208484585</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332685</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.300396999787981</v>
+        <v>-5.500253965330158</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.530884489822375</v>
+        <v>1.450941703605504</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.5091876104568337</v>
+        <v>0.3356124325668801</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.956912280325415</v>
+        <v>3.852767173591443</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231801</v>
+        <v>3.798296784231803</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.190390716310759</v>
+        <v>-5.390247681852936</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.567039890457438</v>
+        <v>1.487097104240568</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.5323921823741089</v>
+        <v>0.3588170044841553</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.962987910719955</v>
+        <v>3.858842803985983</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818516</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.047331140569833</v>
+        <v>-5.24718810611201</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.628513731475783</v>
+        <v>1.548570945258913</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.5404056089640882</v>
+        <v>0.3668304310741346</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.972045977395918</v>
+        <v>3.867900870661945</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051782</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.745884415097995</v>
+        <v>-4.945741380640173</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.756353304547054</v>
+        <v>1.676410518330184</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.8418523344359254</v>
+        <v>0.6682771565459719</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.160174895561556</v>
+        <v>4.056029788827583</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.81263594067962</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.770474659333179</v>
+        <v>-4.970331624875357</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.747488384605691</v>
+        <v>1.667545598388821</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.8418523344359254</v>
+        <v>0.6682771565459719</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.161146073314266</v>
+        <v>4.057000966580294</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.719436283326659</v>
+        <v>-4.919293248868836</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.768746639388055</v>
+        <v>1.688803853171184</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.8418523344359254</v>
+        <v>0.6682771565459719</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.161988977694022</v>
+        <v>4.05784387096005</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969538</v>
+        <v>3.831734516969539</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.678296988460028</v>
+        <v>-4.878153954002205</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.804240456208853</v>
+        <v>1.724297669991982</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8829916293025563</v>
+        <v>0.7094164514126027</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.205710653488146</v>
+        <v>4.101565546754173</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700472</v>
+        <v>3.825752932700474</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.581662076441388</v>
+        <v>-4.781519041983565</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.659078417140243</v>
+        <v>1.579135630923373</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.9796265413211962</v>
+        <v>0.8060513634312426</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.079875596823264</v>
+        <v>3.975730490089292</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077634</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.712242810972231</v>
+        <v>-4.912099776514408</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.61034816740187</v>
+        <v>1.530405381185</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.8490458067903537</v>
+        <v>0.6754706289004001</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.005029200178723</v>
+        <v>3.900884093444751</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833451</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.547746476781269</v>
+        <v>-4.747603442323446</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.660573520154338</v>
+        <v>1.580630733937467</v>
       </c>
       <c r="F2035" t="n">
-        <v>1.013542140981316</v>
+        <v>0.839966963091362</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.088153819769383</v>
+        <v>3.98400871303541</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077623</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.470647875239396</v>
+        <v>-4.670504840781573</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.690600671207516</v>
+        <v>1.610657884990646</v>
       </c>
       <c r="F2036" t="n">
-        <v>1.013542140981316</v>
+        <v>0.839966963091362</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.087341530205812</v>
+        <v>3.98319642347184</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147905</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.481033070129286</v>
+        <v>-4.680890035671463</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.696315372376633</v>
+        <v>1.616372586159762</v>
       </c>
       <c r="F2037" t="n">
-        <v>1.003156946091426</v>
+        <v>0.8295817682014727</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.090979192396952</v>
+        <v>3.986834085662979</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735275</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.499621228851511</v>
+        <v>-4.699478194393688</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.759717114664168</v>
+        <v>1.679774328447298</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9845687873692008</v>
+        <v>0.8109936094792474</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.150663302940041</v>
+        <v>4.046518196206069</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.499919775547546</v>
+        <v>-4.699776741089724</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.756466706804052</v>
+        <v>1.676523920587182</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9842702406731649</v>
+        <v>0.8106950627832115</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.147353185740718</v>
+        <v>4.043208079006746</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108851</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.399096641857119</v>
+        <v>-4.598953607399296</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.801326855219615</v>
+        <v>1.721384069002744</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9967344561575189</v>
+        <v>0.8231592782675653</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.159362609970722</v>
+        <v>4.05521750323675</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.80735616812146</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.208315281104712</v>
+        <v>-4.408172246646889</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.877768652999121</v>
+        <v>1.79782586678225</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.187515816909926</v>
+        <v>1.013940639019973</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.27396067990071</v>
+        <v>4.169815573166738</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.10135192325529</v>
+        <v>-4.301208888797468</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.900390841876486</v>
+        <v>1.820448055659615</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.245980424869728</v>
+        <v>1.072405246979774</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.288876290414187</v>
+        <v>4.184731183680215</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912979</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.046021335353528</v>
+        <v>-4.245878300895705</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.95749001364925</v>
+        <v>1.877547227432379</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.30131101277149</v>
+        <v>1.127735834881536</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.357041579767302</v>
+        <v>4.252896473033331</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539888</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.033967208440565</v>
+        <v>-4.233824173982742</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.955998232315872</v>
+        <v>1.876055446099002</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.313365139684453</v>
+        <v>1.139789961794499</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.357960623816518</v>
+        <v>4.253815517082546</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811003</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.075122328008786</v>
+        <v>-4.274979293550963</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.94141681467272</v>
+        <v>1.861474028455849</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.272210020116232</v>
+        <v>1.098634842226278</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.335148182259721</v>
+        <v>4.23100307552575</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382913</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.007073765317256</v>
+        <v>-4.206930730859433</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.981487265627214</v>
+        <v>1.901544479410344</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.340258582807762</v>
+        <v>1.166683404917808</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.388828345752522</v>
+        <v>4.28468323901855</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013421</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.238674158486757</v>
+        <v>-4.438531124028934</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.909049778533008</v>
+        <v>1.829106992316138</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.340258582807762</v>
+        <v>1.166683404917808</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.409031015926116</v>
+        <v>4.304885909192144</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.288725704015976</v>
+        <v>-4.488582669558153</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.872635396388203</v>
+        <v>1.792692610171332</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.340258582807762</v>
+        <v>1.166683404917808</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.392637251992998</v>
+        <v>4.288492145259026</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800095</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.46383253659242</v>
+        <v>-4.663689502134598</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.762844576951091</v>
+        <v>1.682901790734221</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.340258582807762</v>
+        <v>1.166683404917808</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.352889165586465</v>
+        <v>4.248744058852493</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660847</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.267732383161897</v>
+        <v>-4.467589348704075</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.848307257320241</v>
+        <v>1.76836447110337</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.536358736238284</v>
+        <v>1.362783558348331</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.477571876641719</v>
+        <v>4.373426769907747</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395084</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.114706991048613</v>
+        <v>-4.31456395659079</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.008688413738459</v>
+        <v>1.928745627521588</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.689384128351568</v>
+        <v>1.515808950461615</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.668558111482593</v>
+        <v>4.564413004748621</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791146</v>
+        <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.143014304921883</v>
+        <v>-4.342871270464061</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.184831713097443</v>
+        <v>2.104888926880573</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.689384128351568</v>
+        <v>1.515808950461615</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.856024336390885</v>
+        <v>4.751879229656914</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620432</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.309607530035406</v>
+        <v>-4.509464495577583</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.087597374406117</v>
+        <v>2.007654588189246</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.522790903238046</v>
+        <v>1.349215725348093</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.725471352676855</v>
+        <v>4.621326245942883</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.28657173667384</v>
+        <v>-4.486428702216017</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.100488094412461</v>
+        <v>2.020545308195591</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.522790903238046</v>
+        <v>1.349215725348093</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.729147755338573</v>
+        <v>4.625002648604601</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399466</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.257325756218143</v>
+        <v>-4.45718272176032</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.109804541718235</v>
+        <v>2.029861755501364</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.522790903238046</v>
+        <v>1.349215725348093</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.726765810462068</v>
+        <v>4.622620703728096</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.364251304095994</v>
+        <v>-4.564108269638171</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.064327561724729</v>
+        <v>1.984384775507859</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.415865355360195</v>
+        <v>1.242290177470241</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.659903720892992</v>
+        <v>4.555758614159021</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700997</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.509269862603243</v>
+        <v>-4.70912682814542</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.007748940465064</v>
+        <v>1.927806154248194</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.270846796852946</v>
+        <v>1.097271618962993</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.574321387931877</v>
+        <v>4.470176281197905</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687008</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.62761162838796</v>
+        <v>-4.827468593930138</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.06034347340893</v>
+        <v>1.98040068719206</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.281532835415836</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.680664250327364</v>
+        <v>4.576519143593393</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790798</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.679022050708668</v>
+        <v>-4.878879016250846</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.037565001606586</v>
+        <v>1.957622215389716</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.281532835415836</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.678449947453304</v>
+        <v>4.574304840719331</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437326</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.75844150191642</v>
+        <v>-4.958298467458597</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.005700349197775</v>
+        <v>1.925757562980904</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.281532835415836</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.678353075527593</v>
+        <v>4.574207968793621</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298392</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.853904499833638</v>
+        <v>-5.053761465375815</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.96750904358893</v>
+        <v>1.88756625737206</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.281532835415836</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.678346969085636</v>
+        <v>4.574201862351663</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217994</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.789528588982923</v>
+        <v>-4.9893855545251</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.991355804491827</v>
+        <v>1.911413018274957</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.345908746266552</v>
+        <v>1.172333568376598</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.715068912158675</v>
+        <v>4.610923805424703</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73608941335353</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.844897751115116</v>
+        <v>-5.044754716657294</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.974941957386676</v>
+        <v>1.894999171169806</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.345908746266552</v>
+        <v>1.172333568376598</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.720802729906402</v>
+        <v>4.61665762317243</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113273</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.890335530945944</v>
+        <v>-5.090192496488121</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.956305208797278</v>
+        <v>1.876362422580407</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.303063755588392</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.694634098842439</v>
+        <v>4.590488992108467</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113682</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.802128696798365</v>
+        <v>-5.001985662340543</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.011462335306628</v>
+        <v>1.931519549089757</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.303063755588392</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.714508491692757</v>
+        <v>4.610363384958785</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016435</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.696093701593056</v>
+        <v>-4.895950667135233</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.03757703391348</v>
+        <v>1.957634247696609</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.303063755588392</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.698209192217485</v>
+        <v>4.594064085483513</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307667</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.512882038459961</v>
+        <v>-4.712739004002138</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.113292648630763</v>
+        <v>2.033349862413893</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.303063755588392</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.70064014168153</v>
+        <v>4.596495034947559</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863548</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.44116059144611</v>
+        <v>-4.641017556988287</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.107772413284193</v>
+        <v>2.027829627067323</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.374785202602243</v>
+        <v>1.201210024712289</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.709464195737731</v>
+        <v>4.605319089003759</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394108</v>
+        <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.418787565838404</v>
+        <v>-4.618644531380581</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.063637369448447</v>
+        <v>1.983694583231577</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.386040953715144</v>
+        <v>1.212465775825191</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.663133392326643</v>
+        <v>4.558988285592672</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456724</v>
+        <v>3.715607446456726</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.451803861749148</v>
+        <v>-4.651660827291326</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.235629055969505</v>
+        <v>2.155686269752634</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.316603577048393</v>
+        <v>1.143028399158439</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.806669171211948</v>
+        <v>4.702524064477975</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883671</v>
+        <v>3.713762536883673</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.44027622609954</v>
+        <v>-4.640133191641717</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.232161336057597</v>
+        <v>2.152218549840726</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.375604235249755</v>
+        <v>1.202029057359802</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.833990791961014</v>
+        <v>4.729845685227042</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.71715069923629</v>
+        <v>3.717150699236292</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.537617727441908</v>
+        <v>-4.737474692984086</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.196892848042438</v>
+        <v>2.116950061825568</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.331184053084267</v>
+        <v>1.157608875194313</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.81100679518351</v>
+        <v>4.706861688449537</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427678</v>
+        <v>3.705201079427679</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.623473756781875</v>
+        <v>-4.823330722324052</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.16380151849929</v>
+        <v>2.083858732282419</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.288807983858132</v>
+        <v>1.115232805968178</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.786832235840667</v>
+        <v>4.682687129106695</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610377</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.632310554197995</v>
+        <v>-4.832167519740172</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.142686001353344</v>
+        <v>2.062743215136473</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.281365811216781</v>
+        <v>1.107790633326827</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.764786134076358</v>
+        <v>4.660641027342386</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667449</v>
+        <v>3.715544411667451</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.723693116763453</v>
+        <v>-4.92355008230563</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.11629748737221</v>
+        <v>2.036354701155339</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.244800926497436</v>
+        <v>1.071225748607483</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.753011714289801</v>
+        <v>4.648866607555829</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889185</v>
+        <v>3.673978374889186</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.711986398776447</v>
+        <v>-4.911843364318624</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.22310843239128</v>
+        <v>2.143165646174409</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.256507644484443</v>
+        <v>1.082932466594489</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.862164002906272</v>
+        <v>4.7580188961723</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.68247609940956</v>
+        <v>3.682476099409562</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.612322894692785</v>
+        <v>-4.812179860234962</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.266006172756149</v>
+        <v>2.186063386539279</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.319694727688129</v>
+        <v>1.146119549798176</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.903108591559889</v>
+        <v>4.798963484825917</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452567</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.622638992859136</v>
+        <v>-4.822495958401314</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.474784566767667</v>
+        <v>2.394841780550796</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.319694727688129</v>
+        <v>1.146119549798176</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.116013424837947</v>
+        <v>5.011868318103975</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762281</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.622545024841764</v>
+        <v>-4.822401990383941</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.474000820886705</v>
+        <v>2.394058034669835</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.320064589035447</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.115414008558427</v>
+        <v>5.011268901824455</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988012</v>
+        <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.629763849041608</v>
+        <v>-4.829620814583786</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.465345277151122</v>
+        <v>2.385402490934251</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.320064589035447</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.109645994502781</v>
+        <v>5.005500887768809</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740918</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.62881542592357</v>
+        <v>-4.828672391465747</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.465724646398337</v>
+        <v>2.385781860181466</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.320064589035447</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.109645994502781</v>
+        <v>5.005500887768809</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663622</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.785883884179194</v>
+        <v>-4.985740849721371</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.415624871077179</v>
+        <v>2.335682084860308</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.320064589035447</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.122373602483873</v>
+        <v>5.018228495749901</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424766</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.779891637390382</v>
+        <v>-4.97974860293256</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.419967768217091</v>
+        <v>2.340024982000221</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.320064589035447</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.124319600908261</v>
+        <v>5.020174494174289</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149214</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.691333676259615</v>
+        <v>-4.891190641801792</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.449045088687168</v>
+        <v>2.369102302470297</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.320064589035447</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.11797373692603</v>
+        <v>5.013828630192058</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383087</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.673574598756541</v>
+        <v>-4.873431564298718</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.455457397127393</v>
+        <v>2.375514610910522</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.320064589035447</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.117282414365025</v>
+        <v>5.013137307631053</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.573944447707473</v>
+        <v>-4.77380141324965</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.508091643455606</v>
+        <v>2.428148857238736</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.419694740084515</v>
+        <v>1.246119562194561</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.189842690903053</v>
+        <v>5.085697584169081</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455267</v>
+        <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.623343956396484</v>
+        <v>-4.823200921938661</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.677486105478729</v>
+        <v>2.597543319261858</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.42995357351626</v>
+        <v>1.256378395626306</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.385152256460827</v>
+        <v>5.281007149726854</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.80723192675306</v>
+        <v>3.483232114930687</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.383724663270193</v>
+        <v>-4.616516448296285</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.760522495832107</v>
+        <v>2.667405781821671</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.669572866642551</v>
+        <v>1.463062869268682</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.516112505439462</v>
+        <v>5.392206507015142</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240916.xlsx
+++ b/tame_output/ON/bt/strategyON_20240916.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>60.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>139.8%</t>
+          <t>129.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-36.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.6%</t>
+          <t>422.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-623.2%</t>
+          <t>-606.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-109.5%</t>
+          <t>-113.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-60.8%</t>
+          <t>-58.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-331.8%</t>
+          <t>-328.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-81.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>118.6%</t>
+          <t>113.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>111.1%</t>
+          <t>103.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199279</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969587</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923079</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297742</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017767</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879959</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.867780146422016</v>
+        <v>-3.66792318087984</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.142189934946605</v>
+        <v>1.222132721163475</v>
       </c>
       <c r="F1939" t="n">
         <v>0.6935471348021492</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.859855771837102</v>
+        <v>-3.659998806294926</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.121101713541778</v>
+        <v>1.201044499758648</v>
       </c>
       <c r="F1940" t="n">
         <v>0.6935471348021492</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.853577569267253</v>
+        <v>-3.653720603725077</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.052151307971167</v>
+        <v>1.132094094188037</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6998253373719983</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.79372495006353</v>
+        <v>-3.593867984521354</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.086264742084789</v>
+        <v>1.166207528301659</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6998253373719983</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.707481487037152</v>
+        <v>-3.507624521494977</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.1157083978692</v>
+        <v>1.19565118408607</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6998253373719983</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.752788306436132</v>
+        <v>-3.552931340893957</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.089361445554134</v>
+        <v>1.169304231771004</v>
       </c>
       <c r="F1944" t="n">
         <v>0.6590151743627675</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.781821411138434</v>
+        <v>-3.581964445596258</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.078300076706314</v>
+        <v>1.158242862923185</v>
       </c>
       <c r="F1945" t="n">
         <v>0.6590151743627675</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.689010929687575</v>
+        <v>-3.489153964145399</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.044696961178024</v>
+        <v>1.124639747394894</v>
       </c>
       <c r="F1946" t="n">
         <v>0.7518256558136268</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.733400399017002</v>
+        <v>-3.533543433474827</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.028814649370854</v>
+        <v>1.108757435587724</v>
       </c>
       <c r="F1947" t="n">
         <v>0.7074361864841991</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.712896705131505</v>
+        <v>-3.513039739589329</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.032091835436776</v>
+        <v>1.112034621653646</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7279398803696965</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.752820799714077</v>
+        <v>-3.552963834171901</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.021613493434414</v>
+        <v>1.101556279651284</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7279398803696965</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.78060119761543</v>
+        <v>-3.580744232073255</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.021998536042412</v>
+        <v>1.101941322259282</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7001594824683435</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.898981870345569</v>
+        <v>-3.699124904803393</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8130019869510097</v>
+        <v>0.8929447731678799</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6329416303173673</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.0075959487889</v>
+        <v>-3.807738983246724</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8897060162928829</v>
+        <v>0.9696488025097532</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6329416303173673</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.972186910540757</v>
+        <v>-3.772329944998581</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9183826576944629</v>
+        <v>0.9983254439113332</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6329416303173673</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.980648079196218</v>
+        <v>-3.780791113654042</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9124176315746473</v>
+        <v>0.9923604177915175</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6244804616619062</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.803531749161052</v>
+        <v>-3.603674783618876</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9799931924340159</v>
+        <v>1.059935978650886</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6244804616619062</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.848623993994598</v>
+        <v>-3.648767028452422</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9626396862625108</v>
+        <v>1.042582472479381</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5625844184925164</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011229</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.66924857275583</v>
+        <v>-3.469391607213654</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.028176830064432</v>
+        <v>1.108119616281303</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7193611766632351</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982223</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.714262786276437</v>
+        <v>-3.514405820734261</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9909785999877796</v>
+        <v>1.07092138620465</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6890122813486305</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509532</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.981267296548872</v>
+        <v>-3.781410331006696</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8898683582177511</v>
+        <v>0.9698111444346214</v>
       </c>
       <c r="F1959" t="n">
         <v>0.4946492433056819</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.082465077986045</v>
+        <v>-3.882608112443869</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8485931675393834</v>
+        <v>0.9285359537562536</v>
       </c>
       <c r="F1960" t="n">
         <v>0.4262404297603627</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.075954111371733</v>
+        <v>-3.876097145829556</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8487975157394252</v>
+        <v>0.9287403019562954</v>
       </c>
       <c r="F1961" t="n">
         <v>0.4262404297603627</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.056915983664435</v>
+        <v>-3.857059018122259</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8529374860305889</v>
+        <v>0.9328802722474592</v>
       </c>
       <c r="F1962" t="n">
         <v>0.3680568184291682</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.109431785939256</v>
+        <v>-3.909574820397079</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9512255667548513</v>
+        <v>1.031168352971722</v>
       </c>
       <c r="F1963" t="n">
         <v>0.3680568184291682</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.112840097373835</v>
+        <v>-3.912983131831659</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9506955711671528</v>
+        <v>1.030638357384023</v>
       </c>
       <c r="F1964" t="n">
         <v>0.4005733874385456</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.093483961479988</v>
+        <v>-3.893626995937812</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9644465559216178</v>
+        <v>1.044389342138488</v>
       </c>
       <c r="F1965" t="n">
         <v>0.4005733874385456</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.945740991244986</v>
+        <v>-3.745884025702809</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.921493965292818</v>
+        <v>1.001436751509688</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5683807446734288</v>
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181166</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.502940407636041</v>
+        <v>2.398113895146937</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.029562212519684</v>
+        <v>-3.829705246977507</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8907590983144198</v>
+        <v>0.8658753720421859</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5683807446734288</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.843968854440099</v>
+        <v>2.739142341950994</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394725</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.503602756027699</v>
+        <v>2.398776243538595</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.0234095064669</v>
+        <v>-3.823552540924723</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8938825291271919</v>
+        <v>0.868998802854958</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5745334507262131</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.848322826463427</v>
+        <v>2.743496313974323</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.50268323276781</v>
+        <v>2.397856720278706</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.040218804617401</v>
+        <v>-3.840361839075225</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8862392866071014</v>
+        <v>0.8613555603348677</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5577241525757115</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.837317724313237</v>
+        <v>2.732491211824133</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.569018786564631</v>
+        <v>2.464192274075526</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.97792080584128</v>
+        <v>-3.778063840299103</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.977494039914371</v>
+        <v>0.9526103136421373</v>
       </c>
       <c r="F1970" t="n">
         <v>0.6030184168501536</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.930829836674723</v>
+        <v>2.826003324185619</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.371310788278758</v>
+        <v>2.266484275789654</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.776130608176122</v>
+        <v>-3.576273642633945</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8605021206945613</v>
+        <v>0.8356183944223277</v>
       </c>
       <c r="F1971" t="n">
         <v>0.801036609019308</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.851932753690343</v>
+        <v>2.747106241201239</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.441601020600933</v>
+        <v>2.336774508111829</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.827017320862316</v>
+        <v>-3.627160355320139</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9104376679422588</v>
+        <v>0.8855539416700249</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7501498963331135</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.891690958400801</v>
+        <v>2.786864445911697</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.456228756716976</v>
+        <v>2.351402244227872</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.740406578212509</v>
+        <v>-3.540549612670332</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9597097011182252</v>
+        <v>0.9348259748459915</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8287756275382717</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.95349413323994</v>
+        <v>2.848667620750835</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.454764737541648</v>
+        <v>2.349938225052544</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.800615876217794</v>
+        <v>-3.600758910675617</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9341619627407831</v>
+        <v>0.9092782364685494</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7685663295329872</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.915904535261441</v>
+        <v>2.811078022772337</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.453256355581577</v>
+        <v>2.348429843092473</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.751429227533442</v>
+        <v>-3.551572261991265</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9523282402544522</v>
+        <v>0.9274445139822185</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7685663295329872</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.914396153301369</v>
+        <v>2.809569640812265</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.453119223017013</v>
+        <v>2.348292710527909</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.707056095894874</v>
+        <v>-3.507199130352697</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9699403603453158</v>
+        <v>0.9450566340730822</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8129394611715558</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.940882899719947</v>
+        <v>2.836056387230843</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.447513017155603</v>
+        <v>2.342686504666499</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.729536446753758</v>
+        <v>-3.529679481211581</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9553420141403524</v>
+        <v>0.9304582878681187</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8129394611715558</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.935276693858537</v>
+        <v>2.830450181369433</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.453894774183408</v>
+        <v>2.349068261694303</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.681880716192703</v>
+        <v>-3.482023750650526</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9807860633925793</v>
+        <v>0.9559023371203452</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8605951917326115</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.970251889222975</v>
+        <v>2.865425376733871</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.458787147558133</v>
+        <v>2.353960635069028</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.581362557693948</v>
+        <v>-3.381505592151771</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.025885700166806</v>
+        <v>1.001001973894572</v>
       </c>
       <c r="F1979" t="n">
         <v>0.961113350231366</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.035455157696953</v>
+        <v>2.930628645207848</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.445541820034005</v>
+        <v>2.340715307544901</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.565457228261596</v>
+        <v>-3.365600262719418</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.019002504415619</v>
+        <v>0.9941187781433851</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8820006895221271</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.974742233747282</v>
+        <v>2.869915721258177</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.449639522644634</v>
+        <v>2.344813010155529</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.520618826653198</v>
+        <v>-3.32076186111102</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.041035567669607</v>
+        <v>1.016151841397373</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8865441224669965</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.981565996124832</v>
+        <v>2.876739483635727</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.453800462275712</v>
+        <v>2.348973949786607</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.540117282895206</v>
+        <v>-3.340260317353029</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.037397124803882</v>
+        <v>1.012513398531648</v>
       </c>
       <c r="F1982" t="n">
         <v>0.8384594811870922</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.956876150987967</v>
+        <v>2.852049638498863</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.459680064803549</v>
+        <v>2.354853552314444</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.495914445809305</v>
+        <v>-3.296057480267128</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.060957862166079</v>
+        <v>1.036074135893845</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8826623182729927</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.989277455767345</v>
+        <v>2.88445094327824</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.458090065272796</v>
+        <v>2.353263552783692</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.503474111646352</v>
+        <v>-3.303617146104175</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.056343996300508</v>
+        <v>1.031460270028274</v>
       </c>
       <c r="F1984" t="n">
         <v>0.937465722282812</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.020569498642484</v>
+        <v>2.915742986153379</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.509337830455836</v>
+        <v>2.404511317966731</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.34518269410708</v>
+        <v>-3.145325728564903</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.170908328499256</v>
+        <v>1.146024602227022</v>
       </c>
       <c r="F1985" t="n">
         <v>0.937465722282812</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.071817263825523</v>
+        <v>2.966990751336419</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.507778535050089</v>
+        <v>2.402952022560985</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.137540690472604</v>
+        <v>-2.937683724930427</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.2524058345473</v>
+        <v>1.227522108275066</v>
       </c>
       <c r="F1986" t="n">
         <v>1.145107725917288</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.194843170600462</v>
+        <v>3.090016658111358</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.502726763288359</v>
+        <v>2.397900250799255</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.086508597750076</v>
+        <v>-2.886651632207899</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.267766899874581</v>
+        <v>1.242883173602347</v>
       </c>
       <c r="F1987" t="n">
         <v>1.196139818639816</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.220410654472249</v>
+        <v>3.115584141983144</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.519914167381064</v>
+        <v>2.41508765489196</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.02128441662287</v>
+        <v>-2.821427451080693</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.311043976418168</v>
+        <v>1.286160250145935</v>
       </c>
       <c r="F1988" t="n">
         <v>1.261363999767022</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.276732567241277</v>
+        <v>3.171906054752173</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.515875139680344</v>
+        <v>2.41104862719124</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.983857396551736</v>
+        <v>-2.784000431009559</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.321975756745902</v>
+        <v>1.297092030473668</v>
       </c>
       <c r="F1989" t="n">
         <v>1.266615537796203</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.275844462358067</v>
+        <v>3.171017949868962</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992655</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.517131932011585</v>
+        <v>2.41230541952248</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.003969052586445</v>
+        <v>-2.804112087044267</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.315187886663259</v>
+        <v>1.290304160391025</v>
       </c>
       <c r="F1990" t="n">
         <v>1.277642882793623</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.283717661687759</v>
+        <v>3.178891149198654</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636282</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.677689703032796</v>
+        <v>2.572863190543691</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.975555789486561</v>
+        <v>-2.775698823944384</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.487110962924423</v>
+        <v>1.46222723665219</v>
       </c>
       <c r="F1991" t="n">
         <v>1.218667320047194</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.408890095061112</v>
+        <v>3.304063582572008</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.797802612250613</v>
+        <v>2.692976099761508</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.900773528461548</v>
+        <v>-2.700916562919371</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.637136776552246</v>
+        <v>1.612253050280012</v>
       </c>
       <c r="F1992" t="n">
         <v>1.293449581072206</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.573872360893937</v>
+        <v>3.469045848404832</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.789510588264472</v>
+        <v>2.684684075775367</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.87468944419774</v>
+        <v>-2.674832478655563</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.639278386271628</v>
+        <v>1.614394659999394</v>
       </c>
       <c r="F1993" t="n">
         <v>1.293449581072206</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.565580336907796</v>
+        <v>3.460753824418691</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.787703783848251</v>
+        <v>2.682877271359147</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.78681153108862</v>
+        <v>-2.586954565546443</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.672622747099056</v>
+        <v>1.647739020826822</v>
       </c>
       <c r="F1994" t="n">
         <v>1.409375223495557</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.633328917945586</v>
+        <v>3.528502405456481</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.805258189575043</v>
+        <v>2.700431677085938</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.777919069695336</v>
+        <v>-2.578062104153159</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.69373413738316</v>
+        <v>1.668850411110926</v>
       </c>
       <c r="F1995" t="n">
         <v>1.409375223495557</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.650883323672377</v>
+        <v>3.546056811183273</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.797113236979627</v>
+        <v>2.692286724490522</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.946395186665214</v>
+        <v>-2.746538221123037</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.618198737999793</v>
+        <v>1.593315011727559</v>
       </c>
       <c r="F1996" t="n">
         <v>1.381427387778977</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.625969669647013</v>
+        <v>3.521143157157908</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.778382934167488</v>
+        <v>2.673556421678384</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.500138994035774</v>
+        <v>-2.300282028493597</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.777970912239431</v>
+        <v>1.753087185967197</v>
       </c>
       <c r="F1997" t="n">
         <v>1.286708718109344</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.550408165033095</v>
+        <v>3.44558165254399</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.769046956664393</v>
+        <v>2.664220444175288</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.477417890352622</v>
+        <v>-2.277560924810444</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.777723376209597</v>
+        <v>1.752839649937363</v>
       </c>
       <c r="F1998" t="n">
         <v>1.286708718109344</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.541072187529999</v>
+        <v>3.436245675040895</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.927953082515562</v>
+        <v>2.823126570026457</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.606619703646664</v>
+        <v>-2.406762738104487</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.884948776743149</v>
+        <v>1.860065050470915</v>
       </c>
       <c r="F1999" t="n">
         <v>1.157506904815302</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.622457225404743</v>
+        <v>3.517630712915639</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.965030905009209</v>
+        <v>2.860204392520104</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.63249410212069</v>
+        <v>-2.432637136578513</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.911676839847185</v>
+        <v>1.886793113574951</v>
       </c>
       <c r="F2000" t="n">
         <v>1.202418513527043</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.686482013125434</v>
+        <v>3.58165550063633</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.961706260998754</v>
+        <v>2.856879748509649</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.625439411905516</v>
+        <v>-2.425582446363339</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.911174071922799</v>
+        <v>1.886290345650566</v>
       </c>
       <c r="F2001" t="n">
         <v>1.209473203742217</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.687390183244084</v>
+        <v>3.58256367075498</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.971712414643495</v>
+        <v>2.866885902154391</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.598488187579028</v>
+        <v>-2.398631222036851</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.931960715298136</v>
+        <v>1.907076989025902</v>
       </c>
       <c r="F2002" t="n">
         <v>1.224353549769936</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.706324544505457</v>
+        <v>3.601498032016353</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.155815546788455</v>
+        <v>3.05098903429935</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.620032415409816</v>
+        <v>-2.420175449867638</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.107446156310781</v>
+        <v>2.082562430038547</v>
       </c>
       <c r="F2003" t="n">
         <v>1.224353549769936</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.890427676650417</v>
+        <v>3.785601164161312</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.147932241691448</v>
+        <v>3.043105729202344</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.642440533214688</v>
+        <v>-2.44258356767251</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.090599604091826</v>
+        <v>2.065715877819592</v>
       </c>
       <c r="F2004" t="n">
         <v>1.224353549769936</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.88254437155341</v>
+        <v>3.777717859064305</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.149986241241086</v>
+        <v>3.045159728751981</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.670664768792288</v>
+        <v>-2.470807803250111</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.081363909410423</v>
+        <v>2.056480183138189</v>
       </c>
       <c r="F2005" t="n">
         <v>1.242330302221244</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.895384422573832</v>
+        <v>3.790557910084728</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.206239958962933</v>
+        <v>3.101413446473828</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.680105694680818</v>
+        <v>-2.480248729138641</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.133841256776858</v>
+        <v>2.108957530504624</v>
       </c>
       <c r="F2006" t="n">
         <v>1.364757419764636</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.025094410821715</v>
+        <v>3.92026789833261</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.209131053508234</v>
+        <v>3.104304541019129</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.768982325849292</v>
+        <v>-2.569125360307114</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.101181698854769</v>
+        <v>2.076297972582535</v>
       </c>
       <c r="F2007" t="n">
         <v>1.275880788596162</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.974659526665931</v>
+        <v>3.869833014176827</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.207242866402009</v>
+        <v>3.102416353912904</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.845312303450198</v>
+        <v>-2.64545533790802</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.068761520708182</v>
+        <v>2.043877794435948</v>
       </c>
       <c r="F2008" t="n">
         <v>1.275880788596162</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.972771339559706</v>
+        <v>3.867944827070602</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.202063096004871</v>
+        <v>3.097236583515766</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.938976248127739</v>
+        <v>-2.739119282585562</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.026116172440028</v>
+        <v>2.001232446167794</v>
       </c>
       <c r="F2009" t="n">
         <v>1.182216843918621</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.911393202356043</v>
+        <v>3.806566689866939</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.200497106215023</v>
+        <v>3.095670593725919</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.100544673654994</v>
+        <v>-2.900687708112817</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.959922812439278</v>
+        <v>1.935039086167044</v>
       </c>
       <c r="F2010" t="n">
         <v>1.055433920120741</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.833757458287468</v>
+        <v>3.728930945798364</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.213570513080942</v>
+        <v>3.108744000591837</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.208845335525114</v>
+        <v>-3.008988369982936</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.929675954557149</v>
+        <v>1.904792228284915</v>
       </c>
       <c r="F2011" t="n">
         <v>1.055433920120741</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.846830865153387</v>
+        <v>3.742004352664282</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.205575709863882</v>
+        <v>3.100749197374777</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.226649307245858</v>
+        <v>-3.02679234170368</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.914559562651792</v>
+        <v>1.889675836379557</v>
       </c>
       <c r="F2012" t="n">
         <v>0.9848992972155401</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.796515288193206</v>
+        <v>3.691688775704102</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.204099750990884</v>
+        <v>3.099273238501779</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.254550094355331</v>
+        <v>-3.054693128813153</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.901923288935004</v>
+        <v>1.87703956266277</v>
       </c>
       <c r="F2013" t="n">
         <v>0.9503023730726053</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.774281174834448</v>
+        <v>3.669454662345343</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.200864194968083</v>
+        <v>3.096037682478978</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.377076197058225</v>
+        <v>-3.177219231516047</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.849677291831045</v>
+        <v>1.824793565558811</v>
       </c>
       <c r="F2014" t="n">
         <v>0.8277762703697115</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.69752995718991</v>
+        <v>3.592703444700805</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.267570154558586</v>
+        <v>3.162743642069482</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.607590693243814</v>
+        <v>-3.407733727701636</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.824177452947313</v>
+        <v>1.799293726675079</v>
       </c>
       <c r="F2015" t="n">
         <v>0.5972617741841227</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.625927219069061</v>
+        <v>3.521100706579956</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.407881873560433</v>
+        <v>3.303055361071329</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.956335778468257</v>
+        <v>-3.75647881292608</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.824991137859383</v>
+        <v>1.800107411587149</v>
       </c>
       <c r="F2016" t="n">
         <v>0.4885138202652249</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.700990165719569</v>
+        <v>3.596163653230464</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.476862142706073</v>
+        <v>3.372035630216969</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.110322196244398</v>
+        <v>-3.91046523070222</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.832376839894567</v>
+        <v>1.807493113622333</v>
       </c>
       <c r="F2017" t="n">
         <v>0.4885138202652249</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.769970434865209</v>
+        <v>3.665143922376104</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.462913344826194</v>
+        <v>3.35808683233709</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.314921631107406</v>
+        <v>-4.115064665565229</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.736588268069484</v>
+        <v>1.71170454179725</v>
       </c>
       <c r="F2018" t="n">
         <v>0.4885138202652249</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.756021636985329</v>
+        <v>3.651195124496225</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.474783833881608</v>
+        <v>3.369957321392504</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.567396785115131</v>
+        <v>-4.367539819572953</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.647468695521808</v>
+        <v>1.622584969249574</v>
       </c>
       <c r="F2019" t="n">
         <v>0.4885138202652249</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.767892126040743</v>
+        <v>3.663065613551639</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.475994368400552</v>
+        <v>3.371167855911447</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.860292541594543</v>
+        <v>-4.660435576052365</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.531520927448987</v>
+        <v>1.506637201176753</v>
       </c>
       <c r="F2020" t="n">
         <v>0.4885138202652249</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.769102660559687</v>
+        <v>3.664276148070583</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.480116110627873</v>
+        <v>3.375289598138769</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.046956669729351</v>
+        <v>-4.847099704187174</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.460977018422385</v>
+        <v>1.436093292150151</v>
       </c>
       <c r="F2021" t="n">
         <v>0.461774849440665</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.757181020292272</v>
+        <v>3.652354507803168</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.475193963364063</v>
+        <v>3.370367450874958</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.192977356643313</v>
+        <v>-4.993120391101136</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.39764659639299</v>
+        <v>1.372762870120756</v>
       </c>
       <c r="F2022" t="n">
         <v>0.4526917576468081</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.746809017952148</v>
+        <v>3.641982505463043</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.637398020063107</v>
+        <v>3.532571507574002</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.284691365752898</v>
+        <v>-5.08483440021072</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.5231650494482</v>
+        <v>1.498281323175966</v>
       </c>
       <c r="F2023" t="n">
         <v>0.4526917576468081</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.909013074651192</v>
+        <v>3.804186562162087</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.632244658026921</v>
+        <v>3.527418145537816</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.316343024812867</v>
+        <v>-5.11648605927069</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.505351023788026</v>
+        <v>1.480467297515792</v>
       </c>
       <c r="F2024" t="n">
         <v>0.4475233004023679</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.900758638268342</v>
+        <v>3.795932125779237</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.642474075595412</v>
+        <v>3.537647563106308</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.39827784308175</v>
+        <v>-5.198420877539573</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.482806514048964</v>
+        <v>1.45792278777673</v>
       </c>
       <c r="F2025" t="n">
         <v>0.4375885548152877</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.905027208484585</v>
+        <v>3.800200695995481</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.651399714051315</v>
+        <v>3.54657320156221</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.500253965330158</v>
+        <v>-5.300396999787981</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.450941703605504</v>
+        <v>1.42605797733327</v>
       </c>
       <c r="F2026" t="n">
         <v>0.3356124325668801</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.852767173591443</v>
+        <v>3.747940661102338</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231803</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.64355260129549</v>
+        <v>3.538726088806385</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.390247681852936</v>
+        <v>-5.190390716310759</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.487097104240568</v>
+        <v>1.462213377968334</v>
       </c>
       <c r="F2027" t="n">
         <v>0.3588170044841553</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.858842803985983</v>
+        <v>3.754016291496879</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.647802612017464</v>
+        <v>3.54297609952836</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.24718810611201</v>
+        <v>-5.047331140569833</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.548570945258913</v>
+        <v>1.523687218986678</v>
       </c>
       <c r="F2028" t="n">
         <v>0.3668304310741346</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.867900870661945</v>
+        <v>3.763074358172841</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.6550634949</v>
+        <v>3.550236982410896</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.945741380640173</v>
+        <v>-4.745884415097995</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.676410518330184</v>
+        <v>1.651526792057949</v>
       </c>
       <c r="F2029" t="n">
         <v>0.6682771565459719</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.056029788827583</v>
+        <v>3.951203276338479</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.656034672652711</v>
+        <v>3.551208160163606</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.970331624875357</v>
+        <v>-4.770474659333179</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.667545598388821</v>
+        <v>1.642661872116587</v>
       </c>
       <c r="F2030" t="n">
         <v>0.6682771565459719</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.057000966580294</v>
+        <v>3.95217445409119</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.656877577032466</v>
+        <v>3.552051064543362</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.919293248868836</v>
+        <v>-4.719436283326659</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.688803853171184</v>
+        <v>1.66392012689895</v>
       </c>
       <c r="F2031" t="n">
         <v>0.6682771565459719</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.05784387096005</v>
+        <v>3.953017358470945</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969539</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.675915675906612</v>
+        <v>3.571089163417507</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.878153954002205</v>
+        <v>-4.678296988460028</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.724297669991982</v>
+        <v>1.699413943719748</v>
       </c>
       <c r="F2032" t="n">
         <v>0.7094164514126027</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.101565546754173</v>
+        <v>3.996739034265069</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700474</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.492099672030546</v>
+        <v>3.387273159541442</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.781519041983565</v>
+        <v>-4.581662076441388</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.579135630923373</v>
+        <v>1.554251904651139</v>
       </c>
       <c r="F2033" t="n">
         <v>0.8060513634312426</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.975730490089292</v>
+        <v>3.870903977600188</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077636</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.495601716104511</v>
+        <v>3.390775203615406</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.912099776514408</v>
+        <v>-4.712242810972231</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.530405381185</v>
+        <v>1.505521654912766</v>
       </c>
       <c r="F2034" t="n">
         <v>0.6754706289004001</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.900884093444751</v>
+        <v>3.796057580955646</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.480028535180593</v>
+        <v>3.375202022691489</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.747603442323446</v>
+        <v>-4.547746476781269</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.580630733937467</v>
+        <v>1.555747007665233</v>
       </c>
       <c r="F2035" t="n">
         <v>0.839966963091362</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.98400871303541</v>
+        <v>3.879182200546306</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.479216245617023</v>
+        <v>3.374389733127918</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.670504840781573</v>
+        <v>-4.470647875239396</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.610657884990646</v>
+        <v>1.585774158718412</v>
       </c>
       <c r="F2036" t="n">
         <v>0.839966963091362</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.98319642347184</v>
+        <v>3.878369910982736</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.489085024742095</v>
+        <v>3.384258512252991</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.680890035671463</v>
+        <v>-4.481033070129286</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.616372586159762</v>
+        <v>1.591488859887529</v>
       </c>
       <c r="F2037" t="n">
         <v>0.8295817682014727</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.986834085662979</v>
+        <v>3.882007573173874</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.55992203051852</v>
+        <v>3.455095518029416</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.699478194393688</v>
+        <v>-4.499621228851511</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.679774328447298</v>
+        <v>1.654890602175064</v>
       </c>
       <c r="F2038" t="n">
         <v>0.8109936094792474</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.046518196206069</v>
+        <v>3.941691683716964</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.556791041336819</v>
+        <v>3.451964528847714</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.699776741089724</v>
+        <v>-4.499919775547546</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.676523920587182</v>
+        <v>1.651640194314948</v>
       </c>
       <c r="F2039" t="n">
         <v>0.8106950627832115</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.043208079006746</v>
+        <v>3.938381566517641</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.56132193627621</v>
+        <v>3.456495423787106</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.598953607399296</v>
+        <v>-4.399096641857119</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.721384069002744</v>
+        <v>1.69650034273051</v>
       </c>
       <c r="F2040" t="n">
         <v>0.8231592782675653</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.05521750323675</v>
+        <v>3.950390990747645</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.561451189754754</v>
+        <v>3.456624677265649</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.408172246646889</v>
+        <v>-4.208315281104712</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.79782586678225</v>
+        <v>1.772942140510016</v>
       </c>
       <c r="F2041" t="n">
         <v>1.013940639019973</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.169815573166738</v>
+        <v>4.064989060677633</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.54128803549235</v>
+        <v>3.436461523003246</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.301208888797468</v>
+        <v>-4.10135192325529</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.820448055659615</v>
+        <v>1.795564329387382</v>
       </c>
       <c r="F2042" t="n">
         <v>1.072405246979774</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.184731183680215</v>
+        <v>4.079904671191111</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.576254972104409</v>
+        <v>3.471428459615304</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.245878300895705</v>
+        <v>-4.046021335353528</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.877547227432379</v>
+        <v>1.852663501160145</v>
       </c>
       <c r="F2043" t="n">
         <v>1.127735834881536</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.252896473033331</v>
+        <v>4.148069960544226</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.569941540005846</v>
+        <v>3.465115027516742</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.233824173982742</v>
+        <v>-4.033967208440565</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.876055446099002</v>
+        <v>1.851171719826768</v>
       </c>
       <c r="F2044" t="n">
         <v>1.139789961794499</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.253815517082546</v>
+        <v>4.148989004593441</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.571822170189982</v>
+        <v>3.466995657700878</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.274979293550963</v>
+        <v>-4.075122328008786</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.861474028455849</v>
+        <v>1.836590302183615</v>
       </c>
       <c r="F2045" t="n">
         <v>1.098634842226278</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.23100307552575</v>
+        <v>4.126176563036645</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.584673196067865</v>
+        <v>3.47984668357876</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.206930730859433</v>
+        <v>-4.007073765317256</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.901544479410344</v>
+        <v>1.87666075313811</v>
       </c>
       <c r="F2046" t="n">
         <v>1.166683404917808</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.28468323901855</v>
+        <v>4.179856726529446</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013428</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.604875866241459</v>
+        <v>3.500049353752354</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.438531124028934</v>
+        <v>-4.238674158486757</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.829106992316138</v>
+        <v>1.804223266043904</v>
       </c>
       <c r="F2047" t="n">
         <v>1.166683404917808</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.304885909192144</v>
+        <v>4.20005939670304</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.588482102308341</v>
+        <v>3.483655589819236</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.488582669558153</v>
+        <v>-4.288725704015976</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.792692610171332</v>
+        <v>1.767808883899098</v>
       </c>
       <c r="F2048" t="n">
         <v>1.166683404917808</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.288492145259026</v>
+        <v>4.183665632769921</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.548734015901807</v>
+        <v>3.443907503412703</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.663689502134598</v>
+        <v>-4.46383253659242</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.682901790734221</v>
+        <v>1.658018064461987</v>
       </c>
       <c r="F2049" t="n">
         <v>1.166683404917808</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.248744058852493</v>
+        <v>4.143917546363388</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.555756634898747</v>
+        <v>3.450930122409643</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.467589348704075</v>
+        <v>-4.267732383161897</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.76836447110337</v>
+        <v>1.743480744831136</v>
       </c>
       <c r="F2050" t="n">
         <v>1.362783558348331</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.373426769907747</v>
+        <v>4.268600257418642</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.654927634471652</v>
+        <v>3.550101121982547</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.31456395659079</v>
+        <v>-4.114706991048613</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.928745627521588</v>
+        <v>1.903861901249354</v>
       </c>
       <c r="F2051" t="n">
         <v>1.515808950461615</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.564413004748621</v>
+        <v>4.459586492259517</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.842393859379944</v>
+        <v>3.73756734689084</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.342871270464061</v>
+        <v>-4.143014304921883</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.104888926880573</v>
+        <v>2.080005200608339</v>
       </c>
       <c r="F2052" t="n">
         <v>1.515808950461615</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.751879229656914</v>
+        <v>4.647052717167809</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.811796810734027</v>
+        <v>3.706970298244923</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.509464495577583</v>
+        <v>-4.309607530035406</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.007654588189246</v>
+        <v>1.982770861917012</v>
       </c>
       <c r="F2053" t="n">
         <v>1.349215725348093</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.621326245942883</v>
+        <v>4.516499733453778</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.815473213395745</v>
+        <v>3.71064670090664</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.486428702216017</v>
+        <v>-4.28657173667384</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.020545308195591</v>
+        <v>1.995661581923357</v>
       </c>
       <c r="F2054" t="n">
         <v>1.349215725348093</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.625002648604601</v>
+        <v>4.520176136115496</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399468</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.81309126851924</v>
+        <v>3.708264756030136</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.45718272176032</v>
+        <v>-4.257325756218143</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.029861755501364</v>
+        <v>2.004978029229131</v>
       </c>
       <c r="F2055" t="n">
         <v>1.349215725348093</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.622620703728096</v>
+        <v>4.517794191238991</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.810384507676875</v>
+        <v>3.705557995187771</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.564108269638171</v>
+        <v>-4.370323324413686</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.984384775507859</v>
+        <v>1.957072241108548</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.242290177470241</v>
+        <v>1.23621815715255</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.555758614159021</v>
+        <v>4.447288889479301</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.689942600701003</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.811813309820109</v>
+        <v>3.706986797331005</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.70912682814542</v>
+        <v>-4.515341882920935</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.927806154248194</v>
+        <v>1.900493619848883</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.097271618962993</v>
+        <v>1.091199598645301</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.470176281197905</v>
+        <v>4.361706556518186</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.911744549077862</v>
+        <v>3.806918036588758</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.827468593930138</v>
+        <v>-4.633683648705652</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.98040068719206</v>
+        <v>1.953088152792749</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.107957657525883</v>
+        <v>1.101885637208191</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.576519143593393</v>
+        <v>4.468049418913673</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790804</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.909530246203802</v>
+        <v>3.804703733714697</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.878879016250846</v>
+        <v>-4.68509407102636</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.957622215389716</v>
+        <v>1.930309680990405</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.107957657525883</v>
+        <v>1.101885637208191</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.574304840719331</v>
+        <v>4.465835116039612</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.704757949437332</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.909433374278091</v>
+        <v>3.804606861788986</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.958298467458597</v>
+        <v>-4.764513522234112</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.925757562980904</v>
+        <v>1.898445028581593</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.107957657525883</v>
+        <v>1.101885637208191</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.574207968793621</v>
+        <v>4.465738244113902</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298399</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.909427267836134</v>
+        <v>3.804600755347029</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.053761465375815</v>
+        <v>-4.85997652015133</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.88756625737206</v>
+        <v>1.860253722972749</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.107957657525883</v>
+        <v>1.101885637208191</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.574201862351663</v>
+        <v>4.465732137671944</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960218002</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.907523664398744</v>
+        <v>3.80269715190964</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.9893855545251</v>
+        <v>-4.795600609300615</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.911413018274957</v>
+        <v>1.884100483875646</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.172333568376598</v>
+        <v>1.166261548058906</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.610923805424703</v>
+        <v>4.502454080744984</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.736089413353538</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.913257482146471</v>
+        <v>3.808430969657366</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.044754716657294</v>
+        <v>-4.850969771432808</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.894999171169806</v>
+        <v>1.867686636770495</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.172333568376598</v>
+        <v>1.166261548058906</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.61665762317243</v>
+        <v>4.508187898492711</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113281</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.912795845489403</v>
+        <v>3.807969333000299</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.090192496488121</v>
+        <v>-4.896407551263636</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.876362422580407</v>
+        <v>1.849049888181097</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.129488577698438</v>
+        <v>1.123416557380747</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.590488992108467</v>
+        <v>4.482019267428747</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.79027250011369</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.932670238339722</v>
+        <v>3.827843725850617</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.001985662340543</v>
+        <v>-4.808200717116057</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.931519549089757</v>
+        <v>1.904207014690447</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.129488577698438</v>
+        <v>1.123416557380747</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.610363384958785</v>
+        <v>4.501893660279066</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.91637093886445</v>
+        <v>3.811544426375345</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.895950667135233</v>
+        <v>-4.702165721910748</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.957634247696609</v>
+        <v>1.930321713297298</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.129488577698438</v>
+        <v>1.123416557380747</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.594064085483513</v>
+        <v>4.485594360803794</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.918801888328495</v>
+        <v>3.813975375839391</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.712739004002138</v>
+        <v>-4.518954058777653</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.033349862413893</v>
+        <v>2.006037328014582</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.129488577698438</v>
+        <v>1.123416557380747</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.596495034947559</v>
+        <v>4.488025310267839</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.884593074176385</v>
+        <v>3.779766561687281</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.641017556988287</v>
+        <v>-4.447232611763802</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.027829627067323</v>
+        <v>2.000517092668012</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.201210024712289</v>
+        <v>1.195138004394598</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.605319089003759</v>
+        <v>4.49684936432404</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394109</v>
+        <v>3.723789705394113</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.831508820097557</v>
+        <v>3.726682307608453</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.618644531380581</v>
+        <v>-4.424859586156096</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.983694583231577</v>
+        <v>1.956382048832267</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.212465775825191</v>
+        <v>1.206393755507499</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.558988285592672</v>
+        <v>4.450518560912952</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456726</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.016707024982912</v>
+        <v>3.911880512493808</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.651660827291326</v>
+        <v>-4.45787588206684</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.155686269752634</v>
+        <v>2.128373735353324</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.143028399158439</v>
+        <v>1.136956378840748</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.702524064477975</v>
+        <v>4.594054339798257</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883673</v>
+        <v>3.713762536883678</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.008628250811161</v>
+        <v>3.903801738322058</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.640133191641717</v>
+        <v>-4.446348246417232</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.152218549840726</v>
+        <v>2.124906015441417</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.202029057359802</v>
+        <v>1.19595703704211</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.729845685227042</v>
+        <v>4.621375960547324</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236292</v>
+        <v>3.717150699236299</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.01229636333295</v>
+        <v>3.907469850843846</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.737474692984086</v>
+        <v>-4.543689747759601</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.116950061825568</v>
+        <v>2.089637527426258</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.157608875194313</v>
+        <v>1.151536854876622</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.706861688449537</v>
+        <v>4.59839196376982</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427679</v>
+        <v>3.705201079427686</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.013547445525788</v>
+        <v>3.908720933036685</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.823330722324052</v>
+        <v>-4.629545777099567</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.083858732282419</v>
+        <v>2.05654619788311</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.115232805968178</v>
+        <v>1.109160785650487</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.682687129106695</v>
+        <v>4.574217404426976</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.99596664734629</v>
+        <v>3.891140134857187</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.832167519740172</v>
+        <v>-4.638382574515687</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.062743215136473</v>
+        <v>2.035430680737164</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.107790633326827</v>
+        <v>1.101718613009136</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.660641027342386</v>
+        <v>4.552171302662669</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667451</v>
+        <v>3.715544411667456</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.006131158391339</v>
+        <v>3.901304645902236</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.92355008230563</v>
+        <v>-4.729765137081145</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.036354701155339</v>
+        <v>2.00904216675603</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.071225748607483</v>
+        <v>1.065153728289791</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.648866607555829</v>
+        <v>4.540396882876111</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889186</v>
+        <v>3.673978374889192</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.108259416215606</v>
+        <v>4.003432903726504</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.911843364318624</v>
+        <v>-4.718058419094139</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.143165646174409</v>
+        <v>2.1158531117751</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.082932466594489</v>
+        <v>1.076860446276798</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.7580188961723</v>
+        <v>4.649549171492582</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409562</v>
+        <v>3.682476099409567</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.111291754947011</v>
+        <v>4.006465242457908</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.812179860234962</v>
+        <v>-4.618394915010477</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.186063386539279</v>
+        <v>2.15875085213997</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.146119549798176</v>
+        <v>1.140047529480484</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.798963484825917</v>
+        <v>4.690493760146199</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.324196588225069</v>
+        <v>4.219370075735966</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.822495958401314</v>
+        <v>-4.628711013176829</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.394841780550796</v>
+        <v>2.367529246151487</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.146119549798176</v>
+        <v>1.140047529480484</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.011868318103975</v>
+        <v>4.903398593424257</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762288</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.323375255137159</v>
+        <v>4.218548742648056</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.822401990383941</v>
+        <v>-4.628617045159456</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.394058034669835</v>
+        <v>2.366745500270526</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.146489411145494</v>
+        <v>1.140417390827802</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.011268901824455</v>
+        <v>4.902799177144738</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988014</v>
+        <v>3.633213467988019</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.317607241081513</v>
+        <v>4.21278072859241</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.829620814583786</v>
+        <v>-4.6358358693593</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.385402490934251</v>
+        <v>2.358089956534942</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.146489411145494</v>
+        <v>1.140417390827802</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.005500887768809</v>
+        <v>4.897031163089092</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.317607241081513</v>
+        <v>4.21278072859241</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.828672391465747</v>
+        <v>-4.634887446241262</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.385781860181466</v>
+        <v>2.358469325782157</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.146489411145494</v>
+        <v>1.140417390827802</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.005500887768809</v>
+        <v>4.897031163089092</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.330334849062605</v>
+        <v>4.225508336573502</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.985740849721371</v>
+        <v>-4.791955904496886</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.335682084860308</v>
+        <v>2.308369550460999</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.146489411145494</v>
+        <v>1.140417390827802</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.018228495749901</v>
+        <v>4.909758771070184</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.332280847486992</v>
+        <v>4.22745433499789</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.97974860293256</v>
+        <v>-4.785963657708074</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.340024982000221</v>
+        <v>2.312712447600912</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.146489411145494</v>
+        <v>1.140417390827802</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.020174494174289</v>
+        <v>4.911704769494571</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.325934983504761</v>
+        <v>4.221108471015659</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.891190641801792</v>
+        <v>-4.697405696577307</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.369102302470297</v>
+        <v>2.341789768070988</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.146489411145494</v>
+        <v>1.140417390827802</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.013828630192058</v>
+        <v>4.90535890551234</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.325243660943757</v>
+        <v>4.220417148454654</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.873431564298718</v>
+        <v>-4.679646619074233</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.375514610910522</v>
+        <v>2.348202076511213</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.146489411145494</v>
+        <v>1.140417390827802</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.013137307631053</v>
+        <v>4.904667582951336</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.338025846852344</v>
+        <v>4.233199334363241</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.77380141324965</v>
+        <v>-4.580016468025165</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.428148857238736</v>
+        <v>2.400836322839427</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.246119562194561</v>
+        <v>1.24004754187687</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.085697584169081</v>
+        <v>4.977227859489363</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.52718011235107</v>
+        <v>4.422353599861967</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.823200921938661</v>
+        <v>-4.629415976714176</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.597543319261858</v>
+        <v>2.570230784862549</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.256378395626306</v>
+        <v>1.250306375308615</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.281007149726854</v>
+        <v>5.172537425047136</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.483232114930687</v>
+        <v>3.885981436568635</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.514368785453932</v>
+        <v>4.409542272964829</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.616516448296285</v>
+        <v>-4.452194917208469</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.667405781821671</v>
+        <v>2.628307881767694</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.463062869268682</v>
+        <v>1.427527434814321</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.392206507015142</v>
+        <v>5.266058733853423</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240916.xlsx
+++ b/tame_output/ON/bt/strategyON_20240916.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>43.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>129.3%</t>
+          <t>129.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.7%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-71.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.1%</t>
+          <t>421.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-606.8%</t>
+          <t>-599.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-113.4%</t>
+          <t>-109.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-328.3%</t>
+          <t>-329.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-81.2%</t>
+          <t>-82.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>-5.3%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2088"/>
+  <dimension ref="A1:G2089"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232414</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631707943623</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626475</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.486108227285404</v>
+        <v>-4.50879893065626</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.078663693658653</v>
+        <v>1.069587412310311</v>
       </c>
       <c r="F1926" t="n">
         <v>0.3467883509260594</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.468394540407539</v>
+        <v>-4.491085243778395</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.086427752327139</v>
+        <v>1.077351470978797</v>
       </c>
       <c r="F1927" t="n">
         <v>0.3499696798229762</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.344920269094521</v>
+        <v>-4.367610972465377</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.13281553207234</v>
+        <v>1.123739250723998</v>
       </c>
       <c r="F1928" t="n">
         <v>0.3499696798229762</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.12489947105751</v>
+        <v>-4.147590174428366</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.222402888297758</v>
+        <v>1.213326606949416</v>
       </c>
       <c r="F1929" t="n">
         <v>0.4911895248909565</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.992031781994232</v>
+        <v>-4.014722485365088</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.291444146724893</v>
+        <v>1.28236786537655</v>
       </c>
       <c r="F1930" t="n">
         <v>0.4911895248909565</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.871858698629733</v>
+        <v>-3.89454940200059</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.340659224510995</v>
+        <v>1.331582943162652</v>
       </c>
       <c r="F1931" t="n">
         <v>0.6113626082554554</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.736605337299756</v>
+        <v>-3.759296040670613</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.404848671604425</v>
+        <v>1.395772390256083</v>
       </c>
       <c r="F1932" t="n">
         <v>0.7466159695854325</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.796480164657448</v>
+        <v>-3.819170868028305</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.366936232062774</v>
+        <v>1.357859950714432</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6867411422277404</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.676659933746611</v>
+        <v>-3.699350637117468</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.430153493661318</v>
+        <v>1.421077212312975</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6867411422277404</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.679129640208417</v>
+        <v>-3.701820343579274</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.336809810399037</v>
+        <v>1.327733529050694</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6842714357659343</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.747499826532427</v>
+        <v>-3.770190529903283</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.228723597354734</v>
+        <v>1.219647316006392</v>
       </c>
       <c r="F1936" t="n">
         <v>0.6935471348021492</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.859372106158578</v>
+        <v>-3.882062809529434</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.174411394136165</v>
+        <v>1.165335112787823</v>
       </c>
       <c r="F1937" t="n">
         <v>0.6935471348021492</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.84339744067231</v>
+        <v>-3.866088144043166</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.1473757852547</v>
+        <v>1.138299503906357</v>
       </c>
       <c r="F1938" t="n">
         <v>0.6935471348021492</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.66792318087984</v>
+        <v>-3.690613884250697</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.222132721163475</v>
+        <v>1.213056439815133</v>
       </c>
       <c r="F1939" t="n">
         <v>0.6935471348021492</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.659998806294926</v>
+        <v>-3.682689509665783</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.201044499758648</v>
+        <v>1.191968218410305</v>
       </c>
       <c r="F1940" t="n">
         <v>0.6935471348021492</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.653720603725077</v>
+        <v>-3.676411307095934</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.132094094188037</v>
+        <v>1.123017812839695</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6998253373719983</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.593867984521354</v>
+        <v>-3.616558687892211</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.166207528301659</v>
+        <v>1.157131246953316</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6998253373719983</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.507624521494977</v>
+        <v>-3.530315224865833</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.19565118408607</v>
+        <v>1.186574902737727</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6998253373719983</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.552931340893957</v>
+        <v>-3.575622044264813</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.169304231771004</v>
+        <v>1.160227950422661</v>
       </c>
       <c r="F1944" t="n">
         <v>0.6590151743627675</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.581964445596258</v>
+        <v>-3.604655148967115</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.158242862923185</v>
+        <v>1.149166581574842</v>
       </c>
       <c r="F1945" t="n">
         <v>0.6590151743627675</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.489153964145399</v>
+        <v>-3.511844667516256</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.124639747394894</v>
+        <v>1.115563466046551</v>
       </c>
       <c r="F1946" t="n">
         <v>0.7518256558136268</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.533543433474827</v>
+        <v>-3.556234136845683</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.108757435587724</v>
+        <v>1.099681154239381</v>
       </c>
       <c r="F1947" t="n">
         <v>0.7074361864841991</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.513039739589329</v>
+        <v>-3.535730442960186</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.112034621653646</v>
+        <v>1.102958340305303</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7279398803696965</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.552963834171901</v>
+        <v>-3.575654537542758</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.101556279651284</v>
+        <v>1.092479998302942</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7279398803696965</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.580744232073255</v>
+        <v>-3.603434935444111</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.101941322259282</v>
+        <v>1.092865040910939</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7001594824683435</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.699124904803393</v>
+        <v>-3.72181560817425</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8929447731678799</v>
+        <v>0.8838684918195372</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6329416303173673</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.807738983246724</v>
+        <v>-3.830429686617581</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9696488025097532</v>
+        <v>0.9605725211614105</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6329416303173673</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.772329944998581</v>
+        <v>-3.795020648369438</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9983254439113332</v>
+        <v>0.9892491625629907</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6329416303173673</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.780791113654042</v>
+        <v>-3.803481817024899</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9923604177915175</v>
+        <v>0.9832841364431748</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6244804616619062</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.603674783618876</v>
+        <v>-3.626365486989733</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.059935978650886</v>
+        <v>1.050859697302544</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6244804616619062</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.648767028452422</v>
+        <v>-3.671457731823279</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.042582472479381</v>
+        <v>1.033506191131038</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5625844184925164</v>
@@ -46562,10 +46562,10 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.469391607213654</v>
+        <v>-3.492082310584511</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.108119616281303</v>
+        <v>1.09904333493296</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7193611766632351</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.514405820734261</v>
+        <v>-3.537096524105117</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.07092138620465</v>
+        <v>1.061845104856307</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6890122813486305</v>
@@ -46608,10 +46608,10 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.781410331006696</v>
+        <v>-3.804101034377553</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9698111444346214</v>
+        <v>0.9607348630862786</v>
       </c>
       <c r="F1959" t="n">
         <v>0.4946492433056819</v>
@@ -46631,10 +46631,10 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.882608112443869</v>
+        <v>-3.905298815814725</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9285359537562536</v>
+        <v>0.9194596724079109</v>
       </c>
       <c r="F1960" t="n">
         <v>0.4262404297603627</v>
@@ -46654,10 +46654,10 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.876097145829556</v>
+        <v>-3.898787849200413</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9287403019562954</v>
+        <v>0.9196640206079527</v>
       </c>
       <c r="F1961" t="n">
         <v>0.4262404297603627</v>
@@ -46677,10 +46677,10 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.857059018122259</v>
+        <v>-3.879749721493115</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9328802722474592</v>
+        <v>0.9238039908991167</v>
       </c>
       <c r="F1962" t="n">
         <v>0.3680568184291682</v>
@@ -46700,10 +46700,10 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.909574820397079</v>
+        <v>-3.932265523767935</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.031168352971722</v>
+        <v>1.022092071623379</v>
       </c>
       <c r="F1963" t="n">
         <v>0.3680568184291682</v>
@@ -46723,10 +46723,10 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.912983131831659</v>
+        <v>-3.935673835202515</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.030638357384023</v>
+        <v>1.021562076035681</v>
       </c>
       <c r="F1964" t="n">
         <v>0.4005733874385456</v>
@@ -46746,10 +46746,10 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.893626995937812</v>
+        <v>-3.916317699308668</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.044389342138488</v>
+        <v>1.035313060790145</v>
       </c>
       <c r="F1965" t="n">
         <v>0.4005733874385456</v>
@@ -46769,10 +46769,10 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.745884025702809</v>
+        <v>-3.768574729073666</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.001436751509688</v>
+        <v>0.9923604701613458</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5683807446734288</v>
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.398113895146937</v>
+        <v>2.411460004418285</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.829705246977507</v>
+        <v>-3.751311108585204</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8658753720421859</v>
+        <v>0.9105791366704556</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5683807446734288</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.739142341950994</v>
+        <v>2.752488451222343</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.398776243538595</v>
+        <v>2.412122352809944</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.823552540924723</v>
+        <v>-3.745158402532419</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.868998802854958</v>
+        <v>0.9137025674832278</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5745334507262131</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.743496313974323</v>
+        <v>2.756842423245672</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.397856720278706</v>
+        <v>2.411202829550054</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.840361839075225</v>
+        <v>-3.761967700682921</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8613555603348677</v>
+        <v>0.9060593249631375</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5577241525757115</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.732491211824133</v>
+        <v>2.745837321095481</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.464192274075526</v>
+        <v>2.477538383346875</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.778063840299103</v>
+        <v>-3.699669701906799</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9526103136421373</v>
+        <v>0.9973140782704071</v>
       </c>
       <c r="F1970" t="n">
         <v>0.6030184168501536</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.826003324185619</v>
+        <v>2.839349433456967</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.266484275789654</v>
+        <v>2.279830385061002</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.576273642633945</v>
+        <v>-3.497879504241641</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8356183944223277</v>
+        <v>0.8803221590505974</v>
       </c>
       <c r="F1971" t="n">
         <v>0.801036609019308</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.747106241201239</v>
+        <v>2.760452350472587</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.336774508111829</v>
+        <v>2.350120617383177</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.627160355320139</v>
+        <v>-3.548766216927836</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8855539416700249</v>
+        <v>0.9302577062982946</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7501498963331135</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.786864445911697</v>
+        <v>2.800210555183045</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.351402244227872</v>
+        <v>2.364748353499221</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.540549612670332</v>
+        <v>-3.462155474278028</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9348259748459915</v>
+        <v>0.9795297394742613</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8287756275382717</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.848667620750835</v>
+        <v>2.862013730022184</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.349938225052544</v>
+        <v>2.363284334323892</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.600758910675617</v>
+        <v>-3.522364772283313</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9092782364685494</v>
+        <v>0.9539820010968192</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7685663295329872</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.811078022772337</v>
+        <v>2.824424132043685</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.348429843092473</v>
+        <v>2.361775952363821</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.551572261991265</v>
+        <v>-3.473178123598962</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9274445139822185</v>
+        <v>0.9721482786104882</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7685663295329872</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.809569640812265</v>
+        <v>2.822915750083614</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.348292710527909</v>
+        <v>2.361638819799257</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.507199130352697</v>
+        <v>-3.428804991960393</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9450566340730822</v>
+        <v>0.9897603987013519</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8129394611715558</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.836056387230843</v>
+        <v>2.849402496502191</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.342686504666499</v>
+        <v>2.356032613937848</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.529679481211581</v>
+        <v>-3.451285342819278</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9304582878681187</v>
+        <v>0.9751620524963884</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8129394611715558</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.830450181369433</v>
+        <v>2.843796290640781</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.349068261694303</v>
+        <v>2.362414370965652</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.482023750650526</v>
+        <v>-3.403629612258222</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9559023371203452</v>
+        <v>1.000606101748615</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8605951917326115</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.865425376733871</v>
+        <v>2.87877148600522</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.353960635069028</v>
+        <v>2.367306744340377</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.381505592151771</v>
+        <v>-3.303111453759468</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.001001973894572</v>
+        <v>1.045705738522842</v>
       </c>
       <c r="F1979" t="n">
         <v>0.961113350231366</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.930628645207848</v>
+        <v>2.943974754479197</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.340715307544901</v>
+        <v>2.354061416816249</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.365600262719418</v>
+        <v>-3.287206124327115</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9941187781433851</v>
+        <v>1.038822542771655</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8820006895221271</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.869915721258177</v>
+        <v>2.883261830529526</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.344813010155529</v>
+        <v>2.358159119426878</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.32076186111102</v>
+        <v>-3.242367722718717</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.016151841397373</v>
+        <v>1.060855606025643</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8865441224669965</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.876739483635727</v>
+        <v>2.890085592907076</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.348973949786607</v>
+        <v>2.362320059057956</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.340260317353029</v>
+        <v>-3.261866178960725</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.012513398531648</v>
+        <v>1.057217163159918</v>
       </c>
       <c r="F1982" t="n">
         <v>0.8384594811870922</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.852049638498863</v>
+        <v>2.865395747770211</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.354853552314444</v>
+        <v>2.368199661585793</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.296057480267128</v>
+        <v>-3.217663341874825</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.036074135893845</v>
+        <v>1.080777900522115</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8826623182729927</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.88445094327824</v>
+        <v>2.897797052549589</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.353263552783692</v>
+        <v>2.366609662055041</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.303617146104175</v>
+        <v>-3.225223007711872</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.031460270028274</v>
+        <v>1.076164034656544</v>
       </c>
       <c r="F1984" t="n">
         <v>0.937465722282812</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.915742986153379</v>
+        <v>2.929089095424728</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.404511317966731</v>
+        <v>2.41785742723808</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.145325728564903</v>
+        <v>-3.0669315901726</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.146024602227022</v>
+        <v>1.190728366855292</v>
       </c>
       <c r="F1985" t="n">
         <v>0.937465722282812</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.966990751336419</v>
+        <v>2.980336860607768</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.402952022560985</v>
+        <v>2.416298131832333</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.937683724930427</v>
+        <v>-2.859289586538123</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.227522108275066</v>
+        <v>1.272225872903336</v>
       </c>
       <c r="F1986" t="n">
         <v>1.145107725917288</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.090016658111358</v>
+        <v>3.103362767382706</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.397900250799255</v>
+        <v>2.411246360070603</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.886651632207899</v>
+        <v>-2.808257493815595</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.242883173602347</v>
+        <v>1.287586938230617</v>
       </c>
       <c r="F1987" t="n">
         <v>1.196139818639816</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.115584141983144</v>
+        <v>3.128930251254493</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.41508765489196</v>
+        <v>2.428433764163308</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.821427451080693</v>
+        <v>-2.743033312688389</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.286160250145935</v>
+        <v>1.330864014774205</v>
       </c>
       <c r="F1988" t="n">
         <v>1.261363999767022</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.171906054752173</v>
+        <v>3.185252164023522</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.41104862719124</v>
+        <v>2.424394736462589</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.784000431009559</v>
+        <v>-2.705606292617256</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.297092030473668</v>
+        <v>1.341795795101938</v>
       </c>
       <c r="F1989" t="n">
         <v>1.266615537796203</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.171017949868962</v>
+        <v>3.184364059140311</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.41230541952248</v>
+        <v>2.425651528793829</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.804112087044267</v>
+        <v>-2.725717948651964</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.290304160391025</v>
+        <v>1.335007925019295</v>
       </c>
       <c r="F1990" t="n">
         <v>1.277642882793623</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.178891149198654</v>
+        <v>3.192237258470003</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.572863190543691</v>
+        <v>2.58620929981504</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.775698823944384</v>
+        <v>-2.69730468555208</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.46222723665219</v>
+        <v>1.50693100128046</v>
       </c>
       <c r="F1991" t="n">
         <v>1.218667320047194</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.304063582572008</v>
+        <v>3.317409691843356</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.692976099761508</v>
+        <v>2.706322209032857</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.700916562919371</v>
+        <v>-2.622522424527068</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.612253050280012</v>
+        <v>1.656956814908282</v>
       </c>
       <c r="F1992" t="n">
         <v>1.293449581072206</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.469045848404832</v>
+        <v>3.482391957676181</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.684684075775367</v>
+        <v>2.698030185046716</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.674832478655563</v>
+        <v>-2.59643834026326</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.614394659999394</v>
+        <v>1.659098424627664</v>
       </c>
       <c r="F1993" t="n">
         <v>1.293449581072206</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.460753824418691</v>
+        <v>3.47409993369004</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.682877271359147</v>
+        <v>2.696223380630495</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.586954565546443</v>
+        <v>-2.508560427154139</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.647739020826822</v>
+        <v>1.692442785455092</v>
       </c>
       <c r="F1994" t="n">
         <v>1.409375223495557</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.528502405456481</v>
+        <v>3.54184851472783</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.700431677085938</v>
+        <v>2.713777786357287</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.578062104153159</v>
+        <v>-2.499667965760856</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.668850411110926</v>
+        <v>1.713554175739196</v>
       </c>
       <c r="F1995" t="n">
         <v>1.409375223495557</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.546056811183273</v>
+        <v>3.559402920454621</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.692286724490522</v>
+        <v>2.705632833761871</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.746538221123037</v>
+        <v>-2.668144082730734</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.593315011727559</v>
+        <v>1.638018776355829</v>
       </c>
       <c r="F1996" t="n">
         <v>1.381427387778977</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.521143157157908</v>
+        <v>3.534489266429257</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.673556421678384</v>
+        <v>2.686902530949733</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.300282028493597</v>
+        <v>-2.221887890101294</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.753087185967197</v>
+        <v>1.797790950595467</v>
       </c>
       <c r="F1997" t="n">
         <v>1.286708718109344</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.44558165254399</v>
+        <v>3.458927761815339</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.664220444175288</v>
+        <v>2.677566553446637</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.277560924810444</v>
+        <v>-2.199166786418141</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.752839649937363</v>
+        <v>1.797543414565633</v>
       </c>
       <c r="F1998" t="n">
         <v>1.286708718109344</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.436245675040895</v>
+        <v>3.449591784312243</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777675</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.823126570026457</v>
+        <v>2.836472679297806</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.406762738104487</v>
+        <v>-2.328368599712184</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.860065050470915</v>
+        <v>1.904768815099185</v>
       </c>
       <c r="F1999" t="n">
         <v>1.157506904815302</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.517630712915639</v>
+        <v>3.530976822186987</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.860204392520104</v>
+        <v>2.873550501791453</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.432637136578513</v>
+        <v>-2.354242998186209</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.886793113574951</v>
+        <v>1.931496878203221</v>
       </c>
       <c r="F2000" t="n">
         <v>1.202418513527043</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.58165550063633</v>
+        <v>3.595001609907678</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.856879748509649</v>
+        <v>2.870225857780998</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.425582446363339</v>
+        <v>-2.347188307971036</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.886290345650566</v>
+        <v>1.930994110278835</v>
       </c>
       <c r="F2001" t="n">
         <v>1.209473203742217</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.58256367075498</v>
+        <v>3.595909780026328</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.866885902154391</v>
+        <v>2.880232011425739</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.398631222036851</v>
+        <v>-2.320237083644548</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.907076989025902</v>
+        <v>1.951780753654172</v>
       </c>
       <c r="F2002" t="n">
         <v>1.224353549769936</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.601498032016353</v>
+        <v>3.614844141287701</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.05098903429935</v>
+        <v>3.064335143570699</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.420175449867638</v>
+        <v>-2.341781311475335</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.082562430038547</v>
+        <v>2.127266194666817</v>
       </c>
       <c r="F2003" t="n">
         <v>1.224353549769936</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.785601164161312</v>
+        <v>3.798947273432661</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.043105729202344</v>
+        <v>3.056451838473692</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.44258356767251</v>
+        <v>-2.364189429280207</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.065715877819592</v>
+        <v>2.110419642447861</v>
       </c>
       <c r="F2004" t="n">
         <v>1.224353549769936</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.777717859064305</v>
+        <v>3.791063968335654</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.045159728751981</v>
+        <v>3.05850583802333</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.470807803250111</v>
+        <v>-2.392413664857807</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.056480183138189</v>
+        <v>2.101183947766459</v>
       </c>
       <c r="F2005" t="n">
         <v>1.242330302221244</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.790557910084728</v>
+        <v>3.803904019356076</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.101413446473828</v>
+        <v>3.114759555745177</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.480248729138641</v>
+        <v>-2.401854590746337</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.108957530504624</v>
+        <v>2.153661295132894</v>
       </c>
       <c r="F2006" t="n">
         <v>1.364757419764636</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.92026789833261</v>
+        <v>3.933614007603959</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.104304541019129</v>
+        <v>3.117650650290478</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.569125360307114</v>
+        <v>-2.490731221914811</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.076297972582535</v>
+        <v>2.121001737210805</v>
       </c>
       <c r="F2007" t="n">
         <v>1.275880788596162</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.869833014176827</v>
+        <v>3.883179123448175</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347706</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.102416353912904</v>
+        <v>3.115762463184253</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.64545533790802</v>
+        <v>-2.567061199515717</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.043877794435948</v>
+        <v>2.088581559064218</v>
       </c>
       <c r="F2008" t="n">
         <v>1.275880788596162</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.867944827070602</v>
+        <v>3.881290936341951</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887751</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.097236583515766</v>
+        <v>3.110582692787115</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.739119282585562</v>
+        <v>-2.660725144193258</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.001232446167794</v>
+        <v>2.045936210796064</v>
       </c>
       <c r="F2009" t="n">
         <v>1.182216843918621</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.806566689866939</v>
+        <v>3.819912799138288</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.095670593725919</v>
+        <v>3.109016702997268</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.900687708112817</v>
+        <v>-2.822293569720514</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.935039086167044</v>
+        <v>1.979742850795314</v>
       </c>
       <c r="F2010" t="n">
         <v>1.055433920120741</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.728930945798364</v>
+        <v>3.742277055069712</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.108744000591837</v>
+        <v>3.122090109863186</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.008988369982936</v>
+        <v>-2.930594231590633</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.904792228284915</v>
+        <v>1.949495992913185</v>
       </c>
       <c r="F2011" t="n">
         <v>1.055433920120741</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.742004352664282</v>
+        <v>3.755350461935631</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.100749197374777</v>
+        <v>3.114095306646126</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.02679234170368</v>
+        <v>-2.948398203311377</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.889675836379557</v>
+        <v>1.934379601007827</v>
       </c>
       <c r="F2012" t="n">
         <v>0.9848992972155401</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.691688775704102</v>
+        <v>3.705034884975451</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.099273238501779</v>
+        <v>3.112619347773128</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.054693128813153</v>
+        <v>-2.97629899042085</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.87703956266277</v>
+        <v>1.92174332729104</v>
       </c>
       <c r="F2013" t="n">
         <v>0.9503023730726053</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.669454662345343</v>
+        <v>3.682800771616692</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.096037682478978</v>
+        <v>3.109383791750327</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.177219231516047</v>
+        <v>-3.098825093123744</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.824793565558811</v>
+        <v>1.869497330187081</v>
       </c>
       <c r="F2014" t="n">
         <v>0.8277762703697115</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.592703444700805</v>
+        <v>3.606049553972154</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.162743642069482</v>
+        <v>3.176089751340831</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.407733727701636</v>
+        <v>-3.329339589309333</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.799293726675079</v>
+        <v>1.843997491303349</v>
       </c>
       <c r="F2015" t="n">
         <v>0.5972617741841227</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.521100706579956</v>
+        <v>3.534446815851305</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.303055361071329</v>
+        <v>3.316401470342678</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.75647881292608</v>
+        <v>-3.678084674533777</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.800107411587149</v>
+        <v>1.844811176215419</v>
       </c>
       <c r="F2016" t="n">
         <v>0.4885138202652249</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.596163653230464</v>
+        <v>3.609509762501813</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237096</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.372035630216969</v>
+        <v>3.385381739488317</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.91046523070222</v>
+        <v>-3.832071092309917</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.807493113622333</v>
+        <v>1.852196878250603</v>
       </c>
       <c r="F2017" t="n">
         <v>0.4885138202652249</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.665143922376104</v>
+        <v>3.678490031647453</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423389</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.35808683233709</v>
+        <v>3.371432941608438</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.115064665565229</v>
+        <v>-4.036670527172926</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.71170454179725</v>
+        <v>1.75640830642552</v>
       </c>
       <c r="F2018" t="n">
         <v>0.4885138202652249</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.651195124496225</v>
+        <v>3.664541233767574</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.369957321392504</v>
+        <v>3.383303430663852</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.367539819572953</v>
+        <v>-4.28914568118065</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.622584969249574</v>
+        <v>1.667288733877844</v>
       </c>
       <c r="F2019" t="n">
         <v>0.4885138202652249</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.663065613551639</v>
+        <v>3.676411722822988</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.371167855911447</v>
+        <v>3.384513965182796</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.660435576052365</v>
+        <v>-4.582041437660062</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.506637201176753</v>
+        <v>1.551340965805023</v>
       </c>
       <c r="F2020" t="n">
         <v>0.4885138202652249</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.664276148070583</v>
+        <v>3.677622257341931</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.375289598138769</v>
+        <v>3.388635707410117</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.847099704187174</v>
+        <v>-4.76870556579487</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.436093292150151</v>
+        <v>1.480797056778421</v>
       </c>
       <c r="F2021" t="n">
         <v>0.461774849440665</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.652354507803168</v>
+        <v>3.665700617074517</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916203</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.370367450874958</v>
+        <v>3.383713560146307</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.993120391101136</v>
+        <v>-4.914726252708832</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.372762870120756</v>
+        <v>1.417466634749026</v>
       </c>
       <c r="F2022" t="n">
         <v>0.4526917576468081</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.641982505463043</v>
+        <v>3.655328614734392</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.532571507574002</v>
+        <v>3.545917616845351</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.08483440021072</v>
+        <v>-5.006440261818417</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.498281323175966</v>
+        <v>1.542985087804236</v>
       </c>
       <c r="F2023" t="n">
         <v>0.4526917576468081</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.804186562162087</v>
+        <v>3.817532671433436</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071553</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.527418145537816</v>
+        <v>3.540764254809165</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.11648605927069</v>
+        <v>-5.038091920878387</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.480467297515792</v>
+        <v>1.525171062144063</v>
       </c>
       <c r="F2024" t="n">
         <v>0.4475233004023679</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.795932125779237</v>
+        <v>3.809278235050586</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.537647563106308</v>
+        <v>3.550993672377656</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.198420877539573</v>
+        <v>-5.12002673914727</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.45792278777673</v>
+        <v>1.502626552405</v>
       </c>
       <c r="F2025" t="n">
         <v>0.4375885548152877</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.800200695995481</v>
+        <v>3.813546805266829</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.54657320156221</v>
+        <v>3.559919310833559</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.300396999787981</v>
+        <v>-5.222002861395677</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.42605797733327</v>
+        <v>1.47076174196154</v>
       </c>
       <c r="F2026" t="n">
         <v>0.3356124325668801</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.747940661102338</v>
+        <v>3.761286770373687</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231811</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.538726088806385</v>
+        <v>3.552072198077734</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.190390716310759</v>
+        <v>-5.111996577918456</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.462213377968334</v>
+        <v>1.506917142596604</v>
       </c>
       <c r="F2027" t="n">
         <v>0.3588170044841553</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.754016291496879</v>
+        <v>3.767362400768227</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.54297609952836</v>
+        <v>3.556322208799708</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.047331140569833</v>
+        <v>-4.96893700217753</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.523687218986678</v>
+        <v>1.568390983614949</v>
       </c>
       <c r="F2028" t="n">
         <v>0.3668304310741346</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.763074358172841</v>
+        <v>3.776420467444189</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.550236982410896</v>
+        <v>3.563583091682244</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.745884415097995</v>
+        <v>-4.667490276705692</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.651526792057949</v>
+        <v>1.69623055668622</v>
       </c>
       <c r="F2029" t="n">
         <v>0.6682771565459719</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.951203276338479</v>
+        <v>3.964549385609828</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.551208160163606</v>
+        <v>3.564554269434955</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.770474659333179</v>
+        <v>-4.692080520940876</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.642661872116587</v>
+        <v>1.687365636744857</v>
       </c>
       <c r="F2030" t="n">
         <v>0.6682771565459719</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.95217445409119</v>
+        <v>3.965520563362539</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.552051064543362</v>
+        <v>3.565397173814711</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.719436283326659</v>
+        <v>-4.641042144934356</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.66392012689895</v>
+        <v>1.70862389152722</v>
       </c>
       <c r="F2031" t="n">
         <v>0.6682771565459719</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.953017358470945</v>
+        <v>3.966363467742294</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969545</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.571089163417507</v>
+        <v>3.584435272688856</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.678296988460028</v>
+        <v>-4.599902850067725</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.699413943719748</v>
+        <v>1.744117708348018</v>
       </c>
       <c r="F2032" t="n">
         <v>0.7094164514126027</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.996739034265069</v>
+        <v>4.010085143536418</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.387273159541442</v>
+        <v>3.400619268812791</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.581662076441388</v>
+        <v>-4.503267938049085</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.554251904651139</v>
+        <v>1.598955669279409</v>
       </c>
       <c r="F2033" t="n">
         <v>0.8060513634312426</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.870903977600188</v>
+        <v>3.884250086871536</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077643</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.390775203615406</v>
+        <v>3.404121312886755</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.712242810972231</v>
+        <v>-4.633848672579927</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.505521654912766</v>
+        <v>1.550225419541036</v>
       </c>
       <c r="F2034" t="n">
         <v>0.6754706289004001</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.796057580955646</v>
+        <v>3.809403690226995</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833461</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.375202022691489</v>
+        <v>3.388548131962837</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.547746476781269</v>
+        <v>-4.469352338388966</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.555747007665233</v>
+        <v>1.600450772293503</v>
       </c>
       <c r="F2035" t="n">
         <v>0.839966963091362</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.879182200546306</v>
+        <v>3.892528309817655</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.374389733127918</v>
+        <v>3.387735842399267</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.470647875239396</v>
+        <v>-4.392253736847093</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.585774158718412</v>
+        <v>1.630477923346682</v>
       </c>
       <c r="F2036" t="n">
         <v>0.839966963091362</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.878369910982736</v>
+        <v>3.891716020254084</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.384258512252991</v>
+        <v>3.397604621524339</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.481033070129286</v>
+        <v>-4.402638931736982</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.591488859887529</v>
+        <v>1.636192624515798</v>
       </c>
       <c r="F2037" t="n">
         <v>0.8295817682014727</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.882007573173874</v>
+        <v>3.895353682445223</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.834415493735284</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.455095518029416</v>
+        <v>3.468441627300765</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.499621228851511</v>
+        <v>-4.421227090459207</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.654890602175064</v>
+        <v>1.699594366803334</v>
       </c>
       <c r="F2038" t="n">
         <v>0.8109936094792474</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.941691683716964</v>
+        <v>3.955037792988313</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.451964528847714</v>
+        <v>3.465310638119063</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.499919775547546</v>
+        <v>-4.421525637155243</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.651640194314948</v>
+        <v>1.696343958943218</v>
       </c>
       <c r="F2039" t="n">
         <v>0.8106950627832115</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.938381566517641</v>
+        <v>3.95172767578899</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.815643212108859</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.456495423787106</v>
+        <v>3.469841533058454</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.399096641857119</v>
+        <v>-4.320702503464815</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.69650034273051</v>
+        <v>1.74120410735878</v>
       </c>
       <c r="F2040" t="n">
         <v>0.8231592782675653</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.950390990747645</v>
+        <v>3.963737100018994</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.456624677265649</v>
+        <v>3.469970786536998</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.208315281104712</v>
+        <v>-4.129921142712409</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.772942140510016</v>
+        <v>1.817645905138286</v>
       </c>
       <c r="F2041" t="n">
         <v>1.013940639019973</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.064989060677633</v>
+        <v>4.078335169948982</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.436461523003246</v>
+        <v>3.449807632274594</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.10135192325529</v>
+        <v>-4.022957784862987</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.795564329387382</v>
+        <v>1.840268094015652</v>
       </c>
       <c r="F2042" t="n">
         <v>1.072405246979774</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.079904671191111</v>
+        <v>4.093250780462459</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912985</v>
+        <v>3.785761685912987</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.471428459615304</v>
+        <v>3.484774568886653</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.046021335353528</v>
+        <v>-3.967627196961225</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.852663501160145</v>
+        <v>1.897367265788415</v>
       </c>
       <c r="F2043" t="n">
         <v>1.127735834881536</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.148069960544226</v>
+        <v>4.161416069815575</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539896</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.465115027516742</v>
+        <v>3.47846113678809</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.033967208440565</v>
+        <v>-3.955573070048262</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.851171719826768</v>
+        <v>1.895875484455038</v>
       </c>
       <c r="F2044" t="n">
         <v>1.139789961794499</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.148989004593441</v>
+        <v>4.16233511386479</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.466995657700878</v>
+        <v>3.480341766972226</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.075122328008786</v>
+        <v>-3.996728189616483</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.836590302183615</v>
+        <v>1.881294066811885</v>
       </c>
       <c r="F2045" t="n">
         <v>1.098634842226278</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.126176563036645</v>
+        <v>4.139522672307994</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382922</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.47984668357876</v>
+        <v>3.493192792850109</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.007073765317256</v>
+        <v>-3.928679626924953</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.87666075313811</v>
+        <v>1.92136451776638</v>
       </c>
       <c r="F2046" t="n">
         <v>1.166683404917808</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.179856726529446</v>
+        <v>4.193202835800794</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013428</v>
+        <v>3.64525678001343</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.500049353752354</v>
+        <v>3.513395463023703</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.238674158486757</v>
+        <v>-4.160280020094454</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.804223266043904</v>
+        <v>1.848927030672173</v>
       </c>
       <c r="F2047" t="n">
         <v>1.166683404917808</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.20005939670304</v>
+        <v>4.213405505974388</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.483655589819236</v>
+        <v>3.497001699090585</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.288725704015976</v>
+        <v>-4.210331565623674</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.767808883899098</v>
+        <v>1.812512648527367</v>
       </c>
       <c r="F2048" t="n">
         <v>1.166683404917808</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.183665632769921</v>
+        <v>4.19701174204127</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.443907503412703</v>
+        <v>3.457253612684052</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.46383253659242</v>
+        <v>-4.385438398200119</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.658018064461987</v>
+        <v>1.702721829090256</v>
       </c>
       <c r="F2049" t="n">
         <v>1.166683404917808</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.143917546363388</v>
+        <v>4.157263655634737</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.450930122409643</v>
+        <v>3.464276231680992</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.267732383161897</v>
+        <v>-4.189338244769596</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.743480744831136</v>
+        <v>1.788184509459405</v>
       </c>
       <c r="F2050" t="n">
         <v>1.362783558348331</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.268600257418642</v>
+        <v>4.281946366689991</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.550101121982547</v>
+        <v>3.563447231253896</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.114706991048613</v>
+        <v>-4.036312852656311</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.903861901249354</v>
+        <v>1.948565665877624</v>
       </c>
       <c r="F2051" t="n">
         <v>1.515808950461615</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.459586492259517</v>
+        <v>4.472932601530865</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791148</v>
+        <v>3.74127833279115</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.73756734689084</v>
+        <v>3.750913456162189</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.143014304921883</v>
+        <v>-4.064620166529582</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.080005200608339</v>
+        <v>2.124708965236608</v>
       </c>
       <c r="F2052" t="n">
         <v>1.515808950461615</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.647052717167809</v>
+        <v>4.660398826439158</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.706970298244923</v>
+        <v>3.720316407516271</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.309607530035406</v>
+        <v>-4.231213391643104</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.982770861917012</v>
+        <v>2.027474626545282</v>
       </c>
       <c r="F2053" t="n">
         <v>1.349215725348093</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.516499733453778</v>
+        <v>4.529845842725127</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.708182519285648</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.71064670090664</v>
+        <v>3.723992810177989</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.28657173667384</v>
+        <v>-4.208177598281538</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.995661581923357</v>
+        <v>2.040365346551626</v>
       </c>
       <c r="F2054" t="n">
         <v>1.349215725348093</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.520176136115496</v>
+        <v>4.533522245386845</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399468</v>
+        <v>3.74058140139947</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.708264756030136</v>
+        <v>3.721610865301484</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.257325756218143</v>
+        <v>-4.178931617825842</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.004978029229131</v>
+        <v>2.0496817938574</v>
       </c>
       <c r="F2055" t="n">
         <v>1.349215725348093</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.517794191238991</v>
+        <v>4.53114030051034</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256374</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.705557995187771</v>
+        <v>3.718904104459119</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.370323324413686</v>
+        <v>-4.285857165703693</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.957072241108548</v>
+        <v>2.004204813863894</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.23621815715255</v>
+        <v>1.242290177470241</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.447288889479301</v>
+        <v>4.464278210941265</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701003</v>
+        <v>3.689942600701004</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.706986797331005</v>
+        <v>3.720332906602354</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.515341882920935</v>
+        <v>-4.430875724210941</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.900493619848883</v>
+        <v>1.947626192604229</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.091199598645301</v>
+        <v>1.097271618962993</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.361706556518186</v>
+        <v>4.378695877980149</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.806918036588758</v>
+        <v>3.820264145860107</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.633683648705652</v>
+        <v>-4.549217489995659</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.953088152792749</v>
+        <v>2.000220725548095</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.101885637208191</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.468049418913673</v>
+        <v>4.485038740375637</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790804</v>
+        <v>3.714879051790806</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.804703733714697</v>
+        <v>3.818049842986046</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.68509407102636</v>
+        <v>-4.600627912316367</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.930309680990405</v>
+        <v>1.977442253745751</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.101885637208191</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.465835116039612</v>
+        <v>4.482824437501575</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437332</v>
+        <v>3.704757949437334</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.804606861788986</v>
+        <v>3.817952971060335</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.764513522234112</v>
+        <v>-4.680047363524118</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.898445028581593</v>
+        <v>1.945577601336939</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.101885637208191</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.465738244113902</v>
+        <v>4.482727565575865</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298399</v>
+        <v>3.736804952298401</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.804600755347029</v>
+        <v>3.817946864618378</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.85997652015133</v>
+        <v>-4.775510361441336</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.860253722972749</v>
+        <v>1.907386295728095</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.101885637208191</v>
+        <v>1.107957657525883</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.465732137671944</v>
+        <v>4.482721459133908</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218002</v>
+        <v>3.715372960218004</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.80269715190964</v>
+        <v>3.816043261180988</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.795600609300615</v>
+        <v>-4.711134450590621</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.884100483875646</v>
+        <v>1.931233056630992</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.166261548058906</v>
+        <v>1.172333568376598</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.502454080744984</v>
+        <v>4.519443402206948</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353538</v>
+        <v>3.73608941335354</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.808430969657366</v>
+        <v>3.821777078928715</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.850969771432808</v>
+        <v>-4.766503612722815</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.867686636770495</v>
+        <v>1.914819209525841</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.166261548058906</v>
+        <v>1.172333568376598</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.508187898492711</v>
+        <v>4.525177219954674</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113281</v>
+        <v>3.736822870113283</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.807969333000299</v>
+        <v>3.821315442271648</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.896407551263636</v>
+        <v>-4.811941392553642</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.849049888181097</v>
+        <v>1.896182460936443</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.123416557380747</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.482019267428747</v>
+        <v>4.499008588890711</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.79027250011369</v>
+        <v>3.790272500113692</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.827843725850617</v>
+        <v>3.841189835121966</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.808200717116057</v>
+        <v>-4.723734558406064</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.904207014690447</v>
+        <v>1.951339587445792</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.123416557380747</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.501893660279066</v>
+        <v>4.518882981741029</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.79448684401644</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.811544426375345</v>
+        <v>3.824890535646694</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.702165721910748</v>
+        <v>-4.617699563200754</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.930321713297298</v>
+        <v>1.977454286052645</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.123416557380747</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.485594360803794</v>
+        <v>4.502583682265757</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307671</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.813975375839391</v>
+        <v>3.82732148511074</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.518954058777653</v>
+        <v>-4.434487900067659</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.006037328014582</v>
+        <v>2.053169900769928</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.123416557380747</v>
+        <v>1.129488577698438</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.488025310267839</v>
+        <v>4.505014631729804</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.779766561687281</v>
+        <v>3.79311267095863</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.447232611763802</v>
+        <v>-4.362766453053808</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.000517092668012</v>
+        <v>2.047649665423358</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.195138004394598</v>
+        <v>1.201210024712289</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.49684936432404</v>
+        <v>4.513838685786004</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394113</v>
+        <v>3.723789705394115</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.726682307608453</v>
+        <v>3.740028416879801</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.424859586156096</v>
+        <v>-4.340393427446102</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.956382048832267</v>
+        <v>2.003514621587613</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.206393755507499</v>
+        <v>1.212465775825191</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.450518560912952</v>
+        <v>4.467507882374916</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456732</v>
       </c>
       <c r="C2070" t="n">
-        <v>3.911880512493808</v>
+        <v>3.925226621765157</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.45787588206684</v>
+        <v>-4.373409723356847</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.128373735353324</v>
+        <v>2.175506308108671</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.136956378840748</v>
+        <v>1.143028399158439</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.594054339798257</v>
+        <v>4.61104366126022</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883678</v>
+        <v>3.71376253688368</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.903801738322058</v>
+        <v>3.917147847593407</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.446348246417232</v>
+        <v>-4.361882087707238</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.124906015441417</v>
+        <v>2.172038588196763</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.19595703704211</v>
+        <v>1.202029057359802</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.621375960547324</v>
+        <v>4.638365282009287</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236299</v>
+        <v>3.717150699236301</v>
       </c>
       <c r="C2072" t="n">
-        <v>3.907469850843846</v>
+        <v>3.920815960115195</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.543689747759601</v>
+        <v>-4.459223589049607</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.089637527426258</v>
+        <v>2.136770100181604</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.151536854876622</v>
+        <v>1.157608875194313</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.59839196376982</v>
+        <v>4.615381285231782</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427686</v>
+        <v>3.705201079427687</v>
       </c>
       <c r="C2073" t="n">
-        <v>3.908720933036685</v>
+        <v>3.922067042308033</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.629545777099567</v>
+        <v>-4.545079618389574</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.05654619788311</v>
+        <v>2.103678770638456</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.109160785650487</v>
+        <v>1.115232805968178</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.574217404426976</v>
+        <v>4.59120672588894</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.891140134857187</v>
+        <v>3.904486244128535</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.638382574515687</v>
+        <v>-4.553916415805693</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.035430680737164</v>
+        <v>2.082563253492509</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.101718613009136</v>
+        <v>1.107790633326827</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.552171302662669</v>
+        <v>4.569160624124631</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667456</v>
+        <v>3.715544411667458</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.901304645902236</v>
+        <v>3.914650755173584</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.729765137081145</v>
+        <v>-4.645298978371152</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.00904216675603</v>
+        <v>2.056174739511375</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.065153728289791</v>
+        <v>1.071225748607483</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.540396882876111</v>
+        <v>4.557386204338074</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889192</v>
+        <v>3.673978374889194</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.003432903726504</v>
+        <v>4.016779012997851</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.718058419094139</v>
+        <v>-4.633592260384146</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.1158531117751</v>
+        <v>2.162985684530445</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.076860446276798</v>
+        <v>1.082932466594489</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.649549171492582</v>
+        <v>4.666538492954545</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409567</v>
+        <v>3.682476099409569</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.006465242457908</v>
+        <v>4.019811351729256</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.618394915010477</v>
+        <v>-4.533928756300483</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.15875085213997</v>
+        <v>2.205883424895315</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.140047529480484</v>
+        <v>1.146119549798176</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.690493760146199</v>
+        <v>4.707483081608162</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452572</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.219370075735966</v>
+        <v>4.232716185007314</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.628711013176829</v>
+        <v>-4.544244854466835</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.367529246151487</v>
+        <v>2.414661818906832</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.140047529480484</v>
+        <v>1.146119549798176</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.903398593424257</v>
+        <v>4.92038791488622</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762288</v>
+        <v>3.62396095976229</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.218548742648056</v>
+        <v>4.231894851919404</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.628617045159456</v>
+        <v>-4.544150886449462</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.366745500270526</v>
+        <v>2.413878073025871</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.140417390827802</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.902799177144738</v>
+        <v>4.9197884986067</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988019</v>
+        <v>3.633213467988021</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.21278072859241</v>
+        <v>4.226126837863758</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.6358358693593</v>
+        <v>-4.551369710649307</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.358089956534942</v>
+        <v>2.405222529290287</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.140417390827802</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.897031163089092</v>
+        <v>4.914020484551054</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.21278072859241</v>
+        <v>4.226126837863758</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.634887446241262</v>
+        <v>-4.550421287531268</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.358469325782157</v>
+        <v>2.405601898537503</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.140417390827802</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.897031163089092</v>
+        <v>4.914020484551054</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.225508336573502</v>
+        <v>4.23885444584485</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.791955904496886</v>
+        <v>-4.707489745786892</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.308369550460999</v>
+        <v>2.355502123216345</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.140417390827802</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.909758771070184</v>
+        <v>4.926748092532146</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.22745433499789</v>
+        <v>4.240800444269238</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.785963657708074</v>
+        <v>-4.701497498998081</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.312712447600912</v>
+        <v>2.359845020356257</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.140417390827802</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.911704769494571</v>
+        <v>4.928694090956534</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.221108471015659</v>
+        <v>4.234454580287006</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.697405696577307</v>
+        <v>-4.612939537867313</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.341789768070988</v>
+        <v>2.388922340826333</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.140417390827802</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.90535890551234</v>
+        <v>4.922348226974303</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.220417148454654</v>
+        <v>4.233763257726002</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.679646619074233</v>
+        <v>-4.595180460364239</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.348202076511213</v>
+        <v>2.395334649266558</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.140417390827802</v>
+        <v>1.146489411145494</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.904667582951336</v>
+        <v>4.921656904413299</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.233199334363241</v>
+        <v>4.246545443634589</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.580016468025165</v>
+        <v>-4.495550309315171</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.400836322839427</v>
+        <v>2.447968895594772</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.24004754187687</v>
+        <v>1.246119562194561</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.977227859489363</v>
+        <v>4.994217180951326</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455269</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.422353599861967</v>
+        <v>4.435699709133315</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.629415976714176</v>
+        <v>-4.544949818004183</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.570230784862549</v>
+        <v>2.617363357617895</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.250306375308615</v>
+        <v>1.256378395626306</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.172537425047136</v>
+        <v>5.189526746509099</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,45 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.885981436568635</v>
+        <v>3.749078058963137</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.409542272964829</v>
+        <v>4.422888382236177</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.452194917208469</v>
+        <v>-4.381599147476366</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.628307881767694</v>
+        <v>2.669892298931883</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.427527434814321</v>
+        <v>1.419729066154123</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.266058733853423</v>
+        <v>5.274725821928651</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="2" t="n">
+        <v>45551</v>
+      </c>
+      <c r="B2089" t="n">
+        <v>3.717715068313017</v>
+      </c>
+      <c r="C2089" t="n">
+        <v>4.414211027307431</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>-4.381599147476366</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>2.669892298931883</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>1.419729066154123</v>
+      </c>
+      <c r="G2089" t="n">
+        <v>4.407274824293799</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240916.xlsx
+++ b/tame_output/ON/bt/strategyON_20240916.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>129.8%</t>
+          <t>128.3%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.7%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.6%</t>
+          <t>418.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-599.7%</t>
+          <t>-625.8%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-31.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-109.2%</t>
+          <t>-110.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-58.2%</t>
+          <t>-55.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.3%</t>
+          <t>-323.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-82.0%</t>
+          <t>-90.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,31 +1423,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,42 +1471,42 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-6.8%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097243</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.50879893065626</v>
+        <v>-4.52321824479905</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.069587412310311</v>
+        <v>1.063819686653195</v>
       </c>
       <c r="F1926" t="n">
         <v>0.3467883509260594</v>
@@ -45872,10 +45872,10 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.491085243778395</v>
+        <v>-4.505504557921185</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.077351470978797</v>
+        <v>1.071583745321681</v>
       </c>
       <c r="F1927" t="n">
         <v>0.3499696798229762</v>
@@ -45895,10 +45895,10 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.367610972465377</v>
+        <v>-4.382030286608167</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.123739250723998</v>
+        <v>1.117971525066882</v>
       </c>
       <c r="F1928" t="n">
         <v>0.3499696798229762</v>
@@ -45918,10 +45918,10 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.147590174428366</v>
+        <v>-4.162009488571156</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.213326606949416</v>
+        <v>1.2075588812923</v>
       </c>
       <c r="F1929" t="n">
         <v>0.4911895248909565</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.014722485365088</v>
+        <v>-4.029141799507879</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.28236786537655</v>
+        <v>1.276600139719434</v>
       </c>
       <c r="F1930" t="n">
         <v>0.4911895248909565</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.89454940200059</v>
+        <v>-3.90896871614338</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.331582943162652</v>
+        <v>1.325815217505536</v>
       </c>
       <c r="F1931" t="n">
         <v>0.6113626082554554</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.759296040670613</v>
+        <v>-3.773715354813403</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.395772390256083</v>
+        <v>1.390004664598967</v>
       </c>
       <c r="F1932" t="n">
         <v>0.7466159695854325</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.819170868028305</v>
+        <v>-3.833590182171095</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.357859950714432</v>
+        <v>1.352092225057315</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6867411422277404</v>
@@ -46033,10 +46033,10 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.699350637117468</v>
+        <v>-3.713769951260258</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.421077212312975</v>
+        <v>1.415309486655859</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6867411422277404</v>
@@ -46056,10 +46056,10 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.701820343579274</v>
+        <v>-3.716239657722064</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.327733529050694</v>
+        <v>1.321965803393578</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6842714357659343</v>
@@ -46079,10 +46079,10 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.770190529903283</v>
+        <v>-3.784609844046074</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.219647316006392</v>
+        <v>1.213879590349276</v>
       </c>
       <c r="F1936" t="n">
         <v>0.6935471348021492</v>
@@ -46102,10 +46102,10 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.882062809529434</v>
+        <v>-3.896482123672224</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.165335112787823</v>
+        <v>1.159567387130707</v>
       </c>
       <c r="F1937" t="n">
         <v>0.6935471348021492</v>
@@ -46125,10 +46125,10 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.866088144043166</v>
+        <v>-3.880507458185956</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.138299503906357</v>
+        <v>1.132531778249241</v>
       </c>
       <c r="F1938" t="n">
         <v>0.6935471348021492</v>
@@ -46148,10 +46148,10 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.690613884250697</v>
+        <v>-3.705033198393487</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.213056439815133</v>
+        <v>1.207288714158016</v>
       </c>
       <c r="F1939" t="n">
         <v>0.6935471348021492</v>
@@ -46171,10 +46171,10 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.682689509665783</v>
+        <v>-3.697108823808573</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.191968218410305</v>
+        <v>1.186200492753189</v>
       </c>
       <c r="F1940" t="n">
         <v>0.6935471348021492</v>
@@ -46194,10 +46194,10 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.676411307095934</v>
+        <v>-3.690830621238724</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.123017812839695</v>
+        <v>1.117250087182579</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6998253373719983</v>
@@ -46217,10 +46217,10 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.616558687892211</v>
+        <v>-3.630978002035001</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.157131246953316</v>
+        <v>1.1513635212962</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6998253373719983</v>
@@ -46240,10 +46240,10 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.530315224865833</v>
+        <v>-3.544734539008624</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.186574902737727</v>
+        <v>1.180807177080611</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6998253373719983</v>
@@ -46263,10 +46263,10 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.575622044264813</v>
+        <v>-3.590041358407603</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.160227950422661</v>
+        <v>1.154460224765545</v>
       </c>
       <c r="F1944" t="n">
         <v>0.6590151743627675</v>
@@ -46286,10 +46286,10 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.604655148967115</v>
+        <v>-3.619074463109905</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.149166581574842</v>
+        <v>1.143398855917726</v>
       </c>
       <c r="F1945" t="n">
         <v>0.6590151743627675</v>
@@ -46309,10 +46309,10 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.511844667516256</v>
+        <v>-3.526263981659046</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.115563466046551</v>
+        <v>1.109795740389435</v>
       </c>
       <c r="F1946" t="n">
         <v>0.7518256558136268</v>
@@ -46332,10 +46332,10 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.556234136845683</v>
+        <v>-3.570653450988473</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.099681154239381</v>
+        <v>1.093913428582265</v>
       </c>
       <c r="F1947" t="n">
         <v>0.7074361864841991</v>
@@ -46355,10 +46355,10 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.535730442960186</v>
+        <v>-3.550149757102976</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.102958340305303</v>
+        <v>1.097190614648187</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7279398803696965</v>
@@ -46378,10 +46378,10 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.575654537542758</v>
+        <v>-3.590073851685548</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.092479998302942</v>
+        <v>1.086712272645825</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7279398803696965</v>
@@ -46401,10 +46401,10 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.603434935444111</v>
+        <v>-3.617854249586901</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.092865040910939</v>
+        <v>1.087097315253823</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7001594824683435</v>
@@ -46424,10 +46424,10 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.72181560817425</v>
+        <v>-3.73623492231704</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8838684918195372</v>
+        <v>0.8781007661624212</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6329416303173673</v>
@@ -46447,10 +46447,10 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.830429686617581</v>
+        <v>-3.844849000760371</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9605725211614105</v>
+        <v>0.9548047955042944</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6329416303173673</v>
@@ -46470,10 +46470,10 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.795020648369438</v>
+        <v>-3.809439962512228</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9892491625629907</v>
+        <v>0.9834814369058744</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6329416303173673</v>
@@ -46493,10 +46493,10 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.803481817024899</v>
+        <v>-3.817901131167689</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9832841364431748</v>
+        <v>0.9775164107860588</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6244804616619062</v>
@@ -46516,10 +46516,10 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.626365486989733</v>
+        <v>-3.640784801132523</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.050859697302544</v>
+        <v>1.045091971645427</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6244804616619062</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.671457731823279</v>
+        <v>-3.685877045966069</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.033506191131038</v>
+        <v>1.027738465473922</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5625844184925164</v>
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.492082310584511</v>
+        <v>-3.694775524425815</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.09904333493296</v>
+        <v>1.017966049396438</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7193611766632351</v>
+        <v>0.5945141099225935</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.927849389478454</v>
+        <v>2.852941149434069</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.537096524105117</v>
+        <v>-3.739789737946421</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.061845104856307</v>
+        <v>0.9807678193197855</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6890122813486305</v>
+        <v>0.5641652146079889</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.890447507621281</v>
+        <v>2.815539267576896</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.804101034377553</v>
+        <v>-4.006794248218856</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9607348630862786</v>
+        <v>0.879657577549757</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4946492433056819</v>
+        <v>0.3698021765650403</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.779521247134457</v>
+        <v>2.704613007090072</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.905298815814725</v>
+        <v>-4.10799202965603</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9194596724079109</v>
+        <v>0.8383823868713891</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4262404297603627</v>
+        <v>0.3013933630197211</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.737679880903767</v>
+        <v>2.662771640859382</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.898787849200413</v>
+        <v>-4.101481063041717</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9196640206079527</v>
+        <v>0.8385867350714309</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4262404297603627</v>
+        <v>0.3013933630197211</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.735279842458084</v>
+        <v>2.660371602413699</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.879749721493115</v>
+        <v>-4.08244293533442</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9238039908991167</v>
+        <v>0.8427267053625949</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3680568184291682</v>
+        <v>0.2432097516885265</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.696894394867612</v>
+        <v>2.621986154823227</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.932265523767935</v>
+        <v>-4.13495873760924</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.022092071623379</v>
+        <v>0.941014786086857</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3680568184291682</v>
+        <v>0.2432097516885265</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.816188796501802</v>
+        <v>2.741280556457417</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.935673835202515</v>
+        <v>-4.13836704904382</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.021562076035681</v>
+        <v>0.9404847904991587</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4005733874385456</v>
+        <v>0.2757263206979039</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.836532066893562</v>
+        <v>2.761623826849177</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.916317699308668</v>
+        <v>-4.119010913149973</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.035313060790145</v>
+        <v>0.9542357752536235</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4005733874385456</v>
+        <v>0.2757263206979039</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.842540597290488</v>
+        <v>2.767632357246103</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.768574729073666</v>
+        <v>-3.971267942914971</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9923604701613458</v>
+        <v>0.9112831846248239</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5683807446734288</v>
+        <v>0.4435336779327871</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.841175232908618</v>
+        <v>2.766266992864232</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.411460004418285</v>
+        <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.751311108585204</v>
+        <v>-4.055089164189669</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9105791366704556</v>
+        <v>0.8805483176464257</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5683807446734288</v>
+        <v>0.4435336779327871</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.752488451222343</v>
+        <v>2.769060614395713</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.412122352809944</v>
+        <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.745158402532419</v>
+        <v>-4.048936458136884</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9137025674832278</v>
+        <v>0.8836717484591978</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5745334507262131</v>
+        <v>0.4496863839855714</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.756842423245672</v>
+        <v>2.773414586419042</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.411202829550054</v>
+        <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.761967700682921</v>
+        <v>-4.065745756287386</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9060593249631375</v>
+        <v>0.8760285059391073</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5577241525757115</v>
+        <v>0.4328770858350697</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.745837321095481</v>
+        <v>2.762409484268852</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.477538383346875</v>
+        <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.699669701906799</v>
+        <v>-4.003447757511264</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9973140782704071</v>
+        <v>0.9672832592463769</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6030184168501536</v>
+        <v>0.4781713501095118</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.839349433456967</v>
+        <v>2.855921596630338</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.279830385061002</v>
+        <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.497879504241641</v>
+        <v>-3.801657559846106</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8803221590505974</v>
+        <v>0.850291340026567</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.801036609019308</v>
+        <v>0.6761895422786661</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.760452350472587</v>
+        <v>2.777024513645958</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.350120617383177</v>
+        <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.548766216927836</v>
+        <v>-3.852544272532301</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9302577062982946</v>
+        <v>0.9002268872742645</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7501498963331135</v>
+        <v>0.6253028295924716</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.800210555183045</v>
+        <v>2.816782718356416</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.364748353499221</v>
+        <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.462155474278028</v>
+        <v>-3.765933529882493</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9795297394742613</v>
+        <v>0.9494989204502309</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8287756275382717</v>
+        <v>0.7039285607976299</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.862013730022184</v>
+        <v>2.878585893195555</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.363284334323892</v>
+        <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.522364772283313</v>
+        <v>-3.826142827887778</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9539820010968192</v>
+        <v>0.9239511820727888</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7685663295329872</v>
+        <v>0.6437192627923454</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.824424132043685</v>
+        <v>2.840996295217056</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.361775952363821</v>
+        <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.473178123598962</v>
+        <v>-3.776956179203427</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9721482786104882</v>
+        <v>0.9421174595864579</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7685663295329872</v>
+        <v>0.6437192627923454</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.822915750083614</v>
+        <v>2.839487913256984</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.361638819799257</v>
+        <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.428804991960393</v>
+        <v>-3.732583047564858</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9897603987013519</v>
+        <v>0.9597295796773215</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8129394611715558</v>
+        <v>0.688092394430914</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.849402496502191</v>
+        <v>2.865974659675562</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.356032613937848</v>
+        <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.451285342819278</v>
+        <v>-3.755063398423743</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9751620524963884</v>
+        <v>0.9451312334723583</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8129394611715558</v>
+        <v>0.688092394430914</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.843796290640781</v>
+        <v>2.860368453814152</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.362414370965652</v>
+        <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.403629612258222</v>
+        <v>-3.707407667862687</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.000606101748615</v>
+        <v>0.970575282724585</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8605951917326115</v>
+        <v>0.7357481249919696</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.87877148600522</v>
+        <v>2.89534364917859</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.367306744340377</v>
+        <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.303111453759468</v>
+        <v>-3.606889509363933</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.045705738522842</v>
+        <v>1.015674919498812</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.961113350231366</v>
+        <v>0.8362662834907242</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.943974754479197</v>
+        <v>2.960546917652568</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.354061416816249</v>
+        <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.287206124327115</v>
+        <v>-3.59098417993158</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.038822542771655</v>
+        <v>1.008791723747625</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8820006895221271</v>
+        <v>0.7571536227814852</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.883261830529526</v>
+        <v>2.899833993702897</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.358159119426878</v>
+        <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.242367722718717</v>
+        <v>-3.546145778323182</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.060855606025643</v>
+        <v>1.030824787001613</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8865441224669965</v>
+        <v>0.7616970557263547</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.890085592907076</v>
+        <v>2.906657756080447</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.362320059057956</v>
+        <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.261866178960725</v>
+        <v>-3.56564423456519</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.057217163159918</v>
+        <v>1.027186344135887</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8384594811870922</v>
+        <v>0.7136124144464504</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.865395747770211</v>
+        <v>2.881967910943582</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.368199661585793</v>
+        <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.217663341874825</v>
+        <v>-3.52144139747929</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.080777900522115</v>
+        <v>1.050747081498085</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8826623182729927</v>
+        <v>0.7578152515323509</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.897797052549589</v>
+        <v>2.91436921572296</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.366609662055041</v>
+        <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.225223007711872</v>
+        <v>-3.529001063316337</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.076164034656544</v>
+        <v>1.046133215632514</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.937465722282812</v>
+        <v>0.8126186555421702</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.929089095424728</v>
+        <v>2.945661258598099</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284876</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.41785742723808</v>
+        <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.0669315901726</v>
+        <v>-3.370709645777064</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.190728366855292</v>
+        <v>1.160697547831262</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.937465722282812</v>
+        <v>0.8126186555421702</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.980336860607768</v>
+        <v>2.996909023781138</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.416298131832333</v>
+        <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.859289586538123</v>
+        <v>-3.163067642142588</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.272225872903336</v>
+        <v>1.242195053879306</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.145107725917288</v>
+        <v>1.020260659176646</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.103362767382706</v>
+        <v>3.119934930556077</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.411246360070603</v>
+        <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.808257493815595</v>
+        <v>-3.11203554942006</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.287586938230617</v>
+        <v>1.257556119206587</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.196139818639816</v>
+        <v>1.071292751899174</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.128930251254493</v>
+        <v>3.145502414427864</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.428433764163308</v>
+        <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.743033312688389</v>
+        <v>-3.046811368292854</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.330864014774205</v>
+        <v>1.300833195750174</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.261363999767022</v>
+        <v>1.13651693302638</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.185252164023522</v>
+        <v>3.201824327196892</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.424394736462589</v>
+        <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.705606292617256</v>
+        <v>-3.009384348221721</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.341795795101938</v>
+        <v>1.311764976077908</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.266615537796203</v>
+        <v>1.141768471055562</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.184364059140311</v>
+        <v>3.200936222313682</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.425651528793829</v>
+        <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.725717948651964</v>
+        <v>-3.029496004256429</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.335007925019295</v>
+        <v>1.304977105995265</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.277642882793623</v>
+        <v>1.152795816052981</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.192237258470003</v>
+        <v>3.208809421643374</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.58620929981504</v>
+        <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.69730468555208</v>
+        <v>-3.001082741156545</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.50693100128046</v>
+        <v>1.476900182256429</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.218667320047194</v>
+        <v>1.093820253306552</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.317409691843356</v>
+        <v>3.333981855016727</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.706322209032857</v>
+        <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.622522424527068</v>
+        <v>-2.926300480131533</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.656956814908282</v>
+        <v>1.626925995884252</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.293449581072206</v>
+        <v>1.168602514331565</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.482391957676181</v>
+        <v>3.498964120849552</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.698030185046716</v>
+        <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.59643834026326</v>
+        <v>-2.900216395867725</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.659098424627664</v>
+        <v>1.629067605603634</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.293449581072206</v>
+        <v>1.168602514331565</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.47409993369004</v>
+        <v>3.490672096863411</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.696223380630495</v>
+        <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.508560427154139</v>
+        <v>-2.812338482758604</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.692442785455092</v>
+        <v>1.662411966431061</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.409375223495557</v>
+        <v>1.284528156754916</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.54184851472783</v>
+        <v>3.558420677901201</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.713777786357287</v>
+        <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.499667965760856</v>
+        <v>-2.803446021365321</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.713554175739196</v>
+        <v>1.683523356715166</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.409375223495557</v>
+        <v>1.284528156754916</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.559402920454621</v>
+        <v>3.575975083627992</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.705632833761871</v>
+        <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.668144082730734</v>
+        <v>-2.971922138335199</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.638018776355829</v>
+        <v>1.607987957331799</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.381427387778977</v>
+        <v>1.256580321038335</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.534489266429257</v>
+        <v>3.551061429602628</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.686902530949733</v>
+        <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.221887890101294</v>
+        <v>-2.525665945705759</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.797790950595467</v>
+        <v>1.767760131571437</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.286708718109344</v>
+        <v>1.161861651368702</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.458927761815339</v>
+        <v>3.47549992498871</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.677566553446637</v>
+        <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.199166786418141</v>
+        <v>-2.502944842022606</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.797543414565633</v>
+        <v>1.767512595541602</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.286708718109344</v>
+        <v>1.161861651368702</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.449591784312243</v>
+        <v>3.466163947485614</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777675</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.836472679297806</v>
+        <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.328368599712184</v>
+        <v>-2.632146655316649</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.904768815099185</v>
+        <v>1.874737996075154</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.157506904815302</v>
+        <v>1.03265983807466</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.530976822186987</v>
+        <v>3.547548985360358</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.873550501791453</v>
+        <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.354242998186209</v>
+        <v>-2.658021053790674</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.931496878203221</v>
+        <v>1.901466059179191</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.202418513527043</v>
+        <v>1.077571446786401</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.595001609907678</v>
+        <v>3.611573773081049</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.870225857780998</v>
+        <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.347188307971036</v>
+        <v>-2.650966363575501</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.930994110278835</v>
+        <v>1.900963291254805</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.209473203742217</v>
+        <v>1.084626137001575</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.595909780026328</v>
+        <v>3.612481943199699</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.880232011425739</v>
+        <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.320237083644548</v>
+        <v>-2.624015139249013</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.951780753654172</v>
+        <v>1.921749934630142</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.224353549769936</v>
+        <v>1.099506483029294</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.614844141287701</v>
+        <v>3.631416304461072</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.064335143570699</v>
+        <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.341781311475335</v>
+        <v>-2.6455593670798</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.127266194666817</v>
+        <v>2.097235375642787</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.224353549769936</v>
+        <v>1.099506483029294</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.798947273432661</v>
+        <v>3.815519436606031</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.056451838473692</v>
+        <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.364189429280207</v>
+        <v>-2.667967484884672</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.110419642447861</v>
+        <v>2.080388823423831</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.224353549769936</v>
+        <v>1.099506483029294</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.791063968335654</v>
+        <v>3.807636131509025</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.05850583802333</v>
+        <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.392413664857807</v>
+        <v>-2.696191720462272</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.101183947766459</v>
+        <v>2.071153128742429</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.242330302221244</v>
+        <v>1.117483235480603</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.803904019356076</v>
+        <v>3.820476182529447</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.114759555745177</v>
+        <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.401854590746337</v>
+        <v>-2.705632646350802</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.153661295132894</v>
+        <v>2.123630476108864</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.364757419764636</v>
+        <v>1.239910353023994</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.933614007603959</v>
+        <v>3.95018617077733</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.117650650290478</v>
+        <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.490731221914811</v>
+        <v>-2.794509277519276</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.121001737210805</v>
+        <v>2.090970918186775</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.275880788596162</v>
+        <v>1.15103372185552</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.883179123448175</v>
+        <v>3.899751286621546</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347706</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.115762463184253</v>
+        <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.567061199515717</v>
+        <v>-2.870839255120182</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.088581559064218</v>
+        <v>2.058550740040188</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.275880788596162</v>
+        <v>1.15103372185552</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.881290936341951</v>
+        <v>3.897863099515321</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887751</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.110582692787115</v>
+        <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.660725144193258</v>
+        <v>-2.964503199797723</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.045936210796064</v>
+        <v>2.015905391772034</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.182216843918621</v>
+        <v>1.057369777177979</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.819912799138288</v>
+        <v>3.836484962311658</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.109016702997268</v>
+        <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.822293569720514</v>
+        <v>-3.126071625324979</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.979742850795314</v>
+        <v>1.949712031771284</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.055433920120741</v>
+        <v>0.9305868533800995</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.742277055069712</v>
+        <v>3.758849218243083</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.122090109863186</v>
+        <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.930594231590633</v>
+        <v>-3.234372287195098</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.949495992913185</v>
+        <v>1.919465173889154</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.055433920120741</v>
+        <v>0.9305868533800995</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.755350461935631</v>
+        <v>3.771922625109002</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.114095306646126</v>
+        <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.948398203311377</v>
+        <v>-3.252176258915842</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.934379601007827</v>
+        <v>1.904348781983797</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9848992972155401</v>
+        <v>0.8600522304748983</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.705034884975451</v>
+        <v>3.721607048148821</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.112619347773128</v>
+        <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.97629899042085</v>
+        <v>-3.280077046025315</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.92174332729104</v>
+        <v>1.89171250826701</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9503023730726053</v>
+        <v>0.8254553063319635</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.682800771616692</v>
+        <v>3.699372934790063</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.109383791750327</v>
+        <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.098825093123744</v>
+        <v>-3.402603148728209</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.869497330187081</v>
+        <v>1.839466511163051</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8277762703697115</v>
+        <v>0.7029292036290696</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.606049553972154</v>
+        <v>3.622621717145525</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.176089751340831</v>
+        <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.329339589309333</v>
+        <v>-3.633117644913798</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.843997491303349</v>
+        <v>1.813966672279319</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5972617741841227</v>
+        <v>0.4724147074434809</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.534446815851305</v>
+        <v>3.551018979024675</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.316401470342678</v>
+        <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.678084674533777</v>
+        <v>-3.981862730138241</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.844811176215419</v>
+        <v>1.814780357191389</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4885138202652249</v>
+        <v>0.3636667535245831</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.609509762501813</v>
+        <v>3.626081925675184</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237096</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.385381739488317</v>
+        <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.832071092309917</v>
+        <v>-4.135849147914382</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.852196878250603</v>
+        <v>1.822166059226572</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4885138202652249</v>
+        <v>0.3636667535245831</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.678490031647453</v>
+        <v>3.695062194820824</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423389</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.371432941608438</v>
+        <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.036670527172926</v>
+        <v>-4.34044858277739</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.75640830642552</v>
+        <v>1.72637748740149</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4885138202652249</v>
+        <v>0.3636667535245831</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.664541233767574</v>
+        <v>3.681113396940944</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.383303430663852</v>
+        <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.28914568118065</v>
+        <v>-4.592923736785115</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.667288733877844</v>
+        <v>1.637257914853814</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4885138202652249</v>
+        <v>0.3636667535245831</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.676411722822988</v>
+        <v>3.692983885996358</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.384513965182796</v>
+        <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.582041437660062</v>
+        <v>-4.885819493264527</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.551340965805023</v>
+        <v>1.521310146780993</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4885138202652249</v>
+        <v>0.3636667535245831</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.677622257341931</v>
+        <v>3.694194420515302</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.388635707410117</v>
+        <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.76870556579487</v>
+        <v>-5.072483621399335</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.480797056778421</v>
+        <v>1.450766237754391</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.461774849440665</v>
+        <v>0.3369277827000232</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.665700617074517</v>
+        <v>3.682272780247887</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916203</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.383713560146307</v>
+        <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.914726252708832</v>
+        <v>-5.218504308313297</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.417466634749026</v>
+        <v>1.387435815724996</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4526917576468081</v>
+        <v>0.3278446909061662</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.655328614734392</v>
+        <v>3.671900777907763</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830329</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.545917616845351</v>
+        <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.006440261818417</v>
+        <v>-5.310218317422883</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.542985087804236</v>
+        <v>1.512954268780205</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4526917576468081</v>
+        <v>0.3278446909061662</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.817532671433436</v>
+        <v>3.834104834606807</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071553</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.540764254809165</v>
+        <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.038091920878387</v>
+        <v>-5.341869976482852</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.525171062144063</v>
+        <v>1.495140243120032</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4475233004023679</v>
+        <v>0.322676233661726</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.809278235050586</v>
+        <v>3.825850398223957</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.550993672377656</v>
+        <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.12002673914727</v>
+        <v>-5.423804794751735</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.502626552405</v>
+        <v>1.47259573338097</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4375885548152877</v>
+        <v>0.3127414880746459</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.813546805266829</v>
+        <v>3.8301189684402</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.559919310833559</v>
+        <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.222002861395677</v>
+        <v>-5.525780917000143</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.47076174196154</v>
+        <v>1.440730922937509</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3356124325668801</v>
+        <v>0.2107653658262383</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.761286770373687</v>
+        <v>3.777858933547058</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231811</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.552072198077734</v>
+        <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.111996577918456</v>
+        <v>-5.415774633522921</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.506917142596604</v>
+        <v>1.476886323572573</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3588170044841553</v>
+        <v>0.2339699377435135</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.767362400768227</v>
+        <v>3.783934563941598</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.556322208799708</v>
+        <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.96893700217753</v>
+        <v>-5.272715057781995</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.568390983614949</v>
+        <v>1.538360164590918</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3668304310741346</v>
+        <v>0.2419833643334928</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.776420467444189</v>
+        <v>3.79299263061756</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.563583091682244</v>
+        <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.667490276705692</v>
+        <v>-4.971268332310157</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.69623055668622</v>
+        <v>1.666199737662189</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6682771565459719</v>
+        <v>0.54343008980533</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.964549385609828</v>
+        <v>3.981121548783198</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.564554269434955</v>
+        <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.692080520940876</v>
+        <v>-4.995858576545341</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.687365636744857</v>
+        <v>1.657334817720826</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6682771565459719</v>
+        <v>0.54343008980533</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.965520563362539</v>
+        <v>3.982092726535909</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.565397173814711</v>
+        <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.641042144934356</v>
+        <v>-4.944820200538821</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.70862389152722</v>
+        <v>1.67859307250319</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6682771565459719</v>
+        <v>0.54343008980533</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.966363467742294</v>
+        <v>3.982935630915665</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969545</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.584435272688856</v>
+        <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.599902850067725</v>
+        <v>-4.90368090567219</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.744117708348018</v>
+        <v>1.714086889323987</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7094164514126027</v>
+        <v>0.5845693846719608</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.010085143536418</v>
+        <v>4.026657306709788</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82575293270048</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.400619268812791</v>
+        <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.503267938049085</v>
+        <v>-4.80704599365355</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.598955669279409</v>
+        <v>1.568924850255378</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8060513634312426</v>
+        <v>0.6812042966906008</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.884250086871536</v>
+        <v>3.900822250044907</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077643</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.404121312886755</v>
+        <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.633848672579927</v>
+        <v>-4.937626728184393</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.550225419541036</v>
+        <v>1.520194600517005</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6754706289004001</v>
+        <v>0.5506235621597583</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.809403690226995</v>
+        <v>3.825975853400366</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833461</v>
+        <v>3.775028860833458</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.388548131962837</v>
+        <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.469352338388966</v>
+        <v>-4.773130393993431</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.600450772293503</v>
+        <v>1.570419953269472</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.839966963091362</v>
+        <v>0.7151198963507202</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.892528309817655</v>
+        <v>3.909100472991025</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.387735842399267</v>
+        <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.392253736847093</v>
+        <v>-4.696031792451558</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.630477923346682</v>
+        <v>1.600447104322651</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.839966963091362</v>
+        <v>0.7151198963507202</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.891716020254084</v>
+        <v>3.908288183427455</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.397604621524339</v>
+        <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.402638931736982</v>
+        <v>-4.706416987341448</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.636192624515798</v>
+        <v>1.606161805491768</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8295817682014727</v>
+        <v>0.7047347014608308</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.895353682445223</v>
+        <v>3.911925845618594</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735284</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.468441627300765</v>
+        <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.421227090459207</v>
+        <v>-4.725005146063673</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.699594366803334</v>
+        <v>1.669563547779303</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8109936094792474</v>
+        <v>0.6861465427386055</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.955037792988313</v>
+        <v>3.971609956161684</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.465310638119063</v>
+        <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.421525637155243</v>
+        <v>-4.725303692759709</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.696343958943218</v>
+        <v>1.666313139919187</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8106950627832115</v>
+        <v>0.6858479960425696</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.95172767578899</v>
+        <v>3.968299838962361</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108859</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.469841533058454</v>
+        <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.320702503464815</v>
+        <v>-4.624480559069281</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.74120410735878</v>
+        <v>1.71117328833475</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8231592782675653</v>
+        <v>0.6983122115269235</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.963737100018994</v>
+        <v>3.980309263192365</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121469</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.469970786536998</v>
+        <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.129921142712409</v>
+        <v>-4.433699198316874</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.817645905138286</v>
+        <v>1.787615086114256</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.013940639019973</v>
+        <v>0.8890935722793308</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.078335169948982</v>
+        <v>4.094907333122352</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906082</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.449807632274594</v>
+        <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.022957784862987</v>
+        <v>-4.326735840467452</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.840268094015652</v>
+        <v>1.810237274991621</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.072405246979774</v>
+        <v>0.9475581802391323</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.093250780462459</v>
+        <v>4.10982294363583</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912987</v>
+        <v>3.785761685912983</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.484774568886653</v>
+        <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.967627196961225</v>
+        <v>-4.27140525256569</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.897367265788415</v>
+        <v>1.867336446764384</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.127735834881536</v>
+        <v>1.002888768140894</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.161416069815575</v>
+        <v>4.177988232988946</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539896</v>
+        <v>3.743767956539893</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.47846113678809</v>
+        <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.955573070048262</v>
+        <v>-4.259351125652727</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.895875484455038</v>
+        <v>1.865844665431007</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.139789961794499</v>
+        <v>1.014942895053857</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.16233511386479</v>
+        <v>4.178907277038161</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.480341766972226</v>
+        <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.996728189616483</v>
+        <v>-4.300506245220948</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.881294066811885</v>
+        <v>1.851263247787855</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.098634842226278</v>
+        <v>0.9737877754856363</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.139522672307994</v>
+        <v>4.156094835481364</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382922</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.493192792850109</v>
+        <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.928679626924953</v>
+        <v>-4.232457682529418</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.92136451776638</v>
+        <v>1.891333698742349</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.166683404917808</v>
+        <v>1.041836338177166</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.193202835800794</v>
+        <v>4.209774998974165</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.64525678001343</v>
+        <v>3.645256780013426</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.513395463023703</v>
+        <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.160280020094454</v>
+        <v>-4.464058075698919</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.848927030672173</v>
+        <v>1.818896211648143</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.166683404917808</v>
+        <v>1.041836338177166</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.213405505974388</v>
+        <v>4.229977669147759</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.497001699090585</v>
+        <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.210331565623674</v>
+        <v>-4.514109621228138</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.812512648527367</v>
+        <v>1.782481829503337</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.166683404917808</v>
+        <v>1.041836338177166</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.19701174204127</v>
+        <v>4.213583905214641</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.457253612684052</v>
+        <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.385438398200119</v>
+        <v>-4.689216453804582</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.702721829090256</v>
+        <v>1.672691010066226</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.166683404917808</v>
+        <v>1.041836338177166</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.157263655634737</v>
+        <v>4.173835818808108</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.464276231680992</v>
+        <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.189338244769596</v>
+        <v>-4.49311630037406</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.788184509459405</v>
+        <v>1.758153690435375</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.362783558348331</v>
+        <v>1.237936491607689</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.281946366689991</v>
+        <v>4.298518529863362</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.730570473395084</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.563447231253896</v>
+        <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.036312852656311</v>
+        <v>-4.340090908260775</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.948565665877624</v>
+        <v>1.918534846853594</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.515808950461615</v>
+        <v>1.390961883720973</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.472932601530865</v>
+        <v>4.489504764704236</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74127833279115</v>
+        <v>3.741278332791146</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.750913456162189</v>
+        <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.064620166529582</v>
+        <v>-4.368398222134045</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.124708965236608</v>
+        <v>2.094678146212578</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.515808950461615</v>
+        <v>1.390961883720973</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.660398826439158</v>
+        <v>4.676970989612529</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.720316407516271</v>
+        <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.231213391643104</v>
+        <v>-4.534991447247568</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.027474626545282</v>
+        <v>1.997443807521252</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.349215725348093</v>
+        <v>1.224368658607451</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.529845842725127</v>
+        <v>4.546418005898498</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285648</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.723992810177989</v>
+        <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.208177598281538</v>
+        <v>-4.511955653886002</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.040365346551626</v>
+        <v>2.010334527527596</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.349215725348093</v>
+        <v>1.224368658607451</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.533522245386845</v>
+        <v>4.550094408560216</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.74058140139947</v>
+        <v>3.740581401399466</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.721610865301484</v>
+        <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.178931617825842</v>
+        <v>-4.482709673430305</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.0496817938574</v>
+        <v>2.01965097483337</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.349215725348093</v>
+        <v>1.224368658607451</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.53114030051034</v>
+        <v>4.547712463683711</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256374</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.718904104459119</v>
+        <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.285857165703693</v>
+        <v>-4.589635221308156</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.004204813863894</v>
+        <v>1.974173994839864</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.242290177470241</v>
+        <v>1.117443110729599</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.464278210941265</v>
+        <v>4.480850374114635</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701004</v>
+        <v>3.689942600701001</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.720332906602354</v>
+        <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.430875724210941</v>
+        <v>-4.734653779815405</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.947626192604229</v>
+        <v>1.917595373580199</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.097271618962993</v>
+        <v>0.9724245522223509</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.378695877980149</v>
+        <v>4.39526804115352</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687015</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.820264145860107</v>
+        <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.549217489995659</v>
+        <v>-4.852995545600122</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.000220725548095</v>
+        <v>1.970189906524065</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.107957657525883</v>
+        <v>0.983110590785241</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.485038740375637</v>
+        <v>4.501610903549008</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790806</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.818049842986046</v>
+        <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.600627912316367</v>
+        <v>-4.90440596792083</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.977442253745751</v>
+        <v>1.947411434721721</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.107957657525883</v>
+        <v>0.983110590785241</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.482824437501575</v>
+        <v>4.499396600674946</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437334</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.817952971060335</v>
+        <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.680047363524118</v>
+        <v>-4.983825419128582</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.945577601336939</v>
+        <v>1.91554678231291</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.107957657525883</v>
+        <v>0.983110590785241</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.482727565575865</v>
+        <v>4.499299728749236</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298401</v>
+        <v>3.736804952298398</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.817946864618378</v>
+        <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.775510361441336</v>
+        <v>-5.0792884170458</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.907386295728095</v>
+        <v>1.877355476704066</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.107957657525883</v>
+        <v>0.983110590785241</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.482721459133908</v>
+        <v>4.499293622307278</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218004</v>
+        <v>3.715372960218001</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.816043261180988</v>
+        <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.711134450590621</v>
+        <v>-5.014912506195085</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.931233056630992</v>
+        <v>1.901202237606962</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.172333568376598</v>
+        <v>1.047486501635956</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.519443402206948</v>
+        <v>4.536015565380318</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73608941335354</v>
+        <v>3.736089413353536</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.821777078928715</v>
+        <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.766503612722815</v>
+        <v>-5.070281668327278</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.914819209525841</v>
+        <v>1.884788390501811</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.172333568376598</v>
+        <v>1.047486501635956</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.525177219954674</v>
+        <v>4.541749383128045</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113283</v>
+        <v>3.736822870113279</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.821315442271648</v>
+        <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.811941392553642</v>
+        <v>-5.115719448158106</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.896182460936443</v>
+        <v>1.866151641912413</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.129488577698438</v>
+        <v>1.004641510957796</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.499008588890711</v>
+        <v>4.515580752064081</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113692</v>
+        <v>3.790272500113688</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.841189835121966</v>
+        <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.723734558406064</v>
+        <v>-5.027512614010528</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.951339587445792</v>
+        <v>1.921308768421763</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.129488577698438</v>
+        <v>1.004641510957796</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.518882981741029</v>
+        <v>4.5354551449144</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.79448684401644</v>
+        <v>3.794486844016436</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.824890535646694</v>
+        <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.617699563200754</v>
+        <v>-4.921477618805218</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.977454286052645</v>
+        <v>1.947423467028615</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.129488577698438</v>
+        <v>1.004641510957796</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.502583682265757</v>
+        <v>4.519155845439128</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307671</v>
+        <v>3.794705093307668</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.82732148511074</v>
+        <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.434487900067659</v>
+        <v>-4.738265955672123</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.053169900769928</v>
+        <v>2.023139081745898</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.129488577698438</v>
+        <v>1.004641510957796</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.505014631729804</v>
+        <v>4.521586794903174</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.79311267095863</v>
+        <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.362766453053808</v>
+        <v>-4.666544508658272</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.047649665423358</v>
+        <v>2.017618846399328</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.201210024712289</v>
+        <v>1.076362957971647</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.513838685786004</v>
+        <v>4.530410848959374</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394115</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.740028416879801</v>
+        <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.340393427446102</v>
+        <v>-4.644171483050566</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.003514621587613</v>
+        <v>1.973483802563582</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.212465775825191</v>
+        <v>1.087618709084548</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.467507882374916</v>
+        <v>4.484080045548287</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456732</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
-        <v>3.925226621765157</v>
+        <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.373409723356847</v>
+        <v>-4.677187778961311</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.175506308108671</v>
+        <v>2.14547548908464</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.143028399158439</v>
+        <v>1.018181332417797</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.61104366126022</v>
+        <v>4.62761582443359</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71376253688368</v>
+        <v>3.713762536883676</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.917147847593407</v>
+        <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.361882087707238</v>
+        <v>-4.665660143311702</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.172038588196763</v>
+        <v>2.142007769172732</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.202029057359802</v>
+        <v>1.077181990619159</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.638365282009287</v>
+        <v>4.654937445182657</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236301</v>
+        <v>3.717150699236297</v>
       </c>
       <c r="C2072" t="n">
-        <v>3.920815960115195</v>
+        <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.459223589049607</v>
+        <v>-4.763001644654071</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.136770100181604</v>
+        <v>2.106739281157573</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.157608875194313</v>
+        <v>1.032761808453671</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.615381285231782</v>
+        <v>4.631953448405152</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427687</v>
+        <v>3.705201079427684</v>
       </c>
       <c r="C2073" t="n">
-        <v>3.922067042308033</v>
+        <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.545079618389574</v>
+        <v>-4.848857673994037</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.103678770638456</v>
+        <v>2.073647951614425</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.115232805968178</v>
+        <v>0.9903857392275359</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.59120672588894</v>
+        <v>4.60777888906231</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610378</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.904486244128535</v>
+        <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.553916415805693</v>
+        <v>-4.857694471410157</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.082563253492509</v>
+        <v>2.052532434468478</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.107790633326827</v>
+        <v>0.9829435665861852</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.569160624124631</v>
+        <v>4.585732787298001</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667458</v>
+        <v>3.715544411667454</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.914650755173584</v>
+        <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.645298978371152</v>
+        <v>-4.949077033975615</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.056174739511375</v>
+        <v>2.026143920487344</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.071225748607483</v>
+        <v>0.9463786818668405</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.557386204338074</v>
+        <v>4.573958367511444</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889194</v>
+        <v>3.67397837488919</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.016779012997851</v>
+        <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.633592260384146</v>
+        <v>-4.937370315988609</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.162985684530445</v>
+        <v>2.132954865506414</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.082932466594489</v>
+        <v>0.9580853998538469</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.666538492954545</v>
+        <v>4.683110656127915</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409569</v>
+        <v>3.682476099409565</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.019811351729256</v>
+        <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.533928756300483</v>
+        <v>-4.837706811904947</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.205883424895315</v>
+        <v>2.175852605871284</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.146119549798176</v>
+        <v>1.021272483057533</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.707483081608162</v>
+        <v>4.724055244781532</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452572</v>
+        <v>3.672895177452568</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.232716185007314</v>
+        <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.544244854466835</v>
+        <v>-4.848022910071299</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.414661818906832</v>
+        <v>2.384630999882801</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.146119549798176</v>
+        <v>1.021272483057533</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.92038791488622</v>
+        <v>4.93696007805959</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.62396095976229</v>
+        <v>3.623960959762287</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.231894851919404</v>
+        <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.544150886449462</v>
+        <v>-4.847928942053926</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.413878073025871</v>
+        <v>2.38384725400184</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.146489411145494</v>
+        <v>1.021642344404851</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.9197884986067</v>
+        <v>4.936360661780069</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988021</v>
+        <v>3.633213467988018</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.226126837863758</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.551369710649307</v>
+        <v>-4.85514776625377</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.405222529290287</v>
+        <v>2.375191710266257</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.146489411145494</v>
+        <v>1.021642344404851</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.914020484551054</v>
+        <v>4.930592647724424</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740918</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.226126837863758</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.550421287531268</v>
+        <v>-4.854199343135732</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.405601898537503</v>
+        <v>2.375571079513472</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.146489411145494</v>
+        <v>1.021642344404851</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.914020484551054</v>
+        <v>4.930592647724424</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.23885444584485</v>
+        <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.707489745786892</v>
+        <v>-5.011267801391356</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.355502123216345</v>
+        <v>2.325471304192314</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.146489411145494</v>
+        <v>1.021642344404851</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.926748092532146</v>
+        <v>4.943320255705515</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.240800444269238</v>
+        <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.701497498998081</v>
+        <v>-5.005275554602544</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.359845020356257</v>
+        <v>2.329814201332226</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.146489411145494</v>
+        <v>1.021642344404851</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.928694090956534</v>
+        <v>4.945266254129903</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.234454580287006</v>
+        <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.612939537867313</v>
+        <v>-4.916717593471777</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.388922340826333</v>
+        <v>2.358891521802303</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.146489411145494</v>
+        <v>1.021642344404851</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.922348226974303</v>
+        <v>4.938920390147672</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383087</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.233763257726002</v>
+        <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.595180460364239</v>
+        <v>-4.898958515968703</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.395334649266558</v>
+        <v>2.365303830242528</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.146489411145494</v>
+        <v>1.021642344404851</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.921656904413299</v>
+        <v>4.938229067586668</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.246545443634589</v>
+        <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.495550309315171</v>
+        <v>-4.799328364919635</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.447968895594772</v>
+        <v>2.417938076570741</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.246119562194561</v>
+        <v>1.121272495453919</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.994217180951326</v>
+        <v>5.010789344124695</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455267</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.435699709133315</v>
+        <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.544949818004183</v>
+        <v>-4.848727873608646</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.617363357617895</v>
+        <v>2.587332538593864</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.256378395626306</v>
+        <v>1.131531328885663</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.189526746509099</v>
+        <v>5.206098909682469</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963137</v>
+        <v>3.749078058963134</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.422888382236177</v>
+        <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.381599147476366</v>
+        <v>-4.64204339996627</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.669892298931883</v>
+        <v>2.657195001153676</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.419729066154123</v>
+        <v>1.338215802528039</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.274725821928651</v>
+        <v>5.317298266970756</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.717715068313017</v>
+        <v>3.484867965559948</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.414211027307431</v>
+        <v>4.398974738119499</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.381599147476366</v>
+        <v>-4.64204339996627</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.669892298931883</v>
+        <v>2.657195001153676</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.419729066154123</v>
+        <v>1.338215802528039</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.407274824293799</v>
+        <v>4.392038535105867</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240916.xlsx
+++ b/tame_output/ON/bt/strategyON_20240916.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>155.1%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>106.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>121.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-46.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-70.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>418.4%</t>
+          <t>422.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-625.8%</t>
+          <t>-581.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-110.5%</t>
+          <t>-92.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-55.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-323.4%</t>
+          <t>-314.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-90.2%</t>
+          <t>-76.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,31 +1423,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,57 +1456,57 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.536080696634842</v>
+        <v>-6.400434910604325</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5040899907250038</v>
+        <v>0.5583483051372111</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.8103298254957174</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.879339216277861</v>
+        <v>-6.619188822504445</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3628861480134917</v>
+        <v>0.4669463055228582</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.8103298254957174</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.927542033520205</v>
+        <v>-6.667391639746789</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3420099411715549</v>
+        <v>0.4460700986809214</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.8103298254957174</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.094350693494567</v>
+        <v>-6.834200299721151</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2790654531110186</v>
+        <v>0.3831256106203846</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.852613149208854</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.28107040180387</v>
+        <v>-7.020920008030454</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2003512652528943</v>
+        <v>0.3044114227622607</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.852613149208854</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.664071790546501</v>
+        <v>-7.403921396773085</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.04704860843425784</v>
+        <v>0.1511087659436239</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.852613149208854</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.66855823574789</v>
+        <v>-7.408407841974474</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.04782554632513225</v>
+        <v>0.1518857038344987</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8570995944102426</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.028088558251891</v>
+        <v>-7.767938164478475</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.09063627937841856</v>
+        <v>0.01342387813094836</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8570995944102426</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.078437621706113</v>
+        <v>-7.818287227932697</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1028598848029296</v>
+        <v>0.001200272706436856</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.9074486578644647</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.176056899127509</v>
+        <v>-7.915906505354094</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1388658451497196</v>
+        <v>-0.03480568764035308</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.005067935285861</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.230128398635868</v>
+        <v>-7.969978004862454</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1576008886314906</v>
+        <v>-0.05354073112212454</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.059139434794221</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.233704184727616</v>
+        <v>-7.973553790954202</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1535180059495476</v>
+        <v>-0.04945784844018153</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.084668356710713</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.267357023236089</v>
+        <v>-8.007206629462676</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1624965868685009</v>
+        <v>-0.05843642935913484</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.185081724627751</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.406443137854946</v>
+        <v>-8.146292744081531</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2027593312226226</v>
+        <v>-0.09869917371325654</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.324167839246607</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.58156755524149</v>
+        <v>-8.321417161468075</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2582538774297229</v>
+        <v>-0.1541937199203569</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.499292256633151</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.816019649255979</v>
+        <v>-8.555869255482564</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.359253879937115</v>
+        <v>-0.255193722427749</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.499292256633151</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.920394380282426</v>
+        <v>-8.660243986509011</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4076759631216698</v>
+        <v>-0.3036158056123037</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.603666987659597</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.08290784598101</v>
+        <v>-8.822757452207595</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.471565559562547</v>
+        <v>-0.3675054020531809</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.701300418078284</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.2089446393493</v>
+        <v>-8.948794245575884</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5192865482807481</v>
+        <v>-0.415226390771382</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.676048795268541</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.151872867453369</v>
+        <v>-8.891722473679954</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4924675038359752</v>
+        <v>-0.3884073463266091</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.676048795268541</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.293544709177489</v>
+        <v>-9.033394315404074</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.550611467424365</v>
+        <v>-0.4465513099149989</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.676048795268541</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.243953864752655</v>
+        <v>-8.98380347097924</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5157217194895587</v>
+        <v>-0.4116615619801927</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.626457950843708</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.095035530280798</v>
+        <v>-8.834885136507383</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4692055193474993</v>
+        <v>-0.3651453618381333</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.595208360108535</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.869190377561386</v>
+        <v>-8.609039983787971</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3692883852235256</v>
+        <v>-0.2652282277141595</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.553281684521371</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.744611721223794</v>
+        <v>-8.484461327450379</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.31831777813243</v>
+        <v>-0.214257620623064</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.553281684521371</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.719575039655284</v>
+        <v>-8.459424645881869</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3056693313429184</v>
+        <v>-0.2016091738335524</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.527952596970635</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.647441864367403</v>
+        <v>-8.387291470593988</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2710823569891296</v>
+        <v>-0.1670221994797636</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.527952596970635</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.576075471757756</v>
+        <v>-8.315925077984341</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2522730623391358</v>
+        <v>-0.1482129048297698</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.456586204360987</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.482616437772531</v>
+        <v>-8.222466043999116</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2247729300579535</v>
+        <v>-0.1207127725485875</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.456586204360987</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.4719632562191</v>
+        <v>-8.211812862445685</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2223462179359545</v>
+        <v>-0.1182860604265885</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.456586204360987</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.374056217542609</v>
+        <v>-8.113905823769194</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1834837174388193</v>
+        <v>-0.07942355992945327</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.388600454500431</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.350102676566651</v>
+        <v>-8.089952282793236</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1732337949029423</v>
+        <v>-0.06917363739357629</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.364646913524473</v>
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.086042738243854</v>
+        <v>-7.98074323494275</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.08087013573557567</v>
+        <v>-0.03875033441513409</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.100586975201677</v>
+        <v>-1.255437865673987</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.493551198754708</v>
+        <v>2.400640664471322</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.378963114739016</v>
+        <v>-7.273663611437912</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1991746800060588</v>
+        <v>0.2412944813265003</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.100586975201677</v>
+        <v>-1.255437865673987</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.490764165094407</v>
+        <v>2.397853630811021</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.338778816372826</v>
+        <v>-7.233479313071721</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2155920232403763</v>
+        <v>0.2577118245608179</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.060402676835486</v>
+        <v>-1.215253567307796</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.515218368001963</v>
+        <v>2.422307833718577</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.175378945433463</v>
+        <v>-7.070079442132359</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2803187928368782</v>
+        <v>0.3224385941573198</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8970028058961237</v>
+        <v>-1.051853696368434</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.612625111786337</v>
+        <v>2.519714577502952</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.941897723203865</v>
+        <v>-6.83659821990276</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3816357105665698</v>
+        <v>0.4237555118870118</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6635215836665251</v>
+        <v>-0.818372474138835</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.760638273961949</v>
+        <v>2.667727739678563</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.79223133219635</v>
+        <v>-6.686931828895245</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4386100566566169</v>
+        <v>0.4807298579770585</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5706180924239892</v>
+        <v>-0.725468982896299</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.813488158394511</v>
+        <v>2.720577624111125</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.659955858565463</v>
+        <v>-6.554656355264359</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.392781032116126</v>
+        <v>0.4349008334365676</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4383426187931025</v>
+        <v>-0.5931935092654124</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.794114228580198</v>
+        <v>2.701203694296812</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.488094643000561</v>
+        <v>-6.382795139699456</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4643405790297237</v>
+        <v>0.5064603803501653</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.2664814032281997</v>
+        <v>-0.4213322937005095</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.900046018606776</v>
+        <v>2.80713548432339</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.403129976271241</v>
+        <v>-6.297830472970137</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5112327869451101</v>
+        <v>0.5533525882655517</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1815167364988801</v>
+        <v>-0.3363676269711899</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.963931159868027</v>
+        <v>2.871020625584641</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.508719966044346</v>
+        <v>-6.403420462743242</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3410208614366494</v>
+        <v>0.3831406627570915</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2871067262719845</v>
+        <v>-0.4419576167442943</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.772601236404946</v>
+        <v>2.67969070212156</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.440485381418918</v>
+        <v>-6.335185878117814</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4168590371639072</v>
+        <v>0.4589788384843487</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2686914033994485</v>
+        <v>-0.4235422938717583</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.832194772005554</v>
+        <v>2.739284237722168</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.292545340011319</v>
+        <v>-6.187245836710215</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3594142450885398</v>
+        <v>0.4015340464089814</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2483704874908909</v>
+        <v>-0.4032213779632007</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.727766512912281</v>
+        <v>2.634855978628895</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.239575817757331</v>
+        <v>-6.134276314456226</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3718880677366569</v>
+        <v>0.4140078690570985</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.3502518557092119</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.750834240011196</v>
+        <v>2.65792370572781</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.07378762179704</v>
+        <v>-5.968488118495936</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4312427340256799</v>
+        <v>0.4733625353461219</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.3502518557092119</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.743873627916103</v>
+        <v>2.650963093632717</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.040424415318271</v>
+        <v>-5.935124912017167</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4590503709983307</v>
+        <v>0.5011701723187723</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.3502518557092119</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.758335982297246</v>
+        <v>2.66542544801386</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.932165278195749</v>
+        <v>-5.826865774894645</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4968861463065344</v>
+        <v>0.539005947626976</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.3502518557092119</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.752868102756441</v>
+        <v>2.659957568473055</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.808874143378619</v>
+        <v>-5.703574640077514</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5437006942439635</v>
+        <v>0.5858204955644055</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.07210983041977154</v>
+        <v>-0.2269607208920814</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.824340877657296</v>
+        <v>2.731430343373911</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.756177276247327</v>
+        <v>-5.650877772946223</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5724804193338051</v>
+        <v>0.6146002206542471</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.01941296328848036</v>
+        <v>-0.1742638537607902</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.863659976173396</v>
+        <v>2.77074944189001</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.512411834263883</v>
+        <v>-5.407112330962779</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6657673044742336</v>
+        <v>0.7078871057946756</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.01941296328848036</v>
+        <v>-0.1742638537607902</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.859440684520447</v>
+        <v>2.766530150237061</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.422636161887411</v>
+        <v>-5.317336658586306</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7038018873448384</v>
+        <v>0.7459216886652804</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.04218648162582966</v>
+        <v>-0.1126644088464802</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.898524665389049</v>
+        <v>2.805614131105663</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.172785767938336</v>
+        <v>-5.067486264637232</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7964841199081705</v>
+        <v>0.8386039212286125</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.04218648162582966</v>
+        <v>-0.1126644088464802</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.891266740372751</v>
+        <v>2.798356206089365</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.996893675470904</v>
+        <v>-4.8915941721698</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8704400804157921</v>
+        <v>0.9125598817362339</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.04218648162582966</v>
+        <v>-0.1126644088464802</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.8948658638934</v>
+        <v>2.801955329610014</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.825447212448441</v>
+        <v>-4.720147709147336</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9523461716793311</v>
+        <v>0.9944659729997729</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2136329446482928</v>
+        <v>0.05878205417598298</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.011061247761432</v>
+        <v>2.918150713478045</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.74542492533932</v>
+        <v>-4.640125422038215</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9833755641392765</v>
+        <v>1.025495365459718</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2936552317574138</v>
+        <v>0.1388043412851039</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.058095097643201</v>
+        <v>2.965184563359815</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.681789183105385</v>
+        <v>-4.576489679804281</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.013524662087168</v>
+        <v>1.055644463407609</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3572909739913483</v>
+        <v>0.2024400835190385</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.100971344037879</v>
+        <v>3.008060809754493</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.58809186488899</v>
+        <v>-4.482792361587886</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.032197848157521</v>
+        <v>1.074317649477963</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3572909739913483</v>
+        <v>0.2024400835190385</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.082165602821675</v>
+        <v>2.989255068538289</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.598594487954279</v>
+        <v>-4.493294984653175</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.029739875556283</v>
+        <v>1.071859676876725</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3467883509260594</v>
+        <v>0.1919374604537496</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.077607105607379</v>
+        <v>2.984696571323993</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.52321824479905</v>
+        <v>-4.3808087239843</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.063819686653195</v>
+        <v>1.120783494979095</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3467883509260594</v>
+        <v>0.1919374604537496</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.081536419442199</v>
+        <v>2.988625885158813</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.505504557921185</v>
+        <v>-4.363095037106435</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.071583745321681</v>
+        <v>1.128547553647581</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3499696798229762</v>
+        <v>0.1951187893506664</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.084123800697689</v>
+        <v>2.991213266414303</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.382030286608167</v>
+        <v>-4.239620765793417</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.117971525066882</v>
+        <v>1.174935333392782</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3499696798229762</v>
+        <v>0.1951187893506664</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.081121871917682</v>
+        <v>2.988211337634297</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.162009488571156</v>
+        <v>-4.019599967756406</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.2075588812923</v>
+        <v>1.2645226896182</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4911895248909565</v>
+        <v>0.3363386344186466</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.167432815969085</v>
+        <v>3.074522281685699</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.029141799507879</v>
+        <v>-3.886732278693128</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.276600139719434</v>
+        <v>1.333563948045335</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4911895248909565</v>
+        <v>0.3363386344186466</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.183326998770908</v>
+        <v>3.090416464487522</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.90896871614338</v>
+        <v>-3.766559195328629</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.325815217505536</v>
+        <v>1.382779025831436</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6113626082554554</v>
+        <v>0.4565117177831456</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.256576693229909</v>
+        <v>3.163666158946523</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.773715354813403</v>
+        <v>-3.631305833998652</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.390004664598967</v>
+        <v>1.446968472924867</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7466159695854325</v>
+        <v>0.5917650791131227</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.347816812589335</v>
+        <v>3.254906278305949</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.833590182171095</v>
+        <v>-3.691180661356344</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.352092225057315</v>
+        <v>1.409056033383216</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6867411422277404</v>
+        <v>0.5318902517554306</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.297929407576146</v>
+        <v>3.20501887329276</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.713769951260258</v>
+        <v>-3.571360430445507</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.415309486655859</v>
+        <v>1.472273294981759</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6867411422277404</v>
+        <v>0.5318902517554306</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.313218576810355</v>
+        <v>3.220308042526969</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.716239657722064</v>
+        <v>-3.573830136907313</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.321965803393578</v>
+        <v>1.378929611719478</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6842714357659343</v>
+        <v>0.5294205452936245</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.219380952255712</v>
+        <v>3.126470417972326</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.784609844046074</v>
+        <v>-3.642200323231322</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.213879590349276</v>
+        <v>1.270843398675176</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.5386962443298394</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.144208233162743</v>
+        <v>3.051297698879357</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.896482123672224</v>
+        <v>-3.754072602857473</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.159567387130707</v>
+        <v>1.216531195456607</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.5386962443298394</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.134644941794634</v>
+        <v>3.041734407511248</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.880507458185956</v>
+        <v>-3.738097937371205</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.132531778249241</v>
+        <v>1.189495586575142</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.5386962443298394</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.101219466718661</v>
+        <v>3.008308932435276</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.705033198393487</v>
+        <v>-3.562623677578736</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.207288714158016</v>
+        <v>1.264252522483917</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.5386962443298394</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.105786698710449</v>
+        <v>3.012876164427063</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.697108823808573</v>
+        <v>-3.554699302993822</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.186200492753189</v>
+        <v>1.24316430107909</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.5386962443298394</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.081528727471656</v>
+        <v>2.98861819318827</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.690830621238724</v>
+        <v>-3.548421100423973</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.117250087182579</v>
+        <v>1.174213895508479</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6998253373719983</v>
+        <v>0.5449744468996884</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.013833962415015</v>
+        <v>2.920923428131629</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.630978002035001</v>
+        <v>-3.48856848122025</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.1513635212962</v>
+        <v>1.208327329622101</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6998253373719983</v>
+        <v>0.5449744468996884</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.024006348847148</v>
+        <v>2.931095814563762</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.544734539008624</v>
+        <v>-3.402325018193872</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.180807177080611</v>
+        <v>1.237770985406512</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6998253373719983</v>
+        <v>0.5449744468996884</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.018952619421008</v>
+        <v>2.926042085137622</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.590041358407603</v>
+        <v>-3.447631837592852</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.154460224765545</v>
+        <v>1.211424033091446</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6590151743627675</v>
+        <v>0.5041642838904576</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.986242297059995</v>
+        <v>2.893331762776609</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.619074463109905</v>
+        <v>-3.476664942295154</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.143398855917726</v>
+        <v>1.200362664243626</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6590151743627675</v>
+        <v>0.5041642838904576</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.986794170093097</v>
+        <v>2.893883635809711</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.526263981659046</v>
+        <v>-3.383854460844295</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.109795740389435</v>
+        <v>1.166759548715336</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7518256558136268</v>
+        <v>0.596974765341317</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.971753150854978</v>
+        <v>2.878842616571592</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.570653450988473</v>
+        <v>-3.428243930173722</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.093913428582265</v>
+        <v>1.150877236908166</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7074361864841991</v>
+        <v>0.5525852960118893</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.946992945181922</v>
+        <v>2.854082410898537</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.550149757102976</v>
+        <v>-3.407740236288225</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.097190614648187</v>
+        <v>1.154154422974087</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7279398803696965</v>
+        <v>0.5730889898973867</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.954370870024944</v>
+        <v>2.861460335741558</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.590073851685548</v>
+        <v>-3.447664330870797</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.086712272645825</v>
+        <v>1.143676080971726</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7279398803696965</v>
+        <v>0.5730889898973867</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.959862165855611</v>
+        <v>2.866951631572225</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.617854249586901</v>
+        <v>-3.47544472877215</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.087097315253823</v>
+        <v>1.144061123579724</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7001594824683435</v>
+        <v>0.5453085919960337</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.954691128883338</v>
+        <v>2.861780594599952</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.73623492231704</v>
+        <v>-3.593825401502289</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8781007661624212</v>
+        <v>0.9350645744883217</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6329416303173673</v>
+        <v>0.4780907398450575</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.752716137593405</v>
+        <v>2.65980560331002</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.844849000760371</v>
+        <v>-3.70243947994562</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9548047955042944</v>
+        <v>1.011768603830195</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6329416303173673</v>
+        <v>0.4780907398450575</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.872865798312611</v>
+        <v>2.779955264029225</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.809439962512228</v>
+        <v>-3.667030441697477</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9834814369058744</v>
+        <v>1.040445245231775</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6329416303173673</v>
+        <v>0.4780907398450575</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.887378824414934</v>
+        <v>2.794468290131548</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.817901131167689</v>
+        <v>-3.675491610352938</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9775164107860588</v>
+        <v>1.034480219111959</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6244804616619062</v>
+        <v>0.4696295711895964</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.879721564564026</v>
+        <v>2.78681103028064</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.640784801132523</v>
+        <v>-3.498375280317772</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.045091971645427</v>
+        <v>1.102055779971328</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6244804616619062</v>
+        <v>0.4696295711895964</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.876450593409329</v>
+        <v>2.783540059125943</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.685877045966069</v>
+        <v>-3.543467525151318</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.027738465473922</v>
+        <v>1.084702273799823</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5625844184925164</v>
+        <v>0.4077335280202066</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.839996359269608</v>
+        <v>2.747085824986222</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011232</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.694775524425815</v>
+        <v>-3.36409210391255</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.017966049396438</v>
+        <v>1.150239417601744</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5945141099225935</v>
+        <v>0.5645102861909252</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.852941149434069</v>
+        <v>2.834938855195068</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.739789737946421</v>
+        <v>-3.409106317433156</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9807678193197855</v>
+        <v>1.113041187525091</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5641652146079889</v>
+        <v>0.5341613908763206</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.815539267576896</v>
+        <v>2.797536973337895</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.006794248218856</v>
+        <v>-3.676110827705592</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.879657577549757</v>
+        <v>1.011930945755063</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3698021765650403</v>
+        <v>0.3397983528333721</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.704613007090072</v>
+        <v>2.686610712851071</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.10799202965603</v>
+        <v>-3.777308609142764</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8383823868713891</v>
+        <v>0.9706557550766954</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3013933630197211</v>
+        <v>0.2713895392880529</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.662771640859382</v>
+        <v>2.644769346620381</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.101481063041717</v>
+        <v>-3.770797642528452</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8385867350714309</v>
+        <v>0.9708601032767372</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3013933630197211</v>
+        <v>0.2713895392880529</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.660371602413699</v>
+        <v>2.642369308174698</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.08244293533442</v>
+        <v>-3.751759514821154</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8427267053625949</v>
+        <v>0.975000073567901</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2432097516885265</v>
+        <v>0.2132059279568583</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.621986154823227</v>
+        <v>2.603983860584226</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.13495873760924</v>
+        <v>-3.804275317095974</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.941014786086857</v>
+        <v>1.073288154292163</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2432097516885265</v>
+        <v>0.2132059279568583</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.741280556457417</v>
+        <v>2.723278262218416</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.13836704904382</v>
+        <v>-3.807683628530554</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9404847904991587</v>
+        <v>1.072758158704465</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2757263206979039</v>
+        <v>0.2457224969662357</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.761623826849177</v>
+        <v>2.743621532610176</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.119010913149973</v>
+        <v>-3.788327492636707</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9542357752536235</v>
+        <v>1.08650914345893</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2757263206979039</v>
+        <v>0.2457224969662357</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.767632357246103</v>
+        <v>2.749630063007102</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.971267942914971</v>
+        <v>-3.640584522401705</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9112831846248239</v>
+        <v>1.04355655283013</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4435336779327871</v>
+        <v>0.4135298542011189</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.766266992864232</v>
+        <v>2.748264698625232</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.055089164189669</v>
+        <v>-3.724405743676403</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8805483176464257</v>
+        <v>1.012821685851732</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4435336779327871</v>
+        <v>0.4135298542011189</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.769060614395713</v>
+        <v>2.751058320156713</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.048936458136884</v>
+        <v>-3.718253037623619</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8836717484591978</v>
+        <v>1.015945116664504</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4496863839855714</v>
+        <v>0.4196825602539032</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.773414586419042</v>
+        <v>2.755412292180042</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.065745756287386</v>
+        <v>-3.73506233577412</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8760285059391073</v>
+        <v>1.008301874144414</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4328770858350697</v>
+        <v>0.4028732621034015</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.762409484268852</v>
+        <v>2.744407190029851</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.003447757511264</v>
+        <v>-3.672764336997998</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9672832592463769</v>
+        <v>1.099556627451683</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4781713501095118</v>
+        <v>0.4481675263778436</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.855921596630338</v>
+        <v>2.837919302391337</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.801657559846106</v>
+        <v>-3.47097413933284</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.850291340026567</v>
+        <v>0.9825647082318736</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6761895422786661</v>
+        <v>0.6461857185469979</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.777024513645958</v>
+        <v>2.759022219406956</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.852544272532301</v>
+        <v>-3.521860852019035</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9002268872742645</v>
+        <v>1.032500255479571</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6253028295924716</v>
+        <v>0.5952990058608034</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.816782718356416</v>
+        <v>2.798780424117415</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.765933529882493</v>
+        <v>-3.435250109369228</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9494989204502309</v>
+        <v>1.081772288655537</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7039285607976299</v>
+        <v>0.6739247370659617</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.878585893195555</v>
+        <v>2.860583598956554</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.826142827887778</v>
+        <v>-3.495459407374512</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9239511820727888</v>
+        <v>1.056224550278095</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6437192627923454</v>
+        <v>0.6137154390606772</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.840996295217056</v>
+        <v>2.822994000978055</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.776956179203427</v>
+        <v>-3.446272758690161</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9421174595864579</v>
+        <v>1.074390827791764</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6437192627923454</v>
+        <v>0.6137154390606772</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.839487913256984</v>
+        <v>2.821485619017983</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.732583047564858</v>
+        <v>-3.401899627051592</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9597295796773215</v>
+        <v>1.092002947882628</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.688092394430914</v>
+        <v>0.6580885706992458</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.865974659675562</v>
+        <v>2.847972365436561</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.755063398423743</v>
+        <v>-3.424379977910477</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9451312334723583</v>
+        <v>1.077404601677665</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.688092394430914</v>
+        <v>0.6580885706992458</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.860368453814152</v>
+        <v>2.842366159575151</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.707407667862687</v>
+        <v>-3.376724247349421</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.970575282724585</v>
+        <v>1.102848650929892</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7357481249919696</v>
+        <v>0.7057443012603014</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.89534364917859</v>
+        <v>2.877341354939589</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569612</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.606889509363933</v>
+        <v>-3.276206088850667</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.015674919498812</v>
+        <v>1.147948287704118</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8362662834907242</v>
+        <v>0.806262459759056</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.960546917652568</v>
+        <v>2.942544623413567</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.59098417993158</v>
+        <v>-3.260300759418314</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.008791723747625</v>
+        <v>1.141065091952931</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7571536227814852</v>
+        <v>0.727149799049817</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.899833993702897</v>
+        <v>2.881831699463896</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.546145778323182</v>
+        <v>-3.215462357809916</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.030824787001613</v>
+        <v>1.163098155206919</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7616970557263547</v>
+        <v>0.7316932319946865</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.906657756080447</v>
+        <v>2.888655461841446</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.56564423456519</v>
+        <v>-3.234960814051924</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.027186344135887</v>
+        <v>1.159459712341194</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7136124144464504</v>
+        <v>0.6836085907147822</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.881967910943582</v>
+        <v>2.863965616704581</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.52144139747929</v>
+        <v>-3.190757976966024</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.050747081498085</v>
+        <v>1.183020449703391</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7578152515323509</v>
+        <v>0.7278114278006826</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.91436921572296</v>
+        <v>2.896366921483959</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.529001063316337</v>
+        <v>-3.198317642803071</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.046133215632514</v>
+        <v>1.17840658383782</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8126186555421702</v>
+        <v>0.782614831810502</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.945661258598099</v>
+        <v>2.927658964359098</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284876</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.370709645777064</v>
+        <v>-3.040026225263798</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.160697547831262</v>
+        <v>1.292970916036569</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8126186555421702</v>
+        <v>0.782614831810502</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.996909023781138</v>
+        <v>2.978906729542137</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.163067642142588</v>
+        <v>-2.832384221629322</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.242195053879306</v>
+        <v>1.374468422084612</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.020260659176646</v>
+        <v>0.9902568354449781</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.119934930556077</v>
+        <v>3.101932636317076</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.11203554942006</v>
+        <v>-2.781352128906794</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.257556119206587</v>
+        <v>1.389829487411893</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.071292751899174</v>
+        <v>1.041288928167506</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.145502414427864</v>
+        <v>3.127500120188863</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.046811368292854</v>
+        <v>-2.716127947779588</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.300833195750174</v>
+        <v>1.433106563955481</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.13651693302638</v>
+        <v>1.106513109294712</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.201824327196892</v>
+        <v>3.183822032957892</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.009384348221721</v>
+        <v>-2.678700927708455</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.311764976077908</v>
+        <v>1.444038344283215</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.141768471055562</v>
+        <v>1.111764647323894</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.200936222313682</v>
+        <v>3.182933928074681</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.029496004256429</v>
+        <v>-2.698812583743163</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.304977105995265</v>
+        <v>1.437250474200572</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.152795816052981</v>
+        <v>1.122791992321313</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.208809421643374</v>
+        <v>3.190807127404373</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.001082741156545</v>
+        <v>-2.670399320643279</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.476900182256429</v>
+        <v>1.609173550461736</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.093820253306552</v>
+        <v>1.063816429574884</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.333981855016727</v>
+        <v>3.315979560777726</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.926300480131533</v>
+        <v>-2.595617059618267</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.626925995884252</v>
+        <v>1.759199364089558</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.168602514331565</v>
+        <v>1.138598690599897</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.498964120849552</v>
+        <v>3.480961826610551</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.900216395867725</v>
+        <v>-2.569532975354459</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.629067605603634</v>
+        <v>1.76134097380894</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.168602514331565</v>
+        <v>1.138598690599897</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.490672096863411</v>
+        <v>3.47266980262441</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.812338482758604</v>
+        <v>-2.481655062245338</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.662411966431061</v>
+        <v>1.794685334636368</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.284528156754916</v>
+        <v>1.254524333023248</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.558420677901201</v>
+        <v>3.5404183836622</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.803446021365321</v>
+        <v>-2.472762600852055</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.683523356715166</v>
+        <v>1.815796724920473</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.284528156754916</v>
+        <v>1.254524333023248</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.575975083627992</v>
+        <v>3.557972789388991</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.971922138335199</v>
+        <v>-2.641238717821933</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.607987957331799</v>
+        <v>1.740261325537106</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.256580321038335</v>
+        <v>1.226576497306667</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.551061429602628</v>
+        <v>3.533059135363627</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.525665945705759</v>
+        <v>-2.194982525192493</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.767760131571437</v>
+        <v>1.900033499776743</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.161861651368702</v>
+        <v>1.131857827637034</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.47549992498871</v>
+        <v>3.457497630749709</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.502944842022606</v>
+        <v>-2.17226142150934</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.767512595541602</v>
+        <v>1.899785963746909</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.161861651368702</v>
+        <v>1.131857827637034</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.466163947485614</v>
+        <v>3.448161653246614</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.632146655316649</v>
+        <v>-2.301463234803383</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.874737996075154</v>
+        <v>2.007011364280461</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.03265983807466</v>
+        <v>1.002656014342992</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.547548985360358</v>
+        <v>3.529546691121357</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.658021053790674</v>
+        <v>-2.327337633277408</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.901466059179191</v>
+        <v>2.033739427384497</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.077571446786401</v>
+        <v>1.047567623054733</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.611573773081049</v>
+        <v>3.593571478842049</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799959</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.650966363575501</v>
+        <v>-2.320282943062235</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.900963291254805</v>
+        <v>2.033236659460112</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.084626137001575</v>
+        <v>1.054622313269907</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.612481943199699</v>
+        <v>3.594479648960698</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.624015139249013</v>
+        <v>-2.293331718735747</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.921749934630142</v>
+        <v>2.054023302835449</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.099506483029294</v>
+        <v>1.069502659297626</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.631416304461072</v>
+        <v>3.613414010222071</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.6455593670798</v>
+        <v>-2.314875946566534</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.097235375642787</v>
+        <v>2.229508743848093</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.099506483029294</v>
+        <v>1.069502659297626</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.815519436606031</v>
+        <v>3.797517142367031</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.667967484884672</v>
+        <v>-2.337284064371406</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.080388823423831</v>
+        <v>2.212662191629138</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.099506483029294</v>
+        <v>1.069502659297626</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.807636131509025</v>
+        <v>3.789633837270024</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.696191720462272</v>
+        <v>-2.365508299949006</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.071153128742429</v>
+        <v>2.203426496947735</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.117483235480603</v>
+        <v>1.087479411748935</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.820476182529447</v>
+        <v>3.802473888290447</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.705632646350802</v>
+        <v>-2.374949225837536</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.123630476108864</v>
+        <v>2.25590384431417</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.239910353023994</v>
+        <v>1.209906529292326</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.95018617077733</v>
+        <v>3.932183876538328</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.794509277519276</v>
+        <v>-2.46382585700601</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.090970918186775</v>
+        <v>2.223244286392082</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.15103372185552</v>
+        <v>1.121029898123852</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.899751286621546</v>
+        <v>3.881748992382545</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.870839255120182</v>
+        <v>-2.540155834606916</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.058550740040188</v>
+        <v>2.190824108245494</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.15103372185552</v>
+        <v>1.121029898123852</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.897863099515321</v>
+        <v>3.87986080527632</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.964503199797723</v>
+        <v>-2.633819779284457</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.015905391772034</v>
+        <v>2.14817875997734</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.057369777177979</v>
+        <v>1.027365953446311</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.836484962311658</v>
+        <v>3.818482668072658</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.126071625324979</v>
+        <v>-2.795388204811712</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.949712031771284</v>
+        <v>2.08198539997659</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9305868533800995</v>
+        <v>0.9005830296484315</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.758849218243083</v>
+        <v>3.740846924004082</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.234372287195098</v>
+        <v>-2.903688866681832</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.919465173889154</v>
+        <v>2.051738542094461</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9305868533800995</v>
+        <v>0.9005830296484315</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.771922625109002</v>
+        <v>3.753920330870001</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.252176258915842</v>
+        <v>-2.921492838402576</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.904348781983797</v>
+        <v>2.036622150189103</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8600522304748983</v>
+        <v>0.8300484067432303</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.721607048148821</v>
+        <v>3.70360475390982</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.280077046025315</v>
+        <v>-2.949393625512049</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.89171250826701</v>
+        <v>2.023985876472317</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8254553063319635</v>
+        <v>0.7954514826002955</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.699372934790063</v>
+        <v>3.681370640551061</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.402603148728209</v>
+        <v>-3.071919728214943</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.839466511163051</v>
+        <v>1.971739879368358</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7029292036290696</v>
+        <v>0.6729253798974016</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.622621717145525</v>
+        <v>3.604619422906524</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.633117644913798</v>
+        <v>-3.302434224400532</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.813966672279319</v>
+        <v>1.946240040484626</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4724147074434809</v>
+        <v>0.4424108837118129</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.551018979024675</v>
+        <v>3.533016684785674</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.981862730138241</v>
+        <v>-3.651179309624975</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.814780357191389</v>
+        <v>1.947053725396695</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3636667535245831</v>
+        <v>0.3336629297929151</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.626081925675184</v>
+        <v>3.608079631436183</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.135849147914382</v>
+        <v>-3.805165727401116</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.822166059226572</v>
+        <v>1.954439427431879</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3636667535245831</v>
+        <v>0.3336629297929151</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.695062194820824</v>
+        <v>3.677059900581823</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.34044858277739</v>
+        <v>-4.009765162264125</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.72637748740149</v>
+        <v>1.858650855606796</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3636667535245831</v>
+        <v>0.3336629297929151</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.681113396940944</v>
+        <v>3.663111102701944</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.592923736785115</v>
+        <v>-4.262240316271849</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.637257914853814</v>
+        <v>1.769531283059121</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3636667535245831</v>
+        <v>0.3336629297929151</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.692983885996358</v>
+        <v>3.674981591757358</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.885819493264527</v>
+        <v>-4.555136072751261</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.521310146780993</v>
+        <v>1.653583514986299</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3636667535245831</v>
+        <v>0.3336629297929151</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.694194420515302</v>
+        <v>3.676192126276301</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.072483621399335</v>
+        <v>-4.741800200886069</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.450766237754391</v>
+        <v>1.583039605959698</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3369277827000232</v>
+        <v>0.3069239589683552</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.682272780247887</v>
+        <v>3.664270486008887</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916199</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.218504308313297</v>
+        <v>-4.887820887800031</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.387435815724996</v>
+        <v>1.519709183930302</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3278446909061662</v>
+        <v>0.2978408671744983</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.671900777907763</v>
+        <v>3.653898483668762</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.310218317422883</v>
+        <v>-4.979534896909616</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.512954268780205</v>
+        <v>1.645227636985513</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3278446909061662</v>
+        <v>0.2978408671744983</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.834104834606807</v>
+        <v>3.816102540367806</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.341869976482852</v>
+        <v>-5.011186555969585</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.495140243120032</v>
+        <v>1.627413611325339</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.322676233661726</v>
+        <v>0.2926724099300581</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.825850398223957</v>
+        <v>3.807848103984956</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.423804794751735</v>
+        <v>-5.093121374238469</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.47259573338097</v>
+        <v>1.604869101586277</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3127414880746459</v>
+        <v>0.2827376643429779</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.8301189684402</v>
+        <v>3.812116674201199</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.525780917000143</v>
+        <v>-5.195097496486876</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.440730922937509</v>
+        <v>1.573004291142816</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2107653658262383</v>
+        <v>0.1807615420945703</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.777858933547058</v>
+        <v>3.759856639308057</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.415774633522921</v>
+        <v>-5.085091213009655</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.476886323572573</v>
+        <v>1.60915969177788</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2339699377435135</v>
+        <v>0.2039661140118455</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.783934563941598</v>
+        <v>3.765932269702597</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.272715057781995</v>
+        <v>-4.942031637268729</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.538360164590918</v>
+        <v>1.670633532796225</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2419833643334928</v>
+        <v>0.2119795406018248</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.79299263061756</v>
+        <v>3.77499033637856</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.971268332310157</v>
+        <v>-4.640584911796891</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.666199737662189</v>
+        <v>1.798473105867496</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.54343008980533</v>
+        <v>0.513426266073662</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.981121548783198</v>
+        <v>3.963119254544198</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.995858576545341</v>
+        <v>-4.665175156032075</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.657334817720826</v>
+        <v>1.789608185926133</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.54343008980533</v>
+        <v>0.513426266073662</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.982092726535909</v>
+        <v>3.964090432296908</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.944820200538821</v>
+        <v>-4.614136780025555</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.67859307250319</v>
+        <v>1.810866440708497</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.54343008980533</v>
+        <v>0.513426266073662</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.982935630915665</v>
+        <v>3.964933336676664</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.90368090567219</v>
+        <v>-4.572997485158924</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.714086889323987</v>
+        <v>1.846360257529294</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5845693846719608</v>
+        <v>0.5545655609402929</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.026657306709788</v>
+        <v>4.008655012470788</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.80704599365355</v>
+        <v>-4.476362573140284</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.568924850255378</v>
+        <v>1.701198218460685</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6812042966906008</v>
+        <v>0.6512004729589328</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.900822250044907</v>
+        <v>3.882819955805906</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.937626728184393</v>
+        <v>-4.606943307671126</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.520194600517005</v>
+        <v>1.652467968722312</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5506235621597583</v>
+        <v>0.5206197384280903</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.825975853400366</v>
+        <v>3.807973559161365</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833458</v>
+        <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.773130393993431</v>
+        <v>-4.442446973480164</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.570419953269472</v>
+        <v>1.702693321474779</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7151198963507202</v>
+        <v>0.6851160726190522</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.909100472991025</v>
+        <v>3.891098178752025</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.696031792451558</v>
+        <v>-4.365348371938292</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.600447104322651</v>
+        <v>1.732720472527958</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.7151198963507202</v>
+        <v>0.6851160726190522</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.908288183427455</v>
+        <v>3.890285889188454</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.706416987341448</v>
+        <v>-4.375733566828181</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.606161805491768</v>
+        <v>1.738435173697075</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.7047347014608308</v>
+        <v>0.6747308777291628</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.911925845618594</v>
+        <v>3.893923551379593</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.725005146063673</v>
+        <v>-4.281341537914481</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.669563547779303</v>
+        <v>1.84702899103898</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6861465427386055</v>
+        <v>0.769122906642863</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.971609956161684</v>
+        <v>4.021395774504239</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.725303692759709</v>
+        <v>-4.281640084610517</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.666313139919187</v>
+        <v>1.843778583178864</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6858479960425696</v>
+        <v>0.7688243599468271</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.968299838962361</v>
+        <v>4.018085657304916</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.624480559069281</v>
+        <v>-4.179753222370699</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.71117328833475</v>
+        <v>1.889064223014183</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6983122115269235</v>
+        <v>0.8389188114023837</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.980309263192365</v>
+        <v>4.064673223117641</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.433699198316874</v>
+        <v>-3.988971861618292</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.787615086114256</v>
+        <v>1.965506020793689</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8890935722793308</v>
+        <v>1.029700172154791</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.094907333122352</v>
+        <v>4.179271293047629</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.326735840467452</v>
+        <v>-3.88200850376887</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.810237274991621</v>
+        <v>1.988128209671054</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.9475581802391323</v>
+        <v>1.088164780114592</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.10982294363583</v>
+        <v>4.194186903561106</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.27140525256569</v>
+        <v>-3.826677915867108</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.867336446764384</v>
+        <v>2.045227381443818</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.002888768140894</v>
+        <v>1.143495368016354</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.177988232988946</v>
+        <v>4.262352192914221</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.259351125652727</v>
+        <v>-3.814623788954145</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.865844665431007</v>
+        <v>2.04373560011044</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.014942895053857</v>
+        <v>1.155549494929317</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.178907277038161</v>
+        <v>4.263271236963437</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.300506245220948</v>
+        <v>-3.855778908522366</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.851263247787855</v>
+        <v>2.029154182467288</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9737877754856363</v>
+        <v>1.114394375361096</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.156094835481364</v>
+        <v>4.24045879540664</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.232457682529418</v>
+        <v>-3.787730345830836</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.891333698742349</v>
+        <v>2.069224633421782</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.041836338177166</v>
+        <v>1.182442938052626</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.209774998974165</v>
+        <v>4.294138958899441</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013426</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.464058075698919</v>
+        <v>-4.019330739000337</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.818896211648143</v>
+        <v>1.996787146327576</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.041836338177166</v>
+        <v>1.182442938052626</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.229977669147759</v>
+        <v>4.314341629073035</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.514109621228138</v>
+        <v>-4.069382284529556</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.782481829503337</v>
+        <v>1.96037276418277</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.041836338177166</v>
+        <v>1.182442938052626</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.213583905214641</v>
+        <v>4.297947865139917</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.689216453804582</v>
+        <v>-4.244489117106001</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.672691010066226</v>
+        <v>1.850581944745659</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.041836338177166</v>
+        <v>1.182442938052626</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.173835818808108</v>
+        <v>4.258199778733384</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.49311630037406</v>
+        <v>-4.048388963675478</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.758153690435375</v>
+        <v>1.936044625114808</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.237936491607689</v>
+        <v>1.378543091483149</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.298518529863362</v>
+        <v>4.382882489788638</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.340090908260775</v>
+        <v>-3.895363571562194</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.918534846853594</v>
+        <v>2.096425781533026</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.390961883720973</v>
+        <v>1.531568483596433</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.489504764704236</v>
+        <v>4.573868724629512</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.368398222134045</v>
+        <v>-3.923670885435464</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.094678146212578</v>
+        <v>2.272569080892011</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.390961883720973</v>
+        <v>1.531568483596433</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.676970989612529</v>
+        <v>4.761334949537805</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.534991447247568</v>
+        <v>-4.090264110548986</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.997443807521252</v>
+        <v>2.175334742200685</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.224368658607451</v>
+        <v>1.364975258482911</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.546418005898498</v>
+        <v>4.630781965823774</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.511955653886002</v>
+        <v>-4.06722831718742</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.010334527527596</v>
+        <v>2.188225462207029</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.224368658607451</v>
+        <v>1.364975258482911</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.550094408560216</v>
+        <v>4.634458368485491</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.482709673430305</v>
+        <v>-4.037982336731724</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.01965097483337</v>
+        <v>2.197541909512803</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.224368658607451</v>
+        <v>1.364975258482911</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.547712463683711</v>
+        <v>4.632076423608987</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.589635221308156</v>
+        <v>-4.144907884609575</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.974173994839864</v>
+        <v>2.152064929519297</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.117443110729599</v>
+        <v>1.258049710605059</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.480850374114635</v>
+        <v>4.565214334039911</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701001</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.734653779815405</v>
+        <v>-4.289926443116824</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.917595373580199</v>
+        <v>2.095486308259632</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.9724245522223509</v>
+        <v>1.113031152097811</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.39526804115352</v>
+        <v>4.479632001078796</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.852995545600122</v>
+        <v>-4.408268208901541</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.970189906524065</v>
+        <v>2.148080841203498</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.983110590785241</v>
+        <v>1.123717190660701</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.501610903549008</v>
+        <v>4.585974863474283</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.90440596792083</v>
+        <v>-4.459678631222249</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.947411434721721</v>
+        <v>2.125302369401154</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.983110590785241</v>
+        <v>1.123717190660701</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.499396600674946</v>
+        <v>4.583760560600222</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.983825419128582</v>
+        <v>-4.539098082430001</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.91554678231291</v>
+        <v>2.093437716992343</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.983110590785241</v>
+        <v>1.123717190660701</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.499299728749236</v>
+        <v>4.583663688674512</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298398</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.0792884170458</v>
+        <v>-4.634561080347218</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.877355476704066</v>
+        <v>2.055246411383498</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.983110590785241</v>
+        <v>1.123717190660701</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.499293622307278</v>
+        <v>4.583657582232554</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218001</v>
+        <v>3.715372960217997</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.014912506195085</v>
+        <v>-4.570185169496503</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.901202237606962</v>
+        <v>2.079093172286395</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.047486501635956</v>
+        <v>1.188093101511416</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.536015565380318</v>
+        <v>4.620379525305594</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353536</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.070281668327278</v>
+        <v>-4.625554331628697</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.884788390501811</v>
+        <v>2.062679325181244</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.047486501635956</v>
+        <v>1.188093101511416</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.541749383128045</v>
+        <v>4.626113343053321</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113279</v>
+        <v>3.736822870113276</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.115719448158106</v>
+        <v>-4.670992111459524</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.866151641912413</v>
+        <v>2.044042576591846</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.004641510957796</v>
+        <v>1.145248110833257</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.515580752064081</v>
+        <v>4.599944711989358</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113688</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.027512614010528</v>
+        <v>-4.582785277311946</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.921308768421763</v>
+        <v>2.099199703101196</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.004641510957796</v>
+        <v>1.145248110833257</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.5354551449144</v>
+        <v>4.619819104839676</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.921477618805218</v>
+        <v>-4.476750282106637</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.947423467028615</v>
+        <v>2.125314401708047</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.004641510957796</v>
+        <v>1.145248110833257</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.519155845439128</v>
+        <v>4.603519805364404</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.738265955672123</v>
+        <v>-4.293538618973542</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.023139081745898</v>
+        <v>2.201030016425331</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.004641510957796</v>
+        <v>1.145248110833257</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.521586794903174</v>
+        <v>4.60595075482845</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.666544508658272</v>
+        <v>-4.221817171959691</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.017618846399328</v>
+        <v>2.195509781078761</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.076362957971647</v>
+        <v>1.216969557847107</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.530410848959374</v>
+        <v>4.61477480888465</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.72378970539411</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.644171483050566</v>
+        <v>-4.199444146351984</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.973483802563582</v>
+        <v>2.151374737243015</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.087618709084548</v>
+        <v>1.228225308960009</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.484080045548287</v>
+        <v>4.568444005473562</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456727</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.677187778961311</v>
+        <v>-4.232460442262729</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.14547548908464</v>
+        <v>2.323366423764072</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.018181332417797</v>
+        <v>1.158787932293257</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.62761582443359</v>
+        <v>4.711979784358866</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883676</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.665660143311702</v>
+        <v>-4.220932806613121</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.142007769172732</v>
+        <v>2.319898703852165</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.077181990619159</v>
+        <v>1.21778859049462</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.654937445182657</v>
+        <v>4.739301405107933</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236297</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.763001644654071</v>
+        <v>-4.318274307955489</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.106739281157573</v>
+        <v>2.284630215837006</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.032761808453671</v>
+        <v>1.173368408329131</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.631953448405152</v>
+        <v>4.716317408330429</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427684</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.848857673994037</v>
+        <v>-4.404130337295456</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.073647951614425</v>
+        <v>2.251538886293857</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.9903857392275359</v>
+        <v>1.130992339102996</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.60777888906231</v>
+        <v>4.692142848987586</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.857694471410157</v>
+        <v>-4.412967134711575</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.052532434468478</v>
+        <v>2.230423369147911</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.9829435665861852</v>
+        <v>1.123550166461646</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.585732787298001</v>
+        <v>4.670096747223277</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667454</v>
+        <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.949077033975615</v>
+        <v>-4.504349697277034</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.026143920487344</v>
+        <v>2.204034855166777</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.9463786818668405</v>
+        <v>1.086985281742301</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.573958367511444</v>
+        <v>4.65832232743672</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.67397837488919</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.937370315988609</v>
+        <v>-4.492642979290028</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.132954865506414</v>
+        <v>2.310845800185847</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.9580853998538469</v>
+        <v>1.098691999729307</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.683110656127915</v>
+        <v>4.767474616053191</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409565</v>
+        <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.837706811904947</v>
+        <v>-4.392979475206365</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.175852605871284</v>
+        <v>2.353743540550717</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.021272483057533</v>
+        <v>1.161879082932994</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.724055244781532</v>
+        <v>4.808419204706808</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.848022910071299</v>
+        <v>-4.403295573372717</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.384630999882801</v>
+        <v>2.562521934562234</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.021272483057533</v>
+        <v>1.161879082932994</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.93696007805959</v>
+        <v>5.021324037984866</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762287</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.847928942053926</v>
+        <v>-4.403201605355345</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.38384725400184</v>
+        <v>2.561738188681273</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.021642344404851</v>
+        <v>1.162248944280312</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.936360661780069</v>
+        <v>5.020724621705346</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988018</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.85514776625377</v>
+        <v>-4.410420429555189</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.375191710266257</v>
+        <v>2.553082644945689</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.021642344404851</v>
+        <v>1.162248944280312</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.930592647724424</v>
+        <v>5.0149566076497</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740918</v>
+        <v>3.647907242740919</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.854199343135732</v>
+        <v>-4.40947200643715</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.375571079513472</v>
+        <v>2.553462014192904</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.021642344404851</v>
+        <v>1.162248944280312</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.930592647724424</v>
+        <v>5.0149566076497</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.011267801391356</v>
+        <v>-4.566540464692775</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.325471304192314</v>
+        <v>2.503362238871747</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.021642344404851</v>
+        <v>1.162248944280312</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.943320255705515</v>
+        <v>5.027684215630792</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.005275554602544</v>
+        <v>-4.560548217903963</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.329814201332226</v>
+        <v>2.507705136011659</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.021642344404851</v>
+        <v>1.162248944280312</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.945266254129903</v>
+        <v>5.02963021405518</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.916717593471777</v>
+        <v>-4.471990256773196</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.358891521802303</v>
+        <v>2.536782456481735</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.021642344404851</v>
+        <v>1.162248944280312</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.938920390147672</v>
+        <v>5.023284350072949</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.898958515968703</v>
+        <v>-4.454231179270121</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.365303830242528</v>
+        <v>2.54319476492196</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.021642344404851</v>
+        <v>1.162248944280312</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.938229067586668</v>
+        <v>5.022593027511944</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.799328364919635</v>
+        <v>-4.354601028221054</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.417938076570741</v>
+        <v>2.595829011250174</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.121272495453919</v>
+        <v>1.261879095329379</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.010789344124695</v>
+        <v>5.095153304049972</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.848727873608646</v>
+        <v>-4.404000536910065</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.587332538593864</v>
+        <v>2.765223473273296</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.131531328885663</v>
+        <v>1.272137928761124</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.206098909682469</v>
+        <v>5.290462869607745</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963134</v>
+        <v>3.749078058963133</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.64204339996627</v>
+        <v>-4.197316063267689</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.657195001153676</v>
+        <v>2.835085935833109</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.338215802528039</v>
+        <v>1.4788224024035</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.317298266970756</v>
+        <v>5.401662226896033</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.484867965559948</v>
+        <v>3.912803970438472</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.398974738119499</v>
+        <v>4.667099457637297</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.64204339996627</v>
+        <v>-4.197316063267689</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.657195001153676</v>
+        <v>2.835085935833109</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.338215802528039</v>
+        <v>1.4788224024035</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.392038535105867</v>
+        <v>4.660163254623665</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240916.xlsx
+++ b/tame_output/ON/bt/strategyON_20240916.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>61.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>155.1%</t>
+          <t>163.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.6%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.0%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.1%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.1%</t>
+          <t>422.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-581.3%</t>
+          <t>-596.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>121.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-92.7%</t>
+          <t>-98.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>-63.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-314.5%</t>
+          <t>-329.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-89.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.0%</t>
         </is>
       </c>
     </row>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.400434910604325</v>
+        <v>-6.536080696634842</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5583483051372111</v>
+        <v>0.5040899907250038</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.8103298254957174</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.619188822504445</v>
+        <v>-6.754268442644352</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4669463055228582</v>
+        <v>0.4129144574668953</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.8103298254957174</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.667391639746789</v>
+        <v>-6.802471259886696</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.4460700986809214</v>
+        <v>0.3920382506249589</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.8103298254957174</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.834200299721151</v>
+        <v>-6.969279919861058</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.3831256106203846</v>
+        <v>0.3290937625644221</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.852613149208854</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.020920008030454</v>
+        <v>-7.155999628170361</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.3044114227622607</v>
+        <v>0.2503795747062978</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.852613149208854</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.403921396773085</v>
+        <v>-7.539001016912992</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.1511087659436239</v>
+        <v>0.09707691788766137</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.852613149208854</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.408407841974474</v>
+        <v>-7.54348746211438</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1518857038344987</v>
+        <v>0.09785385577853623</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8570995944102426</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.767938164478475</v>
+        <v>-7.903017784618382</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.01342387813094836</v>
+        <v>-0.04060796992501459</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8570995944102426</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.818287227932697</v>
+        <v>-7.953366848072604</v>
       </c>
       <c r="E1875" t="n">
-        <v>0.001200272706436856</v>
+        <v>-0.05283157534952565</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.9074486578644647</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.915906505354094</v>
+        <v>-8.050986125493999</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.03480568764035308</v>
+        <v>-0.08883753569631514</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.005067935285861</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.969978004862454</v>
+        <v>-8.105057625002358</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.05354073112212454</v>
+        <v>-0.1075725791780866</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.059139434794221</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-7.973553790954202</v>
+        <v>-8.108633411094106</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.04945784844018153</v>
+        <v>-0.1034896964961431</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.084668356710713</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.007206629462676</v>
+        <v>-8.142286249602579</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.05843642935913484</v>
+        <v>-0.1124682774150965</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.185081724627751</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.146292744081531</v>
+        <v>-8.281372364221436</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.09869917371325654</v>
+        <v>-0.1527310217692186</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.324167839246607</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.321417161468075</v>
+        <v>-8.45649678160798</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.1541937199203569</v>
+        <v>-0.208225567976319</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.499292256633151</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.555869255482564</v>
+        <v>-8.690948875622469</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.255193722427749</v>
+        <v>-0.309225570483711</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.499292256633151</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.660243986509011</v>
+        <v>-8.795323606648916</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3036158056123037</v>
+        <v>-0.3576476536682658</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.603666987659597</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.822757452207595</v>
+        <v>-8.9578370723475</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.3675054020531809</v>
+        <v>-0.421537250109143</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.701300418078284</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.948794245575884</v>
+        <v>-9.083873865715789</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.415226390771382</v>
+        <v>-0.4692582388273441</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.676048795268541</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.891722473679954</v>
+        <v>-9.026802093819859</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.3884073463266091</v>
+        <v>-0.4424391943825707</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.676048795268541</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.033394315404074</v>
+        <v>-9.168473935543979</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.4465513099149989</v>
+        <v>-0.5005831579709605</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.676048795268541</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.98380347097924</v>
+        <v>-9.118883091119145</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.4116615619801927</v>
+        <v>-0.4656934100361547</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.626457950843708</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.834885136507383</v>
+        <v>-8.969964756647288</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.3651453618381333</v>
+        <v>-0.4191772098940949</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.595208360108535</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.609039983787971</v>
+        <v>-8.744119603927876</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.2652282277141595</v>
+        <v>-0.3192600757701216</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.553281684521371</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.484461327450379</v>
+        <v>-8.619540947590284</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.214257620623064</v>
+        <v>-0.268289468679026</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.553281684521371</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.459424645881869</v>
+        <v>-8.594504266021774</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2016091738335524</v>
+        <v>-0.2556410218895144</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.527952596970635</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.387291470593988</v>
+        <v>-8.522371090733893</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.1670221994797636</v>
+        <v>-0.2210540475357252</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.527952596970635</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.315925077984341</v>
+        <v>-8.451004698124246</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.1482129048297698</v>
+        <v>-0.2022447528857318</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.456586204360987</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.222466043999116</v>
+        <v>-8.357545664139021</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.1207127725485875</v>
+        <v>-0.1747446206045495</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.456586204360987</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.211812862445685</v>
+        <v>-8.34689248258559</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1182860604265885</v>
+        <v>-0.1723179084825506</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.456586204360987</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.113905823769194</v>
+        <v>-8.248985443909099</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.07942355992945327</v>
+        <v>-0.1334554079854153</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.388600454500431</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.089952282793236</v>
+        <v>-8.225031902933141</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.06917363739357629</v>
+        <v>-0.1232054854495384</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.364646913524473</v>
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.98074323494275</v>
+        <v>-7.960971964610345</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.03875033441513409</v>
+        <v>-0.03084182628217214</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.255437865673987</v>
+        <v>-1.100586975201677</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.400640664471322</v>
+        <v>2.493551198754708</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.273663611437912</v>
+        <v>-7.253892341105507</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2412944813265003</v>
+        <v>0.2492029894594623</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.255437865673987</v>
+        <v>-1.100586975201677</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.397853630811021</v>
+        <v>2.490764165094407</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.233479313071721</v>
+        <v>-7.213708042739317</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2577118245608179</v>
+        <v>0.2656203326937798</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.215253567307796</v>
+        <v>-1.060402676835486</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.422307833718577</v>
+        <v>2.515218368001963</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.070079442132359</v>
+        <v>-7.050308171799954</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3224385941573198</v>
+        <v>0.3303471022902817</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.051853696368434</v>
+        <v>-0.8970028058961237</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.519714577502952</v>
+        <v>2.612625111786337</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.83659821990276</v>
+        <v>-6.816826949570356</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4237555118870118</v>
+        <v>0.4316640200199737</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.818372474138835</v>
+        <v>-0.6635215836665251</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.667727739678563</v>
+        <v>2.760638273961949</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.686931828895245</v>
+        <v>-6.66716055856284</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4807298579770585</v>
+        <v>0.4886383661100204</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.725468982896299</v>
+        <v>-0.5706180924239892</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.720577624111125</v>
+        <v>2.813488158394511</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.554656355264359</v>
+        <v>-6.534885084931954</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4349008334365676</v>
+        <v>0.4428093415695296</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5931935092654124</v>
+        <v>-0.4383426187931025</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.701203694296812</v>
+        <v>2.794114228580198</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.382795139699456</v>
+        <v>-6.363023869367051</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5064603803501653</v>
+        <v>0.5143688884831272</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4213322937005095</v>
+        <v>-0.2664814032281997</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.80713548432339</v>
+        <v>2.900046018606776</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.297830472970137</v>
+        <v>-6.278059202637731</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5533525882655517</v>
+        <v>0.5612610963985141</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.3363676269711899</v>
+        <v>-0.1815167364988801</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.871020625584641</v>
+        <v>2.963931159868027</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.403420462743242</v>
+        <v>-6.383649192410836</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3831406627570915</v>
+        <v>0.3910491708900539</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.4419576167442943</v>
+        <v>-0.2871067262719845</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.67969070212156</v>
+        <v>2.772601236404946</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.335185878117814</v>
+        <v>-6.315414607785408</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4589788384843487</v>
+        <v>0.4668873466173111</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4235422938717583</v>
+        <v>-0.2686914033994485</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.739284237722168</v>
+        <v>2.832194772005554</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.187245836710215</v>
+        <v>-6.167474566377809</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4015340464089814</v>
+        <v>0.4094425545419438</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.4032213779632007</v>
+        <v>-0.2483704874908909</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.634855978628895</v>
+        <v>2.727766512912281</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.134276314456226</v>
+        <v>-6.11450504412382</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4140078690570985</v>
+        <v>0.4219163771900609</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.3502518557092119</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.65792370572781</v>
+        <v>2.750834240011196</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.968488118495936</v>
+        <v>-5.94871684816353</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4733625353461219</v>
+        <v>0.4812710434790843</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.3502518557092119</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.650963093632717</v>
+        <v>2.743873627916103</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.935124912017167</v>
+        <v>-5.915353641684761</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5011701723187723</v>
+        <v>0.5090786804517347</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.3502518557092119</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.66542544801386</v>
+        <v>2.758335982297246</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.826865774894645</v>
+        <v>-5.807094504562239</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.539005947626976</v>
+        <v>0.5469144557599384</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.3502518557092119</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.659957568473055</v>
+        <v>2.752868102756441</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.703574640077514</v>
+        <v>-5.683803369745108</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5858204955644055</v>
+        <v>0.5937290036973675</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2269607208920814</v>
+        <v>-0.07210983041977154</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.731430343373911</v>
+        <v>2.824340877657296</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.650877772946223</v>
+        <v>-5.631106502613817</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6146002206542471</v>
+        <v>0.6225087287872095</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1742638537607902</v>
+        <v>-0.01941296328848036</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.77074944189001</v>
+        <v>2.863659976173396</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.407112330962779</v>
+        <v>-5.387341060630373</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7078871057946756</v>
+        <v>0.7157956139276376</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1742638537607902</v>
+        <v>-0.01941296328848036</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.766530150237061</v>
+        <v>2.859440684520447</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.317336658586306</v>
+        <v>-5.297565388253901</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7459216886652804</v>
+        <v>0.7538301967982428</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1126644088464802</v>
+        <v>0.04218648162582966</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.805614131105663</v>
+        <v>2.898524665389049</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.067486264637232</v>
+        <v>-5.047714994304826</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8386039212286125</v>
+        <v>0.8465124293615744</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1126644088464802</v>
+        <v>0.04218648162582966</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.798356206089365</v>
+        <v>2.891266740372751</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.8915941721698</v>
+        <v>-4.871822901837394</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9125598817362339</v>
+        <v>0.9204683898691961</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1126644088464802</v>
+        <v>0.04218648162582966</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.801955329610014</v>
+        <v>2.8948658638934</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.720147709147336</v>
+        <v>-4.700376438814931</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9944659729997729</v>
+        <v>1.002374481132735</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.05878205417598298</v>
+        <v>0.2136329446482928</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.918150713478045</v>
+        <v>3.011061247761432</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.640125422038215</v>
+        <v>-4.62035415170581</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.025495365459718</v>
+        <v>1.033403873592681</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1388043412851039</v>
+        <v>0.2936552317574138</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.965184563359815</v>
+        <v>3.058095097643201</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.576489679804281</v>
+        <v>-4.556718409471875</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.055644463407609</v>
+        <v>1.063552971540572</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2024400835190385</v>
+        <v>0.3572909739913483</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.008060809754493</v>
+        <v>3.100971344037879</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.482792361587886</v>
+        <v>-4.46302109125548</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.074317649477963</v>
+        <v>1.082226157610925</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2024400835190385</v>
+        <v>0.3572909739913483</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.989255068538289</v>
+        <v>3.082165602821675</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.493294984653175</v>
+        <v>-4.473523714320769</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.071859676876725</v>
+        <v>1.079768185009687</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1919374604537496</v>
+        <v>0.3467883509260594</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.984696571323993</v>
+        <v>3.077607105607379</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.3808087239843</v>
+        <v>-4.361037453651894</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.120783494979095</v>
+        <v>1.128692003112057</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1919374604537496</v>
+        <v>0.3467883509260594</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.988625885158813</v>
+        <v>3.081536419442199</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.363095037106435</v>
+        <v>-4.257872326099297</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.128547553647581</v>
+        <v>1.170636638050436</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1951187893506664</v>
+        <v>0.3733088004030911</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.991213266414303</v>
+        <v>3.098127273045758</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.239620765793417</v>
+        <v>-4.134398054786279</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.174935333392782</v>
+        <v>1.217024417795637</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1951187893506664</v>
+        <v>0.3733088004030911</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.988211337634297</v>
+        <v>3.095125344265751</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.019599967756406</v>
+        <v>-3.914377256749268</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.2645226896182</v>
+        <v>1.306611774021055</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3363386344186466</v>
+        <v>0.5145286454710714</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.074522281685699</v>
+        <v>3.181436288317154</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.886732278693128</v>
+        <v>-3.78150956768599</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.333563948045335</v>
+        <v>1.37565303244819</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3363386344186466</v>
+        <v>0.5145286454710714</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.090416464487522</v>
+        <v>3.197330471118977</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.766559195328629</v>
+        <v>-3.661336484321491</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.382779025831436</v>
+        <v>1.424868110234291</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4565117177831456</v>
+        <v>0.6347017288355703</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.163666158946523</v>
+        <v>3.270580165577978</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.631305833998652</v>
+        <v>-3.526083122991514</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.446968472924867</v>
+        <v>1.489057557327722</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5917650791131227</v>
+        <v>0.7699550901655474</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.254906278305949</v>
+        <v>3.361820284937404</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.691180661356344</v>
+        <v>-3.585957950349206</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.409056033383216</v>
+        <v>1.451145117786071</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5318902517554306</v>
+        <v>0.7100802628078553</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.20501887329276</v>
+        <v>3.311932879924215</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674509</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.571360430445507</v>
+        <v>-3.466137719438369</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.472273294981759</v>
+        <v>1.514362379384615</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5318902517554306</v>
+        <v>0.7100802628078553</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.220308042526969</v>
+        <v>3.327222049158423</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.573830136907313</v>
+        <v>-3.468607425900175</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.378929611719478</v>
+        <v>1.421018696122334</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5294205452936245</v>
+        <v>0.7076105563460491</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.126470417972326</v>
+        <v>3.233384424603781</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.642200323231322</v>
+        <v>-3.536977612224184</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.270843398675176</v>
+        <v>1.312932483078031</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5386962443298394</v>
+        <v>0.716886255382264</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.051297698879357</v>
+        <v>3.158211705510812</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.754072602857473</v>
+        <v>-3.648849891850335</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.216531195456607</v>
+        <v>1.258620279859462</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5386962443298394</v>
+        <v>0.716886255382264</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.041734407511248</v>
+        <v>3.148648414142703</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.738097937371205</v>
+        <v>-3.632875226364067</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.189495586575142</v>
+        <v>1.231584670977997</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5386962443298394</v>
+        <v>0.716886255382264</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.008308932435276</v>
+        <v>3.11522293906673</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.562623677578736</v>
+        <v>-3.457400966571598</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.264252522483917</v>
+        <v>1.306341606886772</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5386962443298394</v>
+        <v>0.716886255382264</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.012876164427063</v>
+        <v>3.119790171058518</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.554699302993822</v>
+        <v>-3.449476591986684</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.24316430107909</v>
+        <v>1.285253385481945</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5386962443298394</v>
+        <v>0.716886255382264</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.98861819318827</v>
+        <v>3.095532199819725</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.548421100423973</v>
+        <v>-3.443198389416835</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.174213895508479</v>
+        <v>1.216302979911334</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5449744468996884</v>
+        <v>0.723164457952113</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.920923428131629</v>
+        <v>3.027837434763084</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.48856848122025</v>
+        <v>-3.383345770213112</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.208327329622101</v>
+        <v>1.250416414024956</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5449744468996884</v>
+        <v>0.723164457952113</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.931095814563762</v>
+        <v>3.038009821195216</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.786949957742296</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.402325018193872</v>
+        <v>-3.297102307186734</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.237770985406512</v>
+        <v>1.279860069809367</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5449744468996884</v>
+        <v>0.723164457952113</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.926042085137622</v>
+        <v>3.032956091769077</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.447631837592852</v>
+        <v>-3.342409126585714</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.211424033091446</v>
+        <v>1.253513117494301</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5041642838904576</v>
+        <v>0.6823542949428822</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.893331762776609</v>
+        <v>3.000245769408064</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.476664942295154</v>
+        <v>-3.371442231288016</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.200362664243626</v>
+        <v>1.242451748646482</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5041642838904576</v>
+        <v>0.6823542949428822</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.893883635809711</v>
+        <v>3.000797642441166</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.383854460844295</v>
+        <v>-3.278631749837157</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.166759548715336</v>
+        <v>1.208848633118191</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.596974765341317</v>
+        <v>0.7751647763937416</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.878842616571592</v>
+        <v>2.985756623203047</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.428243930173722</v>
+        <v>-3.323021219166584</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.150877236908166</v>
+        <v>1.192966321311021</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5525852960118893</v>
+        <v>0.7307753070643139</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.854082410898537</v>
+        <v>2.960996417529991</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472732</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.407740236288225</v>
+        <v>-3.302517525281087</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.154154422974087</v>
+        <v>1.196243507376943</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5730889898973867</v>
+        <v>0.7512790009498113</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.861460335741558</v>
+        <v>2.968374342373012</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798533</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.447664330870797</v>
+        <v>-3.342441619863659</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.143676080971726</v>
+        <v>1.185765165374581</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5730889898973867</v>
+        <v>0.7512790009498113</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.866951631572225</v>
+        <v>2.97386563820368</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.47544472877215</v>
+        <v>-3.370222017765012</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.144061123579724</v>
+        <v>1.186150207982579</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5453085919960337</v>
+        <v>0.7234986030484583</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.861780594599952</v>
+        <v>2.968694601231407</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.593825401502289</v>
+        <v>-3.488602690495151</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9350645744883217</v>
+        <v>0.9771536588911769</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4780907398450575</v>
+        <v>0.6562807508974821</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.65980560331002</v>
+        <v>2.766719609941474</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.70243947994562</v>
+        <v>-3.597216768938482</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.011768603830195</v>
+        <v>1.05385768823305</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4780907398450575</v>
+        <v>0.6562807508974821</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.779955264029225</v>
+        <v>2.88686927066068</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.667030441697477</v>
+        <v>-3.561807730690339</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.040445245231775</v>
+        <v>1.08253432963463</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4780907398450575</v>
+        <v>0.6562807508974821</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.794468290131548</v>
+        <v>2.901382296763003</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.675491610352938</v>
+        <v>-3.5702688993458</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.034480219111959</v>
+        <v>1.076569303514814</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4696295711895964</v>
+        <v>0.647819582242021</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.78681103028064</v>
+        <v>2.893725036912095</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.498375280317772</v>
+        <v>-3.393152569310634</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.102055779971328</v>
+        <v>1.144144864374183</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4696295711895964</v>
+        <v>0.647819582242021</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.783540059125943</v>
+        <v>2.890454065757397</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.543467525151318</v>
+        <v>-3.43824481414418</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.084702273799823</v>
+        <v>1.126791358202678</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4077335280202066</v>
+        <v>0.5859235390726312</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.747085824986222</v>
+        <v>2.853999831617677</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011232</v>
+        <v>3.750729377011229</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.36409210391255</v>
+        <v>-3.258869392905412</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.150239417601744</v>
+        <v>1.192328502004599</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5645102861909252</v>
+        <v>0.7427002972433498</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.834938855195068</v>
+        <v>2.941852861826523</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982222</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.409106317433156</v>
+        <v>-3.303883606426018</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.113041187525091</v>
+        <v>1.155130271927947</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5341613908763206</v>
+        <v>0.7123514019287452</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.797536973337895</v>
+        <v>2.904450979969349</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509531</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.676110827705592</v>
+        <v>-3.570888116698454</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.011930945755063</v>
+        <v>1.054020030157918</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3397983528333721</v>
+        <v>0.5179883638857967</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.686610712851071</v>
+        <v>2.793524719482526</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.777308609142764</v>
+        <v>-3.672085898135626</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9706557550766954</v>
+        <v>1.012744839479551</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2713895392880529</v>
+        <v>0.4495795503404775</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.644769346620381</v>
+        <v>2.751683353251836</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.770797642528452</v>
+        <v>-3.665574931521314</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9708601032767372</v>
+        <v>1.012949187679592</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2713895392880529</v>
+        <v>0.4495795503404775</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.642369308174698</v>
+        <v>2.749283314806153</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.751759514821154</v>
+        <v>-3.646536803814016</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.975000073567901</v>
+        <v>1.017089157970756</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2132059279568583</v>
+        <v>0.391395939009283</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.603983860584226</v>
+        <v>2.710897867215681</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131244</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.804275317095974</v>
+        <v>-3.699052606088836</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.073288154292163</v>
+        <v>1.115377238695018</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2132059279568583</v>
+        <v>0.391395939009283</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.723278262218416</v>
+        <v>2.830192268849871</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.72244736206786</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.807683628530554</v>
+        <v>-3.702460917523416</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.072758158704465</v>
+        <v>1.11484724310732</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2457224969662357</v>
+        <v>0.4239125080186604</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.743621532610176</v>
+        <v>2.850535539241631</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789119</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.788327492636707</v>
+        <v>-3.683104781629569</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.08650914345893</v>
+        <v>1.128598227861785</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2457224969662357</v>
+        <v>0.4239125080186604</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.749630063007102</v>
+        <v>2.856544069638557</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519904</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.640584522401705</v>
+        <v>-3.535361811394567</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.04355655283013</v>
+        <v>1.085645637232985</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4135298542011189</v>
+        <v>0.5917198652535436</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.748264698625232</v>
+        <v>2.855178705256686</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181164</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.724405743676403</v>
+        <v>-3.619183032669265</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.012821685851732</v>
+        <v>1.054910770254587</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4135298542011189</v>
+        <v>0.5917198652535436</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.751058320156713</v>
+        <v>2.857972326788167</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394723</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.718253037623619</v>
+        <v>-3.613030326616481</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.015945116664504</v>
+        <v>1.058034201067359</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4196825602539032</v>
+        <v>0.5978725713063279</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.755412292180042</v>
+        <v>2.862326298811496</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890607</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.73506233577412</v>
+        <v>-3.629839624766982</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.008301874144414</v>
+        <v>1.050390958547269</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4028732621034015</v>
+        <v>0.5810632731558263</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.744407190029851</v>
+        <v>2.851321196661306</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.672764336997998</v>
+        <v>-3.56754162599086</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.099556627451683</v>
+        <v>1.141645711854538</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4481675263778436</v>
+        <v>0.6263575374302683</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.837919302391337</v>
+        <v>2.944833309022792</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992186</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.47097413933284</v>
+        <v>-3.365751428325702</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9825647082318736</v>
+        <v>1.024653792634729</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6461857185469979</v>
+        <v>0.8243757295994227</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.759022219406956</v>
+        <v>2.865936226038412</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852419</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.521860852019035</v>
+        <v>-3.416638141011897</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.032500255479571</v>
+        <v>1.074589339882426</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5952990058608034</v>
+        <v>0.7734890169132282</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.798780424117415</v>
+        <v>2.90569443074887</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319539</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.435250109369228</v>
+        <v>-3.33002739836209</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.081772288655537</v>
+        <v>1.123861373058393</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6739247370659617</v>
+        <v>0.8521147481183865</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.860583598956554</v>
+        <v>2.967497605588009</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.495459407374512</v>
+        <v>-3.390236696367374</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.056224550278095</v>
+        <v>1.098313634680951</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6137154390606772</v>
+        <v>0.791905450113102</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.822994000978055</v>
+        <v>2.92990800760951</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397788</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.446272758690161</v>
+        <v>-3.341050047683023</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.074390827791764</v>
+        <v>1.11647991219462</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6137154390606772</v>
+        <v>0.791905450113102</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.821485619017983</v>
+        <v>2.928399625649438</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316243</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.401899627051592</v>
+        <v>-3.296676916044454</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.092002947882628</v>
+        <v>1.134092032285483</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6580885706992458</v>
+        <v>0.8362785817516706</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.847972365436561</v>
+        <v>2.954886372068016</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.424379977910477</v>
+        <v>-3.319157266903339</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.077404601677665</v>
+        <v>1.11949368608052</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6580885706992458</v>
+        <v>0.8362785817516706</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.842366159575151</v>
+        <v>2.949280166206606</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.376724247349421</v>
+        <v>-3.271501536342283</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.102848650929892</v>
+        <v>1.144937735332747</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7057443012603014</v>
+        <v>0.8839343123127262</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.877341354939589</v>
+        <v>2.984255361571044</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.276206088850667</v>
+        <v>-3.170983377843529</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.147948287704118</v>
+        <v>1.190037372106973</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.806262459759056</v>
+        <v>0.9844524708114808</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.942544623413567</v>
+        <v>3.049458630045021</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.260300759418314</v>
+        <v>-3.155078048411176</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.141065091952931</v>
+        <v>1.183154176355787</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.727149799049817</v>
+        <v>0.9053398101022418</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.881831699463896</v>
+        <v>2.98874570609535</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.215462357809916</v>
+        <v>-3.110239646802778</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.163098155206919</v>
+        <v>1.205187239609774</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7316932319946865</v>
+        <v>0.9098832430471113</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.888655461841446</v>
+        <v>2.995569468472901</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.234960814051924</v>
+        <v>-3.129738103044786</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.159459712341194</v>
+        <v>1.201548796744049</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6836085907147822</v>
+        <v>0.861798601767207</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.863965616704581</v>
+        <v>2.970879623336036</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.190757976966024</v>
+        <v>-3.085535265958886</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.183020449703391</v>
+        <v>1.225109534106247</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7278114278006826</v>
+        <v>0.9060014388531075</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.896366921483959</v>
+        <v>3.003280928115414</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.198317642803071</v>
+        <v>-3.093094931795933</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.17840658383782</v>
+        <v>1.220495668240675</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.782614831810502</v>
+        <v>0.9608048428629268</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.927658964359098</v>
+        <v>3.034572970990553</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284876</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.040026225263798</v>
+        <v>-2.93480351425666</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.292970916036569</v>
+        <v>1.335060000439424</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.782614831810502</v>
+        <v>0.9608048428629268</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.978906729542137</v>
+        <v>3.085820736173592</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.832384221629322</v>
+        <v>-2.727161510622184</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.374468422084612</v>
+        <v>1.416557506487468</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9902568354449781</v>
+        <v>1.168446846497403</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.101932636317076</v>
+        <v>3.208846642948531</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.781352128906794</v>
+        <v>-2.676129417899656</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.389829487411893</v>
+        <v>1.431918571814749</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.041288928167506</v>
+        <v>1.219478939219931</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.127500120188863</v>
+        <v>3.234414126820318</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.716127947779588</v>
+        <v>-2.61090523677245</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.433106563955481</v>
+        <v>1.475195648358336</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.106513109294712</v>
+        <v>1.284703120347136</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.183822032957892</v>
+        <v>3.290736039589346</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.678700927708455</v>
+        <v>-2.573478216701317</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.444038344283215</v>
+        <v>1.48612742868607</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.111764647323894</v>
+        <v>1.289954658376318</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.182933928074681</v>
+        <v>3.289847934706136</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.698812583743163</v>
+        <v>-2.593589872736025</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.437250474200572</v>
+        <v>1.479339558603427</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.122791992321313</v>
+        <v>1.300982003373737</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.190807127404373</v>
+        <v>3.297721134035827</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636281</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.670399320643279</v>
+        <v>-2.565176609636141</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.609173550461736</v>
+        <v>1.651262634864591</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.063816429574884</v>
+        <v>1.242006440627309</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.315979560777726</v>
+        <v>3.422893567409181</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.81322282095762</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.595617059618267</v>
+        <v>-2.490394348611129</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.759199364089558</v>
+        <v>1.801288448492413</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.138598690599897</v>
+        <v>1.316788701652321</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.480961826610551</v>
+        <v>3.587875833242006</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.569532975354459</v>
+        <v>-2.464310264347321</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.76134097380894</v>
+        <v>1.803430058211795</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.138598690599897</v>
+        <v>1.316788701652321</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.47266980262441</v>
+        <v>3.579583809255865</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.481655062245338</v>
+        <v>-2.3764323512382</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.794685334636368</v>
+        <v>1.836774419039223</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.254524333023248</v>
+        <v>1.432714344075672</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.5404183836622</v>
+        <v>3.647332390293655</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.472762600852055</v>
+        <v>-2.367539889844917</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.815796724920473</v>
+        <v>1.857885809323328</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.254524333023248</v>
+        <v>1.432714344075672</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.557972789388991</v>
+        <v>3.664886796020446</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.641238717821933</v>
+        <v>-2.536016006814795</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.740261325537106</v>
+        <v>1.782350409939961</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.226576497306667</v>
+        <v>1.404766508359091</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.533059135363627</v>
+        <v>3.639973141995082</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.194982525192493</v>
+        <v>-2.089759814185355</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.900033499776743</v>
+        <v>1.942122584179598</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.131857827637034</v>
+        <v>1.310047838689459</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.457497630749709</v>
+        <v>3.564411637381164</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.17226142150934</v>
+        <v>-2.067038710502202</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.899785963746909</v>
+        <v>1.941875048149764</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.131857827637034</v>
+        <v>1.310047838689459</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.448161653246614</v>
+        <v>3.555075659878068</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.301463234803383</v>
+        <v>-2.196240523796245</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.007011364280461</v>
+        <v>2.049100448683316</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.002656014342992</v>
+        <v>1.180846025395416</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.529546691121357</v>
+        <v>3.636460697752812</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.327337633277408</v>
+        <v>-2.22211492227027</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.033739427384497</v>
+        <v>2.075828511787353</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.047567623054733</v>
+        <v>1.225757634107158</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.593571478842049</v>
+        <v>3.700485485473503</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.320282943062235</v>
+        <v>-2.215060232055097</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.033236659460112</v>
+        <v>2.075325743862967</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.054622313269907</v>
+        <v>1.232812324322331</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.594479648960698</v>
+        <v>3.701393655592153</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.293331718735747</v>
+        <v>-2.188109007728609</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.054023302835449</v>
+        <v>2.096112387238304</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.069502659297626</v>
+        <v>1.247692670350051</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.613414010222071</v>
+        <v>3.720328016853526</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.314875946566534</v>
+        <v>-2.209653235559396</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.229508743848093</v>
+        <v>2.271597828250949</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.069502659297626</v>
+        <v>1.247692670350051</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.797517142367031</v>
+        <v>3.904431148998486</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.74392550571442</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.337284064371406</v>
+        <v>-2.232061353364268</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.212662191629138</v>
+        <v>2.254751276031993</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.069502659297626</v>
+        <v>1.247692670350051</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.789633837270024</v>
+        <v>3.896547843901479</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.365508299949006</v>
+        <v>-2.260285588941868</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.203426496947735</v>
+        <v>2.24551558135059</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.087479411748935</v>
+        <v>1.265669422801359</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.802473888290447</v>
+        <v>3.909387894921901</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161971</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.374949225837536</v>
+        <v>-2.269726514830398</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.25590384431417</v>
+        <v>2.297992928717025</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.209906529292326</v>
+        <v>1.388096540344751</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.932183876538328</v>
+        <v>4.039097883169783</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321628</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.46382585700601</v>
+        <v>-2.358603145998872</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.223244286392082</v>
+        <v>2.265333370794937</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.121029898123852</v>
+        <v>1.299219909176277</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.881748992382545</v>
+        <v>3.988662999014</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.540155834606916</v>
+        <v>-2.434933123599778</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.190824108245494</v>
+        <v>2.23291319264835</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.121029898123852</v>
+        <v>1.299219909176277</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.87986080527632</v>
+        <v>3.986774811907775</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.633819779284457</v>
+        <v>-2.528597068277319</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.14817875997734</v>
+        <v>2.190267844380196</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.027365953446311</v>
+        <v>1.205555964498735</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.818482668072658</v>
+        <v>3.925396674704112</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.795388204811712</v>
+        <v>-2.690165493804574</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.08198539997659</v>
+        <v>2.124074484379446</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9005830296484315</v>
+        <v>1.078773040700856</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.740846924004082</v>
+        <v>3.847760930635537</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.903688866681832</v>
+        <v>-2.798466155674694</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.051738542094461</v>
+        <v>2.093827626497316</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9005830296484315</v>
+        <v>1.078773040700856</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.753920330870001</v>
+        <v>3.860834337501456</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.921492838402576</v>
+        <v>-2.816270127395438</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.036622150189103</v>
+        <v>2.078711234591959</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8300484067432303</v>
+        <v>1.008238417795655</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.70360475390982</v>
+        <v>3.810518760541275</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.949393625512049</v>
+        <v>-2.844170914504911</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.023985876472317</v>
+        <v>2.066074960875172</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7954514826002955</v>
+        <v>0.9736414936527201</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.681370640551061</v>
+        <v>3.788284647182516</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.071919728214943</v>
+        <v>-2.966697017207805</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.971739879368358</v>
+        <v>2.013828963771213</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6729253798974016</v>
+        <v>0.8511153909498262</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.604619422906524</v>
+        <v>3.711533429537979</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.302434224400532</v>
+        <v>-3.197211513393394</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.946240040484626</v>
+        <v>1.988329124887481</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4424108837118129</v>
+        <v>0.6206008947642375</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.533016684785674</v>
+        <v>3.639930691417129</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.651179309624975</v>
+        <v>-3.545956598617837</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.947053725396695</v>
+        <v>1.98914280979955</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3336629297929151</v>
+        <v>0.5118529408453397</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.608079631436183</v>
+        <v>3.714993638067638</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.805165727401116</v>
+        <v>-3.699943016393978</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.954439427431879</v>
+        <v>1.996528511834734</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3336629297929151</v>
+        <v>0.5118529408453397</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.677059900581823</v>
+        <v>3.783973907213277</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.009765162264125</v>
+        <v>-3.904542451256987</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.858650855606796</v>
+        <v>1.900739940009652</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3336629297929151</v>
+        <v>0.5118529408453397</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.663111102701944</v>
+        <v>3.770025109333398</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.262240316271849</v>
+        <v>-4.157017605264711</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.769531283059121</v>
+        <v>1.811620367461976</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3336629297929151</v>
+        <v>0.5118529408453397</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.674981591757358</v>
+        <v>3.781895598388812</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.555136072751261</v>
+        <v>-4.449913361744123</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.653583514986299</v>
+        <v>1.695672599389155</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3336629297929151</v>
+        <v>0.5118529408453397</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.676192126276301</v>
+        <v>3.783106132907756</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.741800200886069</v>
+        <v>-4.636577489878931</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.583039605959698</v>
+        <v>1.625128690362553</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3069239589683552</v>
+        <v>0.4851139700207798</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.664270486008887</v>
+        <v>3.771184492640341</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.887820887800031</v>
+        <v>-4.782598176792893</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.519709183930302</v>
+        <v>1.561798268333157</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2978408671744983</v>
+        <v>0.4760308782269229</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.653898483668762</v>
+        <v>3.760812490300217</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830324</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.979534896909616</v>
+        <v>-4.874312185902479</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.645227636985513</v>
+        <v>1.687316721388367</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2978408671744983</v>
+        <v>0.4760308782269229</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.816102540367806</v>
+        <v>3.923016546999261</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.011186555969585</v>
+        <v>-4.905963844962448</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.627413611325339</v>
+        <v>1.669502695728194</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2926724099300581</v>
+        <v>0.4708624209824827</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.807848103984956</v>
+        <v>3.914762110616411</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.093121374238469</v>
+        <v>-4.987898663231332</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.604869101586277</v>
+        <v>1.646958185989132</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2827376643429779</v>
+        <v>0.4609276753954025</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.812116674201199</v>
+        <v>3.919030680832654</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.195097496486876</v>
+        <v>-5.089874785479739</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.573004291142816</v>
+        <v>1.615093375545671</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1807615420945703</v>
+        <v>0.3589515531469949</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.759856639308057</v>
+        <v>3.866770645939512</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231803</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.085091213009655</v>
+        <v>-4.979868502002518</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.60915969177788</v>
+        <v>1.651248776180735</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2039661140118455</v>
+        <v>0.3821561250642701</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.765932269702597</v>
+        <v>3.872846276334052</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.942031637268729</v>
+        <v>-4.836808926261591</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.670633532796225</v>
+        <v>1.71272261719908</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2119795406018248</v>
+        <v>0.3901695516542494</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.77499033637856</v>
+        <v>3.881904343010014</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.640584911796891</v>
+        <v>-4.535362200789754</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.798473105867496</v>
+        <v>1.840562190270351</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.513426266073662</v>
+        <v>0.6916162771260866</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.963119254544198</v>
+        <v>4.070033261175652</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.665175156032075</v>
+        <v>-4.559952445024938</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.789608185926133</v>
+        <v>1.831697270328988</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.513426266073662</v>
+        <v>0.6916162771260866</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.964090432296908</v>
+        <v>4.071004438928363</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.614136780025555</v>
+        <v>-4.508914069018418</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.810866440708497</v>
+        <v>1.852955525111351</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.513426266073662</v>
+        <v>0.6916162771260866</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.964933336676664</v>
+        <v>4.071847343308119</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.572997485158924</v>
+        <v>-4.467774774151787</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.846360257529294</v>
+        <v>1.888449341932149</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5545655609402929</v>
+        <v>0.7327555719927175</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.008655012470788</v>
+        <v>4.115569019102242</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.476362573140284</v>
+        <v>-4.371139862133147</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.701198218460685</v>
+        <v>1.74328730286354</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6512004729589328</v>
+        <v>0.8293904840113574</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.882819955805906</v>
+        <v>3.989733962437361</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.606943307671126</v>
+        <v>-4.501720596663989</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.652467968722312</v>
+        <v>1.694557053125167</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5206197384280903</v>
+        <v>0.6988097494805149</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.807973559161365</v>
+        <v>3.91488756579282</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.442446973480164</v>
+        <v>-4.337224262473027</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.702693321474779</v>
+        <v>1.744782405877634</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6851160726190522</v>
+        <v>0.8633060836714768</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.891098178752025</v>
+        <v>3.998012185383479</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.365348371938292</v>
+        <v>-4.260125660931155</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.732720472527958</v>
+        <v>1.774809556930813</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6851160726190522</v>
+        <v>0.8633060836714768</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.890285889188454</v>
+        <v>3.997199895819909</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.375733566828181</v>
+        <v>-4.270510855821044</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.738435173697075</v>
+        <v>1.78052425809993</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6747308777291628</v>
+        <v>0.8529208887815874</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.893923551379593</v>
+        <v>4.000837558011048</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.281341537914481</v>
+        <v>-4.289099014543269</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.84702899103898</v>
+        <v>1.843926000387465</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.769122906642863</v>
+        <v>0.8343327300593621</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.021395774504239</v>
+        <v>4.060521668554138</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.281640084610517</v>
+        <v>-4.289397561239305</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.843778583178864</v>
+        <v>1.840675592527349</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.7688243599468271</v>
+        <v>0.8340341833633262</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.018085657304916</v>
+        <v>4.057211551354815</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.179753222370699</v>
+        <v>-4.188574427548877</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.889064223014183</v>
+        <v>1.885535740942911</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8389188114023837</v>
+        <v>0.8464983988476801</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.064673223117641</v>
+        <v>4.069220975584819</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-3.988971861618292</v>
+        <v>-3.99779306679647</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.965506020793689</v>
+        <v>1.961977538722418</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.029700172154791</v>
+        <v>1.037279759600088</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.179271293047629</v>
+        <v>4.183819045514807</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.88200850376887</v>
+        <v>-3.890829708947048</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.988128209671054</v>
+        <v>1.984599727599783</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.088164780114592</v>
+        <v>1.095744367559889</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.194186903561106</v>
+        <v>4.198734656028284</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.826677915867108</v>
+        <v>-3.835499121045286</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.045227381443818</v>
+        <v>2.041698899372546</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.143495368016354</v>
+        <v>1.151074955461651</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.262352192914221</v>
+        <v>4.266899945381399</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.814623788954145</v>
+        <v>-3.823444994132323</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.04373560011044</v>
+        <v>2.040207118039169</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.155549494929317</v>
+        <v>1.163129082374614</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.263271236963437</v>
+        <v>4.267818989430615</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.855778908522366</v>
+        <v>-3.864600113700544</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.029154182467288</v>
+        <v>2.025625700396017</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.114394375361096</v>
+        <v>1.121973962806393</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.24045879540664</v>
+        <v>4.245006547873818</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.787730345830836</v>
+        <v>-3.796551551009014</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.069224633421782</v>
+        <v>2.065696151350511</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.182442938052626</v>
+        <v>1.190022525497923</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.294138958899441</v>
+        <v>4.298686711366619</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.019330739000337</v>
+        <v>-4.028151944178515</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.996787146327576</v>
+        <v>1.993258664256305</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.182442938052626</v>
+        <v>1.190022525497923</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.314341629073035</v>
+        <v>4.318889381540213</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.069382284529556</v>
+        <v>-4.078203489707734</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.96037276418277</v>
+        <v>1.956844282111499</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.182442938052626</v>
+        <v>1.190022525497923</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.297947865139917</v>
+        <v>4.302495617607095</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800095</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.244489117106001</v>
+        <v>-4.253310322284179</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.850581944745659</v>
+        <v>1.847053462674388</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.182442938052626</v>
+        <v>1.190022525497923</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.258199778733384</v>
+        <v>4.262747531200562</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660847</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.048388963675478</v>
+        <v>-4.057210168853656</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.936044625114808</v>
+        <v>1.932516143043537</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.378543091483149</v>
+        <v>1.386122678928446</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.382882489788638</v>
+        <v>4.387430242255816</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395084</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.895363571562194</v>
+        <v>-3.904184776740372</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.096425781533026</v>
+        <v>2.092897299461755</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.531568483596433</v>
+        <v>1.53914807104173</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.573868724629512</v>
+        <v>4.57841647709669</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791146</v>
+        <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.923670885435464</v>
+        <v>-3.932492090613642</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.272569080892011</v>
+        <v>2.26904059882074</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.531568483596433</v>
+        <v>1.53914807104173</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.761334949537805</v>
+        <v>4.765882702004983</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620432</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.090264110548986</v>
+        <v>-4.099085315727164</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.175334742200685</v>
+        <v>2.171806260129414</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.364975258482911</v>
+        <v>1.372554845928207</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.630781965823774</v>
+        <v>4.635329718290952</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.06722831718742</v>
+        <v>-4.076049522365598</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.188225462207029</v>
+        <v>2.184696980135758</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.364975258482911</v>
+        <v>1.372554845928207</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.634458368485491</v>
+        <v>4.639006120952669</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399466</v>
+        <v>3.740581401399468</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.037982336731724</v>
+        <v>-4.046803541909902</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.197541909512803</v>
+        <v>2.194013427441531</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.364975258482911</v>
+        <v>1.372554845928207</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.632076423608987</v>
+        <v>4.636624176076165</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.144907884609575</v>
+        <v>-4.153729089787753</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.152064929519297</v>
+        <v>2.148536447448026</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.258049710605059</v>
+        <v>1.265629298050356</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.565214334039911</v>
+        <v>4.569762086507089</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.289926443116824</v>
+        <v>-4.298747648295001</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.095486308259632</v>
+        <v>2.091957826188361</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.113031152097811</v>
+        <v>1.120610739543108</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.479632001078796</v>
+        <v>4.484179753545974</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.408268208901541</v>
+        <v>-4.417089414079719</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.148080841203498</v>
+        <v>2.144552359132227</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.123717190660701</v>
+        <v>1.131296778105998</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.585974863474283</v>
+        <v>4.590522615941461</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790801</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.459678631222249</v>
+        <v>-4.468499836400427</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.125302369401154</v>
+        <v>2.121773887329883</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.123717190660701</v>
+        <v>1.131296778105998</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.583760560600222</v>
+        <v>4.5883083130674</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.539098082430001</v>
+        <v>-4.547919287608178</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.093437716992343</v>
+        <v>2.089909234921072</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.123717190660701</v>
+        <v>1.131296778105998</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.583663688674512</v>
+        <v>4.58821144114169</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.634561080347218</v>
+        <v>-4.643382285525396</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.055246411383498</v>
+        <v>2.051717929312227</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.123717190660701</v>
+        <v>1.131296778105998</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.583657582232554</v>
+        <v>4.588205334699732</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217997</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.570185169496503</v>
+        <v>-4.579006374674681</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.079093172286395</v>
+        <v>2.075564690215124</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.188093101511416</v>
+        <v>1.195672688956713</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.620379525305594</v>
+        <v>4.624927277772772</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.625554331628697</v>
+        <v>-4.634375536806875</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.062679325181244</v>
+        <v>2.059150843109973</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.188093101511416</v>
+        <v>1.195672688956713</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.626113343053321</v>
+        <v>4.630661095520499</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113276</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.670992111459524</v>
+        <v>-4.679813316637702</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.044042576591846</v>
+        <v>2.040514094520574</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.145248110833257</v>
+        <v>1.152827698278553</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.599944711989358</v>
+        <v>4.604492464456536</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.582785277311946</v>
+        <v>-4.591606482490124</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.099199703101196</v>
+        <v>2.095671221029924</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.145248110833257</v>
+        <v>1.152827698278553</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.619819104839676</v>
+        <v>4.624366857306854</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016436</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.476750282106637</v>
+        <v>-4.485571487284814</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.125314401708047</v>
+        <v>2.121785919636776</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.145248110833257</v>
+        <v>1.152827698278553</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.603519805364404</v>
+        <v>4.608067557831582</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307668</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.293538618973542</v>
+        <v>-4.302359824151719</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.201030016425331</v>
+        <v>2.19750153435406</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.145248110833257</v>
+        <v>1.152827698278553</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.60595075482845</v>
+        <v>4.610498507295627</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863549</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.221817171959691</v>
+        <v>-4.230638377137868</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.195509781078761</v>
+        <v>2.19198129900749</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.216969557847107</v>
+        <v>1.224549145292404</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.61477480888465</v>
+        <v>4.619322561351828</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.199444146351984</v>
+        <v>-4.208265351530162</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.151374737243015</v>
+        <v>2.147846255171744</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.228225308960009</v>
+        <v>1.235804896405305</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.568444005473562</v>
+        <v>4.57299175794074</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.232460442262729</v>
+        <v>-4.241281647440907</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.323366423764072</v>
+        <v>2.319837941692801</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.158787932293257</v>
+        <v>1.166367519738554</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.711979784358866</v>
+        <v>4.716527536826044</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.220932806613121</v>
+        <v>-4.229754011791298</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.319898703852165</v>
+        <v>2.316370221780894</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.21778859049462</v>
+        <v>1.225368177939916</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.739301405107933</v>
+        <v>4.743849157575111</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236293</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.318274307955489</v>
+        <v>-4.327095513133667</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.284630215837006</v>
+        <v>2.281101733765735</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.173368408329131</v>
+        <v>1.180947995774428</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.716317408330429</v>
+        <v>4.720865160797606</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427679</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.404130337295456</v>
+        <v>-4.412951542473634</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.251538886293857</v>
+        <v>2.248010404222586</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.130992339102996</v>
+        <v>1.138571926548293</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.692142848987586</v>
+        <v>4.696690601454764</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610378</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.412967134711575</v>
+        <v>-4.421788339889753</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.230423369147911</v>
+        <v>2.22689488707664</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.123550166461646</v>
+        <v>1.131129753906942</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.670096747223277</v>
+        <v>4.674644499690455</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667452</v>
+        <v>3.715544411667451</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.504349697277034</v>
+        <v>-4.513170902455212</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.204034855166777</v>
+        <v>2.200506373095506</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.086985281742301</v>
+        <v>1.094564869187598</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.65832232743672</v>
+        <v>4.662870079903898</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889186</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.492642979290028</v>
+        <v>-4.501464184468206</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.310845800185847</v>
+        <v>2.307317318114576</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.098691999729307</v>
+        <v>1.106271587174604</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.767474616053191</v>
+        <v>4.772022368520369</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409563</v>
+        <v>3.682476099409562</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.392979475206365</v>
+        <v>-4.401800680384543</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.353743540550717</v>
+        <v>2.350215058479446</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.161879082932994</v>
+        <v>1.169458670378291</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.808419204706808</v>
+        <v>4.812966957173986</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452568</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.403295573372717</v>
+        <v>-4.412116778550895</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.562521934562234</v>
+        <v>2.558993452490963</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.161879082932994</v>
+        <v>1.169458670378291</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.021324037984866</v>
+        <v>5.025871790452044</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.403201605355345</v>
+        <v>-4.412022810533522</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.561738188681273</v>
+        <v>2.558209706610002</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.162248944280312</v>
+        <v>1.169828531725609</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.020724621705346</v>
+        <v>5.025272374172524</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.410420429555189</v>
+        <v>-4.419241634733367</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.553082644945689</v>
+        <v>2.549554162874418</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.162248944280312</v>
+        <v>1.169828531725609</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.0149566076497</v>
+        <v>5.019504360116878</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740919</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.40947200643715</v>
+        <v>-4.418293211615328</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.553462014192904</v>
+        <v>2.549933532121633</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.162248944280312</v>
+        <v>1.169828531725609</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.0149566076497</v>
+        <v>5.019504360116878</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663622</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.566540464692775</v>
+        <v>-4.575361669870952</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.503362238871747</v>
+        <v>2.499833756800476</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.162248944280312</v>
+        <v>1.169828531725609</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.027684215630792</v>
+        <v>5.03223196809797</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424766</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.560548217903963</v>
+        <v>-4.569369423082141</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.507705136011659</v>
+        <v>2.504176653940388</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.162248944280312</v>
+        <v>1.169828531725609</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.02963021405518</v>
+        <v>5.034177966522358</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149214</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.471990256773196</v>
+        <v>-4.480811461951373</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.536782456481735</v>
+        <v>2.533253974410464</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.162248944280312</v>
+        <v>1.169828531725609</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.023284350072949</v>
+        <v>5.027832102540127</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383087</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.454231179270121</v>
+        <v>-4.463052384448299</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.54319476492196</v>
+        <v>2.539666282850689</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.162248944280312</v>
+        <v>1.169828531725609</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.022593027511944</v>
+        <v>5.027140779979122</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.354601028221054</v>
+        <v>-4.363422233399231</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.595829011250174</v>
+        <v>2.592300529178903</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.261879095329379</v>
+        <v>1.269458682774676</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.095153304049972</v>
+        <v>5.09970105651715</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455267</v>
+        <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.404000536910065</v>
+        <v>-4.412821742088243</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.765223473273296</v>
+        <v>2.761694991202025</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.272137928761124</v>
+        <v>1.279717516206421</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.290462869607745</v>
+        <v>5.295010622074923</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963133</v>
+        <v>3.749078058963135</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.197316063267689</v>
+        <v>-4.346330955687042</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.835085935833109</v>
+        <v>2.775479978865367</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.4788224024035</v>
+        <v>1.346208302607621</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.401662226896033</v>
+        <v>5.322093767018505</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.912803970438472</v>
+        <v>3.896869551899808</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.667099457637297</v>
+        <v>4.747388673340937</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.197316063267689</v>
+        <v>-4.346330955687042</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.835085935833109</v>
+        <v>2.775479978865367</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.4788224024035</v>
+        <v>1.346208302607621</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.660163254623665</v>
+        <v>4.740452470327305</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240916.xlsx
+++ b/tame_output/ON/bt/strategyON_20240916.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>48.3%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>83.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>163.1%</t>
+          <t>133.4%</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>106.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.2%</t>
+          <t>422.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-596.2%</t>
+          <t>-596.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>121.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-98.7%</t>
+          <t>-105.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-63.5%</t>
+          <t>-131.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.6%</t>
+          <t>-327.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-89.4%</t>
+          <t>-65.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>118.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,37 +1466,37 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>93.9%</t>
         </is>
       </c>
     </row>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.754268442644352</v>
+        <v>-6.879339216277861</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4129144574668953</v>
+        <v>0.3628861480134917</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.8103298254957174</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.802471259886696</v>
+        <v>-6.927542033520205</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3920382506249589</v>
+        <v>0.3420099411715549</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.8103298254957174</v>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.969279919861058</v>
+        <v>-7.098474522802566</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.3290937625644221</v>
+        <v>0.2774159213878189</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.852613149208854</v>
+        <v>-0.8720297019147221</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.605594265297281</v>
+        <v>2.59394433367376</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.155999628170361</v>
+        <v>-7.285194231111869</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2503795747062978</v>
+        <v>0.1987017335296946</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.852613149208854</v>
+        <v>-0.8720297019147221</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.601567960762878</v>
+        <v>2.589918029139357</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.539001016912992</v>
+        <v>-7.6681956198545</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.09707691788766137</v>
+        <v>0.04539907671105814</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.852613149208854</v>
+        <v>-0.8720297019147221</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.601465859441294</v>
+        <v>2.589815927817773</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.54348746211438</v>
+        <v>-7.672682065055889</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.09785385577853623</v>
+        <v>0.04617601460193255</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8570995944102426</v>
+        <v>-0.8765161471161107</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.601345508291891</v>
+        <v>2.58969557666837</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.903017784618382</v>
+        <v>-8.032212387559891</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.04060796992501459</v>
+        <v>-0.09228581110161782</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8570995944102426</v>
+        <v>-0.8765161471161107</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.606695811589941</v>
+        <v>2.59504587996642</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.953366848072604</v>
+        <v>-8.082561451014113</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.05283157534952565</v>
+        <v>-0.1045094165261289</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.9074486578644647</v>
+        <v>-0.9268652105703328</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.584402393474585</v>
+        <v>2.572752461851064</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.050986125493999</v>
+        <v>-8.180180728435509</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.08883753569631514</v>
+        <v>-0.1405153768729188</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.005067935285861</v>
+        <v>-1.024484487991729</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.528872577643516</v>
+        <v>2.517222646019995</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.105057625002358</v>
+        <v>-8.234252227943868</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1075725791780866</v>
+        <v>-0.1592504203546898</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.059139434794221</v>
+        <v>-1.078555987500089</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.499323234260073</v>
+        <v>2.487673302636551</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.108633411094106</v>
+        <v>-8.237828014035616</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1034896964961431</v>
+        <v>-0.1551675376727468</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.084668356710713</v>
+        <v>-1.104084909416582</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.489519078228819</v>
+        <v>2.477869146605298</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.142286249602579</v>
+        <v>-8.271480852544089</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1124682774150965</v>
+        <v>-0.1641461185917001</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.185081724627751</v>
+        <v>-1.204498277333619</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.433753611963033</v>
+        <v>2.422103680339512</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.281372364221436</v>
+        <v>-8.410566967162946</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1527310217692186</v>
+        <v>-0.2044088629458218</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.324167839246607</v>
+        <v>-1.343584391952476</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.36567364468514</v>
+        <v>2.354023713061619</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.45649678160798</v>
+        <v>-8.58569138454949</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.208225567976319</v>
+        <v>-0.2599034091529222</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.51870880933902</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.275154215000731</v>
+        <v>2.263504283377209</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.690948875622469</v>
+        <v>-8.820143478563979</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.309225570483711</v>
+        <v>-0.3609034116603143</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.51870880933902</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.267935050099135</v>
+        <v>2.256285118475613</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.795323606648916</v>
+        <v>-8.924518209590426</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3576476536682658</v>
+        <v>-0.409325494844869</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.603666987659597</v>
+        <v>-1.623083540365465</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.198638020709291</v>
+        <v>2.18698808908577</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.9578370723475</v>
+        <v>-9.08703167528901</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.421537250109143</v>
+        <v>-0.4732150912857462</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.701300418078284</v>
+        <v>-1.720716970784152</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.141173752296635</v>
+        <v>2.129523820673114</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.083873865715789</v>
+        <v>-9.213068468657299</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4692582388273441</v>
+        <v>-0.5209360800039473</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.69546534797441</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.159018454611595</v>
+        <v>2.147368522988074</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.026802093819859</v>
+        <v>-9.155996696761369</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4424391943825707</v>
+        <v>-0.4941170355591744</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.69546534797441</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.163008790297996</v>
+        <v>2.151358858674475</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.168473935543979</v>
+        <v>-9.297668538485489</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5005831579709605</v>
+        <v>-0.5522609991475642</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.69546534797441</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.161533563399254</v>
+        <v>2.149883631775733</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.118883091119145</v>
+        <v>-9.248077694060655</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.4656934100361547</v>
+        <v>-0.517371251212758</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.626457950843708</v>
+        <v>-1.645874503549576</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.206341480219027</v>
+        <v>2.194691548595506</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.969964756647288</v>
+        <v>-9.099159359588798</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4191772098940949</v>
+        <v>-0.4708550510706986</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.595208360108535</v>
+        <v>-1.614624912814403</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.212040101013448</v>
+        <v>2.200390169389927</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.744119603927876</v>
+        <v>-8.873314206869388</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3192600757701216</v>
+        <v>-0.3709379169467257</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.572698237227239</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.246775179401955</v>
+        <v>2.235125247778434</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.619540947590284</v>
+        <v>-8.748735550531796</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.268289468679026</v>
+        <v>-0.3199673098556302</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.572698237227239</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.247914323958013</v>
+        <v>2.236264392334493</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.594504266021774</v>
+        <v>-8.723698868963286</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2556410218895144</v>
+        <v>-0.3073188630661186</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.547369149676503</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.265745550650562</v>
+        <v>2.254095619027042</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.522371090733893</v>
+        <v>-8.651565693675405</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2210540475357252</v>
+        <v>-0.2727318887123293</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.547369149676503</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.271479254889199</v>
+        <v>2.259829323265678</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.451004698124246</v>
+        <v>-8.580199301065758</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2022447528857318</v>
+        <v>-0.2539225940623355</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.456586204360987</v>
+        <v>-1.476002757066855</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.304561828061122</v>
+        <v>2.292911896437602</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.357545664139021</v>
+        <v>-8.486740267080533</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.1747446206045495</v>
+        <v>-0.2264224617811537</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.456586204360987</v>
+        <v>-1.476002757066855</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.294678346748215</v>
+        <v>2.283028415124694</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.34689248258559</v>
+        <v>-8.476087085527102</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1723179084825506</v>
+        <v>-0.2239957496591547</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.456586204360987</v>
+        <v>-1.476002757066855</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.292843786248842</v>
+        <v>2.28119385462532</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.248985443909099</v>
+        <v>-8.378180046850611</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1334554079854153</v>
+        <v>-0.185133249162019</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.388600454500431</v>
+        <v>-1.408017007206299</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.333334921191714</v>
+        <v>2.321684989568193</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.225031902933141</v>
+        <v>-8.354226505874653</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1232054854495384</v>
+        <v>-0.1748833266261425</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.364646913524473</v>
+        <v>-1.384063466230341</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.348375551922782</v>
+        <v>2.336725620299262</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.960971964610345</v>
+        <v>-8.090166567551856</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.03084182628217214</v>
+        <v>-0.08251966745877581</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.100586975201677</v>
+        <v>-1.120003527907545</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.493551198754708</v>
+        <v>2.481901267131187</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.253892341105507</v>
+        <v>-7.519722381511008</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2492029894594623</v>
+        <v>0.1428709732972626</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.100586975201677</v>
+        <v>-1.120003527907545</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.490764165094407</v>
+        <v>2.479114233470886</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.213708042739317</v>
+        <v>-7.479538083144818</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2656203326937798</v>
+        <v>0.1592883165315802</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.060402676835486</v>
+        <v>-1.079819229541354</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.515218368001963</v>
+        <v>2.503568436378442</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.050308171799954</v>
+        <v>-7.316138212205455</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3303471022902817</v>
+        <v>0.2240150861280821</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8970028058961237</v>
+        <v>-0.916419358601992</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.612625111786337</v>
+        <v>2.600975180162817</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.816826949570356</v>
+        <v>-7.082656989975857</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4316640200199737</v>
+        <v>0.3253320038577736</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6635215836665251</v>
+        <v>-0.6829381363723934</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.760638273961949</v>
+        <v>2.748988342338428</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.66716055856284</v>
+        <v>-6.932990598968342</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4886383661100204</v>
+        <v>0.3823063499478208</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5706180924239892</v>
+        <v>-0.5900346451298575</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.813488158394511</v>
+        <v>2.80183822677099</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.534885084931954</v>
+        <v>-6.800715125337455</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4428093415695296</v>
+        <v>0.3364773254073299</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4383426187931025</v>
+        <v>-0.4577591714989708</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.794114228580198</v>
+        <v>2.782464296956677</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.363023869367051</v>
+        <v>-6.628853909772553</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5143688884831272</v>
+        <v>0.4080368723209276</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.2664814032281997</v>
+        <v>-0.285897955934068</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.900046018606776</v>
+        <v>2.888396086983255</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.278059202637731</v>
+        <v>-6.543889243043234</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5612610963985141</v>
+        <v>0.454929080236314</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1815167364988801</v>
+        <v>-0.2009332892047484</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.963931159868027</v>
+        <v>2.952281228244506</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.383649192410836</v>
+        <v>-6.649479232816338</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3910491708900539</v>
+        <v>0.2847171547278533</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2871067262719845</v>
+        <v>-0.3065232789778528</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.772601236404946</v>
+        <v>2.760951304781425</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.315414607785408</v>
+        <v>-6.581244648190911</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4668873466173111</v>
+        <v>0.360555330455111</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2686914033994485</v>
+        <v>-0.2881079561053168</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.832194772005554</v>
+        <v>2.820544840382033</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.167474566377809</v>
+        <v>-6.433304606783311</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4094425545419438</v>
+        <v>0.3031105383797437</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2483704874908909</v>
+        <v>-0.2677870401967592</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.727766512912281</v>
+        <v>2.71611658128876</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.11450504412382</v>
+        <v>-6.380335084529323</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4219163771900609</v>
+        <v>0.3155843610278608</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.2148175179427703</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.750834240011196</v>
+        <v>2.739184308387675</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.94871684816353</v>
+        <v>-6.214546888569032</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4812710434790843</v>
+        <v>0.3749390273168838</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.2148175179427703</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.743873627916103</v>
+        <v>2.732223696292582</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.915353641684761</v>
+        <v>-6.181183682090263</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5090786804517347</v>
+        <v>0.4027466642895345</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.2148175179427703</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.758335982297246</v>
+        <v>2.746686050673725</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.807094504562239</v>
+        <v>-6.072924544967742</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5469144557599384</v>
+        <v>0.4405824395977382</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.2148175179427703</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.752868102756441</v>
+        <v>2.74121817113292</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.683803369745108</v>
+        <v>-5.949633410150611</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5937290036973675</v>
+        <v>0.4873969875351674</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.07210983041977154</v>
+        <v>-0.09152638312563982</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.824340877657296</v>
+        <v>2.812690946033775</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.631106502613817</v>
+        <v>-5.896936543019319</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6225087287872095</v>
+        <v>0.516176712625009</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.01941296328848036</v>
+        <v>-0.03882951599434864</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.863659976173396</v>
+        <v>2.852010044549875</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.387341060630373</v>
+        <v>-5.653171101035875</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7157956139276376</v>
+        <v>0.6094635977654375</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.01941296328848036</v>
+        <v>-0.03882951599434864</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.859440684520447</v>
+        <v>2.847790752896926</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.297565388253901</v>
+        <v>-5.563395428659403</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7538301967982428</v>
+        <v>0.6474981806360423</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.04218648162582966</v>
+        <v>0.02276992891996138</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.898524665389049</v>
+        <v>2.886874733765528</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.047714994304826</v>
+        <v>-5.313545034710328</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8465124293615744</v>
+        <v>0.7401804131993743</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.04218648162582966</v>
+        <v>0.02276992891996138</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.891266740372751</v>
+        <v>2.87961680874923</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.871822901837394</v>
+        <v>-5.137652942242896</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9204683898691961</v>
+        <v>0.814136373706996</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.04218648162582966</v>
+        <v>0.02276992891996138</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.8948658638934</v>
+        <v>2.883215932269879</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.700376438814931</v>
+        <v>-4.966206479220433</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.002374481132735</v>
+        <v>0.896042464970535</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2136329446482928</v>
+        <v>0.1942163919424245</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.011061247761432</v>
+        <v>2.99941131613791</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.62035415170581</v>
+        <v>-4.886184192111312</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.033403873592681</v>
+        <v>0.9270718574304804</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2936552317574138</v>
+        <v>0.2742386790515455</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.058095097643201</v>
+        <v>3.04644516601968</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.556718409471875</v>
+        <v>-4.822548449877377</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.063552971540572</v>
+        <v>0.9572209553783715</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3572909739913483</v>
+        <v>0.33787442128548</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.100971344037879</v>
+        <v>3.089321412414358</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.46302109125548</v>
+        <v>-4.728851131660982</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.082226157610925</v>
+        <v>0.9758941414487252</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3572909739913483</v>
+        <v>0.33787442128548</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.082165602821675</v>
+        <v>3.070515671198153</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.473523714320769</v>
+        <v>-4.739353754726271</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.079768185009687</v>
+        <v>0.9734361688474871</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3467883509260594</v>
+        <v>0.3273717982201911</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.077607105607379</v>
+        <v>3.065957173983858</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.361037453651894</v>
+        <v>-4.626867494057397</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.128692003112057</v>
+        <v>1.022359986949857</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3467883509260594</v>
+        <v>0.3273717982201911</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.081536419442199</v>
+        <v>3.069886487818678</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.257872326099297</v>
+        <v>-4.534138930873835</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.170636638050436</v>
+        <v>1.060129996140621</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3733088004030911</v>
+        <v>0.3472359642104752</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.098127273045758</v>
+        <v>3.082483571330188</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.134398054786279</v>
+        <v>-4.410664659560817</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.217024417795637</v>
+        <v>1.106517775885822</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3733088004030911</v>
+        <v>0.3472359642104752</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.095125344265751</v>
+        <v>3.079481642550182</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.914377256749268</v>
+        <v>-4.190643861523807</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.306611774021055</v>
+        <v>1.196105132111241</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5145286454710714</v>
+        <v>0.4884558092784554</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.181436288317154</v>
+        <v>3.165792586601584</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539946</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.78150956768599</v>
+        <v>-4.057776172460529</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.37565303244819</v>
+        <v>1.265146390538375</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5145286454710714</v>
+        <v>0.4884558092784554</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.197330471118977</v>
+        <v>3.181686769403407</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496257</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.661336484321491</v>
+        <v>-3.93760308909603</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.424868110234291</v>
+        <v>1.314361468324476</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6347017288355703</v>
+        <v>0.6086288926429544</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.270580165577978</v>
+        <v>3.254936463862409</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.526083122991514</v>
+        <v>-3.802349727766053</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.489057557327722</v>
+        <v>1.378550915417907</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7699550901655474</v>
+        <v>0.7438822539729315</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.361820284937404</v>
+        <v>3.346176583221835</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.585957950349206</v>
+        <v>-3.862224555123746</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.451145117786071</v>
+        <v>1.340638475876256</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7100802628078553</v>
+        <v>0.6840074266152394</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.311932879924215</v>
+        <v>3.296289178208645</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674509</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.466137719438369</v>
+        <v>-3.742404324212908</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.514362379384615</v>
+        <v>1.4038557374748</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7100802628078553</v>
+        <v>0.6840074266152394</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.327222049158423</v>
+        <v>3.311578347442854</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.468607425900175</v>
+        <v>-3.744874030674714</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.421018696122334</v>
+        <v>1.310512054212519</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7076105563460491</v>
+        <v>0.6815377201534332</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.233384424603781</v>
+        <v>3.217740722888212</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.536977612224184</v>
+        <v>-3.813244216998724</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.312932483078031</v>
+        <v>1.202425841168216</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.716886255382264</v>
+        <v>0.6908134191896481</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.158211705510812</v>
+        <v>3.142568003795242</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.648849891850335</v>
+        <v>-3.925116496624875</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.258620279859462</v>
+        <v>1.148113637949647</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.716886255382264</v>
+        <v>0.6908134191896481</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.148648414142703</v>
+        <v>3.133004712427133</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.632875226364067</v>
+        <v>-3.909141831138607</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.231584670977997</v>
+        <v>1.121078029068182</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.716886255382264</v>
+        <v>0.6908134191896481</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.11522293906673</v>
+        <v>3.099579237351161</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.457400966571598</v>
+        <v>-3.733667571346138</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.306341606886772</v>
+        <v>1.195834964976957</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.716886255382264</v>
+        <v>0.6908134191896481</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.119790171058518</v>
+        <v>3.104146469342949</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.449476591986684</v>
+        <v>-3.725743196761223</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.285253385481945</v>
+        <v>1.17474674357213</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.716886255382264</v>
+        <v>0.6908134191896481</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.095532199819725</v>
+        <v>3.079888498104156</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.443198389416835</v>
+        <v>-3.719464994191374</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.216302979911334</v>
+        <v>1.105796338001519</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.723164457952113</v>
+        <v>0.6970916217594971</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.027837434763084</v>
+        <v>3.012193733047515</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.383345770213112</v>
+        <v>-3.659612374987651</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.250416414024956</v>
+        <v>1.139909772115141</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.723164457952113</v>
+        <v>0.6970916217594971</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.038009821195216</v>
+        <v>3.022366119479647</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742296</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.297102307186734</v>
+        <v>-3.573368911961274</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.279860069809367</v>
+        <v>1.169353427899552</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.723164457952113</v>
+        <v>0.6970916217594971</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.032956091769077</v>
+        <v>3.017312390053507</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316043</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.342409126585714</v>
+        <v>-3.618675731360254</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.253513117494301</v>
+        <v>1.143006475584486</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6823542949428822</v>
+        <v>0.6562814587502663</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.000245769408064</v>
+        <v>2.984602067692494</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803187</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.371442231288016</v>
+        <v>-3.647708836062555</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.242451748646482</v>
+        <v>1.131945106736667</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6823542949428822</v>
+        <v>0.6562814587502663</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.000797642441166</v>
+        <v>2.985153940725596</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.278631749837157</v>
+        <v>-3.554898354611696</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.208848633118191</v>
+        <v>1.098341991208376</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7751647763937416</v>
+        <v>0.7490919402011257</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.985756623203047</v>
+        <v>2.970112921487477</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560422</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.323021219166584</v>
+        <v>-3.599287823941124</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.192966321311021</v>
+        <v>1.082459679401206</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7307753070643139</v>
+        <v>0.704702470871698</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.960996417529991</v>
+        <v>2.945352715814422</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472732</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.302517525281087</v>
+        <v>-3.578784130055626</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.196243507376943</v>
+        <v>1.085736865467128</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7512790009498113</v>
+        <v>0.7252061647571953</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.968374342373012</v>
+        <v>2.952730640657443</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798533</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.342441619863659</v>
+        <v>-3.618708224638199</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.185765165374581</v>
+        <v>1.075258523464766</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7512790009498113</v>
+        <v>0.7252061647571953</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.97386563820368</v>
+        <v>2.95822193648811</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.370222017765012</v>
+        <v>-3.646488622539552</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.186150207982579</v>
+        <v>1.075643566072764</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7234986030484583</v>
+        <v>0.6974257668558423</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.968694601231407</v>
+        <v>2.953050899515838</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705321</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.488602690495151</v>
+        <v>-3.76486929526969</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9771536588911769</v>
+        <v>0.8666470169813618</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6562807508974821</v>
+        <v>0.6302079147048661</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.766719609941474</v>
+        <v>2.751075908225905</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.597216768938482</v>
+        <v>-3.873483373713021</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.05385768823305</v>
+        <v>0.9433510463232349</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6562807508974821</v>
+        <v>0.6302079147048661</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.88686927066068</v>
+        <v>2.87122556894511</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.561807730690339</v>
+        <v>-3.838074335464878</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.08253432963463</v>
+        <v>0.9720276877248151</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6562807508974821</v>
+        <v>0.6302079147048661</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.901382296763003</v>
+        <v>2.885738595047433</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.5702688993458</v>
+        <v>-3.84653550412034</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.076569303514814</v>
+        <v>0.9660626616049992</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.647819582242021</v>
+        <v>0.6217467460494051</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.893725036912095</v>
+        <v>2.878081335196526</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.393152569310634</v>
+        <v>-3.669419174085173</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.144144864374183</v>
+        <v>1.033638222464368</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.647819582242021</v>
+        <v>0.6217467460494051</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.890454065757397</v>
+        <v>2.874810364041828</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.43824481414418</v>
+        <v>-3.714511418918719</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.126791358202678</v>
+        <v>1.016284716292863</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5859235390726312</v>
+        <v>0.5598507028800153</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.853999831617677</v>
+        <v>2.838356129902107</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011229</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.258869392905412</v>
+        <v>-3.535135997679951</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.192328502004599</v>
+        <v>1.081821860094784</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7427002972433498</v>
+        <v>0.7166274610507339</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.941852861826523</v>
+        <v>2.926209160110953</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982222</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.303883606426018</v>
+        <v>-3.580150211200558</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.155130271927947</v>
+        <v>1.044623630018132</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7123514019287452</v>
+        <v>0.6862785657361293</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.904450979969349</v>
+        <v>2.88880727825378</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509531</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.570888116698454</v>
+        <v>-3.847154721472993</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.054020030157918</v>
+        <v>0.9435133882481033</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5179883638857967</v>
+        <v>0.4919155276931808</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.793524719482526</v>
+        <v>2.777881017766957</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760806</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.672085898135626</v>
+        <v>-3.948352502910166</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.012744839479551</v>
+        <v>0.9022381975697356</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4495795503404775</v>
+        <v>0.4235067141478616</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.751683353251836</v>
+        <v>2.736039651536266</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815451</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.665574931521314</v>
+        <v>-3.941841536295853</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.012949187679592</v>
+        <v>0.9024425457697773</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4495795503404775</v>
+        <v>0.4235067141478616</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.749283314806153</v>
+        <v>2.733639613090583</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.646536803814016</v>
+        <v>-3.922803408588556</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.017089157970756</v>
+        <v>0.9065825160609411</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.391395939009283</v>
+        <v>0.3653231028166671</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.710897867215681</v>
+        <v>2.695254165500111</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131244</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.699052606088836</v>
+        <v>-3.975319210863376</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.115377238695018</v>
+        <v>1.004870596785203</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.391395939009283</v>
+        <v>0.3653231028166671</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.830192268849871</v>
+        <v>2.814548567134302</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206786</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.702460917523416</v>
+        <v>-3.978727522297956</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.11484724310732</v>
+        <v>1.004340601197505</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4239125080186604</v>
+        <v>0.3978396718260445</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.850535539241631</v>
+        <v>2.834891837526062</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.683104781629569</v>
+        <v>-3.959371386404109</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.128598227861785</v>
+        <v>1.01809158595197</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4239125080186604</v>
+        <v>0.3978396718260445</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.856544069638557</v>
+        <v>2.840900367922988</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519904</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.535361811394567</v>
+        <v>-3.811628416169107</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.085645637232985</v>
+        <v>0.9751389953231702</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5917198652535436</v>
+        <v>0.5656470290609277</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.855178705256686</v>
+        <v>2.839535003541117</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181164</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.619183032669265</v>
+        <v>-3.895449637443805</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.054910770254587</v>
+        <v>0.9444041283447719</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5917198652535436</v>
+        <v>0.5656470290609277</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.857972326788167</v>
+        <v>2.842328625072598</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394723</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.613030326616481</v>
+        <v>-3.88929693139102</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.058034201067359</v>
+        <v>0.9475275591575441</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5978725713063279</v>
+        <v>0.571799735113712</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.862326298811496</v>
+        <v>2.846682597095927</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890607</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.629839624766982</v>
+        <v>-3.906106229541522</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.050390958547269</v>
+        <v>0.9398843166374538</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5810632731558263</v>
+        <v>0.5549904369632104</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.851321196661306</v>
+        <v>2.835677494945736</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.56754162599086</v>
+        <v>-3.8438082307654</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.141645711854538</v>
+        <v>1.031139069944723</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6263575374302683</v>
+        <v>0.6002847012376524</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.944833309022792</v>
+        <v>2.929189607307222</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992186</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.365751428325702</v>
+        <v>-3.642018033100242</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.024653792634729</v>
+        <v>0.9141471507249137</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.8243757295994227</v>
+        <v>0.7983028934068068</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.865936226038412</v>
+        <v>2.850292524322842</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852419</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.416638141011897</v>
+        <v>-3.692904745786437</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.074589339882426</v>
+        <v>0.9640826979726109</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7734890169132282</v>
+        <v>0.7474161807206123</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.90569443074887</v>
+        <v>2.8900507290333</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319539</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.33002739836209</v>
+        <v>-3.606294003136629</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.123861373058393</v>
+        <v>1.013354731148578</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8521147481183865</v>
+        <v>0.8260419119257706</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.967497605588009</v>
+        <v>2.951853903872439</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.390236696367374</v>
+        <v>-3.666503301141914</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.098313634680951</v>
+        <v>0.9878069927711355</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.791905450113102</v>
+        <v>0.7658326139204861</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.92990800760951</v>
+        <v>2.91426430589394</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397788</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.341050047683023</v>
+        <v>-3.617316652457562</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.11647991219462</v>
+        <v>1.005973270284805</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.791905450113102</v>
+        <v>0.7658326139204861</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.928399625649438</v>
+        <v>2.912755923933869</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316243</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.296676916044454</v>
+        <v>-3.572943520818994</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.134092032285483</v>
+        <v>1.023585390375668</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8362785817516706</v>
+        <v>0.8102057455590547</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.954886372068016</v>
+        <v>2.939242670352446</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.319157266903339</v>
+        <v>-3.595423871677879</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.11949368608052</v>
+        <v>1.008987044170705</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8362785817516706</v>
+        <v>0.8102057455590547</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.949280166206606</v>
+        <v>2.933636464491037</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.271501536342283</v>
+        <v>-3.547768141116823</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.144937735332747</v>
+        <v>1.034431093422932</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8839343123127262</v>
+        <v>0.8578614761201103</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.984255361571044</v>
+        <v>2.968611659855474</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569612</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.170983377843529</v>
+        <v>-3.447249982618068</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.190037372106973</v>
+        <v>1.079530730197158</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9844524708114808</v>
+        <v>0.9583796346188649</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.049458630045021</v>
+        <v>3.033814928329452</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.155078048411176</v>
+        <v>-3.431344653185715</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.183154176355787</v>
+        <v>1.072647534445972</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9053398101022418</v>
+        <v>0.8792669739096259</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.98874570609535</v>
+        <v>2.973102004379781</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.110239646802778</v>
+        <v>-3.386506251577317</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.205187239609774</v>
+        <v>1.094680597699959</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9098832430471113</v>
+        <v>0.8838104068544954</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.995569468472901</v>
+        <v>2.979925766757331</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.129738103044786</v>
+        <v>-3.406004707819326</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.201548796744049</v>
+        <v>1.091042154834234</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.861798601767207</v>
+        <v>0.8357257655745911</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.970879623336036</v>
+        <v>2.955235921620467</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.085535265958886</v>
+        <v>-3.361801870733425</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.225109534106247</v>
+        <v>1.114602892196431</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9060014388531075</v>
+        <v>0.8799286026604916</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.003280928115414</v>
+        <v>2.987637226399844</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.093094931795933</v>
+        <v>-3.369361536570472</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.220495668240675</v>
+        <v>1.10998902633086</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9608048428629268</v>
+        <v>0.9347320066703109</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.034572970990553</v>
+        <v>3.018929269274983</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284876</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.93480351425666</v>
+        <v>-3.2110701190312</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.335060000439424</v>
+        <v>1.224553358529609</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9608048428629268</v>
+        <v>0.9347320066703109</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.085820736173592</v>
+        <v>3.070177034458023</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.727161510622184</v>
+        <v>-3.003428115396724</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.416557506487468</v>
+        <v>1.306050864577653</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.168446846497403</v>
+        <v>1.142374010304787</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.208846642948531</v>
+        <v>3.193202941232962</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.676129417899656</v>
+        <v>-2.952396022674196</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.431918571814749</v>
+        <v>1.321411929904934</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.219478939219931</v>
+        <v>1.193406103027315</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.234414126820318</v>
+        <v>3.218770425104748</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.61090523677245</v>
+        <v>-2.88717184154699</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.475195648358336</v>
+        <v>1.364689006448521</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.284703120347136</v>
+        <v>1.258630284154521</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.290736039589346</v>
+        <v>3.275092337873777</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.573478216701317</v>
+        <v>-2.849744821475856</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.48612742868607</v>
+        <v>1.375620786776255</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.289954658376318</v>
+        <v>1.263881822183702</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.289847934706136</v>
+        <v>3.274204232990566</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.593589872736025</v>
+        <v>-2.869856477510564</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.479339558603427</v>
+        <v>1.368832916693612</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.300982003373737</v>
+        <v>1.274909167181122</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.297721134035827</v>
+        <v>3.282077432320258</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636281</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.565176609636141</v>
+        <v>-2.841443214410681</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.651262634864591</v>
+        <v>1.540755992954776</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.242006440627309</v>
+        <v>1.215933604434693</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.422893567409181</v>
+        <v>3.407249865693612</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095762</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.490394348611129</v>
+        <v>-2.766660953385668</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.801288448492413</v>
+        <v>1.690781806582598</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.316788701652321</v>
+        <v>1.290715865459706</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.587875833242006</v>
+        <v>3.572232131526436</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.464310264347321</v>
+        <v>-2.74057686912186</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.803430058211795</v>
+        <v>1.69292341630198</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.316788701652321</v>
+        <v>1.290715865459706</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.579583809255865</v>
+        <v>3.563940107540295</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.3764323512382</v>
+        <v>-2.65269895601274</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.836774419039223</v>
+        <v>1.726267777129408</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.432714344075672</v>
+        <v>1.406641507883057</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.647332390293655</v>
+        <v>3.631688688578085</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.367539889844917</v>
+        <v>-2.643806494619456</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.857885809323328</v>
+        <v>1.747379167413513</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.432714344075672</v>
+        <v>1.406641507883057</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.664886796020446</v>
+        <v>3.649243094304877</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.536016006814795</v>
+        <v>-2.812282611589334</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.782350409939961</v>
+        <v>1.671843768030146</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.404766508359091</v>
+        <v>1.378693672166476</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.639973141995082</v>
+        <v>3.624329440279512</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.089759814185355</v>
+        <v>-2.366026418959894</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.942122584179598</v>
+        <v>1.831615942269784</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.310047838689459</v>
+        <v>1.283975002496843</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.564411637381164</v>
+        <v>3.548767935665595</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632632</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.067038710502202</v>
+        <v>-2.343305315276742</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.941875048149764</v>
+        <v>1.831368406239949</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.310047838689459</v>
+        <v>1.283975002496843</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.555075659878068</v>
+        <v>3.539431958162499</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.196240523796245</v>
+        <v>-2.472507128570784</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.049100448683316</v>
+        <v>1.938593806773501</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.180846025395416</v>
+        <v>1.154773189202801</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.636460697752812</v>
+        <v>3.620816996037242</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.22211492227027</v>
+        <v>-2.49838152704481</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.075828511787353</v>
+        <v>1.965321869877537</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.225757634107158</v>
+        <v>1.199684797914542</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.700485485473503</v>
+        <v>3.684841783757934</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799959</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.215060232055097</v>
+        <v>-2.491326836829636</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.075325743862967</v>
+        <v>1.964819101953152</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.232812324322331</v>
+        <v>1.206739488129716</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.701393655592153</v>
+        <v>3.685749953876583</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.188109007728609</v>
+        <v>-2.464375612503148</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.096112387238304</v>
+        <v>1.985605745328489</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.247692670350051</v>
+        <v>1.221619834157435</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.720328016853526</v>
+        <v>3.704684315137956</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.209653235559396</v>
+        <v>-2.485919840333935</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.271597828250949</v>
+        <v>2.161091186341134</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.247692670350051</v>
+        <v>1.221619834157435</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.904431148998486</v>
+        <v>3.888787447282916</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571442</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.232061353364268</v>
+        <v>-2.508327958138807</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.254751276031993</v>
+        <v>2.144244634122178</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.247692670350051</v>
+        <v>1.221619834157435</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.896547843901479</v>
+        <v>3.880904142185909</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.260285588941868</v>
+        <v>-2.536552193716408</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.24551558135059</v>
+        <v>2.135008939440775</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.265669422801359</v>
+        <v>1.239596586608744</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.909387894921901</v>
+        <v>3.893744193206332</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161971</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.269726514830398</v>
+        <v>-2.545993119604938</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.297992928717025</v>
+        <v>2.187486286807211</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.388096540344751</v>
+        <v>1.362023704152135</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.039097883169783</v>
+        <v>4.023454181454214</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321628</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.358603145998872</v>
+        <v>-2.634869750773412</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.265333370794937</v>
+        <v>2.154826728885122</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.299219909176277</v>
+        <v>1.273147072983661</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.988662999014</v>
+        <v>3.97301929729843</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.434933123599778</v>
+        <v>-2.711199728374317</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.23291319264835</v>
+        <v>2.122406550738535</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.299219909176277</v>
+        <v>1.273147072983661</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.986774811907775</v>
+        <v>3.971131110192205</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.528597068277319</v>
+        <v>-2.804863673051859</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.190267844380196</v>
+        <v>2.07976120247038</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.205555964498735</v>
+        <v>1.17948312830612</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.925396674704112</v>
+        <v>3.909752972988543</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.690165493804574</v>
+        <v>-2.966432098579114</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.124074484379446</v>
+        <v>2.013567842469631</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.078773040700856</v>
+        <v>1.05270020450824</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.847760930635537</v>
+        <v>3.832117228919968</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.798466155674694</v>
+        <v>-3.074732760449233</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.093827626497316</v>
+        <v>1.983320984587501</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.078773040700856</v>
+        <v>1.05270020450824</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.860834337501456</v>
+        <v>3.845190635785886</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.816270127395438</v>
+        <v>-3.092536732169977</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.078711234591959</v>
+        <v>1.968204592682143</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.008238417795655</v>
+        <v>0.9821655816030392</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.810518760541275</v>
+        <v>3.794875058825706</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.844170914504911</v>
+        <v>-3.12043751927945</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.066074960875172</v>
+        <v>1.955568318965357</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9736414936527201</v>
+        <v>0.9475686574601044</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.788284647182516</v>
+        <v>3.772640945466947</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.966697017207805</v>
+        <v>-3.242963621982344</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.013828963771213</v>
+        <v>1.903322321861398</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8511153909498262</v>
+        <v>0.8250425547572106</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.711533429537979</v>
+        <v>3.695889727822409</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.197211513393394</v>
+        <v>-3.473478118167933</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.988329124887481</v>
+        <v>1.877822482977666</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6206008947642375</v>
+        <v>0.5945280585716218</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.639930691417129</v>
+        <v>3.62428698970156</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.545956598617837</v>
+        <v>-3.822223203392377</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.98914280979955</v>
+        <v>1.878636167889735</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5118529408453397</v>
+        <v>0.485780104652724</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.714993638067638</v>
+        <v>3.699349936352068</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237096</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.699943016393978</v>
+        <v>-3.976209621168517</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.996528511834734</v>
+        <v>1.886021869924919</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5118529408453397</v>
+        <v>0.485780104652724</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.783973907213277</v>
+        <v>3.768330205497708</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423389</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.904542451256987</v>
+        <v>-4.180809056031526</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.900739940009652</v>
+        <v>1.790233298099837</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5118529408453397</v>
+        <v>0.485780104652724</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.770025109333398</v>
+        <v>3.754381407617829</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.157017605264711</v>
+        <v>-4.43328421003925</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.811620367461976</v>
+        <v>1.701113725552161</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5118529408453397</v>
+        <v>0.485780104652724</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.781895598388812</v>
+        <v>3.766251896673243</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.449913361744123</v>
+        <v>-4.726179966518663</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.695672599389155</v>
+        <v>1.58516595747934</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5118529408453397</v>
+        <v>0.485780104652724</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.783106132907756</v>
+        <v>3.767462431192186</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.636577489878931</v>
+        <v>-4.912844094653471</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.625128690362553</v>
+        <v>1.514622048452738</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4851139700207798</v>
+        <v>0.4590411338281641</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.771184492640341</v>
+        <v>3.755540790924772</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.782598176792893</v>
+        <v>-5.058864781567433</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.561798268333157</v>
+        <v>1.451291626423342</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4760308782269229</v>
+        <v>0.4499580420343072</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.760812490300217</v>
+        <v>3.745168788584647</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830324</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.874312185902479</v>
+        <v>-5.150578790677018</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.687316721388367</v>
+        <v>1.576810079478552</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4760308782269229</v>
+        <v>0.4499580420343072</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.923016546999261</v>
+        <v>3.907372845283692</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.905963844962448</v>
+        <v>-5.182230449736988</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.669502695728194</v>
+        <v>1.558996053818379</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4708624209824827</v>
+        <v>0.444789584789867</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.914762110616411</v>
+        <v>3.899118408900841</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.987898663231332</v>
+        <v>-5.264165268005871</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.646958185989132</v>
+        <v>1.536451544079316</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4609276753954025</v>
+        <v>0.4348548392027868</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.919030680832654</v>
+        <v>3.903386979117085</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.089874785479739</v>
+        <v>-5.366141390254278</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.615093375545671</v>
+        <v>1.504586733635856</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3589515531469949</v>
+        <v>0.3328787169543792</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.866770645939512</v>
+        <v>3.851126944223942</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231803</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.979868502002518</v>
+        <v>-5.256135106777057</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.651248776180735</v>
+        <v>1.54074213427092</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3821561250642701</v>
+        <v>0.3560832888716544</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.872846276334052</v>
+        <v>3.857202574618483</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.836808926261591</v>
+        <v>-5.113075531036131</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.71272261719908</v>
+        <v>1.602215975289265</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3901695516542494</v>
+        <v>0.3640967154616337</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.881904343010014</v>
+        <v>3.866260641294445</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.535362200789754</v>
+        <v>-4.811628805564293</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.840562190270351</v>
+        <v>1.730055548360536</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6916162771260866</v>
+        <v>0.665543440933471</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.070033261175652</v>
+        <v>4.054389559460083</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.559952445024938</v>
+        <v>-4.836219049799477</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.831697270328988</v>
+        <v>1.721190628419173</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6916162771260866</v>
+        <v>0.665543440933471</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.071004438928363</v>
+        <v>4.055360737212793</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.508914069018418</v>
+        <v>-4.785180673792957</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.852955525111351</v>
+        <v>1.742448883201536</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6916162771260866</v>
+        <v>0.665543440933471</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.071847343308119</v>
+        <v>4.056203641592549</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.467774774151787</v>
+        <v>-4.744041378926326</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.888449341932149</v>
+        <v>1.777942700022334</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7327555719927175</v>
+        <v>0.7066827358001018</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.115569019102242</v>
+        <v>4.099925317386673</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.371139862133147</v>
+        <v>-4.647406466907686</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.74328730286354</v>
+        <v>1.632780660953725</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8293904840113574</v>
+        <v>0.8033176478187417</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.989733962437361</v>
+        <v>3.974090260721792</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077636</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.501720596663989</v>
+        <v>-4.777987201438529</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.694557053125167</v>
+        <v>1.584050411215352</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6988097494805149</v>
+        <v>0.6727369132878992</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.91488756579282</v>
+        <v>3.89924386407725</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.337224262473027</v>
+        <v>-4.613490867247567</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.744782405877634</v>
+        <v>1.634275763967819</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8633060836714768</v>
+        <v>0.8372332474788611</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.998012185383479</v>
+        <v>3.98236848366791</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.260125660931155</v>
+        <v>-4.536392265705694</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.774809556930813</v>
+        <v>1.664302915020998</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8633060836714768</v>
+        <v>0.8372332474788611</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.997199895819909</v>
+        <v>3.98155619410434</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.270510855821044</v>
+        <v>-4.546777460595584</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.78052425809993</v>
+        <v>1.670017616190115</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8529208887815874</v>
+        <v>0.8268480525889718</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.000837558011048</v>
+        <v>3.985193856295479</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.289099014543269</v>
+        <v>-4.565365619317808</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.843926000387465</v>
+        <v>1.73341935847765</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8343327300593621</v>
+        <v>0.8082598938667465</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.060521668554138</v>
+        <v>4.044877966838569</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496556</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.289397561239305</v>
+        <v>-4.565664166013844</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.840675592527349</v>
+        <v>1.730168950617534</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8340341833633262</v>
+        <v>0.8079613471707106</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.057211551354815</v>
+        <v>4.041567849639246</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.188574427548877</v>
+        <v>-4.464841032323417</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.885535740942911</v>
+        <v>1.775029099033096</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8464983988476801</v>
+        <v>0.8204255626550644</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.069220975584819</v>
+        <v>4.053577273869249</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-3.99779306679647</v>
+        <v>-4.27405967157101</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.961977538722418</v>
+        <v>1.851470896812602</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.037279759600088</v>
+        <v>1.011206923407472</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.183819045514807</v>
+        <v>4.168175343799237</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.890829708947048</v>
+        <v>-4.167096313721588</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.984599727599783</v>
+        <v>1.874093085689968</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.095744367559889</v>
+        <v>1.069671531367273</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.198734656028284</v>
+        <v>4.183090954312714</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.835499121045286</v>
+        <v>-4.111765725819826</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.041698899372546</v>
+        <v>1.931192257462731</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.151074955461651</v>
+        <v>1.125002119269035</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.266899945381399</v>
+        <v>4.25125624366583</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.823444994132323</v>
+        <v>-4.099711598906863</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.040207118039169</v>
+        <v>1.929700476129354</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.163129082374614</v>
+        <v>1.137056246181998</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.267818989430615</v>
+        <v>4.252175287715046</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.864600113700544</v>
+        <v>-4.140866718475084</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.025625700396017</v>
+        <v>1.915119058486201</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.121973962806393</v>
+        <v>1.095901126613777</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.245006547873818</v>
+        <v>4.229362846158248</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.796551551009014</v>
+        <v>-4.072818155783554</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.065696151350511</v>
+        <v>1.955189509440696</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.190022525497923</v>
+        <v>1.163949689305307</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.298686711366619</v>
+        <v>4.283043009651049</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013426</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.028151944178515</v>
+        <v>-4.304418548953055</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.993258664256305</v>
+        <v>1.88275202234649</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.190022525497923</v>
+        <v>1.163949689305307</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.318889381540213</v>
+        <v>4.303245679824643</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498971</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.078203489707734</v>
+        <v>-4.354470094482274</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.956844282111499</v>
+        <v>1.846337640201684</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.190022525497923</v>
+        <v>1.163949689305307</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.302495617607095</v>
+        <v>4.286851915891526</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.6700487028001</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.253310322284179</v>
+        <v>-4.529576927058718</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.847053462674388</v>
+        <v>1.736546820764573</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.190022525497923</v>
+        <v>1.163949689305307</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.262747531200562</v>
+        <v>4.247103829484992</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660853</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.057210168853656</v>
+        <v>-4.333476773628195</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.932516143043537</v>
+        <v>1.822009501133722</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.386122678928446</v>
+        <v>1.36004984273583</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.387430242255816</v>
+        <v>4.371786540540246</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.73057047339509</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.904184776740372</v>
+        <v>-4.180451381514911</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.092897299461755</v>
+        <v>1.982390657551941</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.53914807104173</v>
+        <v>1.513075234849114</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.57841647709669</v>
+        <v>4.562772775381121</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791148</v>
+        <v>3.741278332791151</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.932492090613642</v>
+        <v>-4.208758695388181</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.26904059882074</v>
+        <v>2.158533956910925</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.53914807104173</v>
+        <v>1.513075234849114</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.765882702004983</v>
+        <v>4.750239000289413</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620437</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.099085315727164</v>
+        <v>-4.375351920501704</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.171806260129414</v>
+        <v>2.061299618219599</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.372554845928207</v>
+        <v>1.346482009735592</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.635329718290952</v>
+        <v>4.619686016575383</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.70818251928565</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.076049522365598</v>
+        <v>-4.352316127140138</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.184696980135758</v>
+        <v>2.074190338225943</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.372554845928207</v>
+        <v>1.346482009735592</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.639006120952669</v>
+        <v>4.6233624192371</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399468</v>
+        <v>3.740581401399472</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.046803541909902</v>
+        <v>-4.323070146684441</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.194013427441531</v>
+        <v>2.083506785531716</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.372554845928207</v>
+        <v>1.346482009735592</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.636624176076165</v>
+        <v>4.620980474360596</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256374</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.153729089787753</v>
+        <v>-4.429995694562292</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.148536447448026</v>
+        <v>2.038029805538211</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.265629298050356</v>
+        <v>1.23955646185774</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.569762086507089</v>
+        <v>4.554118384791519</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701</v>
+        <v>3.689942600701004</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.298747648295001</v>
+        <v>-4.441231256114322</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.091957826188361</v>
+        <v>2.034964383060633</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.120610739543108</v>
+        <v>1.22832090030571</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.484179753545974</v>
+        <v>4.548805850003536</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.417089414079719</v>
+        <v>-4.559573021899039</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.144552359132227</v>
+        <v>2.087558916004499</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.131296778105998</v>
+        <v>1.2390069388686</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.590522615941461</v>
+        <v>4.655148712399023</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790801</v>
+        <v>3.714879051790804</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.468499836400427</v>
+        <v>-4.610983444219747</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.121773887329883</v>
+        <v>2.064780444202155</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.131296778105998</v>
+        <v>1.2390069388686</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.5883083130674</v>
+        <v>4.652934409524962</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.704757949437331</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.547919287608178</v>
+        <v>-4.690402895427499</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.089909234921072</v>
+        <v>2.032915791793344</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.131296778105998</v>
+        <v>1.2390069388686</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.58821144114169</v>
+        <v>4.652837537599251</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298398</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.643382285525396</v>
+        <v>-4.785865893344717</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.051717929312227</v>
+        <v>1.994724486184499</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.131296778105998</v>
+        <v>1.2390069388686</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.588205334699732</v>
+        <v>4.652831431157294</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960218</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.579006374674681</v>
+        <v>-4.721489982494002</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.075564690215124</v>
+        <v>2.018571247087396</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.195672688956713</v>
+        <v>1.303382849719316</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.624927277772772</v>
+        <v>4.689553374230334</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.736089413353535</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.634375536806875</v>
+        <v>-4.776859144626195</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.059150843109973</v>
+        <v>2.002157399982246</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.195672688956713</v>
+        <v>1.303382849719316</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.630661095520499</v>
+        <v>4.695287191978061</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113278</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.679813316637702</v>
+        <v>-4.822296924457023</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.040514094520574</v>
+        <v>1.983520651392847</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.152827698278553</v>
+        <v>1.260537859041156</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.604492464456536</v>
+        <v>4.669118560914097</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113687</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.591606482490124</v>
+        <v>-4.734090090309444</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.095671221029924</v>
+        <v>2.038677777902197</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.152827698278553</v>
+        <v>1.260537859041156</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.624366857306854</v>
+        <v>4.688992953764416</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016441</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.485571487284814</v>
+        <v>-4.628055095104135</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.121785919636776</v>
+        <v>2.064792476509049</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.152827698278553</v>
+        <v>1.260537859041156</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.608067557831582</v>
+        <v>4.672693654289144</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.794705093307672</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.302359824151719</v>
+        <v>-4.44484343197104</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.19750153435406</v>
+        <v>2.140508091226332</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.152827698278553</v>
+        <v>1.260537859041156</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.610498507295627</v>
+        <v>4.675124603753189</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.230638377137868</v>
+        <v>-4.373121984957189</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.19198129900749</v>
+        <v>2.134987855879762</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.224549145292404</v>
+        <v>1.332259306055007</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.619322561351828</v>
+        <v>4.683948657809389</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72378970539411</v>
+        <v>3.723789705394114</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.208265351530162</v>
+        <v>-4.350748959349483</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.147846255171744</v>
+        <v>2.090852812044016</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.235804896405305</v>
+        <v>1.343515057167908</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.57299175794074</v>
+        <v>4.637617854398302</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456727</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.241281647440907</v>
+        <v>-4.383765255260228</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.319837941692801</v>
+        <v>2.262844498565074</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.166367519738554</v>
+        <v>1.274077680501157</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.716527536826044</v>
+        <v>4.781153633283607</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883677</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.229754011791298</v>
+        <v>-4.372237619610619</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.316370221780894</v>
+        <v>2.259376778653166</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.225368177939916</v>
+        <v>1.333078338702519</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.743849157575111</v>
+        <v>4.808475254032673</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236293</v>
+        <v>3.717150699236297</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.327095513133667</v>
+        <v>-4.469579120952988</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.281101733765735</v>
+        <v>2.224108290638007</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.180947995774428</v>
+        <v>1.288658156537031</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.720865160797606</v>
+        <v>4.785491257255169</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427679</v>
+        <v>3.705201079427683</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.412951542473634</v>
+        <v>-4.555435150292954</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.248010404222586</v>
+        <v>2.191016961094859</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.138571926548293</v>
+        <v>1.246282087310896</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.696690601454764</v>
+        <v>4.761316697912325</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610383</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.421788339889753</v>
+        <v>-4.564271947709074</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.22689488707664</v>
+        <v>2.169901443948913</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.131129753906942</v>
+        <v>1.238839914669545</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.674644499690455</v>
+        <v>4.739270596148017</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667451</v>
+        <v>3.715544411667454</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.513170902455212</v>
+        <v>-4.655654510274532</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.200506373095506</v>
+        <v>2.143512929967779</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.094564869187598</v>
+        <v>1.2022750299502</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.662870079903898</v>
+        <v>4.727496176361459</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889186</v>
+        <v>3.67397837488919</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.501464184468206</v>
+        <v>-4.643947792287526</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.307317318114576</v>
+        <v>2.250323874986849</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.106271587174604</v>
+        <v>1.213981747937207</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.772022368520369</v>
+        <v>4.83664846497793</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409562</v>
+        <v>3.682476099409566</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.401800680384543</v>
+        <v>-4.544284288203864</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.350215058479446</v>
+        <v>2.293221615351718</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.169458670378291</v>
+        <v>1.277168831140893</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.812966957173986</v>
+        <v>4.877593053631547</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.672895177452573</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.412116778550895</v>
+        <v>-4.554600386370216</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.558993452490963</v>
+        <v>2.502000009363236</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.169458670378291</v>
+        <v>1.277168831140893</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.025871790452044</v>
+        <v>5.090497886909605</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762286</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.412022810533522</v>
+        <v>-4.554506418352843</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.558209706610002</v>
+        <v>2.501216263482275</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.169828531725609</v>
+        <v>1.277538692488211</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.025272374172524</v>
+        <v>5.089898470630086</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988014</v>
+        <v>3.633213467988017</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.419241634733367</v>
+        <v>-4.561725242552687</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.549554162874418</v>
+        <v>2.492560719746691</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.169828531725609</v>
+        <v>1.277538692488211</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.019504360116878</v>
+        <v>5.08413045657444</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740923</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.418293211615328</v>
+        <v>-4.560776819434649</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.549933532121633</v>
+        <v>2.492940088993906</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.169828531725609</v>
+        <v>1.277538692488211</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.019504360116878</v>
+        <v>5.08413045657444</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663627</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.575361669870952</v>
+        <v>-4.717845277690273</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.499833756800476</v>
+        <v>2.442840313672749</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.169828531725609</v>
+        <v>1.277538692488211</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.03223196809797</v>
+        <v>5.096858064555532</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424771</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.569369423082141</v>
+        <v>-4.711853030901461</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.504176653940388</v>
+        <v>2.447183210812661</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.169828531725609</v>
+        <v>1.277538692488211</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.034177966522358</v>
+        <v>5.098804062979919</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149219</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.480811461951373</v>
+        <v>-4.623295069770694</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.533253974410464</v>
+        <v>2.476260531282737</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.169828531725609</v>
+        <v>1.277538692488211</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.027832102540127</v>
+        <v>5.092458198997688</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383092</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.463052384448299</v>
+        <v>-4.60553599226762</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.539666282850689</v>
+        <v>2.482672839722962</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.169828531725609</v>
+        <v>1.277538692488211</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.027140779979122</v>
+        <v>5.091766876436684</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720999</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.363422233399231</v>
+        <v>-4.505905841218552</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.592300529178903</v>
+        <v>2.535307086051175</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.269458682774676</v>
+        <v>1.377168843537279</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.09970105651715</v>
+        <v>5.164327152974711</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455269</v>
+        <v>3.775357097455273</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.412821742088243</v>
+        <v>-4.555305349907563</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.761694991202025</v>
+        <v>2.704701548074298</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.279717516206421</v>
+        <v>1.387427676969024</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.295010622074923</v>
+        <v>5.359636718532485</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963135</v>
+        <v>3.749078058963137</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.346330955687042</v>
+        <v>-4.348620876265187</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.775479978865367</v>
+        <v>2.77456401063411</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.346208302607621</v>
+        <v>1.594112150611399</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.322093767018505</v>
+        <v>5.470836075820772</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.896869551899808</v>
+        <v>3.763417089428135</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.747388673340937</v>
+        <v>4.450156245312197</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.346330955687042</v>
+        <v>-4.347708877735512</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.775479978865367</v>
+        <v>2.710716269904245</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.346208302607621</v>
+        <v>1.581294957447236</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.740452470327305</v>
+        <v>5.398933219780538</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240916.xlsx
+++ b/tame_output/ON/bt/strategyON_20240916.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>61.0%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>133.4%</t>
+          <t>134.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.7%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-71.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.0%</t>
+          <t>422.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-596.3%</t>
+          <t>-605.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-105.2%</t>
+          <t>-107.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-131.8%</t>
+          <t>-65.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-327.3%</t>
+          <t>-328.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-65.9%</t>
+          <t>-86.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>118.8%</t>
+          <t>114.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>104.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>82.7%</t>
         </is>
       </c>
     </row>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.098474522802566</v>
+        <v>-7.095120593611989</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2774159213878189</v>
+        <v>0.2787574930640497</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.8720297019147221</v>
+        <v>-0.8563251372261523</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.59394433367376</v>
+        <v>2.603367072486902</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.285194231111869</v>
+        <v>-7.281840301921291</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1987017335296946</v>
+        <v>0.2000433052059254</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.8720297019147221</v>
+        <v>-0.8563251372261523</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.589918029139357</v>
+        <v>2.599340767952499</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.6681956198545</v>
+        <v>-7.664841690663923</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.04539907671105814</v>
+        <v>0.04674064838728897</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.8720297019147221</v>
+        <v>-0.8563251372261523</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.589815927817773</v>
+        <v>2.599238666630915</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.672682065055889</v>
+        <v>-7.669328135865311</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.04617601460193255</v>
+        <v>0.04751758627816383</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8765161471161107</v>
+        <v>-0.8608115824275411</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.58969557666837</v>
+        <v>2.599118315481511</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.032212387559891</v>
+        <v>-8.028858458369314</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.09228581110161782</v>
+        <v>-0.09094423942538654</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8765161471161107</v>
+        <v>-0.8608115824275411</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.59504587996642</v>
+        <v>2.604468618779562</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.082561451014113</v>
+        <v>-8.079207521823536</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1045094165261289</v>
+        <v>-0.103167844849898</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.9268652105703328</v>
+        <v>-0.9111606458817632</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.572752461851064</v>
+        <v>2.582175200664206</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.180180728435509</v>
+        <v>-8.176826799244932</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1405153768729188</v>
+        <v>-0.1391738051966875</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.024484487991729</v>
+        <v>-1.00877992330316</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.517222646019995</v>
+        <v>2.526645384833137</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.234252227943868</v>
+        <v>-8.23089829875329</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1592504203546898</v>
+        <v>-0.157908848678459</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.078555987500089</v>
+        <v>-1.062851422811519</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.487673302636551</v>
+        <v>2.497096041449693</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.237828014035616</v>
+        <v>-8.234474084845038</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1551675376727468</v>
+        <v>-0.1538259659965155</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.104084909416582</v>
+        <v>-1.088380344728012</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.477869146605298</v>
+        <v>2.48729188541844</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.271480852544089</v>
+        <v>-8.268126923353512</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1641461185917001</v>
+        <v>-0.1628045469154689</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.204498277333619</v>
+        <v>-1.188793712645049</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.422103680339512</v>
+        <v>2.431526419152654</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.410566967162946</v>
+        <v>-8.407213037972369</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2044088629458218</v>
+        <v>-0.2030672912695906</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.343584391952476</v>
+        <v>-1.327879827263906</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.354023713061619</v>
+        <v>2.363446451874761</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.58569138454949</v>
+        <v>-8.582337455358912</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2599034091529222</v>
+        <v>-0.2585618374766914</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.51870880933902</v>
+        <v>-1.50300424465045</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.263504283377209</v>
+        <v>2.272927022190351</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.820143478563979</v>
+        <v>-8.816789549373402</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3609034116603143</v>
+        <v>-0.359561839984083</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.51870880933902</v>
+        <v>-1.50300424465045</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.256285118475613</v>
+        <v>2.265707857288755</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.924518209590426</v>
+        <v>-8.921164280399848</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.409325494844869</v>
+        <v>-0.4079839231686377</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.623083540365465</v>
+        <v>-1.607378975676896</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.18698808908577</v>
+        <v>2.196410827898911</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.08703167528901</v>
+        <v>-9.083677746098433</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4732150912857462</v>
+        <v>-0.4718735196095154</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.720716970784152</v>
+        <v>-1.705012406095582</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.129523820673114</v>
+        <v>2.138946559486256</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.213068468657299</v>
+        <v>-9.209714539466722</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5209360800039473</v>
+        <v>-0.5195945083277165</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.69546534797441</v>
+        <v>-1.67976078328584</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.147368522988074</v>
+        <v>2.156791261801216</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.155996696761369</v>
+        <v>-9.152642767570791</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4941170355591744</v>
+        <v>-0.4927754638829431</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.69546534797441</v>
+        <v>-1.67976078328584</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.151358858674475</v>
+        <v>2.160781597487617</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.297668538485489</v>
+        <v>-9.294314609294911</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5522609991475642</v>
+        <v>-0.5509194274713329</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.69546534797441</v>
+        <v>-1.67976078328584</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.149883631775733</v>
+        <v>2.159306370588875</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.248077694060655</v>
+        <v>-9.244723764870077</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.517371251212758</v>
+        <v>-0.5160296795365271</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.645874503549576</v>
+        <v>-1.630169938861006</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.194691548595506</v>
+        <v>2.204114287408648</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.099159359588798</v>
+        <v>-9.095805430398221</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4708550510706986</v>
+        <v>-0.4695134793944673</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.614624912814403</v>
+        <v>-1.598920348125833</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.200390169389927</v>
+        <v>2.209812908203069</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.873314206869388</v>
+        <v>-8.86996027767881</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3709379169467257</v>
+        <v>-0.3695963452704949</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.572698237227239</v>
+        <v>-1.556993672538669</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.235125247778434</v>
+        <v>2.244547986591575</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.748735550531796</v>
+        <v>-8.745381621341219</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3199673098556302</v>
+        <v>-0.3186257381793989</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.572698237227239</v>
+        <v>-1.556993672538669</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.236264392334493</v>
+        <v>2.245687131147634</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.723698868963286</v>
+        <v>-8.720344939772708</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3073188630661186</v>
+        <v>-0.3059772913898873</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.547369149676503</v>
+        <v>-1.531664584987934</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.254095619027042</v>
+        <v>2.263518357840184</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.651565693675405</v>
+        <v>-8.648211764484827</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2727318887123293</v>
+        <v>-0.2713903170360985</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.547369149676503</v>
+        <v>-1.531664584987934</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.259829323265678</v>
+        <v>2.26925206207882</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.580199301065758</v>
+        <v>-8.57684537187518</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2539225940623355</v>
+        <v>-0.2525810223861047</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.476002757066855</v>
+        <v>-1.460298192378286</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.292911896437602</v>
+        <v>2.302334635250744</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.486740267080533</v>
+        <v>-8.483386337889955</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2264224617811537</v>
+        <v>-0.2250808901049224</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.476002757066855</v>
+        <v>-1.460298192378286</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.283028415124694</v>
+        <v>2.292451153937836</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.476087085527102</v>
+        <v>-8.472733156336524</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2239957496591547</v>
+        <v>-0.2226541779829234</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.476002757066855</v>
+        <v>-1.460298192378286</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.28119385462532</v>
+        <v>2.290616593438462</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.378180046850611</v>
+        <v>-8.374826117660033</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.185133249162019</v>
+        <v>-0.1837916774857882</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.408017007206299</v>
+        <v>-1.39231244251773</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.321684989568193</v>
+        <v>2.331107728381335</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.354226505874653</v>
+        <v>-8.350872576684075</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1748833266261425</v>
+        <v>-0.1735417549499112</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.384063466230341</v>
+        <v>-1.368358901541772</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.336725620299262</v>
+        <v>2.346148359112403</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.090166567551856</v>
+        <v>-8.086812638361279</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.08251966745877581</v>
+        <v>-0.08117809578254498</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.120003527907545</v>
+        <v>-1.104298963218976</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.481901267131187</v>
+        <v>2.491324005944329</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.519722381511008</v>
+        <v>-7.37973301485644</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1428709732972626</v>
+        <v>0.1988667199590894</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.120003527907545</v>
+        <v>-1.104298963218976</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.479114233470886</v>
+        <v>2.488536972284028</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.479538083144818</v>
+        <v>-7.33954871649025</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1592883165315802</v>
+        <v>0.215284063193407</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.079819229541354</v>
+        <v>-1.064114664852785</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.503568436378442</v>
+        <v>2.512991175191584</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.316138212205455</v>
+        <v>-7.176148845550888</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2240150861280821</v>
+        <v>0.2800108327899089</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.916419358601992</v>
+        <v>-0.9007147939134224</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.600975180162817</v>
+        <v>2.610397918975958</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.082656989975857</v>
+        <v>-6.942667623321289</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3253320038577736</v>
+        <v>0.3813277505196009</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6829381363723934</v>
+        <v>-0.6672335716838238</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.748988342338428</v>
+        <v>2.75841108115157</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.932990598968342</v>
+        <v>-6.793001232313774</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3823063499478208</v>
+        <v>0.4383020966096476</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5900346451298575</v>
+        <v>-0.5743300804412879</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.80183822677099</v>
+        <v>2.811260965584132</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.800715125337455</v>
+        <v>-6.660725758682887</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3364773254073299</v>
+        <v>0.3924730720691572</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4577591714989708</v>
+        <v>-0.4420546068104012</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.782464296956677</v>
+        <v>2.791887035769819</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.628853909772553</v>
+        <v>-6.488864543117985</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4080368723209276</v>
+        <v>0.4640326189827548</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.285897955934068</v>
+        <v>-0.2701933912454983</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.888396086983255</v>
+        <v>2.897818825796397</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.543889243043234</v>
+        <v>-6.403899876388666</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.454929080236314</v>
+        <v>0.5109248268981412</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2009332892047484</v>
+        <v>-0.1852287245161788</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.952281228244506</v>
+        <v>2.961703967057648</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.649479232816338</v>
+        <v>-6.50948986616177</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2847171547278533</v>
+        <v>0.3407129013896806</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3065232789778528</v>
+        <v>-0.2908187142892831</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.760951304781425</v>
+        <v>2.770374043594567</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.581244648190911</v>
+        <v>-6.441255281536343</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.360555330455111</v>
+        <v>0.4165510771169378</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2881079561053168</v>
+        <v>-0.2724033914167471</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.820544840382033</v>
+        <v>2.829967579195174</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.433304606783311</v>
+        <v>-6.293315240128743</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3031105383797437</v>
+        <v>0.3591062850415705</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2677870401967592</v>
+        <v>-0.2520824755081896</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.71611658128876</v>
+        <v>2.725539320101902</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.380335084529323</v>
+        <v>-6.240345717874755</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3155843610278608</v>
+        <v>0.3715801076896881</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2148175179427703</v>
+        <v>-0.1991129532542007</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.739184308387675</v>
+        <v>2.748607047200817</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.214546888569032</v>
+        <v>-6.074557521914464</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3749390273168838</v>
+        <v>0.430934773978711</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2148175179427703</v>
+        <v>-0.1991129532542007</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.732223696292582</v>
+        <v>2.741646435105724</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.181183682090263</v>
+        <v>-6.041194315435695</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4027466642895345</v>
+        <v>0.4587424109513618</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2148175179427703</v>
+        <v>-0.1991129532542007</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.746686050673725</v>
+        <v>2.756108789486867</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.072924544967742</v>
+        <v>-5.932935178313174</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4405824395977382</v>
+        <v>0.4965781862595655</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2148175179427703</v>
+        <v>-0.1991129532542007</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.74121817113292</v>
+        <v>2.750640909946062</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.949633410150611</v>
+        <v>-5.809644043496043</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4873969875351674</v>
+        <v>0.5433927341969946</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.09152638312563982</v>
+        <v>-0.0758218184370702</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.812690946033775</v>
+        <v>2.822113684846917</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.896936543019319</v>
+        <v>-5.756947176364752</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.516176712625009</v>
+        <v>0.5721724592868362</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.03882951599434864</v>
+        <v>-0.02312495130577902</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.852010044549875</v>
+        <v>2.861432783363017</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.653171101035875</v>
+        <v>-5.513181734381307</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6094635977654375</v>
+        <v>0.6654593444272647</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.03882951599434864</v>
+        <v>-0.02312495130577902</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.847790752896926</v>
+        <v>2.857213491710068</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.563395428659403</v>
+        <v>-5.423406062004835</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6474981806360423</v>
+        <v>0.7034939272978695</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.02276992891996138</v>
+        <v>0.038474493608531</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.886874733765528</v>
+        <v>2.89629747257867</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.313545034710328</v>
+        <v>-5.17355566805576</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7401804131993743</v>
+        <v>0.7961761598612016</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.02276992891996138</v>
+        <v>0.038474493608531</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.87961680874923</v>
+        <v>2.889039547562372</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.137652942242896</v>
+        <v>-4.997663575588328</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.814136373706996</v>
+        <v>0.8701321203688233</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.02276992891996138</v>
+        <v>0.038474493608531</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.883215932269879</v>
+        <v>2.892638671083021</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.966206479220433</v>
+        <v>-4.826217112565865</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.896042464970535</v>
+        <v>0.9520382116323622</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1942163919424245</v>
+        <v>0.2099209566309941</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.99941131613791</v>
+        <v>3.008834054951052</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.886184192111312</v>
+        <v>-4.746194825456744</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9270718574304804</v>
+        <v>0.9830676040923076</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2742386790515455</v>
+        <v>0.2899432437401151</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.04644516601968</v>
+        <v>3.055867904832822</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.822548449877377</v>
+        <v>-4.682559083222809</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9572209553783715</v>
+        <v>1.013216702040199</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.33787442128548</v>
+        <v>0.3535789859740496</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.089321412414358</v>
+        <v>3.0987441512275</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.728851131660982</v>
+        <v>-4.588861765006414</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9758941414487252</v>
+        <v>1.031889888110552</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.33787442128548</v>
+        <v>0.3535789859740496</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.070515671198153</v>
+        <v>3.079938410011295</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.739353754726271</v>
+        <v>-4.599364388071703</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9734361688474871</v>
+        <v>1.029431915509314</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3273717982201911</v>
+        <v>0.3430763629087608</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.065957173983858</v>
+        <v>3.075379912797</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.626867494057397</v>
+        <v>-4.486878127402829</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.022359986949857</v>
+        <v>1.078355733611684</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3273717982201911</v>
+        <v>0.3430763629087608</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.069886487818678</v>
+        <v>3.07930922663182</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.534138930873835</v>
+        <v>-4.469164440524963</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.060129996140621</v>
+        <v>1.08611979228017</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3472359642104752</v>
+        <v>0.3462576918056776</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.082483571330188</v>
+        <v>3.08189660788731</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.410664659560817</v>
+        <v>-4.33800273309689</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.106517775885822</v>
+        <v>1.135582546471393</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3472359642104752</v>
+        <v>0.3462576918056776</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.079481642550182</v>
+        <v>3.078894679107303</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.190643861523807</v>
+        <v>-4.11798193505988</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.196105132111241</v>
+        <v>1.225169902696811</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4884558092784554</v>
+        <v>0.4874775368736578</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.165792586601584</v>
+        <v>3.165205623158705</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539946</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.057776172460529</v>
+        <v>-3.985114245996602</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.265146390538375</v>
+        <v>1.294211161123946</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4884558092784554</v>
+        <v>0.4874775368736578</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.181686769403407</v>
+        <v>3.181099805960529</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.93760308909603</v>
+        <v>-3.864941162632102</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.314361468324476</v>
+        <v>1.343426238910048</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6086288926429544</v>
+        <v>0.6076506202381567</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.254936463862409</v>
+        <v>3.25434950041953</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.802349727766053</v>
+        <v>-3.729687801302125</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.378550915417907</v>
+        <v>1.407615686003478</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7438822539729315</v>
+        <v>0.7429039815681339</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.346176583221835</v>
+        <v>3.345589619778956</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.862224555123746</v>
+        <v>-3.789562628659818</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.340638475876256</v>
+        <v>1.369703246461827</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6840074266152394</v>
+        <v>0.6830291542104417</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.296289178208645</v>
+        <v>3.295702214765767</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.742404324212908</v>
+        <v>-3.66974239774898</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.4038557374748</v>
+        <v>1.432920508060371</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6840074266152394</v>
+        <v>0.6830291542104417</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.311578347442854</v>
+        <v>3.310991383999975</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.744874030674714</v>
+        <v>-3.672212104210786</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.310512054212519</v>
+        <v>1.33957682479809</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6815377201534332</v>
+        <v>0.6805594477486356</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.217740722888212</v>
+        <v>3.217153759445333</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.813244216998724</v>
+        <v>-3.740582290534796</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.202425841168216</v>
+        <v>1.231490611753787</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6908134191896481</v>
+        <v>0.6898351467848506</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.142568003795242</v>
+        <v>3.141981040352364</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.925116496624875</v>
+        <v>-3.852454570160947</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.148113637949647</v>
+        <v>1.177178408535218</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6908134191896481</v>
+        <v>0.6898351467848506</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.133004712427133</v>
+        <v>3.132417748984255</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.909141831138607</v>
+        <v>-3.836479904674679</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.121078029068182</v>
+        <v>1.150142799653753</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6908134191896481</v>
+        <v>0.6898351467848506</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.099579237351161</v>
+        <v>3.098992273908282</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.733667571346138</v>
+        <v>-3.66100564488221</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.195834964976957</v>
+        <v>1.224899735562528</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6908134191896481</v>
+        <v>0.6898351467848506</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.104146469342949</v>
+        <v>3.10355950590007</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.725743196761223</v>
+        <v>-3.653081270297295</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.17474674357213</v>
+        <v>1.203811514157701</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6908134191896481</v>
+        <v>0.6898351467848506</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.079888498104156</v>
+        <v>3.079301534661277</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.719464994191374</v>
+        <v>-3.646803067727447</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.105796338001519</v>
+        <v>1.13486110858709</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6970916217594971</v>
+        <v>0.6961133493546996</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.012193733047515</v>
+        <v>3.011606769604636</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.659612374987651</v>
+        <v>-3.586950448523723</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.139909772115141</v>
+        <v>1.168974542700712</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6970916217594971</v>
+        <v>0.6961133493546996</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.022366119479647</v>
+        <v>3.021779156036769</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.573368911961274</v>
+        <v>-3.500706985497346</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.169353427899552</v>
+        <v>1.198418198485123</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6970916217594971</v>
+        <v>0.6961133493546996</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.017312390053507</v>
+        <v>3.016725426610629</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.618675731360254</v>
+        <v>-3.546013804896326</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.143006475584486</v>
+        <v>1.172071246170057</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6562814587502663</v>
+        <v>0.6553031863454688</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.984602067692494</v>
+        <v>2.984015104249616</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.647708836062555</v>
+        <v>-3.575046909598627</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.131945106736667</v>
+        <v>1.161009877322238</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6562814587502663</v>
+        <v>0.6553031863454688</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.985153940725596</v>
+        <v>2.984566977282717</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.554898354611696</v>
+        <v>-3.482236428147768</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.098341991208376</v>
+        <v>1.127406761793947</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7490919402011257</v>
+        <v>0.7481136677963282</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.970112921487477</v>
+        <v>2.969525958044599</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.599287823941124</v>
+        <v>-3.526625897477196</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.082459679401206</v>
+        <v>1.111524449986777</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.704702470871698</v>
+        <v>0.7037241984669005</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.945352715814422</v>
+        <v>2.944765752371543</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.578784130055626</v>
+        <v>-3.506122203591699</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.085736865467128</v>
+        <v>1.114801636052699</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7252061647571953</v>
+        <v>0.7242278923523978</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.952730640657443</v>
+        <v>2.952143677214564</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.618708224638199</v>
+        <v>-3.546046298174271</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.075258523464766</v>
+        <v>1.104323294050337</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7252061647571953</v>
+        <v>0.7242278923523978</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.95822193648811</v>
+        <v>2.957634973045232</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.646488622539552</v>
+        <v>-3.573826696075624</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.075643566072764</v>
+        <v>1.104708336658335</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6974257668558423</v>
+        <v>0.6964474944510448</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.953050899515838</v>
+        <v>2.952463936072959</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.76486929526969</v>
+        <v>-3.692207368805762</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8666470169813618</v>
+        <v>0.8957117875669329</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6302079147048661</v>
+        <v>0.6292296423000686</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.751075908225905</v>
+        <v>2.750488944783026</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.873483373713021</v>
+        <v>-3.800821447249093</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9433510463232349</v>
+        <v>0.9724158169088062</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6302079147048661</v>
+        <v>0.6292296423000686</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.87122556894511</v>
+        <v>2.870638605502232</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.838074335464878</v>
+        <v>-3.76541240900095</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9720276877248151</v>
+        <v>1.001092458310386</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6302079147048661</v>
+        <v>0.6292296423000686</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.885738595047433</v>
+        <v>2.885151631604555</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.84653550412034</v>
+        <v>-3.773873577656412</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9660626616049992</v>
+        <v>0.9951274321905705</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6217467460494051</v>
+        <v>0.6207684736446075</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.878081335196526</v>
+        <v>2.877494371753647</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.669419174085173</v>
+        <v>-3.596757247621245</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.033638222464368</v>
+        <v>1.062702993049939</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6217467460494051</v>
+        <v>0.6207684736446075</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.874810364041828</v>
+        <v>2.874223400598949</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.714511418918719</v>
+        <v>-3.641849492454791</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.016284716292863</v>
+        <v>1.045349486878434</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5598507028800153</v>
+        <v>0.5588724304752177</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.838356129902107</v>
+        <v>2.837769166459229</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.535135997679951</v>
+        <v>-3.462474071216024</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.081821860094784</v>
+        <v>1.110886630680356</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7166274610507339</v>
+        <v>0.7156491886459364</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.926209160110953</v>
+        <v>2.925622196668074</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.580150211200558</v>
+        <v>-3.50748828473663</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.044623630018132</v>
+        <v>1.073688400603703</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6862785657361293</v>
+        <v>0.6853002933313318</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.88880727825378</v>
+        <v>2.888220314810901</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.847154721472993</v>
+        <v>-3.774492795009065</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9435133882481033</v>
+        <v>0.9725781588336744</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4919155276931808</v>
+        <v>0.4909372552883833</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.777881017766957</v>
+        <v>2.777294054324078</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.948352502910166</v>
+        <v>-3.875690576446238</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9022381975697356</v>
+        <v>0.9313029681553067</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4235067141478616</v>
+        <v>0.4225284417430641</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.736039651536266</v>
+        <v>2.735452688093388</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.941841536295853</v>
+        <v>-3.869179609831925</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9024425457697773</v>
+        <v>0.9315073163553484</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4235067141478616</v>
+        <v>0.4225284417430641</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.733639613090583</v>
+        <v>2.733052649647704</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.922803408588556</v>
+        <v>-3.850141482124628</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9065825160609411</v>
+        <v>0.9356472866465122</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3653231028166671</v>
+        <v>0.3643448304118695</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.695254165500111</v>
+        <v>2.694667202057233</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.975319210863376</v>
+        <v>-3.902657284399448</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.004870596785203</v>
+        <v>1.033935367370775</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3653231028166671</v>
+        <v>0.3643448304118695</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.814548567134302</v>
+        <v>2.813961603691423</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.978727522297956</v>
+        <v>-3.906065595834028</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.004340601197505</v>
+        <v>1.033405371783076</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3978396718260445</v>
+        <v>0.3968613994212469</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.834891837526062</v>
+        <v>2.834304874083183</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.959371386404109</v>
+        <v>-3.886709459940181</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.01809158595197</v>
+        <v>1.047156356537541</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3978396718260445</v>
+        <v>0.3968613994212469</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.840900367922988</v>
+        <v>2.840313404480109</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.811628416169107</v>
+        <v>-3.738966489705179</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9751389953231702</v>
+        <v>1.004203765908741</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5656470290609277</v>
+        <v>0.5646687566561301</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.839535003541117</v>
+        <v>2.838948040098238</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.895449637443805</v>
+        <v>-3.822787710979877</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9444041283447719</v>
+        <v>0.9734688989303431</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5656470290609277</v>
+        <v>0.5646687566561301</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.842328625072598</v>
+        <v>2.841741661629719</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.503602756027699</v>
+        <v>2.409991647838704</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.88929693139102</v>
+        <v>-3.816635004927092</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9475275591575441</v>
+        <v>0.88298122155412</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.571799735113712</v>
+        <v>0.5708214627089144</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.846682597095927</v>
+        <v>2.752484525464053</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.50268323276781</v>
+        <v>2.409072124578814</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.906106229541522</v>
+        <v>-3.833444303077594</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9398843166374538</v>
+        <v>0.8753379790340297</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5549904369632104</v>
+        <v>0.5540121645584128</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.835677494945736</v>
+        <v>2.741479423313863</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.569018786564631</v>
+        <v>2.475407678375635</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.8438082307654</v>
+        <v>-3.771146304301472</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.031139069944723</v>
+        <v>0.9665927323412993</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6002847012376524</v>
+        <v>0.5993064288328549</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.929189607307222</v>
+        <v>2.834991535675349</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.371310788278758</v>
+        <v>2.277699680089762</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.642018033100242</v>
+        <v>-3.569356106636314</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9141471507249137</v>
+        <v>0.8496008131214896</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7983028934068068</v>
+        <v>0.7973246210020093</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.850292524322842</v>
+        <v>2.756094452690968</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.441601020600933</v>
+        <v>2.347989912411938</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.692904745786437</v>
+        <v>-3.620242819322509</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9640826979726109</v>
+        <v>0.8995363603691868</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7474161807206123</v>
+        <v>0.7464379083158148</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.8900507290333</v>
+        <v>2.795852657401427</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319539</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.456228756716976</v>
+        <v>2.362617648527981</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.606294003136629</v>
+        <v>-3.533632076672701</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.013354731148578</v>
+        <v>0.9488083935451535</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8260419119257706</v>
+        <v>0.8250636395209731</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.951853903872439</v>
+        <v>2.857655832240566</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.454764737541648</v>
+        <v>2.361153629352653</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.666503301141914</v>
+        <v>-3.593841374677986</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9878069927711355</v>
+        <v>0.9232606551677114</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7658326139204861</v>
+        <v>0.7648543415156885</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.91426430589394</v>
+        <v>2.820066234262066</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397788</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.453256355581577</v>
+        <v>2.359645247392582</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.617316652457562</v>
+        <v>-3.544654725993635</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.005973270284805</v>
+        <v>0.9414269326813804</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7658326139204861</v>
+        <v>0.7648543415156885</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.912755923933869</v>
+        <v>2.818557852301995</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316243</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.453119223017013</v>
+        <v>2.359508114828018</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.572943520818994</v>
+        <v>-3.500281594355066</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.023585390375668</v>
+        <v>0.9590390527722441</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8102057455590547</v>
+        <v>0.8092274731542571</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.939242670352446</v>
+        <v>2.845044598720572</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.447513017155603</v>
+        <v>2.353901908966608</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.595423871677879</v>
+        <v>-3.522761945213951</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.008987044170705</v>
+        <v>0.9444407065672806</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8102057455590547</v>
+        <v>0.8092274731542571</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.933636464491037</v>
+        <v>2.839438392859163</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.453894774183408</v>
+        <v>2.360283665994412</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.547768141116823</v>
+        <v>-3.475106214652895</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.034431093422932</v>
+        <v>0.9698847558195072</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8578614761201103</v>
+        <v>0.8568832037153128</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.968611659855474</v>
+        <v>2.8744135882236</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.458787147558133</v>
+        <v>2.365176039369137</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.447249982618068</v>
+        <v>-3.37458805615414</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.079530730197158</v>
+        <v>1.014984392593734</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9583796346188649</v>
+        <v>0.9574013622140674</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.033814928329452</v>
+        <v>2.939616856697578</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.445541820034005</v>
+        <v>2.351930711845009</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.431344653185715</v>
+        <v>-3.358682726721788</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.072647534445972</v>
+        <v>1.008101196842547</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8792669739096259</v>
+        <v>0.8782887015048284</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.973102004379781</v>
+        <v>2.878903932747907</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.449639522644634</v>
+        <v>2.356028414455638</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.386506251577317</v>
+        <v>-3.31384432511339</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.094680597699959</v>
+        <v>1.030134260096535</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8838104068544954</v>
+        <v>0.8828321344496979</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.979925766757331</v>
+        <v>2.885727695125457</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.453800462275712</v>
+        <v>2.360189354086716</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.406004707819326</v>
+        <v>-3.333342781355398</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.091042154834234</v>
+        <v>1.02649581723081</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8357257655745911</v>
+        <v>0.8347474931697936</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.955235921620467</v>
+        <v>2.861037849988592</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.459680064803549</v>
+        <v>2.366068956614553</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.361801870733425</v>
+        <v>-3.289139944269497</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.114602892196431</v>
+        <v>1.050056554593007</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8799286026604916</v>
+        <v>0.878950330255694</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.987637226399844</v>
+        <v>2.89343915476797</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.458090065272796</v>
+        <v>2.364478957083801</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.369361536570472</v>
+        <v>-3.296699610106544</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.10998902633086</v>
+        <v>1.045442688727436</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9347320066703109</v>
+        <v>0.9337537342655133</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.018929269274983</v>
+        <v>2.924731197643109</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284876</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.509337830455836</v>
+        <v>2.41572672226684</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.2110701190312</v>
+        <v>-3.138408192567272</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.224553358529609</v>
+        <v>1.160007020926184</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9347320066703109</v>
+        <v>0.9337537342655133</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.070177034458023</v>
+        <v>2.975978962826149</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.507778535050089</v>
+        <v>2.414167426861094</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.003428115396724</v>
+        <v>-2.930766188932796</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.306050864577653</v>
+        <v>1.241504526974228</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.142374010304787</v>
+        <v>1.141395737899989</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.193202941232962</v>
+        <v>3.099004869601087</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.502726763288359</v>
+        <v>2.409115655099364</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.952396022674196</v>
+        <v>-2.879734096210268</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.321411929904934</v>
+        <v>1.256865592301509</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.193406103027315</v>
+        <v>1.192427830622517</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.218770425104748</v>
+        <v>3.124572353472874</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.519914167381064</v>
+        <v>2.426303059192068</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.88717184154699</v>
+        <v>-2.814509915083062</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.364689006448521</v>
+        <v>1.300142668845097</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.258630284154521</v>
+        <v>1.257652011749723</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.275092337873777</v>
+        <v>3.180894266241903</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.515875139680344</v>
+        <v>2.422264031491349</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.849744821475856</v>
+        <v>-2.777082895011928</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.375620786776255</v>
+        <v>1.31107444917283</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.263881822183702</v>
+        <v>1.262903549778905</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.274204232990566</v>
+        <v>3.180006161358692</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.517131932011585</v>
+        <v>2.423520823822589</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.869856477510564</v>
+        <v>-2.797194551046637</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.368832916693612</v>
+        <v>1.304286579090187</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.274909167181122</v>
+        <v>1.273930894776324</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.282077432320258</v>
+        <v>3.187879360688384</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636281</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.677689703032796</v>
+        <v>2.5840785948438</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.841443214410681</v>
+        <v>-2.768781287946753</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.540755992954776</v>
+        <v>1.476209655351352</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.215933604434693</v>
+        <v>1.214955332029895</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.407249865693612</v>
+        <v>3.313051794061737</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.81322282095762</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.797802612250613</v>
+        <v>2.704191504061617</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.766660953385668</v>
+        <v>-2.69399902692174</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.690781806582598</v>
+        <v>1.626235468979174</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.290715865459706</v>
+        <v>1.289737593054908</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.572232131526436</v>
+        <v>3.478034059894562</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.789510588264472</v>
+        <v>2.695899480075476</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.74057686912186</v>
+        <v>-2.667914942657932</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.69292341630198</v>
+        <v>1.628377078698556</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.290715865459706</v>
+        <v>1.289737593054908</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.563940107540295</v>
+        <v>3.469742035908421</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.787703783848251</v>
+        <v>2.694092675659256</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.65269895601274</v>
+        <v>-2.580037029548812</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.726267777129408</v>
+        <v>1.661721439525984</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.406641507883057</v>
+        <v>1.405663235478259</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.631688688578085</v>
+        <v>3.537490616946211</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.805258189575043</v>
+        <v>2.711647081386047</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.643806494619456</v>
+        <v>-2.571144568155528</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.747379167413513</v>
+        <v>1.682832829810088</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.406641507883057</v>
+        <v>1.405663235478259</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.649243094304877</v>
+        <v>3.555045022673002</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.797113236979627</v>
+        <v>2.703502128790631</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.812282611589334</v>
+        <v>-2.739620685125406</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.671843768030146</v>
+        <v>1.607297430426721</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.378693672166476</v>
+        <v>1.377715399761678</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.624329440279512</v>
+        <v>3.530131368647638</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.778382934167488</v>
+        <v>2.684771825978493</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.366026418959894</v>
+        <v>-2.293364492495966</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.831615942269784</v>
+        <v>1.767069604666359</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.283975002496843</v>
+        <v>1.282996730092045</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.548767935665595</v>
+        <v>3.45456986403372</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.769046956664393</v>
+        <v>2.675435848475397</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.343305315276742</v>
+        <v>-2.270643388812814</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.831368406239949</v>
+        <v>1.766822068636525</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.283975002496843</v>
+        <v>1.282996730092045</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.539431958162499</v>
+        <v>3.445233886530625</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.927953082515562</v>
+        <v>2.834341974326566</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.472507128570784</v>
+        <v>-2.399845202106856</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.938593806773501</v>
+        <v>1.874047469170077</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.154773189202801</v>
+        <v>1.153794916798003</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.620816996037242</v>
+        <v>3.526618924405368</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.965030905009209</v>
+        <v>2.871419796820213</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.49838152704481</v>
+        <v>-2.425719600580882</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.965321869877537</v>
+        <v>1.900775532274113</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.199684797914542</v>
+        <v>1.198706525509744</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.684841783757934</v>
+        <v>3.590643712126059</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.961706260998754</v>
+        <v>2.868095152809758</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.491326836829636</v>
+        <v>-2.418664910365708</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.964819101953152</v>
+        <v>1.900272764349727</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.206739488129716</v>
+        <v>1.205761215724918</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.685749953876583</v>
+        <v>3.591551882244709</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.971712414643495</v>
+        <v>2.8781013064545</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.464375612503148</v>
+        <v>-2.39171368603922</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.985605745328489</v>
+        <v>1.921059407725064</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.221619834157435</v>
+        <v>1.220641561752637</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.704684315137956</v>
+        <v>3.610486243506082</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.155815546788455</v>
+        <v>3.062204438599459</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.485919840333935</v>
+        <v>-2.413257913870007</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.161091186341134</v>
+        <v>2.096544848737709</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.221619834157435</v>
+        <v>1.220641561752637</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.888787447282916</v>
+        <v>3.794589375651042</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.147932241691448</v>
+        <v>3.054321133502452</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.508327958138807</v>
+        <v>-2.435666031674879</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.144244634122178</v>
+        <v>2.079698296518754</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.221619834157435</v>
+        <v>1.220641561752637</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.880904142185909</v>
+        <v>3.786706070554035</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.149986241241086</v>
+        <v>3.05637513305209</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.536552193716408</v>
+        <v>-2.46389026725248</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.135008939440775</v>
+        <v>2.070462601837351</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.239596586608744</v>
+        <v>1.238618314203946</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.893744193206332</v>
+        <v>3.799546121574457</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.206239958962933</v>
+        <v>3.112628850773937</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.545993119604938</v>
+        <v>-2.47333119314101</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.187486286807211</v>
+        <v>2.122939949203786</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.362023704152135</v>
+        <v>1.361045431747337</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.023454181454214</v>
+        <v>3.929256109822339</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.209131053508234</v>
+        <v>3.115519945319238</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.634869750773412</v>
+        <v>-2.562207824309484</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.154826728885122</v>
+        <v>2.090280391281697</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.273147072983661</v>
+        <v>1.272168800578863</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.97301929729843</v>
+        <v>3.878821225666556</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.207242866402009</v>
+        <v>3.113631758213013</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.711199728374317</v>
+        <v>-2.63853780191039</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.122406550738535</v>
+        <v>2.05786021313511</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.273147072983661</v>
+        <v>1.272168800578863</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.971131110192205</v>
+        <v>3.876933038560331</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.202063096004871</v>
+        <v>3.108451987815875</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.804863673051859</v>
+        <v>-2.732201746587931</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.07976120247038</v>
+        <v>2.015214864866956</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.17948312830612</v>
+        <v>1.178504855901322</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.909752972988543</v>
+        <v>3.815554901356669</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.200497106215023</v>
+        <v>3.106885998026028</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.966432098579114</v>
+        <v>-2.893770172115186</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.013567842469631</v>
+        <v>1.949021504866206</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.05270020450824</v>
+        <v>1.051721932103443</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.832117228919968</v>
+        <v>3.737919157288093</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.213570513080942</v>
+        <v>3.119959404891946</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.074732760449233</v>
+        <v>-3.002070833985305</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.983320984587501</v>
+        <v>1.918774646984077</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.05270020450824</v>
+        <v>1.051721932103443</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.845190635785886</v>
+        <v>3.750992564154012</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.205575709863882</v>
+        <v>3.111964601674886</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.092536732169977</v>
+        <v>-3.01987480570605</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.968204592682143</v>
+        <v>1.903658255078719</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9821655816030392</v>
+        <v>0.9811873091982415</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.794875058825706</v>
+        <v>3.700676987193831</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.204099750990884</v>
+        <v>3.110488642801888</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.12043751927945</v>
+        <v>-3.047775592815523</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.955568318965357</v>
+        <v>1.891021981361932</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9475686574601044</v>
+        <v>0.9465903850553067</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.772640945466947</v>
+        <v>3.678442873835072</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.200864194968083</v>
+        <v>3.107253086779087</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.242963621982344</v>
+        <v>-3.170301695518416</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.903322321861398</v>
+        <v>1.838775984257973</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8250425547572106</v>
+        <v>0.8240642823524128</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.695889727822409</v>
+        <v>3.601691656190535</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.267570154558586</v>
+        <v>3.173959046369591</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.473478118167933</v>
+        <v>-3.400816191704005</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.877822482977666</v>
+        <v>1.813276145374241</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5945280585716218</v>
+        <v>0.5935497861668241</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.62428698970156</v>
+        <v>3.530088918069685</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.407881873560433</v>
+        <v>3.314270765371438</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.822223203392377</v>
+        <v>-3.749561276928449</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.878636167889735</v>
+        <v>1.814089830286311</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.485780104652724</v>
+        <v>0.4848018322479263</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.699349936352068</v>
+        <v>3.605151864720194</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237096</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.476862142706073</v>
+        <v>3.383251034517078</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.976209621168517</v>
+        <v>-3.90354769470459</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.886021869924919</v>
+        <v>1.821475532321495</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.485780104652724</v>
+        <v>0.4848018322479263</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.768330205497708</v>
+        <v>3.674132133865834</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423389</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.462913344826194</v>
+        <v>3.369302236637199</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.180809056031526</v>
+        <v>-4.108147129567598</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.790233298099837</v>
+        <v>1.725686960496412</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.485780104652724</v>
+        <v>0.4848018322479263</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.754381407617829</v>
+        <v>3.660183335985955</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.474783833881608</v>
+        <v>3.381172725692613</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.43328421003925</v>
+        <v>-4.360622283575323</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.701113725552161</v>
+        <v>1.636567387948736</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.485780104652724</v>
+        <v>0.4848018322479263</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.766251896673243</v>
+        <v>3.672053825041369</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.475994368400552</v>
+        <v>3.382383260211556</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.726179966518663</v>
+        <v>-4.653518040054735</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.58516595747934</v>
+        <v>1.520619619875915</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.485780104652724</v>
+        <v>0.4848018322479263</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.767462431192186</v>
+        <v>3.673264359560312</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.480116110627873</v>
+        <v>3.386505002438878</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.912844094653471</v>
+        <v>-4.840182168189543</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.514622048452738</v>
+        <v>1.450075710849313</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4590411338281641</v>
+        <v>0.4580628614233664</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.755540790924772</v>
+        <v>3.661342719292898</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.475193963364063</v>
+        <v>3.381582855175067</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.058864781567433</v>
+        <v>-4.986202855103505</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.451291626423342</v>
+        <v>1.386745288819918</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4499580420343072</v>
+        <v>0.4489797696295094</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.745168788584647</v>
+        <v>3.650970716952773</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830323</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.637398020063107</v>
+        <v>3.543786911874111</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.150578790677018</v>
+        <v>-5.077916864213091</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.576810079478552</v>
+        <v>1.512263741875128</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4499580420343072</v>
+        <v>0.4489797696295094</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.907372845283692</v>
+        <v>3.813174773651817</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.632244658026921</v>
+        <v>3.538633549837925</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.182230449736988</v>
+        <v>-5.10956852327306</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.558996053818379</v>
+        <v>1.494449716214954</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.444789584789867</v>
+        <v>0.4438113123850692</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.899118408900841</v>
+        <v>3.804920337268967</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868144</v>
+        <v>3.75004401586814</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.642474075595412</v>
+        <v>3.548862967406416</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.264165268005871</v>
+        <v>-5.191503341541943</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.536451544079316</v>
+        <v>1.471905206475892</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4348548392027868</v>
+        <v>0.433876566797989</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.903386979117085</v>
+        <v>3.80918890748521</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332685</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.651399714051315</v>
+        <v>3.557788605862319</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.366141390254278</v>
+        <v>-5.293479463790351</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.504586733635856</v>
+        <v>1.440040396032432</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3328787169543792</v>
+        <v>0.3319004445495815</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.851126944223942</v>
+        <v>3.756928872592068</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231806</v>
+        <v>3.798296784231801</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.64355260129549</v>
+        <v>3.549941493106494</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.256135106777057</v>
+        <v>-5.183473180313129</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.54074213427092</v>
+        <v>1.476195796667495</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3560832888716544</v>
+        <v>0.3551050164668567</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.857202574618483</v>
+        <v>3.763004502986608</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818516</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.647802612017464</v>
+        <v>3.554191503828469</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.113075531036131</v>
+        <v>-5.040413604572203</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.602215975289265</v>
+        <v>1.53766963768584</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3640967154616337</v>
+        <v>0.3631184430568359</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.866260641294445</v>
+        <v>3.77206256966257</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051782</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.6550634949</v>
+        <v>3.561452386711005</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.811628805564293</v>
+        <v>-4.738966879100365</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.730055548360536</v>
+        <v>1.665509210757111</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.665543440933471</v>
+        <v>0.6645651685286732</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.054389559460083</v>
+        <v>3.960191487828209</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.656034672652711</v>
+        <v>3.562423564463715</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.836219049799477</v>
+        <v>-4.763557123335549</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.721190628419173</v>
+        <v>1.656644290815748</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.665543440933471</v>
+        <v>0.6645651685286732</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.055360737212793</v>
+        <v>3.961162665580919</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.656877577032466</v>
+        <v>3.563266468843471</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.785180673792957</v>
+        <v>-4.712518747329029</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.742448883201536</v>
+        <v>1.677902545598112</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.665543440933471</v>
+        <v>0.6645651685286732</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.056203641592549</v>
+        <v>3.962005569960675</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.675915675906612</v>
+        <v>3.582304567717616</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.744041378926326</v>
+        <v>-4.671379452462398</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.777942700022334</v>
+        <v>1.71339636241891</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7066827358001018</v>
+        <v>0.705704463395304</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.099925317386673</v>
+        <v>4.005727245754799</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700472</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.492099672030546</v>
+        <v>3.398488563841551</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.647406466907686</v>
+        <v>-4.574744540443758</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.632780660953725</v>
+        <v>1.5682343233503</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8033176478187417</v>
+        <v>0.802339375413944</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.974090260721792</v>
+        <v>3.879892189089917</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077634</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.495601716104511</v>
+        <v>3.401990607915515</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.777987201438529</v>
+        <v>-4.705325274974601</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.584050411215352</v>
+        <v>1.519504073611927</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6727369132878992</v>
+        <v>0.6717586408831014</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.89924386407725</v>
+        <v>3.805045792445376</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833451</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.480028535180593</v>
+        <v>3.386417426991597</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.613490867247567</v>
+        <v>-4.540828940783639</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.634275763967819</v>
+        <v>1.569729426364395</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8372332474788611</v>
+        <v>0.8362549750740633</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.98236848366791</v>
+        <v>3.888170412036036</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077623</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.479216245617023</v>
+        <v>3.385605137428027</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.536392265705694</v>
+        <v>-4.463730339241766</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.664302915020998</v>
+        <v>1.599756577417573</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8372332474788611</v>
+        <v>0.8362549750740633</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.98155619410434</v>
+        <v>3.887358122472465</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.489085024742095</v>
+        <v>3.3954739165531</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.546777460595584</v>
+        <v>-4.474115534131656</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.670017616190115</v>
+        <v>1.60547127858669</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8268480525889718</v>
+        <v>0.825869780184174</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.985193856295479</v>
+        <v>3.890995784663605</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735275</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.55992203051852</v>
+        <v>3.466310922329525</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.565365619317808</v>
+        <v>-4.492703692853881</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.73341935847765</v>
+        <v>1.668873020874225</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8082598938667465</v>
+        <v>0.8072816214619487</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.044877966838569</v>
+        <v>3.950679895206695</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496556</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.556791041336819</v>
+        <v>3.463179933147823</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.565664166013844</v>
+        <v>-4.493002239549917</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.730168950617534</v>
+        <v>1.665622613014109</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8079613471707106</v>
+        <v>0.8069830747659128</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.041567849639246</v>
+        <v>3.947369778007372</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108856</v>
+        <v>3.815643212108851</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.56132193627621</v>
+        <v>3.467710828087215</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.464841032323417</v>
+        <v>-4.392179105859489</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.775029099033096</v>
+        <v>1.710482761429672</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8204255626550644</v>
+        <v>0.8194472902502666</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.053577273869249</v>
+        <v>3.959379202237375</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.80735616812146</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.561451189754754</v>
+        <v>3.467840081565758</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.27405967157101</v>
+        <v>-4.201397745107082</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.851470896812602</v>
+        <v>1.786924559209178</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.011206923407472</v>
+        <v>1.010228651002674</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.168175343799237</v>
+        <v>4.073977272167363</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.54128803549235</v>
+        <v>3.447676927303355</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.167096313721588</v>
+        <v>-4.09443438725766</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.874093085689968</v>
+        <v>1.809546748086543</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.069671531367273</v>
+        <v>1.068693258962476</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.183090954312714</v>
+        <v>4.08889288268084</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.576254972104409</v>
+        <v>3.482643863915413</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.111765725819826</v>
+        <v>-4.039103799355898</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.931192257462731</v>
+        <v>1.866645919859307</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.125002119269035</v>
+        <v>1.124023846864238</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.25125624366583</v>
+        <v>4.157058172033956</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.569941540005846</v>
+        <v>3.476330431816851</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.099711598906863</v>
+        <v>-4.027049672442935</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.929700476129354</v>
+        <v>1.865154138525929</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.137056246181998</v>
+        <v>1.1360779737772</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.252175287715046</v>
+        <v>4.157977216083172</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.571822170189982</v>
+        <v>3.478211062000987</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.140866718475084</v>
+        <v>-4.068204792011156</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.915119058486201</v>
+        <v>1.850572720882777</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.095901126613777</v>
+        <v>1.09492285420898</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.229362846158248</v>
+        <v>4.135164774526374</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.584673196067865</v>
+        <v>3.491062087878869</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.072818155783554</v>
+        <v>-4.000156229319626</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.955189509440696</v>
+        <v>1.890643171837271</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.163949689305307</v>
+        <v>1.162971416900509</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.283043009651049</v>
+        <v>4.188844938019175</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013426</v>
+        <v>3.645256780013421</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.604875866241459</v>
+        <v>3.511264758052463</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.304418548953055</v>
+        <v>-4.231756622489127</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.88275202234649</v>
+        <v>1.818205684743065</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.163949689305307</v>
+        <v>1.162971416900509</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.303245679824643</v>
+        <v>4.209047608192769</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498971</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.588482102308341</v>
+        <v>3.494870994119345</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.354470094482274</v>
+        <v>-4.281808168018346</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.846337640201684</v>
+        <v>1.78179130259826</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.163949689305307</v>
+        <v>1.162971416900509</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.286851915891526</v>
+        <v>4.192653844259651</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.6700487028001</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.548734015901807</v>
+        <v>3.455122907712812</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.529576927058718</v>
+        <v>-4.45691500059479</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.736546820764573</v>
+        <v>1.672000483161148</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.163949689305307</v>
+        <v>1.162971416900509</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.247103829484992</v>
+        <v>4.152905757853118</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660853</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.555756634898747</v>
+        <v>3.462145526709752</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.333476773628195</v>
+        <v>-4.260814847164268</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.822009501133722</v>
+        <v>1.757463163530298</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.36004984273583</v>
+        <v>1.359071570331032</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.371786540540246</v>
+        <v>4.277588468908371</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73057047339509</v>
+        <v>3.730570473395084</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.654927634471652</v>
+        <v>3.561316526282656</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.180451381514911</v>
+        <v>-4.107789455050983</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.982390657551941</v>
+        <v>1.917844319948516</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.513075234849114</v>
+        <v>1.512096962444316</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.562772775381121</v>
+        <v>4.468574703749246</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791151</v>
+        <v>3.741278332791146</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.842393859379944</v>
+        <v>3.748782751190949</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.208758695388181</v>
+        <v>-4.136096768924253</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.158533956910925</v>
+        <v>2.0939876193075</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.513075234849114</v>
+        <v>1.512096962444316</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.750239000289413</v>
+        <v>4.656040928657539</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620437</v>
+        <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.811796810734027</v>
+        <v>3.718185702545032</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.375351920501704</v>
+        <v>-4.302689994037776</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.061299618219599</v>
+        <v>1.996753280616174</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.346482009735592</v>
+        <v>1.345503737330794</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.619686016575383</v>
+        <v>4.525487944943508</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.70818251928565</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.815473213395745</v>
+        <v>3.721862105206749</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.352316127140138</v>
+        <v>-4.27965420067621</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.074190338225943</v>
+        <v>2.009644000622518</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.346482009735592</v>
+        <v>1.345503737330794</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.6233624192371</v>
+        <v>4.529164347605226</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399472</v>
+        <v>3.740581401399466</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.81309126851924</v>
+        <v>3.719480160330245</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.323070146684441</v>
+        <v>-4.250408220220513</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.083506785531716</v>
+        <v>2.018960447928292</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.346482009735592</v>
+        <v>1.345503737330794</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.620980474360596</v>
+        <v>4.526782402728721</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256374</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.810384507676875</v>
+        <v>3.71677339948788</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.429995694562292</v>
+        <v>-4.357333768098364</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.038029805538211</v>
+        <v>1.973483467934787</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.23955646185774</v>
+        <v>1.238578189452943</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.554118384791519</v>
+        <v>4.459920313159645</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701004</v>
+        <v>3.689942600700997</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.811813309820109</v>
+        <v>3.718202201631114</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.441231256114322</v>
+        <v>-4.502352326605613</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.034964383060633</v>
+        <v>1.916904846675121</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.22832090030571</v>
+        <v>1.093559630945694</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.548805850003536</v>
+        <v>4.374337980198531</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687015</v>
+        <v>3.711852429687008</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.911744549077862</v>
+        <v>3.818133440888867</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.559573021899039</v>
+        <v>-4.62069409239033</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.087558916004499</v>
+        <v>1.969499379618987</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.2390069388686</v>
+        <v>1.104245669508584</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.655148712399023</v>
+        <v>4.480680842594017</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790804</v>
+        <v>3.714879051790798</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.909530246203802</v>
+        <v>3.815919138014806</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.610983444219747</v>
+        <v>-4.672104514711038</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.064780444202155</v>
+        <v>1.946720907816643</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.2390069388686</v>
+        <v>1.104245669508584</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.652934409524962</v>
+        <v>4.478466539719957</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437331</v>
+        <v>3.704757949437326</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.909433374278091</v>
+        <v>3.815822266089095</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.690402895427499</v>
+        <v>-4.75152396591879</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.032915791793344</v>
+        <v>1.914856255407832</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.2390069388686</v>
+        <v>1.104245669508584</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.652837537599251</v>
+        <v>4.478369667794246</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298398</v>
+        <v>3.736804952298392</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.909427267836134</v>
+        <v>3.815816159647138</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.785865893344717</v>
+        <v>-4.846986963836008</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.994724486184499</v>
+        <v>1.876664949798988</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.2390069388686</v>
+        <v>1.104245669508584</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.652831431157294</v>
+        <v>4.478363561352289</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218</v>
+        <v>3.715372960217994</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.907523664398744</v>
+        <v>3.813912556209749</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.721489982494002</v>
+        <v>-4.782611052985293</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.018571247087396</v>
+        <v>1.900511710701884</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.303382849719316</v>
+        <v>1.168621580359299</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.689553374230334</v>
+        <v>4.515085504425328</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353535</v>
+        <v>3.73608941335353</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.913257482146471</v>
+        <v>3.819646373957475</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.776859144626195</v>
+        <v>-4.837980215117486</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.002157399982246</v>
+        <v>1.884097863596733</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.303382849719316</v>
+        <v>1.168621580359299</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.695287191978061</v>
+        <v>4.520819322173055</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113278</v>
+        <v>3.736822870113273</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.912795845489403</v>
+        <v>3.819184737300408</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.822296924457023</v>
+        <v>-4.883417994948314</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.983520651392847</v>
+        <v>1.865461115007335</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.260537859041156</v>
+        <v>1.12577658968114</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.669118560914097</v>
+        <v>4.494650691109092</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113687</v>
+        <v>3.790272500113682</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.932670238339722</v>
+        <v>3.839059130150726</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.734090090309444</v>
+        <v>-4.795211160800736</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.038677777902197</v>
+        <v>1.920618241516685</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.260537859041156</v>
+        <v>1.12577658968114</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.688992953764416</v>
+        <v>4.514525083959411</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016441</v>
+        <v>3.794486844016435</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.91637093886445</v>
+        <v>3.822759830675454</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.628055095104135</v>
+        <v>-4.689176165595426</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.064792476509049</v>
+        <v>1.946732940123536</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.260537859041156</v>
+        <v>1.12577658968114</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.672693654289144</v>
+        <v>4.498225784484139</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307672</v>
+        <v>3.794705093307667</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.918801888328495</v>
+        <v>3.8251907801395</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.44484343197104</v>
+        <v>-4.505964502462331</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.140508091226332</v>
+        <v>2.022448554840821</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.260537859041156</v>
+        <v>1.12577658968114</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.675124603753189</v>
+        <v>4.500656733948184</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863548</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.884593074176385</v>
+        <v>3.79098196598739</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.373121984957189</v>
+        <v>-4.43424305544848</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.134987855879762</v>
+        <v>2.016928319494251</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.332259306055007</v>
+        <v>1.197498036694991</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.683948657809389</v>
+        <v>4.509480788004384</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394114</v>
+        <v>3.723789705394108</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.831508820097557</v>
+        <v>3.737897711908562</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.350748959349483</v>
+        <v>-4.411870029840774</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.090852812044016</v>
+        <v>1.972793275658505</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.343515057167908</v>
+        <v>1.208753787807892</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.637617854398302</v>
+        <v>4.463149984593297</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456724</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.016707024982912</v>
+        <v>3.923095916793917</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.383765255260228</v>
+        <v>-4.444886325751519</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.262844498565074</v>
+        <v>2.144784962179562</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.274077680501157</v>
+        <v>1.13931641114114</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.781153633283607</v>
+        <v>4.606685763478602</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883677</v>
+        <v>3.713762536883671</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.008628250811161</v>
+        <v>3.915017142622167</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.372237619610619</v>
+        <v>-4.43335869010191</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.259376778653166</v>
+        <v>2.141317242267656</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.333078338702519</v>
+        <v>1.198317069342503</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.808475254032673</v>
+        <v>4.634007384227669</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236297</v>
+        <v>3.71715069923629</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.01229636333295</v>
+        <v>3.918685255143955</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.469579120952988</v>
+        <v>-4.530700191444279</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.224108290638007</v>
+        <v>2.106048754252496</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.288658156537031</v>
+        <v>1.153896887177015</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.785491257255169</v>
+        <v>4.611023387450164</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427683</v>
+        <v>3.705201079427678</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.013547445525788</v>
+        <v>3.919936337336793</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.555435150292954</v>
+        <v>-4.616556220784245</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.191016961094859</v>
+        <v>2.072957424709347</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.246282087310896</v>
+        <v>1.11152081795088</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.761316697912325</v>
+        <v>4.586848828107321</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610383</v>
+        <v>3.691835499610377</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.99596664734629</v>
+        <v>3.902355539157295</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.564271947709074</v>
+        <v>-4.625393018200365</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.169901443948913</v>
+        <v>2.051841907563402</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.238839914669545</v>
+        <v>1.104078645309529</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.739270596148017</v>
+        <v>4.564802726343013</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667454</v>
+        <v>3.715544411667449</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.006131158391339</v>
+        <v>3.912520050202344</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.655654510274532</v>
+        <v>-4.716775580765823</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.143512929967779</v>
+        <v>2.025453393582268</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.2022750299502</v>
+        <v>1.067513760590184</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.727496176361459</v>
+        <v>4.553028306556455</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.67397837488919</v>
+        <v>3.673978374889185</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.108259416215606</v>
+        <v>4.014648308026612</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.643947792287526</v>
+        <v>-4.705068862778817</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.250323874986849</v>
+        <v>2.132264338601337</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.213981747937207</v>
+        <v>1.079220478577191</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.83664846497793</v>
+        <v>4.662180595172926</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409566</v>
+        <v>3.68247609940956</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.111291754947011</v>
+        <v>4.017680646758016</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.544284288203864</v>
+        <v>-4.605405358695155</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.293221615351718</v>
+        <v>2.175162078966207</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.277168831140893</v>
+        <v>1.142407561780877</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.877593053631547</v>
+        <v>4.703125183826543</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452573</v>
+        <v>3.672895177452567</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.324196588225069</v>
+        <v>4.230585480036074</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.554600386370216</v>
+        <v>-4.615721456861507</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.502000009363236</v>
+        <v>2.383940472977724</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.277168831140893</v>
+        <v>1.142407561780877</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.090497886909605</v>
+        <v>4.916030017104601</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762286</v>
+        <v>3.623960959762281</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.323375255137159</v>
+        <v>4.229764146948164</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.554506418352843</v>
+        <v>-4.615627488844134</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.501216263482275</v>
+        <v>2.383156727096763</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.277538692488211</v>
+        <v>1.142777423128195</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.089898470630086</v>
+        <v>4.915430600825081</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988017</v>
+        <v>3.633213467988012</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.317607241081513</v>
+        <v>4.223996132892518</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.561725242552687</v>
+        <v>-4.622846313043978</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.492560719746691</v>
+        <v>2.374501183361179</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.277538692488211</v>
+        <v>1.142777423128195</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.08413045657444</v>
+        <v>4.909662586769436</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740923</v>
+        <v>3.647907242740918</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.317607241081513</v>
+        <v>4.223996132892518</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.560776819434649</v>
+        <v>-4.62189788992594</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.492940088993906</v>
+        <v>2.374880552608395</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.277538692488211</v>
+        <v>1.142777423128195</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.08413045657444</v>
+        <v>4.909662586769436</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663627</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.330334849062605</v>
+        <v>4.23672374087361</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.717845277690273</v>
+        <v>-4.778966348181564</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.442840313672749</v>
+        <v>2.324780777287237</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.277538692488211</v>
+        <v>1.142777423128195</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.096858064555532</v>
+        <v>4.922390194750527</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424771</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.332280847486992</v>
+        <v>4.238669739297998</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.711853030901461</v>
+        <v>-4.772974101392752</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.447183210812661</v>
+        <v>2.32912367442715</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.277538692488211</v>
+        <v>1.142777423128195</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.098804062979919</v>
+        <v>4.924336193174915</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149219</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.325934983504761</v>
+        <v>4.232323875315767</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.623295069770694</v>
+        <v>-4.684416140261985</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.476260531282737</v>
+        <v>2.358200994897225</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.277538692488211</v>
+        <v>1.142777423128195</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.092458198997688</v>
+        <v>4.917990329192683</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383092</v>
+        <v>3.735300721383087</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.325243660943757</v>
+        <v>4.231632552754762</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.60553599226762</v>
+        <v>-4.666657062758911</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.482672839722962</v>
+        <v>2.364613303337451</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.277538692488211</v>
+        <v>1.142777423128195</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.091766876436684</v>
+        <v>4.91729900663168</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720999</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.338025846852344</v>
+        <v>4.244414738663349</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.505905841218552</v>
+        <v>-4.567026911709843</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.535307086051175</v>
+        <v>2.417247549665665</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.377168843537279</v>
+        <v>1.242407574177263</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.164327152974711</v>
+        <v>4.989859283169707</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455273</v>
+        <v>3.775357097455267</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.52718011235107</v>
+        <v>4.433569004162075</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.555305349907563</v>
+        <v>-4.616426420398854</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.704701548074298</v>
+        <v>2.586642011688786</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.387427676969024</v>
+        <v>1.252666407609007</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.359636718532485</v>
+        <v>5.18516884872748</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963137</v>
+        <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.514368785453932</v>
+        <v>4.420757677264938</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.348620876265187</v>
+        <v>-4.416853080773126</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.77456401063411</v>
+        <v>2.65366002064194</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.594112150611399</v>
+        <v>1.452239747234735</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.470836075820772</v>
+        <v>5.292101525605779</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.763417089428135</v>
+        <v>3.891189663059683</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.450156245312197</v>
+        <v>4.462127343761124</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.347708877735512</v>
+        <v>-4.440680637539833</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.710716269904245</v>
+        <v>2.685498664431444</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.581294957447236</v>
+        <v>1.375610843412187</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.398933219780538</v>
+        <v>5.287493849808437</v>
       </c>
     </row>
   </sheetData>
